--- a/data/gated_research/model_ledgers/lol-tiered-elo.xlsx
+++ b/data/gated_research/model_ledgers/lol-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ6"/>
+  <dimension ref="A1:AJ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1166,8 +1166,416 @@
       <c r="AI6" s="2" t="inlineStr"/>
       <c r="AJ6" s="2" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>9b465894820846d6</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>67511</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0.703159</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>0.012756523219814242</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:14:45.283320Z</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr"/>
+      <c r="V7" s="2" t="inlineStr"/>
+      <c r="W7" s="2" t="inlineStr"/>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Z7" s="2" t="inlineStr"/>
+      <c r="AA7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AD7" s="2" t="inlineStr"/>
+      <c r="AE7" s="2" t="inlineStr"/>
+      <c r="AF7" s="2" t="inlineStr"/>
+      <c r="AG7" s="2" t="inlineStr"/>
+      <c r="AH7" s="2" t="inlineStr"/>
+      <c r="AI7" s="2" t="inlineStr"/>
+      <c r="AJ7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>d795f524205e416f</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>67515</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>0.746312</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>0.12654013688212928</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:14:45.864824Z</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr"/>
+      <c r="V8" s="2" t="inlineStr"/>
+      <c r="W8" s="2" t="inlineStr"/>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Z8" s="2" t="inlineStr"/>
+      <c r="AA8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
+      <c r="AE8" s="2" t="inlineStr"/>
+      <c r="AF8" s="2" t="inlineStr"/>
+      <c r="AG8" s="2" t="inlineStr"/>
+      <c r="AH8" s="2" t="inlineStr"/>
+      <c r="AI8" s="2" t="inlineStr"/>
+      <c r="AJ8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>ebe0f1a7e6084e12</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>67566</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>0.74664</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>0.046940300300300275</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:14:46.366525Z</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr"/>
+      <c r="V9" s="2" t="inlineStr"/>
+      <c r="W9" s="2" t="inlineStr"/>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr"/>
+      <c r="Z9" s="2" t="inlineStr"/>
+      <c r="AA9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AD9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="inlineStr"/>
+      <c r="AF9" s="2" t="inlineStr"/>
+      <c r="AG9" s="2" t="inlineStr"/>
+      <c r="AH9" s="2" t="inlineStr"/>
+      <c r="AI9" s="2" t="inlineStr"/>
+      <c r="AJ9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>ea2588d5a3be417f</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>67937</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0.649674</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>0.059510065573770476</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:14:49.714123Z</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr"/>
+      <c r="V10" s="2" t="inlineStr"/>
+      <c r="W10" s="2" t="inlineStr"/>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr"/>
+      <c r="Z10" s="2" t="inlineStr"/>
+      <c r="AA10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr"/>
+      <c r="AD10" s="2" t="inlineStr"/>
+      <c r="AE10" s="2" t="inlineStr"/>
+      <c r="AF10" s="2" t="inlineStr"/>
+      <c r="AG10" s="2" t="inlineStr"/>
+      <c r="AH10" s="2" t="inlineStr"/>
+      <c r="AI10" s="2" t="inlineStr"/>
+      <c r="AJ10" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ6"/>
+  <autoFilter ref="A1:AJ10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/gated_research/model_ledgers/lol-tiered-elo.xlsx
+++ b/data/gated_research/model_ledgers/lol-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ10"/>
+  <dimension ref="A1:AJ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1574,8 +1574,824 @@
       <c r="AI10" s="2" t="inlineStr"/>
       <c r="AJ10" s="2" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>3b2a96af23e84827</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>c576c6ae4e566e0ba129e3c87c62df8c6d7fdaa80aa1e15aa311d3a9b9d64f76</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>67511</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>0.703159</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>0.012756523219814242</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:46:06.296484Z</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr"/>
+      <c r="V11" s="2" t="inlineStr"/>
+      <c r="W11" s="2" t="inlineStr"/>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr"/>
+      <c r="Z11" s="2" t="inlineStr"/>
+      <c r="AA11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AD11" s="2" t="inlineStr"/>
+      <c r="AE11" s="2" t="inlineStr"/>
+      <c r="AF11" s="2" t="inlineStr"/>
+      <c r="AG11" s="2" t="inlineStr"/>
+      <c r="AH11" s="2" t="inlineStr"/>
+      <c r="AI11" s="2" t="inlineStr"/>
+      <c r="AJ11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>71bd9c9fb2fa4e68</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>c576c6ae4e566e0ba129e3c87c62df8c6d7fdaa80aa1e15aa311d3a9b9d64f76</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>67515</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>0.746312</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>0.12654013688212928</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:46:06.744519Z</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr"/>
+      <c r="V12" s="2" t="inlineStr"/>
+      <c r="W12" s="2" t="inlineStr"/>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr"/>
+      <c r="Z12" s="2" t="inlineStr"/>
+      <c r="AA12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AD12" s="2" t="inlineStr"/>
+      <c r="AE12" s="2" t="inlineStr"/>
+      <c r="AF12" s="2" t="inlineStr"/>
+      <c r="AG12" s="2" t="inlineStr"/>
+      <c r="AH12" s="2" t="inlineStr"/>
+      <c r="AI12" s="2" t="inlineStr"/>
+      <c r="AJ12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>841c53fefe6d4f67</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>c576c6ae4e566e0ba129e3c87c62df8c6d7fdaa80aa1e15aa311d3a9b9d64f76</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>67566</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0.74664</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>0.046940300300300275</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:46:07.243416Z</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr"/>
+      <c r="V13" s="2" t="inlineStr"/>
+      <c r="W13" s="2" t="inlineStr"/>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr"/>
+      <c r="Z13" s="2" t="inlineStr"/>
+      <c r="AA13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AD13" s="2" t="inlineStr"/>
+      <c r="AE13" s="2" t="inlineStr"/>
+      <c r="AF13" s="2" t="inlineStr"/>
+      <c r="AG13" s="2" t="inlineStr"/>
+      <c r="AH13" s="2" t="inlineStr"/>
+      <c r="AI13" s="2" t="inlineStr"/>
+      <c r="AJ13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>893992cb29844c36</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>c576c6ae4e566e0ba129e3c87c62df8c6d7fdaa80aa1e15aa311d3a9b9d64f76</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>67937</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>0.649674</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>0.059510065573770476</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:46:10.643274Z</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr"/>
+      <c r="V14" s="2" t="inlineStr"/>
+      <c r="W14" s="2" t="inlineStr"/>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr"/>
+      <c r="Z14" s="2" t="inlineStr"/>
+      <c r="AA14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AD14" s="2" t="inlineStr"/>
+      <c r="AE14" s="2" t="inlineStr"/>
+      <c r="AF14" s="2" t="inlineStr"/>
+      <c r="AG14" s="2" t="inlineStr"/>
+      <c r="AH14" s="2" t="inlineStr"/>
+      <c r="AI14" s="2" t="inlineStr"/>
+      <c r="AJ14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>f7c643c04ce94beb</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>67511</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>0.703159</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>0.012756523219814242</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:53:05.228074Z</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr"/>
+      <c r="V15" s="2" t="inlineStr"/>
+      <c r="W15" s="2" t="inlineStr"/>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr"/>
+      <c r="Z15" s="2" t="inlineStr"/>
+      <c r="AA15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr"/>
+      <c r="AD15" s="2" t="inlineStr"/>
+      <c r="AE15" s="2" t="inlineStr"/>
+      <c r="AF15" s="2" t="inlineStr"/>
+      <c r="AG15" s="2" t="inlineStr"/>
+      <c r="AH15" s="2" t="inlineStr"/>
+      <c r="AI15" s="2" t="inlineStr"/>
+      <c r="AJ15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>cbe74995ec0446a6</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>67515</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0.746312</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>0.12654013688212928</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:53:05.711202Z</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr"/>
+      <c r="V16" s="2" t="inlineStr"/>
+      <c r="W16" s="2" t="inlineStr"/>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr"/>
+      <c r="Z16" s="2" t="inlineStr"/>
+      <c r="AA16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr"/>
+      <c r="AD16" s="2" t="inlineStr"/>
+      <c r="AE16" s="2" t="inlineStr"/>
+      <c r="AF16" s="2" t="inlineStr"/>
+      <c r="AG16" s="2" t="inlineStr"/>
+      <c r="AH16" s="2" t="inlineStr"/>
+      <c r="AI16" s="2" t="inlineStr"/>
+      <c r="AJ16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>88f278a0905b47c3</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>67566</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>0.74664</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>0.046940300300300275</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:53:06.165699Z</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr"/>
+      <c r="V17" s="2" t="inlineStr"/>
+      <c r="W17" s="2" t="inlineStr"/>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr"/>
+      <c r="Z17" s="2" t="inlineStr"/>
+      <c r="AA17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr"/>
+      <c r="AD17" s="2" t="inlineStr"/>
+      <c r="AE17" s="2" t="inlineStr"/>
+      <c r="AF17" s="2" t="inlineStr"/>
+      <c r="AG17" s="2" t="inlineStr"/>
+      <c r="AH17" s="2" t="inlineStr"/>
+      <c r="AI17" s="2" t="inlineStr"/>
+      <c r="AJ17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>9f6f48e503814abf</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>67937</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>0.649674</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>0.059510065573770476</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:53:09.518110Z</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr"/>
+      <c r="V18" s="2" t="inlineStr"/>
+      <c r="W18" s="2" t="inlineStr"/>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr"/>
+      <c r="Z18" s="2" t="inlineStr"/>
+      <c r="AA18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr"/>
+      <c r="AD18" s="2" t="inlineStr"/>
+      <c r="AE18" s="2" t="inlineStr"/>
+      <c r="AF18" s="2" t="inlineStr"/>
+      <c r="AG18" s="2" t="inlineStr"/>
+      <c r="AH18" s="2" t="inlineStr"/>
+      <c r="AI18" s="2" t="inlineStr"/>
+      <c r="AJ18" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ10"/>
+  <autoFilter ref="A1:AJ18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/gated_research/model_ledgers/lol-tiered-elo.xlsx
+++ b/data/gated_research/model_ledgers/lol-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ18"/>
+  <dimension ref="A1:AJ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -742,14 +742,34 @@
       <c r="W2" s="2" t="inlineStr"/>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y2" s="2" t="inlineStr"/>
-      <c r="Z2" s="2" t="inlineStr"/>
-      <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
-      <c r="AC2" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z2" s="2" t="inlineStr">
+        <is>
+          <t>0.540000</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
+          <t>0.000829</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>0.8547</t>
+        </is>
+      </c>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:34:59.891344Z</t>
+        </is>
+      </c>
       <c r="AD2" s="2" t="inlineStr"/>
       <c r="AE2" s="2" t="inlineStr"/>
       <c r="AF2" s="2" t="inlineStr"/>
@@ -2390,8 +2410,416 @@
       <c r="AI18" s="2" t="inlineStr"/>
       <c r="AJ18" s="2" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>25c6efd44be442b1</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>94c9ecefe7862fcd0f8932ee0f8a5cf2fb1ce42b7196a6254eed26b3593462b8</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>67511</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>0.70331</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr"/>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>0.012907523219814254</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:17.281478Z</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr"/>
+      <c r="V19" s="2" t="inlineStr"/>
+      <c r="W19" s="2" t="inlineStr"/>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr"/>
+      <c r="Z19" s="2" t="inlineStr"/>
+      <c r="AA19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AD19" s="2" t="inlineStr"/>
+      <c r="AE19" s="2" t="inlineStr"/>
+      <c r="AF19" s="2" t="inlineStr"/>
+      <c r="AG19" s="2" t="inlineStr"/>
+      <c r="AH19" s="2" t="inlineStr"/>
+      <c r="AI19" s="2" t="inlineStr"/>
+      <c r="AJ19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>7bff0dfbc4af4b25</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>94c9ecefe7862fcd0f8932ee0f8a5cf2fb1ce42b7196a6254eed26b3593462b8</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>67515</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>0.746406</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>0.13703100000000001</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:17.851259Z</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr"/>
+      <c r="V20" s="2" t="inlineStr"/>
+      <c r="W20" s="2" t="inlineStr"/>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr"/>
+      <c r="Z20" s="2" t="inlineStr"/>
+      <c r="AA20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr"/>
+      <c r="AD20" s="2" t="inlineStr"/>
+      <c r="AE20" s="2" t="inlineStr"/>
+      <c r="AF20" s="2" t="inlineStr"/>
+      <c r="AG20" s="2" t="inlineStr"/>
+      <c r="AH20" s="2" t="inlineStr"/>
+      <c r="AI20" s="2" t="inlineStr"/>
+      <c r="AJ20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>df1ae0ba59d849b4</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>94c9ecefe7862fcd0f8932ee0f8a5cf2fb1ce42b7196a6254eed26b3593462b8</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>67566</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>0.746125</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>0.04642530030030034</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:18.386531Z</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr"/>
+      <c r="V21" s="2" t="inlineStr"/>
+      <c r="W21" s="2" t="inlineStr"/>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr"/>
+      <c r="Z21" s="2" t="inlineStr"/>
+      <c r="AA21" s="2" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AD21" s="2" t="inlineStr"/>
+      <c r="AE21" s="2" t="inlineStr"/>
+      <c r="AF21" s="2" t="inlineStr"/>
+      <c r="AG21" s="2" t="inlineStr"/>
+      <c r="AH21" s="2" t="inlineStr"/>
+      <c r="AI21" s="2" t="inlineStr"/>
+      <c r="AJ21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>c761ba00f3d2490f</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>94c9ecefe7862fcd0f8932ee0f8a5cf2fb1ce42b7196a6254eed26b3593462b8</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>67937</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>0.649195</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr"/>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>0.05903106557377047</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:21.959634Z</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr"/>
+      <c r="V22" s="2" t="inlineStr"/>
+      <c r="W22" s="2" t="inlineStr"/>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr"/>
+      <c r="Z22" s="2" t="inlineStr"/>
+      <c r="AA22" s="2" t="inlineStr"/>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AD22" s="2" t="inlineStr"/>
+      <c r="AE22" s="2" t="inlineStr"/>
+      <c r="AF22" s="2" t="inlineStr"/>
+      <c r="AG22" s="2" t="inlineStr"/>
+      <c r="AH22" s="2" t="inlineStr"/>
+      <c r="AI22" s="2" t="inlineStr"/>
+      <c r="AJ22" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ18"/>
+  <autoFilter ref="A1:AJ22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/gated_research/model_ledgers/lol-tiered-elo.xlsx
+++ b/data/gated_research/model_ledgers/lol-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ22"/>
+  <dimension ref="A1:AJ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2818,8 +2818,824 @@
       <c r="AI22" s="2" t="inlineStr"/>
       <c r="AJ22" s="2" t="inlineStr"/>
     </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>792f4ef7a49e40c3</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>ce2799e81af8529b307a74c160b17aa30970ae747db3a1beff420e3fd39f3e8c</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>67511</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>0.70331</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr"/>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>0.012907523219814254</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:08:25.287120Z</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr"/>
+      <c r="W23" s="2" t="inlineStr"/>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr"/>
+      <c r="Z23" s="2" t="inlineStr"/>
+      <c r="AA23" s="2" t="inlineStr"/>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr"/>
+      <c r="AE23" s="2" t="inlineStr"/>
+      <c r="AF23" s="2" t="inlineStr"/>
+      <c r="AG23" s="2" t="inlineStr"/>
+      <c r="AH23" s="2" t="inlineStr"/>
+      <c r="AI23" s="2" t="inlineStr"/>
+      <c r="AJ23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>eb89f6792e774871</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>ce2799e81af8529b307a74c160b17aa30970ae747db3a1beff420e3fd39f3e8c</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>67515</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>0.746406</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr"/>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>0.13703100000000001</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:08:25.777893Z</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr"/>
+      <c r="W24" s="2" t="inlineStr"/>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr"/>
+      <c r="Z24" s="2" t="inlineStr"/>
+      <c r="AA24" s="2" t="inlineStr"/>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="inlineStr"/>
+      <c r="AE24" s="2" t="inlineStr"/>
+      <c r="AF24" s="2" t="inlineStr"/>
+      <c r="AG24" s="2" t="inlineStr"/>
+      <c r="AH24" s="2" t="inlineStr"/>
+      <c r="AI24" s="2" t="inlineStr"/>
+      <c r="AJ24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>538b23fd60284b62</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>ce2799e81af8529b307a74c160b17aa30970ae747db3a1beff420e3fd39f3e8c</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>67566</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0.746125</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr"/>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>0.04642530030030034</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:08:26.282734Z</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr"/>
+      <c r="W25" s="2" t="inlineStr"/>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr"/>
+      <c r="Z25" s="2" t="inlineStr"/>
+      <c r="AA25" s="2" t="inlineStr"/>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr"/>
+      <c r="AE25" s="2" t="inlineStr"/>
+      <c r="AF25" s="2" t="inlineStr"/>
+      <c r="AG25" s="2" t="inlineStr"/>
+      <c r="AH25" s="2" t="inlineStr"/>
+      <c r="AI25" s="2" t="inlineStr"/>
+      <c r="AJ25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>02e1d10a11fa4dea</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>ce2799e81af8529b307a74c160b17aa30970ae747db3a1beff420e3fd39f3e8c</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>67937</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>0.649195</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr"/>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>0.05903106557377047</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:08:29.638928Z</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr"/>
+      <c r="W26" s="2" t="inlineStr"/>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr"/>
+      <c r="Z26" s="2" t="inlineStr"/>
+      <c r="AA26" s="2" t="inlineStr"/>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AD26" s="2" t="inlineStr"/>
+      <c r="AE26" s="2" t="inlineStr"/>
+      <c r="AF26" s="2" t="inlineStr"/>
+      <c r="AG26" s="2" t="inlineStr"/>
+      <c r="AH26" s="2" t="inlineStr"/>
+      <c r="AI26" s="2" t="inlineStr"/>
+      <c r="AJ26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>7fabf1424ccc4465</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>67511</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>0.70331</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr"/>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>0.012907523219814254</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:12:18.085863Z</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr"/>
+      <c r="W27" s="2" t="inlineStr"/>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr"/>
+      <c r="Z27" s="2" t="inlineStr"/>
+      <c r="AA27" s="2" t="inlineStr"/>
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AD27" s="2" t="inlineStr"/>
+      <c r="AE27" s="2" t="inlineStr"/>
+      <c r="AF27" s="2" t="inlineStr"/>
+      <c r="AG27" s="2" t="inlineStr"/>
+      <c r="AH27" s="2" t="inlineStr"/>
+      <c r="AI27" s="2" t="inlineStr"/>
+      <c r="AJ27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>ae686207c56548b8</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>67515</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>0.746406</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr"/>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>0.13703100000000001</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:12:18.584911Z</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr"/>
+      <c r="W28" s="2" t="inlineStr"/>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr"/>
+      <c r="Z28" s="2" t="inlineStr"/>
+      <c r="AA28" s="2" t="inlineStr"/>
+      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AD28" s="2" t="inlineStr"/>
+      <c r="AE28" s="2" t="inlineStr"/>
+      <c r="AF28" s="2" t="inlineStr"/>
+      <c r="AG28" s="2" t="inlineStr"/>
+      <c r="AH28" s="2" t="inlineStr"/>
+      <c r="AI28" s="2" t="inlineStr"/>
+      <c r="AJ28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>e5461fd7ea7149a3</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>67566</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>0.746125</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr"/>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>0.04642530030030034</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:12:19.163906Z</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr"/>
+      <c r="W29" s="2" t="inlineStr"/>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr"/>
+      <c r="Z29" s="2" t="inlineStr"/>
+      <c r="AA29" s="2" t="inlineStr"/>
+      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr"/>
+      <c r="AE29" s="2" t="inlineStr"/>
+      <c r="AF29" s="2" t="inlineStr"/>
+      <c r="AG29" s="2" t="inlineStr"/>
+      <c r="AH29" s="2" t="inlineStr"/>
+      <c r="AI29" s="2" t="inlineStr"/>
+      <c r="AJ29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>67c5ba308fb04787</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>67937</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>0.649195</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr"/>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>0.05903106557377047</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:12:22.895388Z</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr"/>
+      <c r="W30" s="2" t="inlineStr"/>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr"/>
+      <c r="Z30" s="2" t="inlineStr"/>
+      <c r="AA30" s="2" t="inlineStr"/>
+      <c r="AB30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AD30" s="2" t="inlineStr"/>
+      <c r="AE30" s="2" t="inlineStr"/>
+      <c r="AF30" s="2" t="inlineStr"/>
+      <c r="AG30" s="2" t="inlineStr"/>
+      <c r="AH30" s="2" t="inlineStr"/>
+      <c r="AI30" s="2" t="inlineStr"/>
+      <c r="AJ30" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ22"/>
+  <autoFilter ref="A1:AJ30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/gated_research/model_ledgers/lol-tiered-elo.xlsx
+++ b/data/gated_research/model_ledgers/lol-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ30"/>
+  <dimension ref="A1:AJ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -3634,8 +3634,416 @@
       <c r="AI30" s="2" t="inlineStr"/>
       <c r="AJ30" s="2" t="inlineStr"/>
     </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>814fe78ddc60431b</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>67511</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>0.70331</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr"/>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>0.012907523219814254</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:09.781954Z</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr"/>
+      <c r="W31" s="2" t="inlineStr"/>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr"/>
+      <c r="Z31" s="2" t="inlineStr"/>
+      <c r="AA31" s="2" t="inlineStr"/>
+      <c r="AB31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AD31" s="2" t="inlineStr"/>
+      <c r="AE31" s="2" t="inlineStr"/>
+      <c r="AF31" s="2" t="inlineStr"/>
+      <c r="AG31" s="2" t="inlineStr"/>
+      <c r="AH31" s="2" t="inlineStr"/>
+      <c r="AI31" s="2" t="inlineStr"/>
+      <c r="AJ31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>475d2427615f4059</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>67515</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>0.746406</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr"/>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>0.13703100000000001</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:10.279453Z</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr"/>
+      <c r="W32" s="2" t="inlineStr"/>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr"/>
+      <c r="Z32" s="2" t="inlineStr"/>
+      <c r="AA32" s="2" t="inlineStr"/>
+      <c r="AB32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr"/>
+      <c r="AE32" s="2" t="inlineStr"/>
+      <c r="AF32" s="2" t="inlineStr"/>
+      <c r="AG32" s="2" t="inlineStr"/>
+      <c r="AH32" s="2" t="inlineStr"/>
+      <c r="AI32" s="2" t="inlineStr"/>
+      <c r="AJ32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>ba18db444962471c</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>67566</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>0.746125</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr"/>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>0.04642530030030034</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:10.786284Z</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr"/>
+      <c r="W33" s="2" t="inlineStr"/>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr"/>
+      <c r="Z33" s="2" t="inlineStr"/>
+      <c r="AA33" s="2" t="inlineStr"/>
+      <c r="AB33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AD33" s="2" t="inlineStr"/>
+      <c r="AE33" s="2" t="inlineStr"/>
+      <c r="AF33" s="2" t="inlineStr"/>
+      <c r="AG33" s="2" t="inlineStr"/>
+      <c r="AH33" s="2" t="inlineStr"/>
+      <c r="AI33" s="2" t="inlineStr"/>
+      <c r="AJ33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>7351fcfa021846b4</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>67937</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>0.649195</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr"/>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>0.05903106557377047</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:14.243617Z</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr"/>
+      <c r="W34" s="2" t="inlineStr"/>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr"/>
+      <c r="Z34" s="2" t="inlineStr"/>
+      <c r="AA34" s="2" t="inlineStr"/>
+      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AD34" s="2" t="inlineStr"/>
+      <c r="AE34" s="2" t="inlineStr"/>
+      <c r="AF34" s="2" t="inlineStr"/>
+      <c r="AG34" s="2" t="inlineStr"/>
+      <c r="AH34" s="2" t="inlineStr"/>
+      <c r="AI34" s="2" t="inlineStr"/>
+      <c r="AJ34" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ30"/>
+  <autoFilter ref="A1:AJ34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/gated_research/model_ledgers/lol-tiered-elo.xlsx
+++ b/data/gated_research/model_ledgers/lol-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$120</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ34"/>
+  <dimension ref="A1:AJ120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -4042,8 +4042,8840 @@
       <c r="AI34" s="2" t="inlineStr"/>
       <c r="AJ34" s="2" t="inlineStr"/>
     </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>87a11f8b1185498d</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>7f215a94db11a9833f6a5964d076d3e12a68bb6a9f43ac6efcc73865a22bae73</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>67511</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>0.70331</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr"/>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>0.012907523219814254</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:49:45.200871Z</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr"/>
+      <c r="W35" s="2" t="inlineStr"/>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr"/>
+      <c r="Z35" s="2" t="inlineStr"/>
+      <c r="AA35" s="2" t="inlineStr"/>
+      <c r="AB35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AD35" s="2" t="inlineStr"/>
+      <c r="AE35" s="2" t="inlineStr"/>
+      <c r="AF35" s="2" t="inlineStr"/>
+      <c r="AG35" s="2" t="inlineStr"/>
+      <c r="AH35" s="2" t="inlineStr"/>
+      <c r="AI35" s="2" t="inlineStr"/>
+      <c r="AJ35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>b29317d27d624949</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>7f215a94db11a9833f6a5964d076d3e12a68bb6a9f43ac6efcc73865a22bae73</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>67515</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>0.746406</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr"/>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>0.1755905493562232</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:49:45.773269Z</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr"/>
+      <c r="W36" s="2" t="inlineStr"/>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr"/>
+      <c r="Z36" s="2" t="inlineStr"/>
+      <c r="AA36" s="2" t="inlineStr"/>
+      <c r="AB36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AD36" s="2" t="inlineStr"/>
+      <c r="AE36" s="2" t="inlineStr"/>
+      <c r="AF36" s="2" t="inlineStr"/>
+      <c r="AG36" s="2" t="inlineStr"/>
+      <c r="AH36" s="2" t="inlineStr"/>
+      <c r="AI36" s="2" t="inlineStr"/>
+      <c r="AJ36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>f3f6eed9034841e3</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>7f215a94db11a9833f6a5964d076d3e12a68bb6a9f43ac6efcc73865a22bae73</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>67937</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>0.649195</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr"/>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>0.05903106557377047</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:49:49.909064Z</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr"/>
+      <c r="W37" s="2" t="inlineStr"/>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr"/>
+      <c r="Z37" s="2" t="inlineStr"/>
+      <c r="AA37" s="2" t="inlineStr"/>
+      <c r="AB37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AD37" s="2" t="inlineStr"/>
+      <c r="AE37" s="2" t="inlineStr"/>
+      <c r="AF37" s="2" t="inlineStr"/>
+      <c r="AG37" s="2" t="inlineStr"/>
+      <c r="AH37" s="2" t="inlineStr"/>
+      <c r="AI37" s="2" t="inlineStr"/>
+      <c r="AJ37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>201b6d2c057c443d</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>a161bb829c72b371179b80277ac6040e23e9c1e5a3f2acacb2830d614f5bb6c8</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>67511</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>0.70331</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr"/>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>0.012907523219814254</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:31:21.067894Z</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr"/>
+      <c r="W38" s="2" t="inlineStr"/>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr"/>
+      <c r="Z38" s="2" t="inlineStr"/>
+      <c r="AA38" s="2" t="inlineStr"/>
+      <c r="AB38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AD38" s="2" t="inlineStr"/>
+      <c r="AE38" s="2" t="inlineStr"/>
+      <c r="AF38" s="2" t="inlineStr"/>
+      <c r="AG38" s="2" t="inlineStr"/>
+      <c r="AH38" s="2" t="inlineStr"/>
+      <c r="AI38" s="2" t="inlineStr"/>
+      <c r="AJ38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>d66f9fa698f84bc2</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>a161bb829c72b371179b80277ac6040e23e9c1e5a3f2acacb2830d614f5bb6c8</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>67515</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>0.746406</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr"/>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>0.1755905493562232</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:31:21.571520Z</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr"/>
+      <c r="W39" s="2" t="inlineStr"/>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr"/>
+      <c r="Z39" s="2" t="inlineStr"/>
+      <c r="AA39" s="2" t="inlineStr"/>
+      <c r="AB39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AD39" s="2" t="inlineStr"/>
+      <c r="AE39" s="2" t="inlineStr"/>
+      <c r="AF39" s="2" t="inlineStr"/>
+      <c r="AG39" s="2" t="inlineStr"/>
+      <c r="AH39" s="2" t="inlineStr"/>
+      <c r="AI39" s="2" t="inlineStr"/>
+      <c r="AJ39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>4308532ea5874603</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>a161bb829c72b371179b80277ac6040e23e9c1e5a3f2acacb2830d614f5bb6c8</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>67937</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>0.649195</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr"/>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>0.05903106557377047</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:31:25.473996Z</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr"/>
+      <c r="W40" s="2" t="inlineStr"/>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr"/>
+      <c r="Z40" s="2" t="inlineStr"/>
+      <c r="AA40" s="2" t="inlineStr"/>
+      <c r="AB40" s="2" t="inlineStr"/>
+      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AD40" s="2" t="inlineStr"/>
+      <c r="AE40" s="2" t="inlineStr"/>
+      <c r="AF40" s="2" t="inlineStr"/>
+      <c r="AG40" s="2" t="inlineStr"/>
+      <c r="AH40" s="2" t="inlineStr"/>
+      <c r="AI40" s="2" t="inlineStr"/>
+      <c r="AJ40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>7f1ef99422a14834</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>650e7c7f417bcd3169ab8494192d75dd0aab79892dfbad4d32d40b0d5e5c28e9</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>67511</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>0.703892</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>0.6296296296296295</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr"/>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>0.07426237037037042</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:16:17.126076Z</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr"/>
+      <c r="W41" s="2" t="inlineStr"/>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr"/>
+      <c r="Z41" s="2" t="inlineStr"/>
+      <c r="AA41" s="2" t="inlineStr"/>
+      <c r="AB41" s="2" t="inlineStr"/>
+      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AD41" s="2" t="inlineStr"/>
+      <c r="AE41" s="2" t="inlineStr"/>
+      <c r="AF41" s="2" t="inlineStr"/>
+      <c r="AG41" s="2" t="inlineStr"/>
+      <c r="AH41" s="2" t="inlineStr"/>
+      <c r="AI41" s="2" t="inlineStr"/>
+      <c r="AJ41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>ed76b8871b29448a</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>650e7c7f417bcd3169ab8494192d75dd0aab79892dfbad4d32d40b0d5e5c28e9</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>67515</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>0.747007</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr"/>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>0.17619154935622316</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:16:17.637259Z</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr"/>
+      <c r="W42" s="2" t="inlineStr"/>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr"/>
+      <c r="Z42" s="2" t="inlineStr"/>
+      <c r="AA42" s="2" t="inlineStr"/>
+      <c r="AB42" s="2" t="inlineStr"/>
+      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AD42" s="2" t="inlineStr"/>
+      <c r="AE42" s="2" t="inlineStr"/>
+      <c r="AF42" s="2" t="inlineStr"/>
+      <c r="AG42" s="2" t="inlineStr"/>
+      <c r="AH42" s="2" t="inlineStr"/>
+      <c r="AI42" s="2" t="inlineStr"/>
+      <c r="AJ42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>aff5aafe25e243c1</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>650e7c7f417bcd3169ab8494192d75dd0aab79892dfbad4d32d40b0d5e5c28e9</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>67937</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>0.649181</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr"/>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>0.04918099999999992</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:16:21.653591Z</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr"/>
+      <c r="W43" s="2" t="inlineStr"/>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr"/>
+      <c r="Z43" s="2" t="inlineStr"/>
+      <c r="AA43" s="2" t="inlineStr"/>
+      <c r="AB43" s="2" t="inlineStr"/>
+      <c r="AC43" s="2" t="inlineStr"/>
+      <c r="AD43" s="2" t="inlineStr"/>
+      <c r="AE43" s="2" t="inlineStr"/>
+      <c r="AF43" s="2" t="inlineStr"/>
+      <c r="AG43" s="2" t="inlineStr"/>
+      <c r="AH43" s="2" t="inlineStr"/>
+      <c r="AI43" s="2" t="inlineStr"/>
+      <c r="AJ43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>b81c8d39efbc4963</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>44ab665aa526759b4af81e080faf878d5dc45998ab7d0bbf58d6e571138ea288</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>67511</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>0.703892</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr"/>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>0.06360423021582728</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T02:46:23.410346Z</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr"/>
+      <c r="W44" s="2" t="inlineStr"/>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr"/>
+      <c r="Z44" s="2" t="inlineStr"/>
+      <c r="AA44" s="2" t="inlineStr"/>
+      <c r="AB44" s="2" t="inlineStr"/>
+      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AD44" s="2" t="inlineStr"/>
+      <c r="AE44" s="2" t="inlineStr"/>
+      <c r="AF44" s="2" t="inlineStr"/>
+      <c r="AG44" s="2" t="inlineStr"/>
+      <c r="AH44" s="2" t="inlineStr"/>
+      <c r="AI44" s="2" t="inlineStr"/>
+      <c r="AJ44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>eeac516f7548420b</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>44ab665aa526759b4af81e080faf878d5dc45998ab7d0bbf58d6e571138ea288</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>67515</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>0.747005</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr"/>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>0.13763000000000003</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T02:46:23.933103Z</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr"/>
+      <c r="W45" s="2" t="inlineStr"/>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr"/>
+      <c r="Z45" s="2" t="inlineStr"/>
+      <c r="AA45" s="2" t="inlineStr"/>
+      <c r="AB45" s="2" t="inlineStr"/>
+      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AD45" s="2" t="inlineStr"/>
+      <c r="AE45" s="2" t="inlineStr"/>
+      <c r="AF45" s="2" t="inlineStr"/>
+      <c r="AG45" s="2" t="inlineStr"/>
+      <c r="AH45" s="2" t="inlineStr"/>
+      <c r="AI45" s="2" t="inlineStr"/>
+      <c r="AJ45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>51b3d1ccce4940a7</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>c100c32d5e007d4dac6376e6cd512202b274199d1bd3affe60fa155337906220</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>67511</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>0.703892</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>0.6296296296296295</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr"/>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>0.07426237037037042</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T04:18:07.869396Z</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr"/>
+      <c r="W46" s="2" t="inlineStr"/>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr"/>
+      <c r="Z46" s="2" t="inlineStr"/>
+      <c r="AA46" s="2" t="inlineStr"/>
+      <c r="AB46" s="2" t="inlineStr"/>
+      <c r="AC46" s="2" t="inlineStr"/>
+      <c r="AD46" s="2" t="inlineStr"/>
+      <c r="AE46" s="2" t="inlineStr"/>
+      <c r="AF46" s="2" t="inlineStr"/>
+      <c r="AG46" s="2" t="inlineStr"/>
+      <c r="AH46" s="2" t="inlineStr"/>
+      <c r="AI46" s="2" t="inlineStr"/>
+      <c r="AJ46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>b5532b629170482f</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>c100c32d5e007d4dac6376e6cd512202b274199d1bd3affe60fa155337906220</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>67515</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>0.747005</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>0.6805111821086262</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr"/>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>0.06649381789137387</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T04:18:08.482236Z</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr"/>
+      <c r="W47" s="2" t="inlineStr"/>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr"/>
+      <c r="Z47" s="2" t="inlineStr"/>
+      <c r="AA47" s="2" t="inlineStr"/>
+      <c r="AB47" s="2" t="inlineStr"/>
+      <c r="AC47" s="2" t="inlineStr"/>
+      <c r="AD47" s="2" t="inlineStr"/>
+      <c r="AE47" s="2" t="inlineStr"/>
+      <c r="AF47" s="2" t="inlineStr"/>
+      <c r="AG47" s="2" t="inlineStr"/>
+      <c r="AH47" s="2" t="inlineStr"/>
+      <c r="AI47" s="2" t="inlineStr"/>
+      <c r="AJ47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>91d92c98059e4df7</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>c100c32d5e007d4dac6376e6cd512202b274199d1bd3affe60fa155337906220</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>67655</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>0.619109</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr"/>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>0.06955945045045053</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T04:18:11.030982Z</t>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr"/>
+      <c r="W48" s="2" t="inlineStr"/>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr"/>
+      <c r="Z48" s="2" t="inlineStr"/>
+      <c r="AA48" s="2" t="inlineStr"/>
+      <c r="AB48" s="2" t="inlineStr"/>
+      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AD48" s="2" t="inlineStr"/>
+      <c r="AE48" s="2" t="inlineStr"/>
+      <c r="AF48" s="2" t="inlineStr"/>
+      <c r="AG48" s="2" t="inlineStr"/>
+      <c r="AH48" s="2" t="inlineStr"/>
+      <c r="AI48" s="2" t="inlineStr"/>
+      <c r="AJ48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2aa02d615b7b4e5d</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>c100c32d5e007d4dac6376e6cd512202b274199d1bd3affe60fa155337906220</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>68509</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>0.632041</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>0.4694835680751174</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr"/>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>0.1625574319248826</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T04:18:17.797946Z</t>
+        </is>
+      </c>
+      <c r="S49" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr"/>
+      <c r="W49" s="2" t="inlineStr"/>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr"/>
+      <c r="Z49" s="2" t="inlineStr"/>
+      <c r="AA49" s="2" t="inlineStr"/>
+      <c r="AB49" s="2" t="inlineStr"/>
+      <c r="AC49" s="2" t="inlineStr"/>
+      <c r="AD49" s="2" t="inlineStr"/>
+      <c r="AE49" s="2" t="inlineStr"/>
+      <c r="AF49" s="2" t="inlineStr"/>
+      <c r="AG49" s="2" t="inlineStr"/>
+      <c r="AH49" s="2" t="inlineStr"/>
+      <c r="AI49" s="2" t="inlineStr"/>
+      <c r="AJ49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>c88513819b374892</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>c100c32d5e007d4dac6376e6cd512202b274199d1bd3affe60fa155337906220</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>68690</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>0.551482</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>0.4608294930875576</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr"/>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>0.09065250691244242</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T04:18:22.553719Z</t>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr"/>
+      <c r="W50" s="2" t="inlineStr"/>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr"/>
+      <c r="Z50" s="2" t="inlineStr"/>
+      <c r="AA50" s="2" t="inlineStr"/>
+      <c r="AB50" s="2" t="inlineStr"/>
+      <c r="AC50" s="2" t="inlineStr"/>
+      <c r="AD50" s="2" t="inlineStr"/>
+      <c r="AE50" s="2" t="inlineStr"/>
+      <c r="AF50" s="2" t="inlineStr"/>
+      <c r="AG50" s="2" t="inlineStr"/>
+      <c r="AH50" s="2" t="inlineStr"/>
+      <c r="AI50" s="2" t="inlineStr"/>
+      <c r="AJ50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>d63b34ca4be04c70</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>c100c32d5e007d4dac6376e6cd512202b274199d1bd3affe60fa155337906220</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>69143</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>0.625211</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr"/>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>0.00543913688212927</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T04:18:26.293380Z</t>
+        </is>
+      </c>
+      <c r="S51" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr"/>
+      <c r="W51" s="2" t="inlineStr"/>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr"/>
+      <c r="Z51" s="2" t="inlineStr"/>
+      <c r="AA51" s="2" t="inlineStr"/>
+      <c r="AB51" s="2" t="inlineStr"/>
+      <c r="AC51" s="2" t="inlineStr"/>
+      <c r="AD51" s="2" t="inlineStr"/>
+      <c r="AE51" s="2" t="inlineStr"/>
+      <c r="AF51" s="2" t="inlineStr"/>
+      <c r="AG51" s="2" t="inlineStr"/>
+      <c r="AH51" s="2" t="inlineStr"/>
+      <c r="AI51" s="2" t="inlineStr"/>
+      <c r="AJ51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>ae2a21a88b5744e4</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>c100c32d5e007d4dac6376e6cd512202b274199d1bd3affe60fa155337906220</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>69144</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>0.673437</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>0.390625</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr"/>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>0.28281199999999995</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T04:18:26.859455Z</t>
+        </is>
+      </c>
+      <c r="S52" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr"/>
+      <c r="W52" s="2" t="inlineStr"/>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr"/>
+      <c r="Z52" s="2" t="inlineStr"/>
+      <c r="AA52" s="2" t="inlineStr"/>
+      <c r="AB52" s="2" t="inlineStr"/>
+      <c r="AC52" s="2" t="inlineStr"/>
+      <c r="AD52" s="2" t="inlineStr"/>
+      <c r="AE52" s="2" t="inlineStr"/>
+      <c r="AF52" s="2" t="inlineStr"/>
+      <c r="AG52" s="2" t="inlineStr"/>
+      <c r="AH52" s="2" t="inlineStr"/>
+      <c r="AI52" s="2" t="inlineStr"/>
+      <c r="AJ52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>0722531cc04b4d9d</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>ff2b770f59073a39e60976cbc1ae4f05ce9c0ac0477f1609e756119cbdd7431b</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>67511</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>0.703892</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>0.6296296296296295</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr"/>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>0.07426237037037042</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T06:30:13.245481Z</t>
+        </is>
+      </c>
+      <c r="S53" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr"/>
+      <c r="W53" s="2" t="inlineStr"/>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>0.630000</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>0.000370</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>-2.0000</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T13:27:36.949533Z</t>
+        </is>
+      </c>
+      <c r="AD53" s="2" t="inlineStr"/>
+      <c r="AE53" s="2" t="inlineStr"/>
+      <c r="AF53" s="2" t="inlineStr"/>
+      <c r="AG53" s="2" t="inlineStr"/>
+      <c r="AH53" s="2" t="inlineStr"/>
+      <c r="AI53" s="2" t="inlineStr"/>
+      <c r="AJ53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>6b50a53a7aee4fe1</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>ff2b770f59073a39e60976cbc1ae4f05ce9c0ac0477f1609e756119cbdd7431b</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>67515</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>0.747005</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>0.6805111821086262</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr"/>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>0.06649381789137387</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T06:30:13.736104Z</t>
+        </is>
+      </c>
+      <c r="S54" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr"/>
+      <c r="W54" s="2" t="inlineStr"/>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr"/>
+      <c r="Z54" s="2" t="inlineStr"/>
+      <c r="AA54" s="2" t="inlineStr"/>
+      <c r="AB54" s="2" t="inlineStr"/>
+      <c r="AC54" s="2" t="inlineStr"/>
+      <c r="AD54" s="2" t="inlineStr"/>
+      <c r="AE54" s="2" t="inlineStr"/>
+      <c r="AF54" s="2" t="inlineStr"/>
+      <c r="AG54" s="2" t="inlineStr"/>
+      <c r="AH54" s="2" t="inlineStr"/>
+      <c r="AI54" s="2" t="inlineStr"/>
+      <c r="AJ54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>81270029924f47ea</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>ff2b770f59073a39e60976cbc1ae4f05ce9c0ac0477f1609e756119cbdd7431b</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>67655</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>0.619109</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr"/>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>0.06955945045045053</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T06:30:16.744903Z</t>
+        </is>
+      </c>
+      <c r="S55" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr"/>
+      <c r="W55" s="2" t="inlineStr"/>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr"/>
+      <c r="Z55" s="2" t="inlineStr"/>
+      <c r="AA55" s="2" t="inlineStr"/>
+      <c r="AB55" s="2" t="inlineStr"/>
+      <c r="AC55" s="2" t="inlineStr"/>
+      <c r="AD55" s="2" t="inlineStr"/>
+      <c r="AE55" s="2" t="inlineStr"/>
+      <c r="AF55" s="2" t="inlineStr"/>
+      <c r="AG55" s="2" t="inlineStr"/>
+      <c r="AH55" s="2" t="inlineStr"/>
+      <c r="AI55" s="2" t="inlineStr"/>
+      <c r="AJ55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>df9fd91a1db94663</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>ff2b770f59073a39e60976cbc1ae4f05ce9c0ac0477f1609e756119cbdd7431b</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>63451</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>0.726357</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr"/>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr"/>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>0.035954523219814294</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T06:30:17.197243Z</t>
+        </is>
+      </c>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr"/>
+      <c r="W56" s="2" t="inlineStr"/>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr"/>
+      <c r="Z56" s="2" t="inlineStr"/>
+      <c r="AA56" s="2" t="inlineStr"/>
+      <c r="AB56" s="2" t="inlineStr"/>
+      <c r="AC56" s="2" t="inlineStr"/>
+      <c r="AD56" s="2" t="inlineStr"/>
+      <c r="AE56" s="2" t="inlineStr"/>
+      <c r="AF56" s="2" t="inlineStr"/>
+      <c r="AG56" s="2" t="inlineStr"/>
+      <c r="AH56" s="2" t="inlineStr"/>
+      <c r="AI56" s="2" t="inlineStr"/>
+      <c r="AJ56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>08be90feb03843ec</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>ff2b770f59073a39e60976cbc1ae4f05ce9c0ac0477f1609e756119cbdd7431b</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>68509</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>0.632041</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr"/>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>0.4694835680751174</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr"/>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>0.1625574319248826</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T06:30:23.121194Z</t>
+        </is>
+      </c>
+      <c r="S57" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr"/>
+      <c r="W57" s="2" t="inlineStr"/>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr"/>
+      <c r="Z57" s="2" t="inlineStr"/>
+      <c r="AA57" s="2" t="inlineStr"/>
+      <c r="AB57" s="2" t="inlineStr"/>
+      <c r="AC57" s="2" t="inlineStr"/>
+      <c r="AD57" s="2" t="inlineStr"/>
+      <c r="AE57" s="2" t="inlineStr"/>
+      <c r="AF57" s="2" t="inlineStr"/>
+      <c r="AG57" s="2" t="inlineStr"/>
+      <c r="AH57" s="2" t="inlineStr"/>
+      <c r="AI57" s="2" t="inlineStr"/>
+      <c r="AJ57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>9c60c2658da44e34</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>ff2b770f59073a39e60976cbc1ae4f05ce9c0ac0477f1609e756119cbdd7431b</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>68690</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>0.551482</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr"/>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>0.4608294930875576</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr"/>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>0.09065250691244242</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T06:30:27.980099Z</t>
+        </is>
+      </c>
+      <c r="S58" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr"/>
+      <c r="W58" s="2" t="inlineStr"/>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr"/>
+      <c r="Z58" s="2" t="inlineStr"/>
+      <c r="AA58" s="2" t="inlineStr"/>
+      <c r="AB58" s="2" t="inlineStr"/>
+      <c r="AC58" s="2" t="inlineStr"/>
+      <c r="AD58" s="2" t="inlineStr"/>
+      <c r="AE58" s="2" t="inlineStr"/>
+      <c r="AF58" s="2" t="inlineStr"/>
+      <c r="AG58" s="2" t="inlineStr"/>
+      <c r="AH58" s="2" t="inlineStr"/>
+      <c r="AI58" s="2" t="inlineStr"/>
+      <c r="AJ58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>ab904f63a42f4fc2</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>ff2b770f59073a39e60976cbc1ae4f05ce9c0ac0477f1609e756119cbdd7431b</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>69143</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>0.625211</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr"/>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>0.00543913688212927</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T06:30:31.514183Z</t>
+        </is>
+      </c>
+      <c r="S59" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr"/>
+      <c r="W59" s="2" t="inlineStr"/>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr"/>
+      <c r="Z59" s="2" t="inlineStr"/>
+      <c r="AA59" s="2" t="inlineStr"/>
+      <c r="AB59" s="2" t="inlineStr"/>
+      <c r="AC59" s="2" t="inlineStr"/>
+      <c r="AD59" s="2" t="inlineStr"/>
+      <c r="AE59" s="2" t="inlineStr"/>
+      <c r="AF59" s="2" t="inlineStr"/>
+      <c r="AG59" s="2" t="inlineStr"/>
+      <c r="AH59" s="2" t="inlineStr"/>
+      <c r="AI59" s="2" t="inlineStr"/>
+      <c r="AJ59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>9209f9d62e8f4899</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>ff2b770f59073a39e60976cbc1ae4f05ce9c0ac0477f1609e756119cbdd7431b</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>69144</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>0.673437</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr"/>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>0.390625</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr"/>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>0.28281199999999995</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T06:30:32.090117Z</t>
+        </is>
+      </c>
+      <c r="S60" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr"/>
+      <c r="W60" s="2" t="inlineStr"/>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr"/>
+      <c r="Z60" s="2" t="inlineStr"/>
+      <c r="AA60" s="2" t="inlineStr"/>
+      <c r="AB60" s="2" t="inlineStr"/>
+      <c r="AC60" s="2" t="inlineStr"/>
+      <c r="AD60" s="2" t="inlineStr"/>
+      <c r="AE60" s="2" t="inlineStr"/>
+      <c r="AF60" s="2" t="inlineStr"/>
+      <c r="AG60" s="2" t="inlineStr"/>
+      <c r="AH60" s="2" t="inlineStr"/>
+      <c r="AI60" s="2" t="inlineStr"/>
+      <c r="AJ60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>215bcec5b6484c99</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>3746c7f78cdda704f52e709da19cd4f6a76cfc5f34610bf1fe0352705e49ca11</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>67566</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>0.746349</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr"/>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr"/>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>0.046649300300300345</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:13:44.870248Z</t>
+        </is>
+      </c>
+      <c r="S61" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr"/>
+      <c r="W61" s="2" t="inlineStr"/>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr"/>
+      <c r="Z61" s="2" t="inlineStr"/>
+      <c r="AA61" s="2" t="inlineStr"/>
+      <c r="AB61" s="2" t="inlineStr"/>
+      <c r="AC61" s="2" t="inlineStr"/>
+      <c r="AD61" s="2" t="inlineStr"/>
+      <c r="AE61" s="2" t="inlineStr"/>
+      <c r="AF61" s="2" t="inlineStr"/>
+      <c r="AG61" s="2" t="inlineStr"/>
+      <c r="AH61" s="2" t="inlineStr"/>
+      <c r="AI61" s="2" t="inlineStr"/>
+      <c r="AJ61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>6466a75621124d8a</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>3746c7f78cdda704f52e709da19cd4f6a76cfc5f34610bf1fe0352705e49ca11</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>67655</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>0.618839</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr"/>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>0.05936763436123349</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:13:46.797835Z</t>
+        </is>
+      </c>
+      <c r="S62" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr"/>
+      <c r="W62" s="2" t="inlineStr"/>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr"/>
+      <c r="Z62" s="2" t="inlineStr"/>
+      <c r="AA62" s="2" t="inlineStr"/>
+      <c r="AB62" s="2" t="inlineStr"/>
+      <c r="AC62" s="2" t="inlineStr"/>
+      <c r="AD62" s="2" t="inlineStr"/>
+      <c r="AE62" s="2" t="inlineStr"/>
+      <c r="AF62" s="2" t="inlineStr"/>
+      <c r="AG62" s="2" t="inlineStr"/>
+      <c r="AH62" s="2" t="inlineStr"/>
+      <c r="AI62" s="2" t="inlineStr"/>
+      <c r="AJ62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>b00c823e06f448d8</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>3746c7f78cdda704f52e709da19cd4f6a76cfc5f34610bf1fe0352705e49ca11</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>63451</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>0.72731</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr"/>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>0.036907523219814276</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:13:47.727396Z</t>
+        </is>
+      </c>
+      <c r="S63" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr"/>
+      <c r="W63" s="2" t="inlineStr"/>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr"/>
+      <c r="Z63" s="2" t="inlineStr"/>
+      <c r="AA63" s="2" t="inlineStr"/>
+      <c r="AB63" s="2" t="inlineStr"/>
+      <c r="AC63" s="2" t="inlineStr"/>
+      <c r="AD63" s="2" t="inlineStr"/>
+      <c r="AE63" s="2" t="inlineStr"/>
+      <c r="AF63" s="2" t="inlineStr"/>
+      <c r="AG63" s="2" t="inlineStr"/>
+      <c r="AH63" s="2" t="inlineStr"/>
+      <c r="AI63" s="2" t="inlineStr"/>
+      <c r="AJ63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>2c3be607890f4cdc</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>3746c7f78cdda704f52e709da19cd4f6a76cfc5f34610bf1fe0352705e49ca11</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>68509</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>0.631806</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>0.4694835680751174</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr"/>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>0.1623224319248826</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:13:54.673967Z</t>
+        </is>
+      </c>
+      <c r="S64" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr"/>
+      <c r="W64" s="2" t="inlineStr"/>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr"/>
+      <c r="Z64" s="2" t="inlineStr"/>
+      <c r="AA64" s="2" t="inlineStr"/>
+      <c r="AB64" s="2" t="inlineStr"/>
+      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AD64" s="2" t="inlineStr"/>
+      <c r="AE64" s="2" t="inlineStr"/>
+      <c r="AF64" s="2" t="inlineStr"/>
+      <c r="AG64" s="2" t="inlineStr"/>
+      <c r="AH64" s="2" t="inlineStr"/>
+      <c r="AI64" s="2" t="inlineStr"/>
+      <c r="AJ64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>a9b5da737ecd4ae4</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>3746c7f78cdda704f52e709da19cd4f6a76cfc5f34610bf1fe0352705e49ca11</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>69143</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>0.624834</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr"/>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>0.005062136882129309</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:14:02.348665Z</t>
+        </is>
+      </c>
+      <c r="S65" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr"/>
+      <c r="W65" s="2" t="inlineStr"/>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr"/>
+      <c r="Z65" s="2" t="inlineStr"/>
+      <c r="AA65" s="2" t="inlineStr"/>
+      <c r="AB65" s="2" t="inlineStr"/>
+      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AD65" s="2" t="inlineStr"/>
+      <c r="AE65" s="2" t="inlineStr"/>
+      <c r="AF65" s="2" t="inlineStr"/>
+      <c r="AG65" s="2" t="inlineStr"/>
+      <c r="AH65" s="2" t="inlineStr"/>
+      <c r="AI65" s="2" t="inlineStr"/>
+      <c r="AJ65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>db7c3b98e6ce4375</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>3746c7f78cdda704f52e709da19cd4f6a76cfc5f34610bf1fe0352705e49ca11</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>69144</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>0.673324</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>0.390625</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr"/>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>0.28269900000000003</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:14:02.920479Z</t>
+        </is>
+      </c>
+      <c r="S66" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr"/>
+      <c r="W66" s="2" t="inlineStr"/>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr"/>
+      <c r="Z66" s="2" t="inlineStr"/>
+      <c r="AA66" s="2" t="inlineStr"/>
+      <c r="AB66" s="2" t="inlineStr"/>
+      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AD66" s="2" t="inlineStr"/>
+      <c r="AE66" s="2" t="inlineStr"/>
+      <c r="AF66" s="2" t="inlineStr"/>
+      <c r="AG66" s="2" t="inlineStr"/>
+      <c r="AH66" s="2" t="inlineStr"/>
+      <c r="AI66" s="2" t="inlineStr"/>
+      <c r="AJ66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>f1014ba6b44146e2</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>252293c0656e970fcd8f959b81c88abb29c4ae4c82479c180ab25f5c206db6c3</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>67566</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>0.745981</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr"/>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>0.05557852321981427</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:49:14.689846Z</t>
+        </is>
+      </c>
+      <c r="S67" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr"/>
+      <c r="W67" s="2" t="inlineStr"/>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr"/>
+      <c r="Z67" s="2" t="inlineStr"/>
+      <c r="AA67" s="2" t="inlineStr"/>
+      <c r="AB67" s="2" t="inlineStr"/>
+      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AD67" s="2" t="inlineStr"/>
+      <c r="AE67" s="2" t="inlineStr"/>
+      <c r="AF67" s="2" t="inlineStr"/>
+      <c r="AG67" s="2" t="inlineStr"/>
+      <c r="AH67" s="2" t="inlineStr"/>
+      <c r="AI67" s="2" t="inlineStr"/>
+      <c r="AJ67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>04179a311ece4647</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>252293c0656e970fcd8f959b81c88abb29c4ae4c82479c180ab25f5c206db6c3</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>67655</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>0.618504</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr"/>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>0.059032634361233516</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:49:16.759918Z</t>
+        </is>
+      </c>
+      <c r="S68" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr"/>
+      <c r="W68" s="2" t="inlineStr"/>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr"/>
+      <c r="Z68" s="2" t="inlineStr"/>
+      <c r="AA68" s="2" t="inlineStr"/>
+      <c r="AB68" s="2" t="inlineStr"/>
+      <c r="AC68" s="2" t="inlineStr"/>
+      <c r="AD68" s="2" t="inlineStr"/>
+      <c r="AE68" s="2" t="inlineStr"/>
+      <c r="AF68" s="2" t="inlineStr"/>
+      <c r="AG68" s="2" t="inlineStr"/>
+      <c r="AH68" s="2" t="inlineStr"/>
+      <c r="AI68" s="2" t="inlineStr"/>
+      <c r="AJ68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>2865626b622247c5</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>252293c0656e970fcd8f959b81c88abb29c4ae4c82479c180ab25f5c206db6c3</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>63451</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>0.727337</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr"/>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>0.036934523219814275</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:49:17.879779Z</t>
+        </is>
+      </c>
+      <c r="S69" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr"/>
+      <c r="W69" s="2" t="inlineStr"/>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr"/>
+      <c r="Z69" s="2" t="inlineStr"/>
+      <c r="AA69" s="2" t="inlineStr"/>
+      <c r="AB69" s="2" t="inlineStr"/>
+      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AD69" s="2" t="inlineStr"/>
+      <c r="AE69" s="2" t="inlineStr"/>
+      <c r="AF69" s="2" t="inlineStr"/>
+      <c r="AG69" s="2" t="inlineStr"/>
+      <c r="AH69" s="2" t="inlineStr"/>
+      <c r="AI69" s="2" t="inlineStr"/>
+      <c r="AJ69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>1804eba7a1d64442</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>252293c0656e970fcd8f959b81c88abb29c4ae4c82479c180ab25f5c206db6c3</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>68509</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>0.631465</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>0.4694835680751174</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr"/>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>0.16198143192488268</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:49:25.548452Z</t>
+        </is>
+      </c>
+      <c r="S70" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr"/>
+      <c r="W70" s="2" t="inlineStr"/>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr"/>
+      <c r="Z70" s="2" t="inlineStr"/>
+      <c r="AA70" s="2" t="inlineStr"/>
+      <c r="AB70" s="2" t="inlineStr"/>
+      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AD70" s="2" t="inlineStr"/>
+      <c r="AE70" s="2" t="inlineStr"/>
+      <c r="AF70" s="2" t="inlineStr"/>
+      <c r="AG70" s="2" t="inlineStr"/>
+      <c r="AH70" s="2" t="inlineStr"/>
+      <c r="AI70" s="2" t="inlineStr"/>
+      <c r="AJ70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>39ca2f9317a44fc4</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>252293c0656e970fcd8f959b81c88abb29c4ae4c82479c180ab25f5c206db6c3</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>69143</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>0.624496</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr"/>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>0.0047241368821293594</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:49:33.236683Z</t>
+        </is>
+      </c>
+      <c r="S71" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr"/>
+      <c r="W71" s="2" t="inlineStr"/>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr"/>
+      <c r="Z71" s="2" t="inlineStr"/>
+      <c r="AA71" s="2" t="inlineStr"/>
+      <c r="AB71" s="2" t="inlineStr"/>
+      <c r="AC71" s="2" t="inlineStr"/>
+      <c r="AD71" s="2" t="inlineStr"/>
+      <c r="AE71" s="2" t="inlineStr"/>
+      <c r="AF71" s="2" t="inlineStr"/>
+      <c r="AG71" s="2" t="inlineStr"/>
+      <c r="AH71" s="2" t="inlineStr"/>
+      <c r="AI71" s="2" t="inlineStr"/>
+      <c r="AJ71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>c03ca3bfb1ed4733</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>252293c0656e970fcd8f959b81c88abb29c4ae4c82479c180ab25f5c206db6c3</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>69144</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>0.672965</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>0.390625</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr"/>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>0.28234000000000004</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:49:33.789151Z</t>
+        </is>
+      </c>
+      <c r="S72" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr"/>
+      <c r="W72" s="2" t="inlineStr"/>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr"/>
+      <c r="Z72" s="2" t="inlineStr"/>
+      <c r="AA72" s="2" t="inlineStr"/>
+      <c r="AB72" s="2" t="inlineStr"/>
+      <c r="AC72" s="2" t="inlineStr"/>
+      <c r="AD72" s="2" t="inlineStr"/>
+      <c r="AE72" s="2" t="inlineStr"/>
+      <c r="AF72" s="2" t="inlineStr"/>
+      <c r="AG72" s="2" t="inlineStr"/>
+      <c r="AH72" s="2" t="inlineStr"/>
+      <c r="AI72" s="2" t="inlineStr"/>
+      <c r="AJ72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>9cd3044602eb4562</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>5b25b8a2e33548a0db52ea4fd5a95a2359dd1c4e1da2bf1b622a20ed63533636</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>67566</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>0.745981</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr"/>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr"/>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>0.05557852321981427</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:59:41.776596Z</t>
+        </is>
+      </c>
+      <c r="S73" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr"/>
+      <c r="W73" s="2" t="inlineStr"/>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr"/>
+      <c r="Z73" s="2" t="inlineStr"/>
+      <c r="AA73" s="2" t="inlineStr"/>
+      <c r="AB73" s="2" t="inlineStr"/>
+      <c r="AC73" s="2" t="inlineStr"/>
+      <c r="AD73" s="2" t="inlineStr"/>
+      <c r="AE73" s="2" t="inlineStr"/>
+      <c r="AF73" s="2" t="inlineStr"/>
+      <c r="AG73" s="2" t="inlineStr"/>
+      <c r="AH73" s="2" t="inlineStr"/>
+      <c r="AI73" s="2" t="inlineStr"/>
+      <c r="AJ73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>bcbb471bf2b24b40</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>5b25b8a2e33548a0db52ea4fd5a95a2359dd1c4e1da2bf1b622a20ed63533636</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>67655</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>0.618504</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr"/>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr"/>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>0.059032634361233516</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:59:43.959369Z</t>
+        </is>
+      </c>
+      <c r="S74" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr"/>
+      <c r="W74" s="2" t="inlineStr"/>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr"/>
+      <c r="Z74" s="2" t="inlineStr"/>
+      <c r="AA74" s="2" t="inlineStr"/>
+      <c r="AB74" s="2" t="inlineStr"/>
+      <c r="AC74" s="2" t="inlineStr"/>
+      <c r="AD74" s="2" t="inlineStr"/>
+      <c r="AE74" s="2" t="inlineStr"/>
+      <c r="AF74" s="2" t="inlineStr"/>
+      <c r="AG74" s="2" t="inlineStr"/>
+      <c r="AH74" s="2" t="inlineStr"/>
+      <c r="AI74" s="2" t="inlineStr"/>
+      <c r="AJ74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>8c259fdfa41d47ea</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>5b25b8a2e33548a0db52ea4fd5a95a2359dd1c4e1da2bf1b622a20ed63533636</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>63451</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>0.727337</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr"/>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr"/>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>0.036934523219814275</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:59:45.064882Z</t>
+        </is>
+      </c>
+      <c r="S75" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr"/>
+      <c r="W75" s="2" t="inlineStr"/>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr"/>
+      <c r="Z75" s="2" t="inlineStr"/>
+      <c r="AA75" s="2" t="inlineStr"/>
+      <c r="AB75" s="2" t="inlineStr"/>
+      <c r="AC75" s="2" t="inlineStr"/>
+      <c r="AD75" s="2" t="inlineStr"/>
+      <c r="AE75" s="2" t="inlineStr"/>
+      <c r="AF75" s="2" t="inlineStr"/>
+      <c r="AG75" s="2" t="inlineStr"/>
+      <c r="AH75" s="2" t="inlineStr"/>
+      <c r="AI75" s="2" t="inlineStr"/>
+      <c r="AJ75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>02f0c46d9d414a54</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>5b25b8a2e33548a0db52ea4fd5a95a2359dd1c4e1da2bf1b622a20ed63533636</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>68509</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>0.631465</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr"/>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>0.4694835680751174</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr"/>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>0.16198143192488268</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:59:51.977078Z</t>
+        </is>
+      </c>
+      <c r="S76" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr"/>
+      <c r="W76" s="2" t="inlineStr"/>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr"/>
+      <c r="Z76" s="2" t="inlineStr"/>
+      <c r="AA76" s="2" t="inlineStr"/>
+      <c r="AB76" s="2" t="inlineStr"/>
+      <c r="AC76" s="2" t="inlineStr"/>
+      <c r="AD76" s="2" t="inlineStr"/>
+      <c r="AE76" s="2" t="inlineStr"/>
+      <c r="AF76" s="2" t="inlineStr"/>
+      <c r="AG76" s="2" t="inlineStr"/>
+      <c r="AH76" s="2" t="inlineStr"/>
+      <c r="AI76" s="2" t="inlineStr"/>
+      <c r="AJ76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>064733b61f7f451a</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>5b25b8a2e33548a0db52ea4fd5a95a2359dd1c4e1da2bf1b622a20ed63533636</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>69143</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>0.624496</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr"/>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr"/>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>0.0047241368821293594</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:59:59.632796Z</t>
+        </is>
+      </c>
+      <c r="S77" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr"/>
+      <c r="W77" s="2" t="inlineStr"/>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr"/>
+      <c r="Z77" s="2" t="inlineStr"/>
+      <c r="AA77" s="2" t="inlineStr"/>
+      <c r="AB77" s="2" t="inlineStr"/>
+      <c r="AC77" s="2" t="inlineStr"/>
+      <c r="AD77" s="2" t="inlineStr"/>
+      <c r="AE77" s="2" t="inlineStr"/>
+      <c r="AF77" s="2" t="inlineStr"/>
+      <c r="AG77" s="2" t="inlineStr"/>
+      <c r="AH77" s="2" t="inlineStr"/>
+      <c r="AI77" s="2" t="inlineStr"/>
+      <c r="AJ77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>10c3db23b4904c5d</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>5b25b8a2e33548a0db52ea4fd5a95a2359dd1c4e1da2bf1b622a20ed63533636</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>69144</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>0.672965</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr"/>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>0.390625</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr"/>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>0.28234000000000004</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T11:00:00.219070Z</t>
+        </is>
+      </c>
+      <c r="S78" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr"/>
+      <c r="W78" s="2" t="inlineStr"/>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr"/>
+      <c r="Z78" s="2" t="inlineStr"/>
+      <c r="AA78" s="2" t="inlineStr"/>
+      <c r="AB78" s="2" t="inlineStr"/>
+      <c r="AC78" s="2" t="inlineStr"/>
+      <c r="AD78" s="2" t="inlineStr"/>
+      <c r="AE78" s="2" t="inlineStr"/>
+      <c r="AF78" s="2" t="inlineStr"/>
+      <c r="AG78" s="2" t="inlineStr"/>
+      <c r="AH78" s="2" t="inlineStr"/>
+      <c r="AI78" s="2" t="inlineStr"/>
+      <c r="AJ78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>15ff0f204a974ad2</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>8e100718c38982e9b6a67d6c835251aad775fa6c0f7d64cbcae66021f2cd7f9c</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>67566</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>0.745478</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr"/>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr"/>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>0.05507552321981424</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T13:30:33.645010Z</t>
+        </is>
+      </c>
+      <c r="S79" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr"/>
+      <c r="W79" s="2" t="inlineStr"/>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>0.690000</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>-0.000402</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>0.8969</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T16:48:25.314153Z</t>
+        </is>
+      </c>
+      <c r="AD79" s="2" t="inlineStr"/>
+      <c r="AE79" s="2" t="inlineStr"/>
+      <c r="AF79" s="2" t="inlineStr"/>
+      <c r="AG79" s="2" t="inlineStr"/>
+      <c r="AH79" s="2" t="inlineStr"/>
+      <c r="AI79" s="2" t="inlineStr"/>
+      <c r="AJ79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>6cf2ae363c8c4d9b</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>8e100718c38982e9b6a67d6c835251aad775fa6c0f7d64cbcae66021f2cd7f9c</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>67655</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>0.617946</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr"/>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr"/>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>0.06839645045045051</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T13:30:35.946950Z</t>
+        </is>
+      </c>
+      <c r="S80" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr"/>
+      <c r="V80" s="2" t="inlineStr"/>
+      <c r="W80" s="2" t="inlineStr"/>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr"/>
+      <c r="Z80" s="2" t="inlineStr"/>
+      <c r="AA80" s="2" t="inlineStr"/>
+      <c r="AB80" s="2" t="inlineStr"/>
+      <c r="AC80" s="2" t="inlineStr"/>
+      <c r="AD80" s="2" t="inlineStr"/>
+      <c r="AE80" s="2" t="inlineStr"/>
+      <c r="AF80" s="2" t="inlineStr"/>
+      <c r="AG80" s="2" t="inlineStr"/>
+      <c r="AH80" s="2" t="inlineStr"/>
+      <c r="AI80" s="2" t="inlineStr"/>
+      <c r="AJ80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>313d225d4d3747f3</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>8e100718c38982e9b6a67d6c835251aad775fa6c0f7d64cbcae66021f2cd7f9c</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>63451</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>0.727674</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr"/>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr"/>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>0.037271523219814306</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T13:30:36.997710Z</t>
+        </is>
+      </c>
+      <c r="S81" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr"/>
+      <c r="V81" s="2" t="inlineStr"/>
+      <c r="W81" s="2" t="inlineStr"/>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr"/>
+      <c r="Z81" s="2" t="inlineStr"/>
+      <c r="AA81" s="2" t="inlineStr"/>
+      <c r="AB81" s="2" t="inlineStr"/>
+      <c r="AC81" s="2" t="inlineStr"/>
+      <c r="AD81" s="2" t="inlineStr"/>
+      <c r="AE81" s="2" t="inlineStr"/>
+      <c r="AF81" s="2" t="inlineStr"/>
+      <c r="AG81" s="2" t="inlineStr"/>
+      <c r="AH81" s="2" t="inlineStr"/>
+      <c r="AI81" s="2" t="inlineStr"/>
+      <c r="AJ81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>babafe2fea4c46a4</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>8e100718c38982e9b6a67d6c835251aad775fa6c0f7d64cbcae66021f2cd7f9c</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>68509</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>0.63091</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr"/>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr"/>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>0.13090999999999997</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T13:30:46.543407Z</t>
+        </is>
+      </c>
+      <c r="S82" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr"/>
+      <c r="V82" s="2" t="inlineStr"/>
+      <c r="W82" s="2" t="inlineStr"/>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr"/>
+      <c r="Z82" s="2" t="inlineStr"/>
+      <c r="AA82" s="2" t="inlineStr"/>
+      <c r="AB82" s="2" t="inlineStr"/>
+      <c r="AC82" s="2" t="inlineStr"/>
+      <c r="AD82" s="2" t="inlineStr"/>
+      <c r="AE82" s="2" t="inlineStr"/>
+      <c r="AF82" s="2" t="inlineStr"/>
+      <c r="AG82" s="2" t="inlineStr"/>
+      <c r="AH82" s="2" t="inlineStr"/>
+      <c r="AI82" s="2" t="inlineStr"/>
+      <c r="AJ82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>d5ce611c5a644a1b</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>8e100718c38982e9b6a67d6c835251aad775fa6c0f7d64cbcae66021f2cd7f9c</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>69143</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>0.623938</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr"/>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr"/>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>0.004166136882129301</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T13:30:54.591219Z</t>
+        </is>
+      </c>
+      <c r="S83" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr"/>
+      <c r="V83" s="2" t="inlineStr"/>
+      <c r="W83" s="2" t="inlineStr"/>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr"/>
+      <c r="Z83" s="2" t="inlineStr"/>
+      <c r="AA83" s="2" t="inlineStr"/>
+      <c r="AB83" s="2" t="inlineStr"/>
+      <c r="AC83" s="2" t="inlineStr"/>
+      <c r="AD83" s="2" t="inlineStr"/>
+      <c r="AE83" s="2" t="inlineStr"/>
+      <c r="AF83" s="2" t="inlineStr"/>
+      <c r="AG83" s="2" t="inlineStr"/>
+      <c r="AH83" s="2" t="inlineStr"/>
+      <c r="AI83" s="2" t="inlineStr"/>
+      <c r="AJ83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>5dea3f5f4f014c7f</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>1df881e42491d670230c39c2a2044a2d352eb451f3de82bb7e4ae7d3d6dca4e4</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>67655</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>0.617946</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr"/>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>0.05847463436123346</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:56:18.475479Z</t>
+        </is>
+      </c>
+      <c r="S84" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr"/>
+      <c r="V84" s="2" t="inlineStr"/>
+      <c r="W84" s="2" t="inlineStr"/>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr"/>
+      <c r="Z84" s="2" t="inlineStr"/>
+      <c r="AA84" s="2" t="inlineStr"/>
+      <c r="AB84" s="2" t="inlineStr"/>
+      <c r="AC84" s="2" t="inlineStr"/>
+      <c r="AD84" s="2" t="inlineStr"/>
+      <c r="AE84" s="2" t="inlineStr"/>
+      <c r="AF84" s="2" t="inlineStr"/>
+      <c r="AG84" s="2" t="inlineStr"/>
+      <c r="AH84" s="2" t="inlineStr"/>
+      <c r="AI84" s="2" t="inlineStr"/>
+      <c r="AJ84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>48acea6319aa4211</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>1df881e42491d670230c39c2a2044a2d352eb451f3de82bb7e4ae7d3d6dca4e4</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>63451</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>0.727674</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr"/>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr"/>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>0.037271523219814306</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:56:19.509117Z</t>
+        </is>
+      </c>
+      <c r="S85" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr"/>
+      <c r="V85" s="2" t="inlineStr"/>
+      <c r="W85" s="2" t="inlineStr"/>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr"/>
+      <c r="Z85" s="2" t="inlineStr"/>
+      <c r="AA85" s="2" t="inlineStr"/>
+      <c r="AB85" s="2" t="inlineStr"/>
+      <c r="AC85" s="2" t="inlineStr"/>
+      <c r="AD85" s="2" t="inlineStr"/>
+      <c r="AE85" s="2" t="inlineStr"/>
+      <c r="AF85" s="2" t="inlineStr"/>
+      <c r="AG85" s="2" t="inlineStr"/>
+      <c r="AH85" s="2" t="inlineStr"/>
+      <c r="AI85" s="2" t="inlineStr"/>
+      <c r="AJ85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>84450d48997842b4</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>1df881e42491d670230c39c2a2044a2d352eb451f3de82bb7e4ae7d3d6dca4e4</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>68509</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>0.63091</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr"/>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>0.13090999999999997</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:56:26.826179Z</t>
+        </is>
+      </c>
+      <c r="S86" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr"/>
+      <c r="V86" s="2" t="inlineStr"/>
+      <c r="W86" s="2" t="inlineStr"/>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr"/>
+      <c r="Z86" s="2" t="inlineStr"/>
+      <c r="AA86" s="2" t="inlineStr"/>
+      <c r="AB86" s="2" t="inlineStr"/>
+      <c r="AC86" s="2" t="inlineStr"/>
+      <c r="AD86" s="2" t="inlineStr"/>
+      <c r="AE86" s="2" t="inlineStr"/>
+      <c r="AF86" s="2" t="inlineStr"/>
+      <c r="AG86" s="2" t="inlineStr"/>
+      <c r="AH86" s="2" t="inlineStr"/>
+      <c r="AI86" s="2" t="inlineStr"/>
+      <c r="AJ86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>ccaf5d4575bd4d28</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>1df881e42491d670230c39c2a2044a2d352eb451f3de82bb7e4ae7d3d6dca4e4</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>69143</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>0.623938</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr"/>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>0.004166136882129301</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:56:34.388333Z</t>
+        </is>
+      </c>
+      <c r="S87" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr"/>
+      <c r="V87" s="2" t="inlineStr"/>
+      <c r="W87" s="2" t="inlineStr"/>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr"/>
+      <c r="Z87" s="2" t="inlineStr"/>
+      <c r="AA87" s="2" t="inlineStr"/>
+      <c r="AB87" s="2" t="inlineStr"/>
+      <c r="AC87" s="2" t="inlineStr"/>
+      <c r="AD87" s="2" t="inlineStr"/>
+      <c r="AE87" s="2" t="inlineStr"/>
+      <c r="AF87" s="2" t="inlineStr"/>
+      <c r="AG87" s="2" t="inlineStr"/>
+      <c r="AH87" s="2" t="inlineStr"/>
+      <c r="AI87" s="2" t="inlineStr"/>
+      <c r="AJ87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>a3b282e8157e4f1b</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>1df881e42491d670230c39c2a2044a2d352eb451f3de82bb7e4ae7d3d6dca4e4</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>69144</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>0.67242</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>0.42016806722689076</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr"/>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>0.25225193277310926</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:56:35.014500Z</t>
+        </is>
+      </c>
+      <c r="S88" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr"/>
+      <c r="V88" s="2" t="inlineStr"/>
+      <c r="W88" s="2" t="inlineStr"/>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr"/>
+      <c r="Z88" s="2" t="inlineStr"/>
+      <c r="AA88" s="2" t="inlineStr"/>
+      <c r="AB88" s="2" t="inlineStr"/>
+      <c r="AC88" s="2" t="inlineStr"/>
+      <c r="AD88" s="2" t="inlineStr"/>
+      <c r="AE88" s="2" t="inlineStr"/>
+      <c r="AF88" s="2" t="inlineStr"/>
+      <c r="AG88" s="2" t="inlineStr"/>
+      <c r="AH88" s="2" t="inlineStr"/>
+      <c r="AI88" s="2" t="inlineStr"/>
+      <c r="AJ88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>169882ed216a443f</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>1ea058b3787e110001b0b2566432119ad0db112ed8a0f99c6473f0ece994db7c</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>67655</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>0.617946</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr"/>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>0.008570999999999995</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T16:30:56.570837Z</t>
+        </is>
+      </c>
+      <c r="S89" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr"/>
+      <c r="V89" s="2" t="inlineStr"/>
+      <c r="W89" s="2" t="inlineStr"/>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr"/>
+      <c r="Z89" s="2" t="inlineStr"/>
+      <c r="AA89" s="2" t="inlineStr"/>
+      <c r="AB89" s="2" t="inlineStr"/>
+      <c r="AC89" s="2" t="inlineStr"/>
+      <c r="AD89" s="2" t="inlineStr"/>
+      <c r="AE89" s="2" t="inlineStr"/>
+      <c r="AF89" s="2" t="inlineStr"/>
+      <c r="AG89" s="2" t="inlineStr"/>
+      <c r="AH89" s="2" t="inlineStr"/>
+      <c r="AI89" s="2" t="inlineStr"/>
+      <c r="AJ89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>70e0d5a0439c4462</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>1ea058b3787e110001b0b2566432119ad0db112ed8a0f99c6473f0ece994db7c</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>63451</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>0.727674</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr"/>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>0.037271523219814306</t>
+        </is>
+      </c>
+      <c r="R90" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T16:30:57.594643Z</t>
+        </is>
+      </c>
+      <c r="S90" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr"/>
+      <c r="V90" s="2" t="inlineStr"/>
+      <c r="W90" s="2" t="inlineStr"/>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr"/>
+      <c r="Z90" s="2" t="inlineStr"/>
+      <c r="AA90" s="2" t="inlineStr"/>
+      <c r="AB90" s="2" t="inlineStr"/>
+      <c r="AC90" s="2" t="inlineStr"/>
+      <c r="AD90" s="2" t="inlineStr"/>
+      <c r="AE90" s="2" t="inlineStr"/>
+      <c r="AF90" s="2" t="inlineStr"/>
+      <c r="AG90" s="2" t="inlineStr"/>
+      <c r="AH90" s="2" t="inlineStr"/>
+      <c r="AI90" s="2" t="inlineStr"/>
+      <c r="AJ90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>dee7059057ce47e8</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>1ea058b3787e110001b0b2566432119ad0db112ed8a0f99c6473f0ece994db7c</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>68509</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>0.63091</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr"/>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
+          <t>0.13090999999999997</t>
+        </is>
+      </c>
+      <c r="R91" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T16:31:06.427025Z</t>
+        </is>
+      </c>
+      <c r="S91" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr"/>
+      <c r="V91" s="2" t="inlineStr"/>
+      <c r="W91" s="2" t="inlineStr"/>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr"/>
+      <c r="Z91" s="2" t="inlineStr"/>
+      <c r="AA91" s="2" t="inlineStr"/>
+      <c r="AB91" s="2" t="inlineStr"/>
+      <c r="AC91" s="2" t="inlineStr"/>
+      <c r="AD91" s="2" t="inlineStr"/>
+      <c r="AE91" s="2" t="inlineStr"/>
+      <c r="AF91" s="2" t="inlineStr"/>
+      <c r="AG91" s="2" t="inlineStr"/>
+      <c r="AH91" s="2" t="inlineStr"/>
+      <c r="AI91" s="2" t="inlineStr"/>
+      <c r="AJ91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>07d5a8ec8216443d</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>1ea058b3787e110001b0b2566432119ad0db112ed8a0f99c6473f0ece994db7c</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>69143</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>0.623938</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr"/>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>0.004166136882129301</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T16:31:15.001532Z</t>
+        </is>
+      </c>
+      <c r="S92" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr"/>
+      <c r="V92" s="2" t="inlineStr"/>
+      <c r="W92" s="2" t="inlineStr"/>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr"/>
+      <c r="Z92" s="2" t="inlineStr"/>
+      <c r="AA92" s="2" t="inlineStr"/>
+      <c r="AB92" s="2" t="inlineStr"/>
+      <c r="AC92" s="2" t="inlineStr"/>
+      <c r="AD92" s="2" t="inlineStr"/>
+      <c r="AE92" s="2" t="inlineStr"/>
+      <c r="AF92" s="2" t="inlineStr"/>
+      <c r="AG92" s="2" t="inlineStr"/>
+      <c r="AH92" s="2" t="inlineStr"/>
+      <c r="AI92" s="2" t="inlineStr"/>
+      <c r="AJ92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>5f7a63706ded4e18</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>1ea058b3787e110001b0b2566432119ad0db112ed8a0f99c6473f0ece994db7c</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>69144</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>0.67242</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr"/>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>0.42016806722689076</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr"/>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>0.25225193277310926</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T16:31:15.511082Z</t>
+        </is>
+      </c>
+      <c r="S93" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr"/>
+      <c r="V93" s="2" t="inlineStr"/>
+      <c r="W93" s="2" t="inlineStr"/>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr"/>
+      <c r="Z93" s="2" t="inlineStr"/>
+      <c r="AA93" s="2" t="inlineStr"/>
+      <c r="AB93" s="2" t="inlineStr"/>
+      <c r="AC93" s="2" t="inlineStr"/>
+      <c r="AD93" s="2" t="inlineStr"/>
+      <c r="AE93" s="2" t="inlineStr"/>
+      <c r="AF93" s="2" t="inlineStr"/>
+      <c r="AG93" s="2" t="inlineStr"/>
+      <c r="AH93" s="2" t="inlineStr"/>
+      <c r="AI93" s="2" t="inlineStr"/>
+      <c r="AJ93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>27c45128f3e44787</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>3f847e696c6cfee2a2c70922594f6bd120d4cf7ba6558e1e546e8c0ef9dc560a</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>63451</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>0.727674</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr"/>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>0.037271523219814306</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T16:51:13.464811Z</t>
+        </is>
+      </c>
+      <c r="S94" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr"/>
+      <c r="V94" s="2" t="inlineStr"/>
+      <c r="W94" s="2" t="inlineStr"/>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr"/>
+      <c r="Z94" s="2" t="inlineStr"/>
+      <c r="AA94" s="2" t="inlineStr"/>
+      <c r="AB94" s="2" t="inlineStr"/>
+      <c r="AC94" s="2" t="inlineStr"/>
+      <c r="AD94" s="2" t="inlineStr"/>
+      <c r="AE94" s="2" t="inlineStr"/>
+      <c r="AF94" s="2" t="inlineStr"/>
+      <c r="AG94" s="2" t="inlineStr"/>
+      <c r="AH94" s="2" t="inlineStr"/>
+      <c r="AI94" s="2" t="inlineStr"/>
+      <c r="AJ94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>5223b27aef3642e0</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>3f847e696c6cfee2a2c70922594f6bd120d4cf7ba6558e1e546e8c0ef9dc560a</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>68509</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>0.63091</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr"/>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>0.13090999999999997</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T16:51:21.594292Z</t>
+        </is>
+      </c>
+      <c r="S95" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr"/>
+      <c r="V95" s="2" t="inlineStr"/>
+      <c r="W95" s="2" t="inlineStr"/>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr"/>
+      <c r="Z95" s="2" t="inlineStr"/>
+      <c r="AA95" s="2" t="inlineStr"/>
+      <c r="AB95" s="2" t="inlineStr"/>
+      <c r="AC95" s="2" t="inlineStr"/>
+      <c r="AD95" s="2" t="inlineStr"/>
+      <c r="AE95" s="2" t="inlineStr"/>
+      <c r="AF95" s="2" t="inlineStr"/>
+      <c r="AG95" s="2" t="inlineStr"/>
+      <c r="AH95" s="2" t="inlineStr"/>
+      <c r="AI95" s="2" t="inlineStr"/>
+      <c r="AJ95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>57b978c9eed6426c</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>3f847e696c6cfee2a2c70922594f6bd120d4cf7ba6558e1e546e8c0ef9dc560a</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>69143</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>0.623938</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr"/>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr"/>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>0.004166136882129301</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T16:51:29.691277Z</t>
+        </is>
+      </c>
+      <c r="S96" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr"/>
+      <c r="V96" s="2" t="inlineStr"/>
+      <c r="W96" s="2" t="inlineStr"/>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr"/>
+      <c r="Z96" s="2" t="inlineStr"/>
+      <c r="AA96" s="2" t="inlineStr"/>
+      <c r="AB96" s="2" t="inlineStr"/>
+      <c r="AC96" s="2" t="inlineStr"/>
+      <c r="AD96" s="2" t="inlineStr"/>
+      <c r="AE96" s="2" t="inlineStr"/>
+      <c r="AF96" s="2" t="inlineStr"/>
+      <c r="AG96" s="2" t="inlineStr"/>
+      <c r="AH96" s="2" t="inlineStr"/>
+      <c r="AI96" s="2" t="inlineStr"/>
+      <c r="AJ96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>bf4063bb49ae4e12</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>3f847e696c6cfee2a2c70922594f6bd120d4cf7ba6558e1e546e8c0ef9dc560a</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>69336</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>0.702804</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr"/>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr"/>
+      <c r="Q97" s="2" t="inlineStr">
+        <is>
+          <t>0.08303213688212929</t>
+        </is>
+      </c>
+      <c r="R97" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T16:51:34.016285Z</t>
+        </is>
+      </c>
+      <c r="S97" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr"/>
+      <c r="V97" s="2" t="inlineStr"/>
+      <c r="W97" s="2" t="inlineStr"/>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr"/>
+      <c r="Z97" s="2" t="inlineStr"/>
+      <c r="AA97" s="2" t="inlineStr"/>
+      <c r="AB97" s="2" t="inlineStr"/>
+      <c r="AC97" s="2" t="inlineStr"/>
+      <c r="AD97" s="2" t="inlineStr"/>
+      <c r="AE97" s="2" t="inlineStr"/>
+      <c r="AF97" s="2" t="inlineStr"/>
+      <c r="AG97" s="2" t="inlineStr"/>
+      <c r="AH97" s="2" t="inlineStr"/>
+      <c r="AI97" s="2" t="inlineStr"/>
+      <c r="AJ97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>e366f248aa0e4acd</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>efcbb93ea7594fbafcf9325219d1c95ecb0ddde1698943dd2007a07a55350fa4</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>63451</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>0.727674</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr"/>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr"/>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>0.037271523219814306</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T17:08:43.723243Z</t>
+        </is>
+      </c>
+      <c r="S98" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr"/>
+      <c r="V98" s="2" t="inlineStr"/>
+      <c r="W98" s="2" t="inlineStr"/>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>0.690000</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>-0.000402</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>-2.0000</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T19:52:17.274179Z</t>
+        </is>
+      </c>
+      <c r="AD98" s="2" t="inlineStr"/>
+      <c r="AE98" s="2" t="inlineStr"/>
+      <c r="AF98" s="2" t="inlineStr"/>
+      <c r="AG98" s="2" t="inlineStr"/>
+      <c r="AH98" s="2" t="inlineStr"/>
+      <c r="AI98" s="2" t="inlineStr"/>
+      <c r="AJ98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>b53e0ed29bc8490f</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>efcbb93ea7594fbafcf9325219d1c95ecb0ddde1698943dd2007a07a55350fa4</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>68509</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>0.630908</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr"/>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr"/>
+      <c r="Q99" s="2" t="inlineStr">
+        <is>
+          <t>0.13090800000000002</t>
+        </is>
+      </c>
+      <c r="R99" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T17:08:51.190253Z</t>
+        </is>
+      </c>
+      <c r="S99" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr"/>
+      <c r="V99" s="2" t="inlineStr"/>
+      <c r="W99" s="2" t="inlineStr"/>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr"/>
+      <c r="Z99" s="2" t="inlineStr"/>
+      <c r="AA99" s="2" t="inlineStr"/>
+      <c r="AB99" s="2" t="inlineStr"/>
+      <c r="AC99" s="2" t="inlineStr"/>
+      <c r="AD99" s="2" t="inlineStr"/>
+      <c r="AE99" s="2" t="inlineStr"/>
+      <c r="AF99" s="2" t="inlineStr"/>
+      <c r="AG99" s="2" t="inlineStr"/>
+      <c r="AH99" s="2" t="inlineStr"/>
+      <c r="AI99" s="2" t="inlineStr"/>
+      <c r="AJ99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>157dabf1633e41e8</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>efcbb93ea7594fbafcf9325219d1c95ecb0ddde1698943dd2007a07a55350fa4</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>68870</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>0.561757</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr"/>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>0.30959752321981426</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr"/>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>0.2521594767801857</t>
+        </is>
+      </c>
+      <c r="R100" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T17:08:58.199439Z</t>
+        </is>
+      </c>
+      <c r="S100" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr"/>
+      <c r="V100" s="2" t="inlineStr"/>
+      <c r="W100" s="2" t="inlineStr"/>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr"/>
+      <c r="Z100" s="2" t="inlineStr"/>
+      <c r="AA100" s="2" t="inlineStr"/>
+      <c r="AB100" s="2" t="inlineStr"/>
+      <c r="AC100" s="2" t="inlineStr"/>
+      <c r="AD100" s="2" t="inlineStr"/>
+      <c r="AE100" s="2" t="inlineStr"/>
+      <c r="AF100" s="2" t="inlineStr"/>
+      <c r="AG100" s="2" t="inlineStr"/>
+      <c r="AH100" s="2" t="inlineStr"/>
+      <c r="AI100" s="2" t="inlineStr"/>
+      <c r="AJ100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>e8ea5c4a413f4ca0</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>efcbb93ea7594fbafcf9325219d1c95ecb0ddde1698943dd2007a07a55350fa4</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>69143</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>0.623938</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr"/>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr"/>
+      <c r="Q101" s="2" t="inlineStr">
+        <is>
+          <t>0.004166136882129301</t>
+        </is>
+      </c>
+      <c r="R101" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T17:08:59.308171Z</t>
+        </is>
+      </c>
+      <c r="S101" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr"/>
+      <c r="V101" s="2" t="inlineStr"/>
+      <c r="W101" s="2" t="inlineStr"/>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr"/>
+      <c r="Z101" s="2" t="inlineStr"/>
+      <c r="AA101" s="2" t="inlineStr"/>
+      <c r="AB101" s="2" t="inlineStr"/>
+      <c r="AC101" s="2" t="inlineStr"/>
+      <c r="AD101" s="2" t="inlineStr"/>
+      <c r="AE101" s="2" t="inlineStr"/>
+      <c r="AF101" s="2" t="inlineStr"/>
+      <c r="AG101" s="2" t="inlineStr"/>
+      <c r="AH101" s="2" t="inlineStr"/>
+      <c r="AI101" s="2" t="inlineStr"/>
+      <c r="AJ101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>9d902ea92f7e4cb5</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>efcbb93ea7594fbafcf9325219d1c95ecb0ddde1698943dd2007a07a55350fa4</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>69144</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>0.67242</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr"/>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>0.3597122302158273</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr"/>
+      <c r="Q102" s="2" t="inlineStr">
+        <is>
+          <t>0.3127077697841727</t>
+        </is>
+      </c>
+      <c r="R102" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T17:08:59.939668Z</t>
+        </is>
+      </c>
+      <c r="S102" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr"/>
+      <c r="V102" s="2" t="inlineStr"/>
+      <c r="W102" s="2" t="inlineStr"/>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr"/>
+      <c r="Z102" s="2" t="inlineStr"/>
+      <c r="AA102" s="2" t="inlineStr"/>
+      <c r="AB102" s="2" t="inlineStr"/>
+      <c r="AC102" s="2" t="inlineStr"/>
+      <c r="AD102" s="2" t="inlineStr"/>
+      <c r="AE102" s="2" t="inlineStr"/>
+      <c r="AF102" s="2" t="inlineStr"/>
+      <c r="AG102" s="2" t="inlineStr"/>
+      <c r="AH102" s="2" t="inlineStr"/>
+      <c r="AI102" s="2" t="inlineStr"/>
+      <c r="AJ102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>a0c513eee5a642e0</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>9ed3b7c0f543c614a78fccecbb0979eec8778e51fbb9fd911e0de01bc829c3f7</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>70566</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>0.694793</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr"/>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>0.30959752321981426</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr"/>
+      <c r="Q103" s="2" t="inlineStr">
+        <is>
+          <t>0.38519547678018573</t>
+        </is>
+      </c>
+      <c r="R103" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T19:54:51.742330Z</t>
+        </is>
+      </c>
+      <c r="S103" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr"/>
+      <c r="V103" s="2" t="inlineStr"/>
+      <c r="W103" s="2" t="inlineStr"/>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr"/>
+      <c r="Z103" s="2" t="inlineStr"/>
+      <c r="AA103" s="2" t="inlineStr"/>
+      <c r="AB103" s="2" t="inlineStr"/>
+      <c r="AC103" s="2" t="inlineStr"/>
+      <c r="AD103" s="2" t="inlineStr"/>
+      <c r="AE103" s="2" t="inlineStr"/>
+      <c r="AF103" s="2" t="inlineStr"/>
+      <c r="AG103" s="2" t="inlineStr"/>
+      <c r="AH103" s="2" t="inlineStr"/>
+      <c r="AI103" s="2" t="inlineStr"/>
+      <c r="AJ103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>af9c4622368c4ec8</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>9ed3b7c0f543c614a78fccecbb0979eec8778e51fbb9fd911e0de01bc829c3f7</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>68509</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>0.631145</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr"/>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr"/>
+      <c r="Q104" s="2" t="inlineStr">
+        <is>
+          <t>0.13114499999999996</t>
+        </is>
+      </c>
+      <c r="R104" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T19:54:53.215592Z</t>
+        </is>
+      </c>
+      <c r="S104" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr"/>
+      <c r="V104" s="2" t="inlineStr"/>
+      <c r="W104" s="2" t="inlineStr"/>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr"/>
+      <c r="Z104" s="2" t="inlineStr"/>
+      <c r="AA104" s="2" t="inlineStr"/>
+      <c r="AB104" s="2" t="inlineStr"/>
+      <c r="AC104" s="2" t="inlineStr"/>
+      <c r="AD104" s="2" t="inlineStr"/>
+      <c r="AE104" s="2" t="inlineStr"/>
+      <c r="AF104" s="2" t="inlineStr"/>
+      <c r="AG104" s="2" t="inlineStr"/>
+      <c r="AH104" s="2" t="inlineStr"/>
+      <c r="AI104" s="2" t="inlineStr"/>
+      <c r="AJ104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>29e07a8c11c64eec</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>9ed3b7c0f543c614a78fccecbb0979eec8778e51fbb9fd911e0de01bc829c3f7</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>69143</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>0.624041</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr"/>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr"/>
+      <c r="Q105" s="2" t="inlineStr">
+        <is>
+          <t>0.004269136882129265</t>
+        </is>
+      </c>
+      <c r="R105" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T19:55:01.856735Z</t>
+        </is>
+      </c>
+      <c r="S105" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr"/>
+      <c r="V105" s="2" t="inlineStr"/>
+      <c r="W105" s="2" t="inlineStr"/>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr"/>
+      <c r="Z105" s="2" t="inlineStr"/>
+      <c r="AA105" s="2" t="inlineStr"/>
+      <c r="AB105" s="2" t="inlineStr"/>
+      <c r="AC105" s="2" t="inlineStr"/>
+      <c r="AD105" s="2" t="inlineStr"/>
+      <c r="AE105" s="2" t="inlineStr"/>
+      <c r="AF105" s="2" t="inlineStr"/>
+      <c r="AG105" s="2" t="inlineStr"/>
+      <c r="AH105" s="2" t="inlineStr"/>
+      <c r="AI105" s="2" t="inlineStr"/>
+      <c r="AJ105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>af9b69eba1df4309</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>9ed3b7c0f543c614a78fccecbb0979eec8778e51fbb9fd911e0de01bc829c3f7</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>69144</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>0.63532</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr"/>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr"/>
+      <c r="Q106" s="2" t="inlineStr">
+        <is>
+          <t>0.0961494930875576</t>
+        </is>
+      </c>
+      <c r="R106" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T19:55:02.395842Z</t>
+        </is>
+      </c>
+      <c r="S106" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="inlineStr"/>
+      <c r="V106" s="2" t="inlineStr"/>
+      <c r="W106" s="2" t="inlineStr"/>
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr"/>
+      <c r="Z106" s="2" t="inlineStr"/>
+      <c r="AA106" s="2" t="inlineStr"/>
+      <c r="AB106" s="2" t="inlineStr"/>
+      <c r="AC106" s="2" t="inlineStr"/>
+      <c r="AD106" s="2" t="inlineStr"/>
+      <c r="AE106" s="2" t="inlineStr"/>
+      <c r="AF106" s="2" t="inlineStr"/>
+      <c r="AG106" s="2" t="inlineStr"/>
+      <c r="AH106" s="2" t="inlineStr"/>
+      <c r="AI106" s="2" t="inlineStr"/>
+      <c r="AJ106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>5797a320944e4e91</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>9ed3b7c0f543c614a78fccecbb0979eec8778e51fbb9fd911e0de01bc829c3f7</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>69233</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>0.571895</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr"/>
+      <c r="N107" s="2" t="inlineStr"/>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P107" s="2" t="inlineStr"/>
+      <c r="Q107" s="2" t="inlineStr">
+        <is>
+          <t>0.0010795493562232306</t>
+        </is>
+      </c>
+      <c r="R107" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T19:55:02.964867Z</t>
+        </is>
+      </c>
+      <c r="S107" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T107" s="2" t="inlineStr"/>
+      <c r="U107" s="2" t="inlineStr"/>
+      <c r="V107" s="2" t="inlineStr"/>
+      <c r="W107" s="2" t="inlineStr"/>
+      <c r="X107" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y107" s="2" t="inlineStr"/>
+      <c r="Z107" s="2" t="inlineStr"/>
+      <c r="AA107" s="2" t="inlineStr"/>
+      <c r="AB107" s="2" t="inlineStr"/>
+      <c r="AC107" s="2" t="inlineStr"/>
+      <c r="AD107" s="2" t="inlineStr"/>
+      <c r="AE107" s="2" t="inlineStr"/>
+      <c r="AF107" s="2" t="inlineStr"/>
+      <c r="AG107" s="2" t="inlineStr"/>
+      <c r="AH107" s="2" t="inlineStr"/>
+      <c r="AI107" s="2" t="inlineStr"/>
+      <c r="AJ107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>ab796c99828649d6</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>d3933d1bafaceb7c0a077e0f753c3ba13c021ffc2d56410541757708511322bf</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>70566</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr"/>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>0.694972</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr"/>
+      <c r="N108" s="2" t="inlineStr"/>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>0.30959752321981426</t>
+        </is>
+      </c>
+      <c r="P108" s="2" t="inlineStr"/>
+      <c r="Q108" s="2" t="inlineStr">
+        <is>
+          <t>0.38537447678018577</t>
+        </is>
+      </c>
+      <c r="R108" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T22:57:51.999221Z</t>
+        </is>
+      </c>
+      <c r="S108" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T108" s="2" t="inlineStr"/>
+      <c r="U108" s="2" t="inlineStr"/>
+      <c r="V108" s="2" t="inlineStr"/>
+      <c r="W108" s="2" t="inlineStr"/>
+      <c r="X108" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y108" s="2" t="inlineStr"/>
+      <c r="Z108" s="2" t="inlineStr"/>
+      <c r="AA108" s="2" t="inlineStr"/>
+      <c r="AB108" s="2" t="inlineStr"/>
+      <c r="AC108" s="2" t="inlineStr"/>
+      <c r="AD108" s="2" t="inlineStr"/>
+      <c r="AE108" s="2" t="inlineStr"/>
+      <c r="AF108" s="2" t="inlineStr"/>
+      <c r="AG108" s="2" t="inlineStr"/>
+      <c r="AH108" s="2" t="inlineStr"/>
+      <c r="AI108" s="2" t="inlineStr"/>
+      <c r="AJ108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>03a72a6f0ac84a2d</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>d3933d1bafaceb7c0a077e0f753c3ba13c021ffc2d56410541757708511322bf</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>68509</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr"/>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>0.631434</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr"/>
+      <c r="N109" s="2" t="inlineStr"/>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>0.5098039215686274</t>
+        </is>
+      </c>
+      <c r="P109" s="2" t="inlineStr"/>
+      <c r="Q109" s="2" t="inlineStr">
+        <is>
+          <t>0.12163007843137263</t>
+        </is>
+      </c>
+      <c r="R109" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T22:57:52.549068Z</t>
+        </is>
+      </c>
+      <c r="S109" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="T109" s="2" t="inlineStr"/>
+      <c r="U109" s="2" t="inlineStr"/>
+      <c r="V109" s="2" t="inlineStr"/>
+      <c r="W109" s="2" t="inlineStr"/>
+      <c r="X109" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y109" s="2" t="inlineStr"/>
+      <c r="Z109" s="2" t="inlineStr"/>
+      <c r="AA109" s="2" t="inlineStr"/>
+      <c r="AB109" s="2" t="inlineStr"/>
+      <c r="AC109" s="2" t="inlineStr"/>
+      <c r="AD109" s="2" t="inlineStr"/>
+      <c r="AE109" s="2" t="inlineStr"/>
+      <c r="AF109" s="2" t="inlineStr"/>
+      <c r="AG109" s="2" t="inlineStr"/>
+      <c r="AH109" s="2" t="inlineStr"/>
+      <c r="AI109" s="2" t="inlineStr"/>
+      <c r="AJ109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>d3f6b40bb0b24f85</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>d3933d1bafaceb7c0a077e0f753c3ba13c021ffc2d56410541757708511322bf</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>69143</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr"/>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>0.62429</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="inlineStr"/>
+      <c r="N110" s="2" t="inlineStr"/>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P110" s="2" t="inlineStr"/>
+      <c r="Q110" s="2" t="inlineStr">
+        <is>
+          <t>0.00451813688212932</t>
+        </is>
+      </c>
+      <c r="R110" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T22:58:00.727507Z</t>
+        </is>
+      </c>
+      <c r="S110" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T110" s="2" t="inlineStr"/>
+      <c r="U110" s="2" t="inlineStr"/>
+      <c r="V110" s="2" t="inlineStr"/>
+      <c r="W110" s="2" t="inlineStr"/>
+      <c r="X110" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y110" s="2" t="inlineStr"/>
+      <c r="Z110" s="2" t="inlineStr"/>
+      <c r="AA110" s="2" t="inlineStr"/>
+      <c r="AB110" s="2" t="inlineStr"/>
+      <c r="AC110" s="2" t="inlineStr"/>
+      <c r="AD110" s="2" t="inlineStr"/>
+      <c r="AE110" s="2" t="inlineStr"/>
+      <c r="AF110" s="2" t="inlineStr"/>
+      <c r="AG110" s="2" t="inlineStr"/>
+      <c r="AH110" s="2" t="inlineStr"/>
+      <c r="AI110" s="2" t="inlineStr"/>
+      <c r="AJ110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>164f03071e934fe3</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>d3933d1bafaceb7c0a077e0f753c3ba13c021ffc2d56410541757708511322bf</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>69144</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr"/>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>0.591582</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="inlineStr"/>
+      <c r="N111" s="2" t="inlineStr"/>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P111" s="2" t="inlineStr"/>
+      <c r="Q111" s="2" t="inlineStr">
+        <is>
+          <t>0.05241149308755766</t>
+        </is>
+      </c>
+      <c r="R111" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T22:58:01.217657Z</t>
+        </is>
+      </c>
+      <c r="S111" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T111" s="2" t="inlineStr"/>
+      <c r="U111" s="2" t="inlineStr"/>
+      <c r="V111" s="2" t="inlineStr"/>
+      <c r="W111" s="2" t="inlineStr"/>
+      <c r="X111" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y111" s="2" t="inlineStr"/>
+      <c r="Z111" s="2" t="inlineStr"/>
+      <c r="AA111" s="2" t="inlineStr"/>
+      <c r="AB111" s="2" t="inlineStr"/>
+      <c r="AC111" s="2" t="inlineStr"/>
+      <c r="AD111" s="2" t="inlineStr"/>
+      <c r="AE111" s="2" t="inlineStr"/>
+      <c r="AF111" s="2" t="inlineStr"/>
+      <c r="AG111" s="2" t="inlineStr"/>
+      <c r="AH111" s="2" t="inlineStr"/>
+      <c r="AI111" s="2" t="inlineStr"/>
+      <c r="AJ111" s="2" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>eb509956de5541c5</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>d3933d1bafaceb7c0a077e0f753c3ba13c021ffc2d56410541757708511322bf</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>69233</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr"/>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t>0.592547</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="inlineStr"/>
+      <c r="N112" s="2" t="inlineStr"/>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>0.4291845493562232</t>
+        </is>
+      </c>
+      <c r="P112" s="2" t="inlineStr"/>
+      <c r="Q112" s="2" t="inlineStr">
+        <is>
+          <t>0.16336245064377686</t>
+        </is>
+      </c>
+      <c r="R112" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T22:58:02.196480Z</t>
+        </is>
+      </c>
+      <c r="S112" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T112" s="2" t="inlineStr"/>
+      <c r="U112" s="2" t="inlineStr"/>
+      <c r="V112" s="2" t="inlineStr"/>
+      <c r="W112" s="2" t="inlineStr"/>
+      <c r="X112" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y112" s="2" t="inlineStr"/>
+      <c r="Z112" s="2" t="inlineStr"/>
+      <c r="AA112" s="2" t="inlineStr"/>
+      <c r="AB112" s="2" t="inlineStr"/>
+      <c r="AC112" s="2" t="inlineStr"/>
+      <c r="AD112" s="2" t="inlineStr"/>
+      <c r="AE112" s="2" t="inlineStr"/>
+      <c r="AF112" s="2" t="inlineStr"/>
+      <c r="AG112" s="2" t="inlineStr"/>
+      <c r="AH112" s="2" t="inlineStr"/>
+      <c r="AI112" s="2" t="inlineStr"/>
+      <c r="AJ112" s="2" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>a0ee84faa67b44b7</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>70566</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr"/>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>0.69409</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="inlineStr"/>
+      <c r="N113" s="2" t="inlineStr"/>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>0.30959752321981426</t>
+        </is>
+      </c>
+      <c r="P113" s="2" t="inlineStr"/>
+      <c r="Q113" s="2" t="inlineStr">
+        <is>
+          <t>0.3844924767801857</t>
+        </is>
+      </c>
+      <c r="R113" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:43.286617Z</t>
+        </is>
+      </c>
+      <c r="S113" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T113" s="2" t="inlineStr"/>
+      <c r="U113" s="2" t="inlineStr"/>
+      <c r="V113" s="2" t="inlineStr"/>
+      <c r="W113" s="2" t="inlineStr"/>
+      <c r="X113" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y113" s="2" t="inlineStr"/>
+      <c r="Z113" s="2" t="inlineStr"/>
+      <c r="AA113" s="2" t="inlineStr"/>
+      <c r="AB113" s="2" t="inlineStr"/>
+      <c r="AC113" s="2" t="inlineStr"/>
+      <c r="AD113" s="2" t="inlineStr"/>
+      <c r="AE113" s="2" t="inlineStr"/>
+      <c r="AF113" s="2" t="inlineStr"/>
+      <c r="AG113" s="2" t="inlineStr"/>
+      <c r="AH113" s="2" t="inlineStr"/>
+      <c r="AI113" s="2" t="inlineStr"/>
+      <c r="AJ113" s="2" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>e8c10eb970bf4358</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>68509</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr"/>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t>0.631317</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="inlineStr"/>
+      <c r="N114" s="2" t="inlineStr"/>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>0.5098039215686274</t>
+        </is>
+      </c>
+      <c r="P114" s="2" t="inlineStr"/>
+      <c r="Q114" s="2" t="inlineStr">
+        <is>
+          <t>0.1215130784313726</t>
+        </is>
+      </c>
+      <c r="R114" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:44.932625Z</t>
+        </is>
+      </c>
+      <c r="S114" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="T114" s="2" t="inlineStr"/>
+      <c r="U114" s="2" t="inlineStr"/>
+      <c r="V114" s="2" t="inlineStr"/>
+      <c r="W114" s="2" t="inlineStr"/>
+      <c r="X114" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y114" s="2" t="inlineStr"/>
+      <c r="Z114" s="2" t="inlineStr"/>
+      <c r="AA114" s="2" t="inlineStr"/>
+      <c r="AB114" s="2" t="inlineStr"/>
+      <c r="AC114" s="2" t="inlineStr"/>
+      <c r="AD114" s="2" t="inlineStr"/>
+      <c r="AE114" s="2" t="inlineStr"/>
+      <c r="AF114" s="2" t="inlineStr"/>
+      <c r="AG114" s="2" t="inlineStr"/>
+      <c r="AH114" s="2" t="inlineStr"/>
+      <c r="AI114" s="2" t="inlineStr"/>
+      <c r="AJ114" s="2" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>b6b4d8614e174aef</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>68689</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr"/>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>0.573934</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="inlineStr"/>
+      <c r="N115" s="2" t="inlineStr"/>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P115" s="2" t="inlineStr"/>
+      <c r="Q115" s="2" t="inlineStr">
+        <is>
+          <t>0.0031185493562232436</t>
+        </is>
+      </c>
+      <c r="R115" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:48.567590Z</t>
+        </is>
+      </c>
+      <c r="S115" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T115" s="2" t="inlineStr"/>
+      <c r="U115" s="2" t="inlineStr"/>
+      <c r="V115" s="2" t="inlineStr"/>
+      <c r="W115" s="2" t="inlineStr"/>
+      <c r="X115" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y115" s="2" t="inlineStr"/>
+      <c r="Z115" s="2" t="inlineStr"/>
+      <c r="AA115" s="2" t="inlineStr"/>
+      <c r="AB115" s="2" t="inlineStr"/>
+      <c r="AC115" s="2" t="inlineStr"/>
+      <c r="AD115" s="2" t="inlineStr"/>
+      <c r="AE115" s="2" t="inlineStr"/>
+      <c r="AF115" s="2" t="inlineStr"/>
+      <c r="AG115" s="2" t="inlineStr"/>
+      <c r="AH115" s="2" t="inlineStr"/>
+      <c r="AI115" s="2" t="inlineStr"/>
+      <c r="AJ115" s="2" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>8b7565d8e4dd4449</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>68690</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr"/>
+      <c r="L116" s="2" t="inlineStr">
+        <is>
+          <t>0.55055</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="inlineStr"/>
+      <c r="N116" s="2" t="inlineStr"/>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P116" s="2" t="inlineStr"/>
+      <c r="Q116" s="2" t="inlineStr">
+        <is>
+          <t>0.0010004504504504963</t>
+        </is>
+      </c>
+      <c r="R116" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:49.613554Z</t>
+        </is>
+      </c>
+      <c r="S116" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T116" s="2" t="inlineStr"/>
+      <c r="U116" s="2" t="inlineStr"/>
+      <c r="V116" s="2" t="inlineStr"/>
+      <c r="W116" s="2" t="inlineStr"/>
+      <c r="X116" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y116" s="2" t="inlineStr"/>
+      <c r="Z116" s="2" t="inlineStr"/>
+      <c r="AA116" s="2" t="inlineStr"/>
+      <c r="AB116" s="2" t="inlineStr"/>
+      <c r="AC116" s="2" t="inlineStr"/>
+      <c r="AD116" s="2" t="inlineStr"/>
+      <c r="AE116" s="2" t="inlineStr"/>
+      <c r="AF116" s="2" t="inlineStr"/>
+      <c r="AG116" s="2" t="inlineStr"/>
+      <c r="AH116" s="2" t="inlineStr"/>
+      <c r="AI116" s="2" t="inlineStr"/>
+      <c r="AJ116" s="2" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>519df67dff88419c</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>69143</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr"/>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>0.624143</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="inlineStr"/>
+      <c r="N117" s="2" t="inlineStr"/>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P117" s="2" t="inlineStr"/>
+      <c r="Q117" s="2" t="inlineStr">
+        <is>
+          <t>0.004371136882129312</t>
+        </is>
+      </c>
+      <c r="R117" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:52.417381Z</t>
+        </is>
+      </c>
+      <c r="S117" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T117" s="2" t="inlineStr"/>
+      <c r="U117" s="2" t="inlineStr"/>
+      <c r="V117" s="2" t="inlineStr"/>
+      <c r="W117" s="2" t="inlineStr"/>
+      <c r="X117" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y117" s="2" t="inlineStr"/>
+      <c r="Z117" s="2" t="inlineStr"/>
+      <c r="AA117" s="2" t="inlineStr"/>
+      <c r="AB117" s="2" t="inlineStr"/>
+      <c r="AC117" s="2" t="inlineStr"/>
+      <c r="AD117" s="2" t="inlineStr"/>
+      <c r="AE117" s="2" t="inlineStr"/>
+      <c r="AF117" s="2" t="inlineStr"/>
+      <c r="AG117" s="2" t="inlineStr"/>
+      <c r="AH117" s="2" t="inlineStr"/>
+      <c r="AI117" s="2" t="inlineStr"/>
+      <c r="AJ117" s="2" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>7a953e0ac8ce49d5</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>69144</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr"/>
+      <c r="L118" s="2" t="inlineStr">
+        <is>
+          <t>0.591618</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="inlineStr"/>
+      <c r="N118" s="2" t="inlineStr"/>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P118" s="2" t="inlineStr"/>
+      <c r="Q118" s="2" t="inlineStr">
+        <is>
+          <t>0.03214663436123344</t>
+        </is>
+      </c>
+      <c r="R118" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:53.026230Z</t>
+        </is>
+      </c>
+      <c r="S118" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T118" s="2" t="inlineStr"/>
+      <c r="U118" s="2" t="inlineStr"/>
+      <c r="V118" s="2" t="inlineStr"/>
+      <c r="W118" s="2" t="inlineStr"/>
+      <c r="X118" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y118" s="2" t="inlineStr"/>
+      <c r="Z118" s="2" t="inlineStr"/>
+      <c r="AA118" s="2" t="inlineStr"/>
+      <c r="AB118" s="2" t="inlineStr"/>
+      <c r="AC118" s="2" t="inlineStr"/>
+      <c r="AD118" s="2" t="inlineStr"/>
+      <c r="AE118" s="2" t="inlineStr"/>
+      <c r="AF118" s="2" t="inlineStr"/>
+      <c r="AG118" s="2" t="inlineStr"/>
+      <c r="AH118" s="2" t="inlineStr"/>
+      <c r="AI118" s="2" t="inlineStr"/>
+      <c r="AJ118" s="2" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>e05978469edf4d91</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>69273</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr"/>
+      <c r="L119" s="2" t="inlineStr">
+        <is>
+          <t>0.604656</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="inlineStr"/>
+      <c r="N119" s="2" t="inlineStr"/>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P119" s="2" t="inlineStr"/>
+      <c r="Q119" s="2" t="inlineStr">
+        <is>
+          <t>0.0046559999999998825</t>
+        </is>
+      </c>
+      <c r="R119" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:55.187744Z</t>
+        </is>
+      </c>
+      <c r="S119" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="T119" s="2" t="inlineStr"/>
+      <c r="U119" s="2" t="inlineStr"/>
+      <c r="V119" s="2" t="inlineStr"/>
+      <c r="W119" s="2" t="inlineStr"/>
+      <c r="X119" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y119" s="2" t="inlineStr"/>
+      <c r="Z119" s="2" t="inlineStr"/>
+      <c r="AA119" s="2" t="inlineStr"/>
+      <c r="AB119" s="2" t="inlineStr"/>
+      <c r="AC119" s="2" t="inlineStr"/>
+      <c r="AD119" s="2" t="inlineStr"/>
+      <c r="AE119" s="2" t="inlineStr"/>
+      <c r="AF119" s="2" t="inlineStr"/>
+      <c r="AG119" s="2" t="inlineStr"/>
+      <c r="AH119" s="2" t="inlineStr"/>
+      <c r="AI119" s="2" t="inlineStr"/>
+      <c r="AJ119" s="2" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>9187cf6fb87e43ab</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>69336</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr"/>
+      <c r="L120" s="2" t="inlineStr">
+        <is>
+          <t>0.74222</t>
+        </is>
+      </c>
+      <c r="M120" s="2" t="inlineStr"/>
+      <c r="N120" s="2" t="inlineStr"/>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>0.66996699669967</t>
+        </is>
+      </c>
+      <c r="P120" s="2" t="inlineStr"/>
+      <c r="Q120" s="2" t="inlineStr">
+        <is>
+          <t>0.07225300330033002</t>
+        </is>
+      </c>
+      <c r="R120" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:56.301588Z</t>
+        </is>
+      </c>
+      <c r="S120" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="T120" s="2" t="inlineStr"/>
+      <c r="U120" s="2" t="inlineStr"/>
+      <c r="V120" s="2" t="inlineStr"/>
+      <c r="W120" s="2" t="inlineStr"/>
+      <c r="X120" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y120" s="2" t="inlineStr"/>
+      <c r="Z120" s="2" t="inlineStr"/>
+      <c r="AA120" s="2" t="inlineStr"/>
+      <c r="AB120" s="2" t="inlineStr"/>
+      <c r="AC120" s="2" t="inlineStr"/>
+      <c r="AD120" s="2" t="inlineStr"/>
+      <c r="AE120" s="2" t="inlineStr"/>
+      <c r="AF120" s="2" t="inlineStr"/>
+      <c r="AG120" s="2" t="inlineStr"/>
+      <c r="AH120" s="2" t="inlineStr"/>
+      <c r="AI120" s="2" t="inlineStr"/>
+      <c r="AJ120" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ34"/>
+  <autoFilter ref="A1:AJ120"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/gated_research/model_ledgers/lol-tiered-elo.xlsx
+++ b/data/gated_research/model_ledgers/lol-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$120</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$155</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ120"/>
+  <dimension ref="A1:AJ155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -12874,8 +12874,3578 @@
       <c r="AI120" s="2" t="inlineStr"/>
       <c r="AJ120" s="2" t="inlineStr"/>
     </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>bbf62e81808d4b35</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>68509</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr"/>
+      <c r="L121" s="2" t="inlineStr">
+        <is>
+          <t>0.631317</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="inlineStr"/>
+      <c r="N121" s="2" t="inlineStr"/>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>0.5098039215686274</t>
+        </is>
+      </c>
+      <c r="P121" s="2" t="inlineStr"/>
+      <c r="Q121" s="2" t="inlineStr">
+        <is>
+          <t>0.1215130784313726</t>
+        </is>
+      </c>
+      <c r="R121" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:24.115171Z</t>
+        </is>
+      </c>
+      <c r="S121" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="T121" s="2" t="inlineStr"/>
+      <c r="U121" s="2" t="inlineStr"/>
+      <c r="V121" s="2" t="inlineStr"/>
+      <c r="W121" s="2" t="inlineStr"/>
+      <c r="X121" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y121" s="2" t="inlineStr"/>
+      <c r="Z121" s="2" t="inlineStr"/>
+      <c r="AA121" s="2" t="inlineStr"/>
+      <c r="AB121" s="2" t="inlineStr"/>
+      <c r="AC121" s="2" t="inlineStr"/>
+      <c r="AD121" s="2" t="inlineStr"/>
+      <c r="AE121" s="2" t="inlineStr"/>
+      <c r="AF121" s="2" t="inlineStr"/>
+      <c r="AG121" s="2" t="inlineStr"/>
+      <c r="AH121" s="2" t="inlineStr"/>
+      <c r="AI121" s="2" t="inlineStr"/>
+      <c r="AJ121" s="2" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>e578a5dfbc1f49dd</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>68690</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr"/>
+      <c r="L122" s="2" t="inlineStr">
+        <is>
+          <t>0.55055</t>
+        </is>
+      </c>
+      <c r="M122" s="2" t="inlineStr"/>
+      <c r="N122" s="2" t="inlineStr"/>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P122" s="2" t="inlineStr"/>
+      <c r="Q122" s="2" t="inlineStr">
+        <is>
+          <t>0.01137949308755759</t>
+        </is>
+      </c>
+      <c r="R122" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:29.630272Z</t>
+        </is>
+      </c>
+      <c r="S122" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T122" s="2" t="inlineStr"/>
+      <c r="U122" s="2" t="inlineStr"/>
+      <c r="V122" s="2" t="inlineStr"/>
+      <c r="W122" s="2" t="inlineStr"/>
+      <c r="X122" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y122" s="2" t="inlineStr"/>
+      <c r="Z122" s="2" t="inlineStr"/>
+      <c r="AA122" s="2" t="inlineStr"/>
+      <c r="AB122" s="2" t="inlineStr"/>
+      <c r="AC122" s="2" t="inlineStr"/>
+      <c r="AD122" s="2" t="inlineStr"/>
+      <c r="AE122" s="2" t="inlineStr"/>
+      <c r="AF122" s="2" t="inlineStr"/>
+      <c r="AG122" s="2" t="inlineStr"/>
+      <c r="AH122" s="2" t="inlineStr"/>
+      <c r="AI122" s="2" t="inlineStr"/>
+      <c r="AJ122" s="2" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>989cb81eb2714ae3</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>69143</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr"/>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>0.624143</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="inlineStr"/>
+      <c r="N123" s="2" t="inlineStr"/>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P123" s="2" t="inlineStr"/>
+      <c r="Q123" s="2" t="inlineStr">
+        <is>
+          <t>0.004371136882129312</t>
+        </is>
+      </c>
+      <c r="R123" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:32.661629Z</t>
+        </is>
+      </c>
+      <c r="S123" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T123" s="2" t="inlineStr"/>
+      <c r="U123" s="2" t="inlineStr"/>
+      <c r="V123" s="2" t="inlineStr"/>
+      <c r="W123" s="2" t="inlineStr"/>
+      <c r="X123" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y123" s="2" t="inlineStr"/>
+      <c r="Z123" s="2" t="inlineStr"/>
+      <c r="AA123" s="2" t="inlineStr"/>
+      <c r="AB123" s="2" t="inlineStr"/>
+      <c r="AC123" s="2" t="inlineStr"/>
+      <c r="AD123" s="2" t="inlineStr"/>
+      <c r="AE123" s="2" t="inlineStr"/>
+      <c r="AF123" s="2" t="inlineStr"/>
+      <c r="AG123" s="2" t="inlineStr"/>
+      <c r="AH123" s="2" t="inlineStr"/>
+      <c r="AI123" s="2" t="inlineStr"/>
+      <c r="AJ123" s="2" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>dd6e52eff8784ef1</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>69144</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr"/>
+      <c r="L124" s="2" t="inlineStr">
+        <is>
+          <t>0.591618</t>
+        </is>
+      </c>
+      <c r="M124" s="2" t="inlineStr"/>
+      <c r="N124" s="2" t="inlineStr"/>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>0.4291845493562232</t>
+        </is>
+      </c>
+      <c r="P124" s="2" t="inlineStr"/>
+      <c r="Q124" s="2" t="inlineStr">
+        <is>
+          <t>0.1624334506437768</t>
+        </is>
+      </c>
+      <c r="R124" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:33.243967Z</t>
+        </is>
+      </c>
+      <c r="S124" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T124" s="2" t="inlineStr"/>
+      <c r="U124" s="2" t="inlineStr"/>
+      <c r="V124" s="2" t="inlineStr"/>
+      <c r="W124" s="2" t="inlineStr"/>
+      <c r="X124" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y124" s="2" t="inlineStr"/>
+      <c r="Z124" s="2" t="inlineStr"/>
+      <c r="AA124" s="2" t="inlineStr"/>
+      <c r="AB124" s="2" t="inlineStr"/>
+      <c r="AC124" s="2" t="inlineStr"/>
+      <c r="AD124" s="2" t="inlineStr"/>
+      <c r="AE124" s="2" t="inlineStr"/>
+      <c r="AF124" s="2" t="inlineStr"/>
+      <c r="AG124" s="2" t="inlineStr"/>
+      <c r="AH124" s="2" t="inlineStr"/>
+      <c r="AI124" s="2" t="inlineStr"/>
+      <c r="AJ124" s="2" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>66b51c7af1074c90</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>69233</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr"/>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>0.5725</t>
+        </is>
+      </c>
+      <c r="M125" s="2" t="inlineStr"/>
+      <c r="N125" s="2" t="inlineStr"/>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>0.3401360544217687</t>
+        </is>
+      </c>
+      <c r="P125" s="2" t="inlineStr"/>
+      <c r="Q125" s="2" t="inlineStr">
+        <is>
+          <t>0.2323639455782313</t>
+        </is>
+      </c>
+      <c r="R125" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:35.140661Z</t>
+        </is>
+      </c>
+      <c r="S125" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T125" s="2" t="inlineStr"/>
+      <c r="U125" s="2" t="inlineStr"/>
+      <c r="V125" s="2" t="inlineStr"/>
+      <c r="W125" s="2" t="inlineStr"/>
+      <c r="X125" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y125" s="2" t="inlineStr"/>
+      <c r="Z125" s="2" t="inlineStr"/>
+      <c r="AA125" s="2" t="inlineStr"/>
+      <c r="AB125" s="2" t="inlineStr"/>
+      <c r="AC125" s="2" t="inlineStr"/>
+      <c r="AD125" s="2" t="inlineStr"/>
+      <c r="AE125" s="2" t="inlineStr"/>
+      <c r="AF125" s="2" t="inlineStr"/>
+      <c r="AG125" s="2" t="inlineStr"/>
+      <c r="AH125" s="2" t="inlineStr"/>
+      <c r="AI125" s="2" t="inlineStr"/>
+      <c r="AJ125" s="2" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>84c5b50e65ac46ed</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>69273</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr"/>
+      <c r="L126" s="2" t="inlineStr">
+        <is>
+          <t>0.604656</t>
+        </is>
+      </c>
+      <c r="M126" s="2" t="inlineStr"/>
+      <c r="N126" s="2" t="inlineStr"/>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P126" s="2" t="inlineStr"/>
+      <c r="Q126" s="2" t="inlineStr">
+        <is>
+          <t>0.03384054935622316</t>
+        </is>
+      </c>
+      <c r="R126" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:35.709175Z</t>
+        </is>
+      </c>
+      <c r="S126" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="T126" s="2" t="inlineStr"/>
+      <c r="U126" s="2" t="inlineStr"/>
+      <c r="V126" s="2" t="inlineStr"/>
+      <c r="W126" s="2" t="inlineStr"/>
+      <c r="X126" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y126" s="2" t="inlineStr"/>
+      <c r="Z126" s="2" t="inlineStr"/>
+      <c r="AA126" s="2" t="inlineStr"/>
+      <c r="AB126" s="2" t="inlineStr"/>
+      <c r="AC126" s="2" t="inlineStr"/>
+      <c r="AD126" s="2" t="inlineStr"/>
+      <c r="AE126" s="2" t="inlineStr"/>
+      <c r="AF126" s="2" t="inlineStr"/>
+      <c r="AG126" s="2" t="inlineStr"/>
+      <c r="AH126" s="2" t="inlineStr"/>
+      <c r="AI126" s="2" t="inlineStr"/>
+      <c r="AJ126" s="2" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>dc6afc2105e44ffe</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>69507</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr"/>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>0.638913</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="inlineStr"/>
+      <c r="N127" s="2" t="inlineStr"/>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P127" s="2" t="inlineStr"/>
+      <c r="Q127" s="2" t="inlineStr">
+        <is>
+          <t>0.05908106722689077</t>
+        </is>
+      </c>
+      <c r="R127" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:37.478514Z</t>
+        </is>
+      </c>
+      <c r="S127" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="T127" s="2" t="inlineStr"/>
+      <c r="U127" s="2" t="inlineStr"/>
+      <c r="V127" s="2" t="inlineStr"/>
+      <c r="W127" s="2" t="inlineStr"/>
+      <c r="X127" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y127" s="2" t="inlineStr"/>
+      <c r="Z127" s="2" t="inlineStr"/>
+      <c r="AA127" s="2" t="inlineStr"/>
+      <c r="AB127" s="2" t="inlineStr"/>
+      <c r="AC127" s="2" t="inlineStr"/>
+      <c r="AD127" s="2" t="inlineStr"/>
+      <c r="AE127" s="2" t="inlineStr"/>
+      <c r="AF127" s="2" t="inlineStr"/>
+      <c r="AG127" s="2" t="inlineStr"/>
+      <c r="AH127" s="2" t="inlineStr"/>
+      <c r="AI127" s="2" t="inlineStr"/>
+      <c r="AJ127" s="2" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>768ee0829ae04bba</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>69512</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr"/>
+      <c r="L128" s="2" t="inlineStr">
+        <is>
+          <t>0.739915</t>
+        </is>
+      </c>
+      <c r="M128" s="2" t="inlineStr"/>
+      <c r="N128" s="2" t="inlineStr"/>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P128" s="2" t="inlineStr"/>
+      <c r="Q128" s="2" t="inlineStr">
+        <is>
+          <t>0.04951252321981425</t>
+        </is>
+      </c>
+      <c r="R128" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:38.799435Z</t>
+        </is>
+      </c>
+      <c r="S128" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T128" s="2" t="inlineStr"/>
+      <c r="U128" s="2" t="inlineStr"/>
+      <c r="V128" s="2" t="inlineStr"/>
+      <c r="W128" s="2" t="inlineStr"/>
+      <c r="X128" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y128" s="2" t="inlineStr"/>
+      <c r="Z128" s="2" t="inlineStr"/>
+      <c r="AA128" s="2" t="inlineStr"/>
+      <c r="AB128" s="2" t="inlineStr"/>
+      <c r="AC128" s="2" t="inlineStr"/>
+      <c r="AD128" s="2" t="inlineStr"/>
+      <c r="AE128" s="2" t="inlineStr"/>
+      <c r="AF128" s="2" t="inlineStr"/>
+      <c r="AG128" s="2" t="inlineStr"/>
+      <c r="AH128" s="2" t="inlineStr"/>
+      <c r="AI128" s="2" t="inlineStr"/>
+      <c r="AJ128" s="2" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>cbe9a74a72c44e82</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>69511</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr"/>
+      <c r="L129" s="2" t="inlineStr">
+        <is>
+          <t>0.699554</t>
+        </is>
+      </c>
+      <c r="M129" s="2" t="inlineStr"/>
+      <c r="N129" s="2" t="inlineStr"/>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P129" s="2" t="inlineStr"/>
+      <c r="Q129" s="2" t="inlineStr">
+        <is>
+          <t>0.09017900000000001</t>
+        </is>
+      </c>
+      <c r="R129" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:39.448018Z</t>
+        </is>
+      </c>
+      <c r="S129" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T129" s="2" t="inlineStr"/>
+      <c r="U129" s="2" t="inlineStr"/>
+      <c r="V129" s="2" t="inlineStr"/>
+      <c r="W129" s="2" t="inlineStr"/>
+      <c r="X129" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y129" s="2" t="inlineStr"/>
+      <c r="Z129" s="2" t="inlineStr"/>
+      <c r="AA129" s="2" t="inlineStr"/>
+      <c r="AB129" s="2" t="inlineStr"/>
+      <c r="AC129" s="2" t="inlineStr"/>
+      <c r="AD129" s="2" t="inlineStr"/>
+      <c r="AE129" s="2" t="inlineStr"/>
+      <c r="AF129" s="2" t="inlineStr"/>
+      <c r="AG129" s="2" t="inlineStr"/>
+      <c r="AH129" s="2" t="inlineStr"/>
+      <c r="AI129" s="2" t="inlineStr"/>
+      <c r="AJ129" s="2" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>09686a7e1472446a</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>69539</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr"/>
+      <c r="L130" s="2" t="inlineStr">
+        <is>
+          <t>0.637225</t>
+        </is>
+      </c>
+      <c r="M130" s="2" t="inlineStr"/>
+      <c r="N130" s="2" t="inlineStr"/>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P130" s="2" t="inlineStr"/>
+      <c r="Q130" s="2" t="inlineStr">
+        <is>
+          <t>0.0777536343612335</t>
+        </is>
+      </c>
+      <c r="R130" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:40.623507Z</t>
+        </is>
+      </c>
+      <c r="S130" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T130" s="2" t="inlineStr"/>
+      <c r="U130" s="2" t="inlineStr"/>
+      <c r="V130" s="2" t="inlineStr"/>
+      <c r="W130" s="2" t="inlineStr"/>
+      <c r="X130" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y130" s="2" t="inlineStr"/>
+      <c r="Z130" s="2" t="inlineStr"/>
+      <c r="AA130" s="2" t="inlineStr"/>
+      <c r="AB130" s="2" t="inlineStr"/>
+      <c r="AC130" s="2" t="inlineStr"/>
+      <c r="AD130" s="2" t="inlineStr"/>
+      <c r="AE130" s="2" t="inlineStr"/>
+      <c r="AF130" s="2" t="inlineStr"/>
+      <c r="AG130" s="2" t="inlineStr"/>
+      <c r="AH130" s="2" t="inlineStr"/>
+      <c r="AI130" s="2" t="inlineStr"/>
+      <c r="AJ130" s="2" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>a725369e0ecb4787</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr"/>
+      <c r="L131" s="2" t="inlineStr">
+        <is>
+          <t>0.665588</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="inlineStr"/>
+      <c r="N131" s="2" t="inlineStr"/>
+      <c r="O131" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P131" s="2" t="inlineStr"/>
+      <c r="Q131" s="2" t="inlineStr">
+        <is>
+          <t>0.10611663436123342</t>
+        </is>
+      </c>
+      <c r="R131" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:45.008665Z</t>
+        </is>
+      </c>
+      <c r="S131" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="T131" s="2" t="inlineStr"/>
+      <c r="U131" s="2" t="inlineStr"/>
+      <c r="V131" s="2" t="inlineStr"/>
+      <c r="W131" s="2" t="inlineStr"/>
+      <c r="X131" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y131" s="2" t="inlineStr"/>
+      <c r="Z131" s="2" t="inlineStr"/>
+      <c r="AA131" s="2" t="inlineStr"/>
+      <c r="AB131" s="2" t="inlineStr"/>
+      <c r="AC131" s="2" t="inlineStr"/>
+      <c r="AD131" s="2" t="inlineStr"/>
+      <c r="AE131" s="2" t="inlineStr"/>
+      <c r="AF131" s="2" t="inlineStr"/>
+      <c r="AG131" s="2" t="inlineStr"/>
+      <c r="AH131" s="2" t="inlineStr"/>
+      <c r="AI131" s="2" t="inlineStr"/>
+      <c r="AJ131" s="2" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>e077b35ccb094e73</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>69817</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr"/>
+      <c r="L132" s="2" t="inlineStr">
+        <is>
+          <t>0.560327</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="inlineStr"/>
+      <c r="N132" s="2" t="inlineStr"/>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="P132" s="2" t="inlineStr"/>
+      <c r="Q132" s="2" t="inlineStr">
+        <is>
+          <t>0.06032700000000002</t>
+        </is>
+      </c>
+      <c r="R132" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:45.501478Z</t>
+        </is>
+      </c>
+      <c r="S132" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="T132" s="2" t="inlineStr"/>
+      <c r="U132" s="2" t="inlineStr"/>
+      <c r="V132" s="2" t="inlineStr"/>
+      <c r="W132" s="2" t="inlineStr"/>
+      <c r="X132" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y132" s="2" t="inlineStr"/>
+      <c r="Z132" s="2" t="inlineStr"/>
+      <c r="AA132" s="2" t="inlineStr"/>
+      <c r="AB132" s="2" t="inlineStr"/>
+      <c r="AC132" s="2" t="inlineStr"/>
+      <c r="AD132" s="2" t="inlineStr"/>
+      <c r="AE132" s="2" t="inlineStr"/>
+      <c r="AF132" s="2" t="inlineStr"/>
+      <c r="AG132" s="2" t="inlineStr"/>
+      <c r="AH132" s="2" t="inlineStr"/>
+      <c r="AI132" s="2" t="inlineStr"/>
+      <c r="AJ132" s="2" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>2feb17c939e142d6</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>69871</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr"/>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>0.561203</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="inlineStr"/>
+      <c r="N133" s="2" t="inlineStr"/>
+      <c r="O133" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P133" s="2" t="inlineStr"/>
+      <c r="Q133" s="2" t="inlineStr">
+        <is>
+          <t>0.12067436563876655</t>
+        </is>
+      </c>
+      <c r="R133" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:47.185518Z</t>
+        </is>
+      </c>
+      <c r="S133" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T133" s="2" t="inlineStr"/>
+      <c r="U133" s="2" t="inlineStr"/>
+      <c r="V133" s="2" t="inlineStr"/>
+      <c r="W133" s="2" t="inlineStr"/>
+      <c r="X133" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y133" s="2" t="inlineStr"/>
+      <c r="Z133" s="2" t="inlineStr"/>
+      <c r="AA133" s="2" t="inlineStr"/>
+      <c r="AB133" s="2" t="inlineStr"/>
+      <c r="AC133" s="2" t="inlineStr"/>
+      <c r="AD133" s="2" t="inlineStr"/>
+      <c r="AE133" s="2" t="inlineStr"/>
+      <c r="AF133" s="2" t="inlineStr"/>
+      <c r="AG133" s="2" t="inlineStr"/>
+      <c r="AH133" s="2" t="inlineStr"/>
+      <c r="AI133" s="2" t="inlineStr"/>
+      <c r="AJ133" s="2" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>b9c172fa8dc44f09</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>70569</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr"/>
+      <c r="L134" s="2" t="inlineStr">
+        <is>
+          <t>0.832591</t>
+        </is>
+      </c>
+      <c r="M134" s="2" t="inlineStr"/>
+      <c r="N134" s="2" t="inlineStr"/>
+      <c r="O134" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P134" s="2" t="inlineStr"/>
+      <c r="Q134" s="2" t="inlineStr">
+        <is>
+          <t>0.24242706557377047</t>
+        </is>
+      </c>
+      <c r="R134" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:48.331322Z</t>
+        </is>
+      </c>
+      <c r="S134" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T134" s="2" t="inlineStr"/>
+      <c r="U134" s="2" t="inlineStr"/>
+      <c r="V134" s="2" t="inlineStr"/>
+      <c r="W134" s="2" t="inlineStr"/>
+      <c r="X134" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y134" s="2" t="inlineStr"/>
+      <c r="Z134" s="2" t="inlineStr"/>
+      <c r="AA134" s="2" t="inlineStr"/>
+      <c r="AB134" s="2" t="inlineStr"/>
+      <c r="AC134" s="2" t="inlineStr"/>
+      <c r="AD134" s="2" t="inlineStr"/>
+      <c r="AE134" s="2" t="inlineStr"/>
+      <c r="AF134" s="2" t="inlineStr"/>
+      <c r="AG134" s="2" t="inlineStr"/>
+      <c r="AH134" s="2" t="inlineStr"/>
+      <c r="AI134" s="2" t="inlineStr"/>
+      <c r="AJ134" s="2" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>03d43382dd2241aa</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>69931</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr"/>
+      <c r="L135" s="2" t="inlineStr">
+        <is>
+          <t>0.577055</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="inlineStr"/>
+      <c r="N135" s="2" t="inlineStr"/>
+      <c r="O135" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="P135" s="2" t="inlineStr"/>
+      <c r="Q135" s="2" t="inlineStr">
+        <is>
+          <t>0.07705499999999998</t>
+        </is>
+      </c>
+      <c r="R135" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:48.838641Z</t>
+        </is>
+      </c>
+      <c r="S135" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:30:00Z</t>
+        </is>
+      </c>
+      <c r="T135" s="2" t="inlineStr"/>
+      <c r="U135" s="2" t="inlineStr"/>
+      <c r="V135" s="2" t="inlineStr"/>
+      <c r="W135" s="2" t="inlineStr"/>
+      <c r="X135" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y135" s="2" t="inlineStr"/>
+      <c r="Z135" s="2" t="inlineStr"/>
+      <c r="AA135" s="2" t="inlineStr"/>
+      <c r="AB135" s="2" t="inlineStr"/>
+      <c r="AC135" s="2" t="inlineStr"/>
+      <c r="AD135" s="2" t="inlineStr"/>
+      <c r="AE135" s="2" t="inlineStr"/>
+      <c r="AF135" s="2" t="inlineStr"/>
+      <c r="AG135" s="2" t="inlineStr"/>
+      <c r="AH135" s="2" t="inlineStr"/>
+      <c r="AI135" s="2" t="inlineStr"/>
+      <c r="AJ135" s="2" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>32449cbf0d294419</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>70045</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr"/>
+      <c r="L136" s="2" t="inlineStr">
+        <is>
+          <t>0.607498</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="inlineStr"/>
+      <c r="N136" s="2" t="inlineStr"/>
+      <c r="O136" s="2" t="inlineStr">
+        <is>
+          <t>0.5098039215686274</t>
+        </is>
+      </c>
+      <c r="P136" s="2" t="inlineStr"/>
+      <c r="Q136" s="2" t="inlineStr">
+        <is>
+          <t>0.09769407843137257</t>
+        </is>
+      </c>
+      <c r="R136" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:53.353991Z</t>
+        </is>
+      </c>
+      <c r="S136" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="T136" s="2" t="inlineStr"/>
+      <c r="U136" s="2" t="inlineStr"/>
+      <c r="V136" s="2" t="inlineStr"/>
+      <c r="W136" s="2" t="inlineStr"/>
+      <c r="X136" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y136" s="2" t="inlineStr"/>
+      <c r="Z136" s="2" t="inlineStr"/>
+      <c r="AA136" s="2" t="inlineStr"/>
+      <c r="AB136" s="2" t="inlineStr"/>
+      <c r="AC136" s="2" t="inlineStr"/>
+      <c r="AD136" s="2" t="inlineStr"/>
+      <c r="AE136" s="2" t="inlineStr"/>
+      <c r="AF136" s="2" t="inlineStr"/>
+      <c r="AG136" s="2" t="inlineStr"/>
+      <c r="AH136" s="2" t="inlineStr"/>
+      <c r="AI136" s="2" t="inlineStr"/>
+      <c r="AJ136" s="2" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>bbddfe2cb3bf4dee</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>70301</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr"/>
+      <c r="L137" s="2" t="inlineStr">
+        <is>
+          <t>0.658548</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="inlineStr"/>
+      <c r="N137" s="2" t="inlineStr"/>
+      <c r="O137" s="2" t="inlineStr">
+        <is>
+          <t>0.4807692307692307</t>
+        </is>
+      </c>
+      <c r="P137" s="2" t="inlineStr"/>
+      <c r="Q137" s="2" t="inlineStr">
+        <is>
+          <t>0.1777787692307693</t>
+        </is>
+      </c>
+      <c r="R137" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:53.849186Z</t>
+        </is>
+      </c>
+      <c r="S137" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T137" s="2" t="inlineStr"/>
+      <c r="U137" s="2" t="inlineStr"/>
+      <c r="V137" s="2" t="inlineStr"/>
+      <c r="W137" s="2" t="inlineStr"/>
+      <c r="X137" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y137" s="2" t="inlineStr"/>
+      <c r="Z137" s="2" t="inlineStr"/>
+      <c r="AA137" s="2" t="inlineStr"/>
+      <c r="AB137" s="2" t="inlineStr"/>
+      <c r="AC137" s="2" t="inlineStr"/>
+      <c r="AD137" s="2" t="inlineStr"/>
+      <c r="AE137" s="2" t="inlineStr"/>
+      <c r="AF137" s="2" t="inlineStr"/>
+      <c r="AG137" s="2" t="inlineStr"/>
+      <c r="AH137" s="2" t="inlineStr"/>
+      <c r="AI137" s="2" t="inlineStr"/>
+      <c r="AJ137" s="2" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>9cf5104ddfbc486e</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>70453</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr"/>
+      <c r="L138" s="2" t="inlineStr">
+        <is>
+          <t>0.590765</t>
+        </is>
+      </c>
+      <c r="M138" s="2" t="inlineStr"/>
+      <c r="N138" s="2" t="inlineStr"/>
+      <c r="O138" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P138" s="2" t="inlineStr"/>
+      <c r="Q138" s="2" t="inlineStr">
+        <is>
+          <t>0.0412154504504505</t>
+        </is>
+      </c>
+      <c r="R138" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:58.736471Z</t>
+        </is>
+      </c>
+      <c r="S138" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="T138" s="2" t="inlineStr"/>
+      <c r="U138" s="2" t="inlineStr"/>
+      <c r="V138" s="2" t="inlineStr"/>
+      <c r="W138" s="2" t="inlineStr"/>
+      <c r="X138" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y138" s="2" t="inlineStr"/>
+      <c r="Z138" s="2" t="inlineStr"/>
+      <c r="AA138" s="2" t="inlineStr"/>
+      <c r="AB138" s="2" t="inlineStr"/>
+      <c r="AC138" s="2" t="inlineStr"/>
+      <c r="AD138" s="2" t="inlineStr"/>
+      <c r="AE138" s="2" t="inlineStr"/>
+      <c r="AF138" s="2" t="inlineStr"/>
+      <c r="AG138" s="2" t="inlineStr"/>
+      <c r="AH138" s="2" t="inlineStr"/>
+      <c r="AI138" s="2" t="inlineStr"/>
+      <c r="AJ138" s="2" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>9c16b7fd6261484a</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>68509</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr"/>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>0.631317</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="inlineStr"/>
+      <c r="N139" s="2" t="inlineStr"/>
+      <c r="O139" s="2" t="inlineStr">
+        <is>
+          <t>0.5192307692307692</t>
+        </is>
+      </c>
+      <c r="P139" s="2" t="inlineStr"/>
+      <c r="Q139" s="2" t="inlineStr">
+        <is>
+          <t>0.11208623076923085</t>
+        </is>
+      </c>
+      <c r="R139" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:25.701342Z</t>
+        </is>
+      </c>
+      <c r="S139" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="T139" s="2" t="inlineStr"/>
+      <c r="U139" s="2" t="inlineStr"/>
+      <c r="V139" s="2" t="inlineStr"/>
+      <c r="W139" s="2" t="inlineStr"/>
+      <c r="X139" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y139" s="2" t="inlineStr"/>
+      <c r="Z139" s="2" t="inlineStr"/>
+      <c r="AA139" s="2" t="inlineStr"/>
+      <c r="AB139" s="2" t="inlineStr"/>
+      <c r="AC139" s="2" t="inlineStr"/>
+      <c r="AD139" s="2" t="inlineStr"/>
+      <c r="AE139" s="2" t="inlineStr"/>
+      <c r="AF139" s="2" t="inlineStr"/>
+      <c r="AG139" s="2" t="inlineStr"/>
+      <c r="AH139" s="2" t="inlineStr"/>
+      <c r="AI139" s="2" t="inlineStr"/>
+      <c r="AJ139" s="2" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>63186df746744e13</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>68690</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr"/>
+      <c r="L140" s="2" t="inlineStr">
+        <is>
+          <t>0.55055</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="inlineStr"/>
+      <c r="N140" s="2" t="inlineStr"/>
+      <c r="O140" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P140" s="2" t="inlineStr"/>
+      <c r="Q140" s="2" t="inlineStr">
+        <is>
+          <t>0.01137949308755759</t>
+        </is>
+      </c>
+      <c r="R140" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:29.939077Z</t>
+        </is>
+      </c>
+      <c r="S140" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T140" s="2" t="inlineStr"/>
+      <c r="U140" s="2" t="inlineStr"/>
+      <c r="V140" s="2" t="inlineStr"/>
+      <c r="W140" s="2" t="inlineStr"/>
+      <c r="X140" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y140" s="2" t="inlineStr"/>
+      <c r="Z140" s="2" t="inlineStr"/>
+      <c r="AA140" s="2" t="inlineStr"/>
+      <c r="AB140" s="2" t="inlineStr"/>
+      <c r="AC140" s="2" t="inlineStr"/>
+      <c r="AD140" s="2" t="inlineStr"/>
+      <c r="AE140" s="2" t="inlineStr"/>
+      <c r="AF140" s="2" t="inlineStr"/>
+      <c r="AG140" s="2" t="inlineStr"/>
+      <c r="AH140" s="2" t="inlineStr"/>
+      <c r="AI140" s="2" t="inlineStr"/>
+      <c r="AJ140" s="2" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>c4354f93c7024062</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>69143</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr"/>
+      <c r="L141" s="2" t="inlineStr">
+        <is>
+          <t>0.624143</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="inlineStr"/>
+      <c r="N141" s="2" t="inlineStr"/>
+      <c r="O141" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P141" s="2" t="inlineStr"/>
+      <c r="Q141" s="2" t="inlineStr">
+        <is>
+          <t>0.004371136882129312</t>
+        </is>
+      </c>
+      <c r="R141" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:34.284466Z</t>
+        </is>
+      </c>
+      <c r="S141" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T141" s="2" t="inlineStr"/>
+      <c r="U141" s="2" t="inlineStr"/>
+      <c r="V141" s="2" t="inlineStr"/>
+      <c r="W141" s="2" t="inlineStr"/>
+      <c r="X141" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y141" s="2" t="inlineStr"/>
+      <c r="Z141" s="2" t="inlineStr"/>
+      <c r="AA141" s="2" t="inlineStr"/>
+      <c r="AB141" s="2" t="inlineStr"/>
+      <c r="AC141" s="2" t="inlineStr"/>
+      <c r="AD141" s="2" t="inlineStr"/>
+      <c r="AE141" s="2" t="inlineStr"/>
+      <c r="AF141" s="2" t="inlineStr"/>
+      <c r="AG141" s="2" t="inlineStr"/>
+      <c r="AH141" s="2" t="inlineStr"/>
+      <c r="AI141" s="2" t="inlineStr"/>
+      <c r="AJ141" s="2" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>a742add90251442f</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>69144</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr"/>
+      <c r="L142" s="2" t="inlineStr">
+        <is>
+          <t>0.591618</t>
+        </is>
+      </c>
+      <c r="M142" s="2" t="inlineStr"/>
+      <c r="N142" s="2" t="inlineStr"/>
+      <c r="O142" s="2" t="inlineStr">
+        <is>
+          <t>0.49019607843137253</t>
+        </is>
+      </c>
+      <c r="P142" s="2" t="inlineStr"/>
+      <c r="Q142" s="2" t="inlineStr">
+        <is>
+          <t>0.10142192156862745</t>
+        </is>
+      </c>
+      <c r="R142" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:34.823771Z</t>
+        </is>
+      </c>
+      <c r="S142" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T142" s="2" t="inlineStr"/>
+      <c r="U142" s="2" t="inlineStr"/>
+      <c r="V142" s="2" t="inlineStr"/>
+      <c r="W142" s="2" t="inlineStr"/>
+      <c r="X142" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y142" s="2" t="inlineStr"/>
+      <c r="Z142" s="2" t="inlineStr"/>
+      <c r="AA142" s="2" t="inlineStr"/>
+      <c r="AB142" s="2" t="inlineStr"/>
+      <c r="AC142" s="2" t="inlineStr"/>
+      <c r="AD142" s="2" t="inlineStr"/>
+      <c r="AE142" s="2" t="inlineStr"/>
+      <c r="AF142" s="2" t="inlineStr"/>
+      <c r="AG142" s="2" t="inlineStr"/>
+      <c r="AH142" s="2" t="inlineStr"/>
+      <c r="AI142" s="2" t="inlineStr"/>
+      <c r="AJ142" s="2" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>9403da7f2bd44f25</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>69233</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr"/>
+      <c r="L143" s="2" t="inlineStr">
+        <is>
+          <t>0.5725</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="inlineStr"/>
+      <c r="N143" s="2" t="inlineStr"/>
+      <c r="O143" s="2" t="inlineStr">
+        <is>
+          <t>0.3401360544217687</t>
+        </is>
+      </c>
+      <c r="P143" s="2" t="inlineStr"/>
+      <c r="Q143" s="2" t="inlineStr">
+        <is>
+          <t>0.2323639455782313</t>
+        </is>
+      </c>
+      <c r="R143" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:36.567095Z</t>
+        </is>
+      </c>
+      <c r="S143" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T143" s="2" t="inlineStr"/>
+      <c r="U143" s="2" t="inlineStr"/>
+      <c r="V143" s="2" t="inlineStr"/>
+      <c r="W143" s="2" t="inlineStr"/>
+      <c r="X143" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y143" s="2" t="inlineStr"/>
+      <c r="Z143" s="2" t="inlineStr"/>
+      <c r="AA143" s="2" t="inlineStr"/>
+      <c r="AB143" s="2" t="inlineStr"/>
+      <c r="AC143" s="2" t="inlineStr"/>
+      <c r="AD143" s="2" t="inlineStr"/>
+      <c r="AE143" s="2" t="inlineStr"/>
+      <c r="AF143" s="2" t="inlineStr"/>
+      <c r="AG143" s="2" t="inlineStr"/>
+      <c r="AH143" s="2" t="inlineStr"/>
+      <c r="AI143" s="2" t="inlineStr"/>
+      <c r="AJ143" s="2" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>06c344582ff84f23</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>69273</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr"/>
+      <c r="L144" s="2" t="inlineStr">
+        <is>
+          <t>0.604656</t>
+        </is>
+      </c>
+      <c r="M144" s="2" t="inlineStr"/>
+      <c r="N144" s="2" t="inlineStr"/>
+      <c r="O144" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P144" s="2" t="inlineStr"/>
+      <c r="Q144" s="2" t="inlineStr">
+        <is>
+          <t>0.06548549308755758</t>
+        </is>
+      </c>
+      <c r="R144" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:37.194950Z</t>
+        </is>
+      </c>
+      <c r="S144" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="T144" s="2" t="inlineStr"/>
+      <c r="U144" s="2" t="inlineStr"/>
+      <c r="V144" s="2" t="inlineStr"/>
+      <c r="W144" s="2" t="inlineStr"/>
+      <c r="X144" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y144" s="2" t="inlineStr"/>
+      <c r="Z144" s="2" t="inlineStr"/>
+      <c r="AA144" s="2" t="inlineStr"/>
+      <c r="AB144" s="2" t="inlineStr"/>
+      <c r="AC144" s="2" t="inlineStr"/>
+      <c r="AD144" s="2" t="inlineStr"/>
+      <c r="AE144" s="2" t="inlineStr"/>
+      <c r="AF144" s="2" t="inlineStr"/>
+      <c r="AG144" s="2" t="inlineStr"/>
+      <c r="AH144" s="2" t="inlineStr"/>
+      <c r="AI144" s="2" t="inlineStr"/>
+      <c r="AJ144" s="2" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>dd2a20562c8f46a6</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>69507</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr"/>
+      <c r="L145" s="2" t="inlineStr">
+        <is>
+          <t>0.638913</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="inlineStr"/>
+      <c r="N145" s="2" t="inlineStr"/>
+      <c r="O145" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P145" s="2" t="inlineStr"/>
+      <c r="Q145" s="2" t="inlineStr">
+        <is>
+          <t>0.05908106722689077</t>
+        </is>
+      </c>
+      <c r="R145" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:38.863908Z</t>
+        </is>
+      </c>
+      <c r="S145" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="T145" s="2" t="inlineStr"/>
+      <c r="U145" s="2" t="inlineStr"/>
+      <c r="V145" s="2" t="inlineStr"/>
+      <c r="W145" s="2" t="inlineStr"/>
+      <c r="X145" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y145" s="2" t="inlineStr"/>
+      <c r="Z145" s="2" t="inlineStr"/>
+      <c r="AA145" s="2" t="inlineStr"/>
+      <c r="AB145" s="2" t="inlineStr"/>
+      <c r="AC145" s="2" t="inlineStr"/>
+      <c r="AD145" s="2" t="inlineStr"/>
+      <c r="AE145" s="2" t="inlineStr"/>
+      <c r="AF145" s="2" t="inlineStr"/>
+      <c r="AG145" s="2" t="inlineStr"/>
+      <c r="AH145" s="2" t="inlineStr"/>
+      <c r="AI145" s="2" t="inlineStr"/>
+      <c r="AJ145" s="2" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>02cbb24d58ed4a2f</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>69512</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr"/>
+      <c r="L146" s="2" t="inlineStr">
+        <is>
+          <t>0.739915</t>
+        </is>
+      </c>
+      <c r="M146" s="2" t="inlineStr"/>
+      <c r="N146" s="2" t="inlineStr"/>
+      <c r="O146" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P146" s="2" t="inlineStr"/>
+      <c r="Q146" s="2" t="inlineStr">
+        <is>
+          <t>0.04951252321981425</t>
+        </is>
+      </c>
+      <c r="R146" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:39.828051Z</t>
+        </is>
+      </c>
+      <c r="S146" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T146" s="2" t="inlineStr"/>
+      <c r="U146" s="2" t="inlineStr"/>
+      <c r="V146" s="2" t="inlineStr"/>
+      <c r="W146" s="2" t="inlineStr"/>
+      <c r="X146" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y146" s="2" t="inlineStr"/>
+      <c r="Z146" s="2" t="inlineStr"/>
+      <c r="AA146" s="2" t="inlineStr"/>
+      <c r="AB146" s="2" t="inlineStr"/>
+      <c r="AC146" s="2" t="inlineStr"/>
+      <c r="AD146" s="2" t="inlineStr"/>
+      <c r="AE146" s="2" t="inlineStr"/>
+      <c r="AF146" s="2" t="inlineStr"/>
+      <c r="AG146" s="2" t="inlineStr"/>
+      <c r="AH146" s="2" t="inlineStr"/>
+      <c r="AI146" s="2" t="inlineStr"/>
+      <c r="AJ146" s="2" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>f25ced268f5b4b46</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>69511</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr"/>
+      <c r="L147" s="2" t="inlineStr">
+        <is>
+          <t>0.699554</t>
+        </is>
+      </c>
+      <c r="M147" s="2" t="inlineStr"/>
+      <c r="N147" s="2" t="inlineStr"/>
+      <c r="O147" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P147" s="2" t="inlineStr"/>
+      <c r="Q147" s="2" t="inlineStr">
+        <is>
+          <t>0.09017900000000001</t>
+        </is>
+      </c>
+      <c r="R147" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:40.294698Z</t>
+        </is>
+      </c>
+      <c r="S147" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T147" s="2" t="inlineStr"/>
+      <c r="U147" s="2" t="inlineStr"/>
+      <c r="V147" s="2" t="inlineStr"/>
+      <c r="W147" s="2" t="inlineStr"/>
+      <c r="X147" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y147" s="2" t="inlineStr"/>
+      <c r="Z147" s="2" t="inlineStr"/>
+      <c r="AA147" s="2" t="inlineStr"/>
+      <c r="AB147" s="2" t="inlineStr"/>
+      <c r="AC147" s="2" t="inlineStr"/>
+      <c r="AD147" s="2" t="inlineStr"/>
+      <c r="AE147" s="2" t="inlineStr"/>
+      <c r="AF147" s="2" t="inlineStr"/>
+      <c r="AG147" s="2" t="inlineStr"/>
+      <c r="AH147" s="2" t="inlineStr"/>
+      <c r="AI147" s="2" t="inlineStr"/>
+      <c r="AJ147" s="2" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>9edaedc46c804c14</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>69539</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr"/>
+      <c r="L148" s="2" t="inlineStr">
+        <is>
+          <t>0.637225</t>
+        </is>
+      </c>
+      <c r="M148" s="2" t="inlineStr"/>
+      <c r="N148" s="2" t="inlineStr"/>
+      <c r="O148" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P148" s="2" t="inlineStr"/>
+      <c r="Q148" s="2" t="inlineStr">
+        <is>
+          <t>0.0777536343612335</t>
+        </is>
+      </c>
+      <c r="R148" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:41.252699Z</t>
+        </is>
+      </c>
+      <c r="S148" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T148" s="2" t="inlineStr"/>
+      <c r="U148" s="2" t="inlineStr"/>
+      <c r="V148" s="2" t="inlineStr"/>
+      <c r="W148" s="2" t="inlineStr"/>
+      <c r="X148" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y148" s="2" t="inlineStr"/>
+      <c r="Z148" s="2" t="inlineStr"/>
+      <c r="AA148" s="2" t="inlineStr"/>
+      <c r="AB148" s="2" t="inlineStr"/>
+      <c r="AC148" s="2" t="inlineStr"/>
+      <c r="AD148" s="2" t="inlineStr"/>
+      <c r="AE148" s="2" t="inlineStr"/>
+      <c r="AF148" s="2" t="inlineStr"/>
+      <c r="AG148" s="2" t="inlineStr"/>
+      <c r="AH148" s="2" t="inlineStr"/>
+      <c r="AI148" s="2" t="inlineStr"/>
+      <c r="AJ148" s="2" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>13bf58eb324c411d</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr"/>
+      <c r="L149" s="2" t="inlineStr">
+        <is>
+          <t>0.665588</t>
+        </is>
+      </c>
+      <c r="M149" s="2" t="inlineStr"/>
+      <c r="N149" s="2" t="inlineStr"/>
+      <c r="O149" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P149" s="2" t="inlineStr"/>
+      <c r="Q149" s="2" t="inlineStr">
+        <is>
+          <t>0.045816136882129266</t>
+        </is>
+      </c>
+      <c r="R149" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:44.546269Z</t>
+        </is>
+      </c>
+      <c r="S149" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="T149" s="2" t="inlineStr"/>
+      <c r="U149" s="2" t="inlineStr"/>
+      <c r="V149" s="2" t="inlineStr"/>
+      <c r="W149" s="2" t="inlineStr"/>
+      <c r="X149" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y149" s="2" t="inlineStr"/>
+      <c r="Z149" s="2" t="inlineStr"/>
+      <c r="AA149" s="2" t="inlineStr"/>
+      <c r="AB149" s="2" t="inlineStr"/>
+      <c r="AC149" s="2" t="inlineStr"/>
+      <c r="AD149" s="2" t="inlineStr"/>
+      <c r="AE149" s="2" t="inlineStr"/>
+      <c r="AF149" s="2" t="inlineStr"/>
+      <c r="AG149" s="2" t="inlineStr"/>
+      <c r="AH149" s="2" t="inlineStr"/>
+      <c r="AI149" s="2" t="inlineStr"/>
+      <c r="AJ149" s="2" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>9acb09c7646b482b</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>69871</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr"/>
+      <c r="L150" s="2" t="inlineStr">
+        <is>
+          <t>0.561203</t>
+        </is>
+      </c>
+      <c r="M150" s="2" t="inlineStr"/>
+      <c r="N150" s="2" t="inlineStr"/>
+      <c r="O150" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P150" s="2" t="inlineStr"/>
+      <c r="Q150" s="2" t="inlineStr">
+        <is>
+          <t>0.12067436563876655</t>
+        </is>
+      </c>
+      <c r="R150" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:46.445811Z</t>
+        </is>
+      </c>
+      <c r="S150" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T150" s="2" t="inlineStr"/>
+      <c r="U150" s="2" t="inlineStr"/>
+      <c r="V150" s="2" t="inlineStr"/>
+      <c r="W150" s="2" t="inlineStr"/>
+      <c r="X150" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y150" s="2" t="inlineStr"/>
+      <c r="Z150" s="2" t="inlineStr"/>
+      <c r="AA150" s="2" t="inlineStr"/>
+      <c r="AB150" s="2" t="inlineStr"/>
+      <c r="AC150" s="2" t="inlineStr"/>
+      <c r="AD150" s="2" t="inlineStr"/>
+      <c r="AE150" s="2" t="inlineStr"/>
+      <c r="AF150" s="2" t="inlineStr"/>
+      <c r="AG150" s="2" t="inlineStr"/>
+      <c r="AH150" s="2" t="inlineStr"/>
+      <c r="AI150" s="2" t="inlineStr"/>
+      <c r="AJ150" s="2" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>2d467cb5ac254449</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>70569</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="inlineStr"/>
+      <c r="L151" s="2" t="inlineStr">
+        <is>
+          <t>0.832591</t>
+        </is>
+      </c>
+      <c r="M151" s="2" t="inlineStr"/>
+      <c r="N151" s="2" t="inlineStr"/>
+      <c r="O151" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P151" s="2" t="inlineStr"/>
+      <c r="Q151" s="2" t="inlineStr">
+        <is>
+          <t>0.24242706557377047</t>
+        </is>
+      </c>
+      <c r="R151" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:47.442405Z</t>
+        </is>
+      </c>
+      <c r="S151" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T151" s="2" t="inlineStr"/>
+      <c r="U151" s="2" t="inlineStr"/>
+      <c r="V151" s="2" t="inlineStr"/>
+      <c r="W151" s="2" t="inlineStr"/>
+      <c r="X151" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y151" s="2" t="inlineStr"/>
+      <c r="Z151" s="2" t="inlineStr"/>
+      <c r="AA151" s="2" t="inlineStr"/>
+      <c r="AB151" s="2" t="inlineStr"/>
+      <c r="AC151" s="2" t="inlineStr"/>
+      <c r="AD151" s="2" t="inlineStr"/>
+      <c r="AE151" s="2" t="inlineStr"/>
+      <c r="AF151" s="2" t="inlineStr"/>
+      <c r="AG151" s="2" t="inlineStr"/>
+      <c r="AH151" s="2" t="inlineStr"/>
+      <c r="AI151" s="2" t="inlineStr"/>
+      <c r="AJ151" s="2" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>a40638ef4fdc4727</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>69931</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="inlineStr"/>
+      <c r="L152" s="2" t="inlineStr">
+        <is>
+          <t>0.577055</t>
+        </is>
+      </c>
+      <c r="M152" s="2" t="inlineStr"/>
+      <c r="N152" s="2" t="inlineStr"/>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="P152" s="2" t="inlineStr"/>
+      <c r="Q152" s="2" t="inlineStr">
+        <is>
+          <t>0.07705499999999998</t>
+        </is>
+      </c>
+      <c r="R152" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:47.949141Z</t>
+        </is>
+      </c>
+      <c r="S152" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:30:00Z</t>
+        </is>
+      </c>
+      <c r="T152" s="2" t="inlineStr"/>
+      <c r="U152" s="2" t="inlineStr"/>
+      <c r="V152" s="2" t="inlineStr"/>
+      <c r="W152" s="2" t="inlineStr"/>
+      <c r="X152" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y152" s="2" t="inlineStr"/>
+      <c r="Z152" s="2" t="inlineStr"/>
+      <c r="AA152" s="2" t="inlineStr"/>
+      <c r="AB152" s="2" t="inlineStr"/>
+      <c r="AC152" s="2" t="inlineStr"/>
+      <c r="AD152" s="2" t="inlineStr"/>
+      <c r="AE152" s="2" t="inlineStr"/>
+      <c r="AF152" s="2" t="inlineStr"/>
+      <c r="AG152" s="2" t="inlineStr"/>
+      <c r="AH152" s="2" t="inlineStr"/>
+      <c r="AI152" s="2" t="inlineStr"/>
+      <c r="AJ152" s="2" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>a265e2ec99c14dfa</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>70045</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="inlineStr"/>
+      <c r="L153" s="2" t="inlineStr">
+        <is>
+          <t>0.607498</t>
+        </is>
+      </c>
+      <c r="M153" s="2" t="inlineStr"/>
+      <c r="N153" s="2" t="inlineStr"/>
+      <c r="O153" s="2" t="inlineStr">
+        <is>
+          <t>0.5192307692307692</t>
+        </is>
+      </c>
+      <c r="P153" s="2" t="inlineStr"/>
+      <c r="Q153" s="2" t="inlineStr">
+        <is>
+          <t>0.08826723076923082</t>
+        </is>
+      </c>
+      <c r="R153" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:51.809850Z</t>
+        </is>
+      </c>
+      <c r="S153" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="T153" s="2" t="inlineStr"/>
+      <c r="U153" s="2" t="inlineStr"/>
+      <c r="V153" s="2" t="inlineStr"/>
+      <c r="W153" s="2" t="inlineStr"/>
+      <c r="X153" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y153" s="2" t="inlineStr"/>
+      <c r="Z153" s="2" t="inlineStr"/>
+      <c r="AA153" s="2" t="inlineStr"/>
+      <c r="AB153" s="2" t="inlineStr"/>
+      <c r="AC153" s="2" t="inlineStr"/>
+      <c r="AD153" s="2" t="inlineStr"/>
+      <c r="AE153" s="2" t="inlineStr"/>
+      <c r="AF153" s="2" t="inlineStr"/>
+      <c r="AG153" s="2" t="inlineStr"/>
+      <c r="AH153" s="2" t="inlineStr"/>
+      <c r="AI153" s="2" t="inlineStr"/>
+      <c r="AJ153" s="2" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>7fb09070fdd74274</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>70379</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr"/>
+      <c r="L154" s="2" t="inlineStr">
+        <is>
+          <t>0.566884</t>
+        </is>
+      </c>
+      <c r="M154" s="2" t="inlineStr"/>
+      <c r="N154" s="2" t="inlineStr"/>
+      <c r="O154" s="2" t="inlineStr">
+        <is>
+          <t>0.4291845493562232</t>
+        </is>
+      </c>
+      <c r="P154" s="2" t="inlineStr"/>
+      <c r="Q154" s="2" t="inlineStr">
+        <is>
+          <t>0.13769945064377687</t>
+        </is>
+      </c>
+      <c r="R154" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:54.874184Z</t>
+        </is>
+      </c>
+      <c r="S154" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="T154" s="2" t="inlineStr"/>
+      <c r="U154" s="2" t="inlineStr"/>
+      <c r="V154" s="2" t="inlineStr"/>
+      <c r="W154" s="2" t="inlineStr"/>
+      <c r="X154" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y154" s="2" t="inlineStr"/>
+      <c r="Z154" s="2" t="inlineStr"/>
+      <c r="AA154" s="2" t="inlineStr"/>
+      <c r="AB154" s="2" t="inlineStr"/>
+      <c r="AC154" s="2" t="inlineStr"/>
+      <c r="AD154" s="2" t="inlineStr"/>
+      <c r="AE154" s="2" t="inlineStr"/>
+      <c r="AF154" s="2" t="inlineStr"/>
+      <c r="AG154" s="2" t="inlineStr"/>
+      <c r="AH154" s="2" t="inlineStr"/>
+      <c r="AI154" s="2" t="inlineStr"/>
+      <c r="AJ154" s="2" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>e7d29fd040ea484c</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>70453</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K155" s="2" t="inlineStr"/>
+      <c r="L155" s="2" t="inlineStr">
+        <is>
+          <t>0.590765</t>
+        </is>
+      </c>
+      <c r="M155" s="2" t="inlineStr"/>
+      <c r="N155" s="2" t="inlineStr"/>
+      <c r="O155" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P155" s="2" t="inlineStr"/>
+      <c r="Q155" s="2" t="inlineStr">
+        <is>
+          <t>0.019949549356223173</t>
+        </is>
+      </c>
+      <c r="R155" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:56.469425Z</t>
+        </is>
+      </c>
+      <c r="S155" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="T155" s="2" t="inlineStr"/>
+      <c r="U155" s="2" t="inlineStr"/>
+      <c r="V155" s="2" t="inlineStr"/>
+      <c r="W155" s="2" t="inlineStr"/>
+      <c r="X155" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y155" s="2" t="inlineStr"/>
+      <c r="Z155" s="2" t="inlineStr"/>
+      <c r="AA155" s="2" t="inlineStr"/>
+      <c r="AB155" s="2" t="inlineStr"/>
+      <c r="AC155" s="2" t="inlineStr"/>
+      <c r="AD155" s="2" t="inlineStr"/>
+      <c r="AE155" s="2" t="inlineStr"/>
+      <c r="AF155" s="2" t="inlineStr"/>
+      <c r="AG155" s="2" t="inlineStr"/>
+      <c r="AH155" s="2" t="inlineStr"/>
+      <c r="AI155" s="2" t="inlineStr"/>
+      <c r="AJ155" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ120"/>
+  <autoFilter ref="A1:AJ155"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/gated_research/model_ledgers/lol-tiered-elo.xlsx
+++ b/data/gated_research/model_ledgers/lol-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$155</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$207</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ155"/>
+  <dimension ref="A1:AJ207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -16444,8 +16444,5312 @@
       <c r="AI155" s="2" t="inlineStr"/>
       <c r="AJ155" s="2" t="inlineStr"/>
     </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>f6749001da80434e</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>a133d940e25d9cbdc2b3f31895589b6e57301f9bda1c8081525b7d6a894d0ca6</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>68509</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr"/>
+      <c r="L156" s="2" t="inlineStr">
+        <is>
+          <t>0.63094</t>
+        </is>
+      </c>
+      <c r="M156" s="2" t="inlineStr"/>
+      <c r="N156" s="2" t="inlineStr"/>
+      <c r="O156" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P156" s="2" t="inlineStr"/>
+      <c r="Q156" s="2" t="inlineStr">
+        <is>
+          <t>0.05110806722689076</t>
+        </is>
+      </c>
+      <c r="R156" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:01:39.332314Z</t>
+        </is>
+      </c>
+      <c r="S156" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="T156" s="2" t="inlineStr"/>
+      <c r="U156" s="2" t="inlineStr"/>
+      <c r="V156" s="2" t="inlineStr"/>
+      <c r="W156" s="2" t="inlineStr"/>
+      <c r="X156" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y156" s="2" t="inlineStr"/>
+      <c r="Z156" s="2" t="inlineStr"/>
+      <c r="AA156" s="2" t="inlineStr"/>
+      <c r="AB156" s="2" t="inlineStr"/>
+      <c r="AC156" s="2" t="inlineStr"/>
+      <c r="AD156" s="2" t="inlineStr"/>
+      <c r="AE156" s="2" t="inlineStr"/>
+      <c r="AF156" s="2" t="inlineStr"/>
+      <c r="AG156" s="2" t="inlineStr"/>
+      <c r="AH156" s="2" t="inlineStr"/>
+      <c r="AI156" s="2" t="inlineStr"/>
+      <c r="AJ156" s="2" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>c249bc6b93b54ba5</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>a133d940e25d9cbdc2b3f31895589b6e57301f9bda1c8081525b7d6a894d0ca6</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>68690</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K157" s="2" t="inlineStr"/>
+      <c r="L157" s="2" t="inlineStr">
+        <is>
+          <t>0.550089</t>
+        </is>
+      </c>
+      <c r="M157" s="2" t="inlineStr"/>
+      <c r="N157" s="2" t="inlineStr"/>
+      <c r="O157" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P157" s="2" t="inlineStr"/>
+      <c r="Q157" s="2" t="inlineStr">
+        <is>
+          <t>0.010918493087557657</t>
+        </is>
+      </c>
+      <c r="R157" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:01:48.356421Z</t>
+        </is>
+      </c>
+      <c r="S157" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T157" s="2" t="inlineStr"/>
+      <c r="U157" s="2" t="inlineStr"/>
+      <c r="V157" s="2" t="inlineStr"/>
+      <c r="W157" s="2" t="inlineStr"/>
+      <c r="X157" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y157" s="2" t="inlineStr"/>
+      <c r="Z157" s="2" t="inlineStr"/>
+      <c r="AA157" s="2" t="inlineStr"/>
+      <c r="AB157" s="2" t="inlineStr"/>
+      <c r="AC157" s="2" t="inlineStr"/>
+      <c r="AD157" s="2" t="inlineStr"/>
+      <c r="AE157" s="2" t="inlineStr"/>
+      <c r="AF157" s="2" t="inlineStr"/>
+      <c r="AG157" s="2" t="inlineStr"/>
+      <c r="AH157" s="2" t="inlineStr"/>
+      <c r="AI157" s="2" t="inlineStr"/>
+      <c r="AJ157" s="2" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>0236aa5f93d746ca</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>a133d940e25d9cbdc2b3f31895589b6e57301f9bda1c8081525b7d6a894d0ca6</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>69143</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K158" s="2" t="inlineStr"/>
+      <c r="L158" s="2" t="inlineStr">
+        <is>
+          <t>0.623759</t>
+        </is>
+      </c>
+      <c r="M158" s="2" t="inlineStr"/>
+      <c r="N158" s="2" t="inlineStr"/>
+      <c r="O158" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P158" s="2" t="inlineStr"/>
+      <c r="Q158" s="2" t="inlineStr">
+        <is>
+          <t>0.003987136882129261</t>
+        </is>
+      </c>
+      <c r="R158" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:01:55.660758Z</t>
+        </is>
+      </c>
+      <c r="S158" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T158" s="2" t="inlineStr"/>
+      <c r="U158" s="2" t="inlineStr"/>
+      <c r="V158" s="2" t="inlineStr"/>
+      <c r="W158" s="2" t="inlineStr"/>
+      <c r="X158" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y158" s="2" t="inlineStr"/>
+      <c r="Z158" s="2" t="inlineStr"/>
+      <c r="AA158" s="2" t="inlineStr"/>
+      <c r="AB158" s="2" t="inlineStr"/>
+      <c r="AC158" s="2" t="inlineStr"/>
+      <c r="AD158" s="2" t="inlineStr"/>
+      <c r="AE158" s="2" t="inlineStr"/>
+      <c r="AF158" s="2" t="inlineStr"/>
+      <c r="AG158" s="2" t="inlineStr"/>
+      <c r="AH158" s="2" t="inlineStr"/>
+      <c r="AI158" s="2" t="inlineStr"/>
+      <c r="AJ158" s="2" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>7d3dffbb889b4da9</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>a133d940e25d9cbdc2b3f31895589b6e57301f9bda1c8081525b7d6a894d0ca6</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>69144</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K159" s="2" t="inlineStr"/>
+      <c r="L159" s="2" t="inlineStr">
+        <is>
+          <t>0.591217</t>
+        </is>
+      </c>
+      <c r="M159" s="2" t="inlineStr"/>
+      <c r="N159" s="2" t="inlineStr"/>
+      <c r="O159" s="2" t="inlineStr">
+        <is>
+          <t>0.4807692307692307</t>
+        </is>
+      </c>
+      <c r="P159" s="2" t="inlineStr"/>
+      <c r="Q159" s="2" t="inlineStr">
+        <is>
+          <t>0.11044776923076927</t>
+        </is>
+      </c>
+      <c r="R159" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:01:56.721224Z</t>
+        </is>
+      </c>
+      <c r="S159" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T159" s="2" t="inlineStr"/>
+      <c r="U159" s="2" t="inlineStr"/>
+      <c r="V159" s="2" t="inlineStr"/>
+      <c r="W159" s="2" t="inlineStr"/>
+      <c r="X159" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y159" s="2" t="inlineStr"/>
+      <c r="Z159" s="2" t="inlineStr"/>
+      <c r="AA159" s="2" t="inlineStr"/>
+      <c r="AB159" s="2" t="inlineStr"/>
+      <c r="AC159" s="2" t="inlineStr"/>
+      <c r="AD159" s="2" t="inlineStr"/>
+      <c r="AE159" s="2" t="inlineStr"/>
+      <c r="AF159" s="2" t="inlineStr"/>
+      <c r="AG159" s="2" t="inlineStr"/>
+      <c r="AH159" s="2" t="inlineStr"/>
+      <c r="AI159" s="2" t="inlineStr"/>
+      <c r="AJ159" s="2" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>c6a80f62e0ce40fb</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>a133d940e25d9cbdc2b3f31895589b6e57301f9bda1c8081525b7d6a894d0ca6</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>69233</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K160" s="2" t="inlineStr"/>
+      <c r="L160" s="2" t="inlineStr">
+        <is>
+          <t>0.572038</t>
+        </is>
+      </c>
+      <c r="M160" s="2" t="inlineStr"/>
+      <c r="N160" s="2" t="inlineStr"/>
+      <c r="O160" s="2" t="inlineStr">
+        <is>
+          <t>0.3401360544217687</t>
+        </is>
+      </c>
+      <c r="P160" s="2" t="inlineStr"/>
+      <c r="Q160" s="2" t="inlineStr">
+        <is>
+          <t>0.23190194557823135</t>
+        </is>
+      </c>
+      <c r="R160" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:01:59.898656Z</t>
+        </is>
+      </c>
+      <c r="S160" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T160" s="2" t="inlineStr"/>
+      <c r="U160" s="2" t="inlineStr"/>
+      <c r="V160" s="2" t="inlineStr"/>
+      <c r="W160" s="2" t="inlineStr"/>
+      <c r="X160" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y160" s="2" t="inlineStr"/>
+      <c r="Z160" s="2" t="inlineStr"/>
+      <c r="AA160" s="2" t="inlineStr"/>
+      <c r="AB160" s="2" t="inlineStr"/>
+      <c r="AC160" s="2" t="inlineStr"/>
+      <c r="AD160" s="2" t="inlineStr"/>
+      <c r="AE160" s="2" t="inlineStr"/>
+      <c r="AF160" s="2" t="inlineStr"/>
+      <c r="AG160" s="2" t="inlineStr"/>
+      <c r="AH160" s="2" t="inlineStr"/>
+      <c r="AI160" s="2" t="inlineStr"/>
+      <c r="AJ160" s="2" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>cbdf01c0b4da4154</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>a133d940e25d9cbdc2b3f31895589b6e57301f9bda1c8081525b7d6a894d0ca6</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>69273</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K161" s="2" t="inlineStr"/>
+      <c r="L161" s="2" t="inlineStr">
+        <is>
+          <t>0.604197</t>
+        </is>
+      </c>
+      <c r="M161" s="2" t="inlineStr"/>
+      <c r="N161" s="2" t="inlineStr"/>
+      <c r="O161" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P161" s="2" t="inlineStr"/>
+      <c r="Q161" s="2" t="inlineStr">
+        <is>
+          <t>0.06502649308755759</t>
+        </is>
+      </c>
+      <c r="R161" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:02:02.094269Z</t>
+        </is>
+      </c>
+      <c r="S161" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="T161" s="2" t="inlineStr"/>
+      <c r="U161" s="2" t="inlineStr"/>
+      <c r="V161" s="2" t="inlineStr"/>
+      <c r="W161" s="2" t="inlineStr"/>
+      <c r="X161" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y161" s="2" t="inlineStr"/>
+      <c r="Z161" s="2" t="inlineStr"/>
+      <c r="AA161" s="2" t="inlineStr"/>
+      <c r="AB161" s="2" t="inlineStr"/>
+      <c r="AC161" s="2" t="inlineStr"/>
+      <c r="AD161" s="2" t="inlineStr"/>
+      <c r="AE161" s="2" t="inlineStr"/>
+      <c r="AF161" s="2" t="inlineStr"/>
+      <c r="AG161" s="2" t="inlineStr"/>
+      <c r="AH161" s="2" t="inlineStr"/>
+      <c r="AI161" s="2" t="inlineStr"/>
+      <c r="AJ161" s="2" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>e95c4fb5323c4373</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>a133d940e25d9cbdc2b3f31895589b6e57301f9bda1c8081525b7d6a894d0ca6</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>69507</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K162" s="2" t="inlineStr"/>
+      <c r="L162" s="2" t="inlineStr">
+        <is>
+          <t>0.638392</t>
+        </is>
+      </c>
+      <c r="M162" s="2" t="inlineStr"/>
+      <c r="N162" s="2" t="inlineStr"/>
+      <c r="O162" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P162" s="2" t="inlineStr"/>
+      <c r="Q162" s="2" t="inlineStr">
+        <is>
+          <t>0.05856006722689078</t>
+        </is>
+      </c>
+      <c r="R162" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:02:06.549923Z</t>
+        </is>
+      </c>
+      <c r="S162" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="T162" s="2" t="inlineStr"/>
+      <c r="U162" s="2" t="inlineStr"/>
+      <c r="V162" s="2" t="inlineStr"/>
+      <c r="W162" s="2" t="inlineStr"/>
+      <c r="X162" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y162" s="2" t="inlineStr"/>
+      <c r="Z162" s="2" t="inlineStr"/>
+      <c r="AA162" s="2" t="inlineStr"/>
+      <c r="AB162" s="2" t="inlineStr"/>
+      <c r="AC162" s="2" t="inlineStr"/>
+      <c r="AD162" s="2" t="inlineStr"/>
+      <c r="AE162" s="2" t="inlineStr"/>
+      <c r="AF162" s="2" t="inlineStr"/>
+      <c r="AG162" s="2" t="inlineStr"/>
+      <c r="AH162" s="2" t="inlineStr"/>
+      <c r="AI162" s="2" t="inlineStr"/>
+      <c r="AJ162" s="2" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>cac1996d2dbd4fa2</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>a133d940e25d9cbdc2b3f31895589b6e57301f9bda1c8081525b7d6a894d0ca6</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>69512</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K163" s="2" t="inlineStr"/>
+      <c r="L163" s="2" t="inlineStr">
+        <is>
+          <t>0.740276</t>
+        </is>
+      </c>
+      <c r="M163" s="2" t="inlineStr"/>
+      <c r="N163" s="2" t="inlineStr"/>
+      <c r="O163" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P163" s="2" t="inlineStr"/>
+      <c r="Q163" s="2" t="inlineStr">
+        <is>
+          <t>0.04987352321981431</t>
+        </is>
+      </c>
+      <c r="R163" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:02:07.342777Z</t>
+        </is>
+      </c>
+      <c r="S163" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T163" s="2" t="inlineStr"/>
+      <c r="U163" s="2" t="inlineStr"/>
+      <c r="V163" s="2" t="inlineStr"/>
+      <c r="W163" s="2" t="inlineStr"/>
+      <c r="X163" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y163" s="2" t="inlineStr"/>
+      <c r="Z163" s="2" t="inlineStr"/>
+      <c r="AA163" s="2" t="inlineStr"/>
+      <c r="AB163" s="2" t="inlineStr"/>
+      <c r="AC163" s="2" t="inlineStr"/>
+      <c r="AD163" s="2" t="inlineStr"/>
+      <c r="AE163" s="2" t="inlineStr"/>
+      <c r="AF163" s="2" t="inlineStr"/>
+      <c r="AG163" s="2" t="inlineStr"/>
+      <c r="AH163" s="2" t="inlineStr"/>
+      <c r="AI163" s="2" t="inlineStr"/>
+      <c r="AJ163" s="2" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>abd5451071b74c8c</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>a133d940e25d9cbdc2b3f31895589b6e57301f9bda1c8081525b7d6a894d0ca6</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>69511</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K164" s="2" t="inlineStr"/>
+      <c r="L164" s="2" t="inlineStr">
+        <is>
+          <t>0.69928</t>
+        </is>
+      </c>
+      <c r="M164" s="2" t="inlineStr"/>
+      <c r="N164" s="2" t="inlineStr"/>
+      <c r="O164" s="2" t="inlineStr">
+        <is>
+          <t>0.6296296296296295</t>
+        </is>
+      </c>
+      <c r="P164" s="2" t="inlineStr"/>
+      <c r="Q164" s="2" t="inlineStr">
+        <is>
+          <t>0.06965037037037047</t>
+        </is>
+      </c>
+      <c r="R164" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:02:08.262036Z</t>
+        </is>
+      </c>
+      <c r="S164" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T164" s="2" t="inlineStr"/>
+      <c r="U164" s="2" t="inlineStr"/>
+      <c r="V164" s="2" t="inlineStr"/>
+      <c r="W164" s="2" t="inlineStr"/>
+      <c r="X164" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y164" s="2" t="inlineStr"/>
+      <c r="Z164" s="2" t="inlineStr"/>
+      <c r="AA164" s="2" t="inlineStr"/>
+      <c r="AB164" s="2" t="inlineStr"/>
+      <c r="AC164" s="2" t="inlineStr"/>
+      <c r="AD164" s="2" t="inlineStr"/>
+      <c r="AE164" s="2" t="inlineStr"/>
+      <c r="AF164" s="2" t="inlineStr"/>
+      <c r="AG164" s="2" t="inlineStr"/>
+      <c r="AH164" s="2" t="inlineStr"/>
+      <c r="AI164" s="2" t="inlineStr"/>
+      <c r="AJ164" s="2" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>51cc2074e4cb4643</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>a133d940e25d9cbdc2b3f31895589b6e57301f9bda1c8081525b7d6a894d0ca6</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>69539</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K165" s="2" t="inlineStr"/>
+      <c r="L165" s="2" t="inlineStr">
+        <is>
+          <t>0.602809</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="inlineStr"/>
+      <c r="N165" s="2" t="inlineStr"/>
+      <c r="O165" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P165" s="2" t="inlineStr"/>
+      <c r="Q165" s="2" t="inlineStr">
+        <is>
+          <t>0.05325945045045055</t>
+        </is>
+      </c>
+      <c r="R165" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:02:10.316791Z</t>
+        </is>
+      </c>
+      <c r="S165" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T165" s="2" t="inlineStr"/>
+      <c r="U165" s="2" t="inlineStr"/>
+      <c r="V165" s="2" t="inlineStr"/>
+      <c r="W165" s="2" t="inlineStr"/>
+      <c r="X165" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y165" s="2" t="inlineStr"/>
+      <c r="Z165" s="2" t="inlineStr"/>
+      <c r="AA165" s="2" t="inlineStr"/>
+      <c r="AB165" s="2" t="inlineStr"/>
+      <c r="AC165" s="2" t="inlineStr"/>
+      <c r="AD165" s="2" t="inlineStr"/>
+      <c r="AE165" s="2" t="inlineStr"/>
+      <c r="AF165" s="2" t="inlineStr"/>
+      <c r="AG165" s="2" t="inlineStr"/>
+      <c r="AH165" s="2" t="inlineStr"/>
+      <c r="AI165" s="2" t="inlineStr"/>
+      <c r="AJ165" s="2" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>7e04d6dab2524d06</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>a133d940e25d9cbdc2b3f31895589b6e57301f9bda1c8081525b7d6a894d0ca6</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>69817</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K166" s="2" t="inlineStr"/>
+      <c r="L166" s="2" t="inlineStr">
+        <is>
+          <t>0.560868</t>
+        </is>
+      </c>
+      <c r="M166" s="2" t="inlineStr"/>
+      <c r="N166" s="2" t="inlineStr"/>
+      <c r="O166" s="2" t="inlineStr">
+        <is>
+          <t>0.4807692307692307</t>
+        </is>
+      </c>
+      <c r="P166" s="2" t="inlineStr"/>
+      <c r="Q166" s="2" t="inlineStr">
+        <is>
+          <t>0.0800987692307693</t>
+        </is>
+      </c>
+      <c r="R166" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:02:22.084500Z</t>
+        </is>
+      </c>
+      <c r="S166" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="T166" s="2" t="inlineStr"/>
+      <c r="U166" s="2" t="inlineStr"/>
+      <c r="V166" s="2" t="inlineStr"/>
+      <c r="W166" s="2" t="inlineStr"/>
+      <c r="X166" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y166" s="2" t="inlineStr"/>
+      <c r="Z166" s="2" t="inlineStr"/>
+      <c r="AA166" s="2" t="inlineStr"/>
+      <c r="AB166" s="2" t="inlineStr"/>
+      <c r="AC166" s="2" t="inlineStr"/>
+      <c r="AD166" s="2" t="inlineStr"/>
+      <c r="AE166" s="2" t="inlineStr"/>
+      <c r="AF166" s="2" t="inlineStr"/>
+      <c r="AG166" s="2" t="inlineStr"/>
+      <c r="AH166" s="2" t="inlineStr"/>
+      <c r="AI166" s="2" t="inlineStr"/>
+      <c r="AJ166" s="2" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>42875cfa9920416a</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>a133d940e25d9cbdc2b3f31895589b6e57301f9bda1c8081525b7d6a894d0ca6</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>70569</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K167" s="2" t="inlineStr"/>
+      <c r="L167" s="2" t="inlineStr">
+        <is>
+          <t>0.832476</t>
+        </is>
+      </c>
+      <c r="M167" s="2" t="inlineStr"/>
+      <c r="N167" s="2" t="inlineStr"/>
+      <c r="O167" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P167" s="2" t="inlineStr"/>
+      <c r="Q167" s="2" t="inlineStr">
+        <is>
+          <t>0.2616605493562232</t>
+        </is>
+      </c>
+      <c r="R167" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:02:24.446521Z</t>
+        </is>
+      </c>
+      <c r="S167" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T167" s="2" t="inlineStr"/>
+      <c r="U167" s="2" t="inlineStr"/>
+      <c r="V167" s="2" t="inlineStr"/>
+      <c r="W167" s="2" t="inlineStr"/>
+      <c r="X167" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y167" s="2" t="inlineStr"/>
+      <c r="Z167" s="2" t="inlineStr"/>
+      <c r="AA167" s="2" t="inlineStr"/>
+      <c r="AB167" s="2" t="inlineStr"/>
+      <c r="AC167" s="2" t="inlineStr"/>
+      <c r="AD167" s="2" t="inlineStr"/>
+      <c r="AE167" s="2" t="inlineStr"/>
+      <c r="AF167" s="2" t="inlineStr"/>
+      <c r="AG167" s="2" t="inlineStr"/>
+      <c r="AH167" s="2" t="inlineStr"/>
+      <c r="AI167" s="2" t="inlineStr"/>
+      <c r="AJ167" s="2" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>2b72e56a108b4344</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>a133d940e25d9cbdc2b3f31895589b6e57301f9bda1c8081525b7d6a894d0ca6</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>69871</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K168" s="2" t="inlineStr"/>
+      <c r="L168" s="2" t="inlineStr">
+        <is>
+          <t>0.560751</t>
+        </is>
+      </c>
+      <c r="M168" s="2" t="inlineStr"/>
+      <c r="N168" s="2" t="inlineStr"/>
+      <c r="O168" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P168" s="2" t="inlineStr"/>
+      <c r="Q168" s="2" t="inlineStr">
+        <is>
+          <t>0.12022236563876654</t>
+        </is>
+      </c>
+      <c r="R168" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:02:25.483078Z</t>
+        </is>
+      </c>
+      <c r="S168" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T168" s="2" t="inlineStr"/>
+      <c r="U168" s="2" t="inlineStr"/>
+      <c r="V168" s="2" t="inlineStr"/>
+      <c r="W168" s="2" t="inlineStr"/>
+      <c r="X168" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y168" s="2" t="inlineStr"/>
+      <c r="Z168" s="2" t="inlineStr"/>
+      <c r="AA168" s="2" t="inlineStr"/>
+      <c r="AB168" s="2" t="inlineStr"/>
+      <c r="AC168" s="2" t="inlineStr"/>
+      <c r="AD168" s="2" t="inlineStr"/>
+      <c r="AE168" s="2" t="inlineStr"/>
+      <c r="AF168" s="2" t="inlineStr"/>
+      <c r="AG168" s="2" t="inlineStr"/>
+      <c r="AH168" s="2" t="inlineStr"/>
+      <c r="AI168" s="2" t="inlineStr"/>
+      <c r="AJ168" s="2" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>e444961c43004f61</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>a133d940e25d9cbdc2b3f31895589b6e57301f9bda1c8081525b7d6a894d0ca6</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>69931</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr"/>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>0.576619</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="inlineStr"/>
+      <c r="N169" s="2" t="inlineStr"/>
+      <c r="O169" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="P169" s="2" t="inlineStr"/>
+      <c r="Q169" s="2" t="inlineStr">
+        <is>
+          <t>0.07661899999999999</t>
+        </is>
+      </c>
+      <c r="R169" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:02:27.931942Z</t>
+        </is>
+      </c>
+      <c r="S169" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:30:00Z</t>
+        </is>
+      </c>
+      <c r="T169" s="2" t="inlineStr"/>
+      <c r="U169" s="2" t="inlineStr"/>
+      <c r="V169" s="2" t="inlineStr"/>
+      <c r="W169" s="2" t="inlineStr"/>
+      <c r="X169" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y169" s="2" t="inlineStr"/>
+      <c r="Z169" s="2" t="inlineStr"/>
+      <c r="AA169" s="2" t="inlineStr"/>
+      <c r="AB169" s="2" t="inlineStr"/>
+      <c r="AC169" s="2" t="inlineStr"/>
+      <c r="AD169" s="2" t="inlineStr"/>
+      <c r="AE169" s="2" t="inlineStr"/>
+      <c r="AF169" s="2" t="inlineStr"/>
+      <c r="AG169" s="2" t="inlineStr"/>
+      <c r="AH169" s="2" t="inlineStr"/>
+      <c r="AI169" s="2" t="inlineStr"/>
+      <c r="AJ169" s="2" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>685bd106395047cf</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>a133d940e25d9cbdc2b3f31895589b6e57301f9bda1c8081525b7d6a894d0ca6</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>70045</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr"/>
+      <c r="L170" s="2" t="inlineStr">
+        <is>
+          <t>0.608055</t>
+        </is>
+      </c>
+      <c r="M170" s="2" t="inlineStr"/>
+      <c r="N170" s="2" t="inlineStr"/>
+      <c r="O170" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P170" s="2" t="inlineStr"/>
+      <c r="Q170" s="2" t="inlineStr">
+        <is>
+          <t>0.048583634361233474</t>
+        </is>
+      </c>
+      <c r="R170" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:02:37.767390Z</t>
+        </is>
+      </c>
+      <c r="S170" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="T170" s="2" t="inlineStr"/>
+      <c r="U170" s="2" t="inlineStr"/>
+      <c r="V170" s="2" t="inlineStr"/>
+      <c r="W170" s="2" t="inlineStr"/>
+      <c r="X170" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y170" s="2" t="inlineStr"/>
+      <c r="Z170" s="2" t="inlineStr"/>
+      <c r="AA170" s="2" t="inlineStr"/>
+      <c r="AB170" s="2" t="inlineStr"/>
+      <c r="AC170" s="2" t="inlineStr"/>
+      <c r="AD170" s="2" t="inlineStr"/>
+      <c r="AE170" s="2" t="inlineStr"/>
+      <c r="AF170" s="2" t="inlineStr"/>
+      <c r="AG170" s="2" t="inlineStr"/>
+      <c r="AH170" s="2" t="inlineStr"/>
+      <c r="AI170" s="2" t="inlineStr"/>
+      <c r="AJ170" s="2" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>9d6527e2e7b44174</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>a133d940e25d9cbdc2b3f31895589b6e57301f9bda1c8081525b7d6a894d0ca6</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>70301</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr"/>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>0.658204</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr"/>
+      <c r="N171" s="2" t="inlineStr"/>
+      <c r="O171" s="2" t="inlineStr">
+        <is>
+          <t>0.4694835680751174</t>
+        </is>
+      </c>
+      <c r="P171" s="2" t="inlineStr"/>
+      <c r="Q171" s="2" t="inlineStr">
+        <is>
+          <t>0.18872043192488264</t>
+        </is>
+      </c>
+      <c r="R171" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:02:38.937936Z</t>
+        </is>
+      </c>
+      <c r="S171" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T171" s="2" t="inlineStr"/>
+      <c r="U171" s="2" t="inlineStr"/>
+      <c r="V171" s="2" t="inlineStr"/>
+      <c r="W171" s="2" t="inlineStr"/>
+      <c r="X171" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y171" s="2" t="inlineStr"/>
+      <c r="Z171" s="2" t="inlineStr"/>
+      <c r="AA171" s="2" t="inlineStr"/>
+      <c r="AB171" s="2" t="inlineStr"/>
+      <c r="AC171" s="2" t="inlineStr"/>
+      <c r="AD171" s="2" t="inlineStr"/>
+      <c r="AE171" s="2" t="inlineStr"/>
+      <c r="AF171" s="2" t="inlineStr"/>
+      <c r="AG171" s="2" t="inlineStr"/>
+      <c r="AH171" s="2" t="inlineStr"/>
+      <c r="AI171" s="2" t="inlineStr"/>
+      <c r="AJ171" s="2" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>506910e2dfe0497c</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>a133d940e25d9cbdc2b3f31895589b6e57301f9bda1c8081525b7d6a894d0ca6</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>70379</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K172" s="2" t="inlineStr"/>
+      <c r="L172" s="2" t="inlineStr">
+        <is>
+          <t>0.567396</t>
+        </is>
+      </c>
+      <c r="M172" s="2" t="inlineStr"/>
+      <c r="N172" s="2" t="inlineStr"/>
+      <c r="O172" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P172" s="2" t="inlineStr"/>
+      <c r="Q172" s="2" t="inlineStr">
+        <is>
+          <t>0.12686736563876655</t>
+        </is>
+      </c>
+      <c r="R172" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:02:45.270183Z</t>
+        </is>
+      </c>
+      <c r="S172" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="T172" s="2" t="inlineStr"/>
+      <c r="U172" s="2" t="inlineStr"/>
+      <c r="V172" s="2" t="inlineStr"/>
+      <c r="W172" s="2" t="inlineStr"/>
+      <c r="X172" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y172" s="2" t="inlineStr"/>
+      <c r="Z172" s="2" t="inlineStr"/>
+      <c r="AA172" s="2" t="inlineStr"/>
+      <c r="AB172" s="2" t="inlineStr"/>
+      <c r="AC172" s="2" t="inlineStr"/>
+      <c r="AD172" s="2" t="inlineStr"/>
+      <c r="AE172" s="2" t="inlineStr"/>
+      <c r="AF172" s="2" t="inlineStr"/>
+      <c r="AG172" s="2" t="inlineStr"/>
+      <c r="AH172" s="2" t="inlineStr"/>
+      <c r="AI172" s="2" t="inlineStr"/>
+      <c r="AJ172" s="2" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>cf5efd49acbb47ec</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>a133d940e25d9cbdc2b3f31895589b6e57301f9bda1c8081525b7d6a894d0ca6</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>70453</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr"/>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>0.591359</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr"/>
+      <c r="N173" s="2" t="inlineStr"/>
+      <c r="O173" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P173" s="2" t="inlineStr"/>
+      <c r="Q173" s="2" t="inlineStr">
+        <is>
+          <t>0.03188763436123343</t>
+        </is>
+      </c>
+      <c r="R173" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:02:47.312150Z</t>
+        </is>
+      </c>
+      <c r="S173" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="T173" s="2" t="inlineStr"/>
+      <c r="U173" s="2" t="inlineStr"/>
+      <c r="V173" s="2" t="inlineStr"/>
+      <c r="W173" s="2" t="inlineStr"/>
+      <c r="X173" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y173" s="2" t="inlineStr"/>
+      <c r="Z173" s="2" t="inlineStr"/>
+      <c r="AA173" s="2" t="inlineStr"/>
+      <c r="AB173" s="2" t="inlineStr"/>
+      <c r="AC173" s="2" t="inlineStr"/>
+      <c r="AD173" s="2" t="inlineStr"/>
+      <c r="AE173" s="2" t="inlineStr"/>
+      <c r="AF173" s="2" t="inlineStr"/>
+      <c r="AG173" s="2" t="inlineStr"/>
+      <c r="AH173" s="2" t="inlineStr"/>
+      <c r="AI173" s="2" t="inlineStr"/>
+      <c r="AJ173" s="2" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>b40e627723654257</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>46f5fcde49f942cdafa52f104990c598da2a615146ee49a1e1afd06b01f9493b</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>68509</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K174" s="2" t="inlineStr"/>
+      <c r="L174" s="2" t="inlineStr">
+        <is>
+          <t>0.631258</t>
+        </is>
+      </c>
+      <c r="M174" s="2" t="inlineStr"/>
+      <c r="N174" s="2" t="inlineStr"/>
+      <c r="O174" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P174" s="2" t="inlineStr"/>
+      <c r="Q174" s="2" t="inlineStr">
+        <is>
+          <t>0.051426067226890804</t>
+        </is>
+      </c>
+      <c r="R174" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:07:08.156074Z</t>
+        </is>
+      </c>
+      <c r="S174" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="T174" s="2" t="inlineStr"/>
+      <c r="U174" s="2" t="inlineStr"/>
+      <c r="V174" s="2" t="inlineStr"/>
+      <c r="W174" s="2" t="inlineStr"/>
+      <c r="X174" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y174" s="2" t="inlineStr"/>
+      <c r="Z174" s="2" t="inlineStr"/>
+      <c r="AA174" s="2" t="inlineStr"/>
+      <c r="AB174" s="2" t="inlineStr"/>
+      <c r="AC174" s="2" t="inlineStr"/>
+      <c r="AD174" s="2" t="inlineStr"/>
+      <c r="AE174" s="2" t="inlineStr"/>
+      <c r="AF174" s="2" t="inlineStr"/>
+      <c r="AG174" s="2" t="inlineStr"/>
+      <c r="AH174" s="2" t="inlineStr"/>
+      <c r="AI174" s="2" t="inlineStr"/>
+      <c r="AJ174" s="2" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>9945caf70fce49d9</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>46f5fcde49f942cdafa52f104990c598da2a615146ee49a1e1afd06b01f9493b</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>68690</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr"/>
+      <c r="L175" s="2" t="inlineStr">
+        <is>
+          <t>0.55095</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="inlineStr"/>
+      <c r="N175" s="2" t="inlineStr"/>
+      <c r="O175" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P175" s="2" t="inlineStr"/>
+      <c r="Q175" s="2" t="inlineStr">
+        <is>
+          <t>0.011779493087557658</t>
+        </is>
+      </c>
+      <c r="R175" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:07:11.531686Z</t>
+        </is>
+      </c>
+      <c r="S175" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T175" s="2" t="inlineStr"/>
+      <c r="U175" s="2" t="inlineStr"/>
+      <c r="V175" s="2" t="inlineStr"/>
+      <c r="W175" s="2" t="inlineStr"/>
+      <c r="X175" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y175" s="2" t="inlineStr"/>
+      <c r="Z175" s="2" t="inlineStr"/>
+      <c r="AA175" s="2" t="inlineStr"/>
+      <c r="AB175" s="2" t="inlineStr"/>
+      <c r="AC175" s="2" t="inlineStr"/>
+      <c r="AD175" s="2" t="inlineStr"/>
+      <c r="AE175" s="2" t="inlineStr"/>
+      <c r="AF175" s="2" t="inlineStr"/>
+      <c r="AG175" s="2" t="inlineStr"/>
+      <c r="AH175" s="2" t="inlineStr"/>
+      <c r="AI175" s="2" t="inlineStr"/>
+      <c r="AJ175" s="2" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>a4afac8206c44a1e</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>46f5fcde49f942cdafa52f104990c598da2a615146ee49a1e1afd06b01f9493b</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>69143</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K176" s="2" t="inlineStr"/>
+      <c r="L176" s="2" t="inlineStr">
+        <is>
+          <t>0.624122</t>
+        </is>
+      </c>
+      <c r="M176" s="2" t="inlineStr"/>
+      <c r="N176" s="2" t="inlineStr"/>
+      <c r="O176" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P176" s="2" t="inlineStr"/>
+      <c r="Q176" s="2" t="inlineStr">
+        <is>
+          <t>0.004350136882129263</t>
+        </is>
+      </c>
+      <c r="R176" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:07:15.572053Z</t>
+        </is>
+      </c>
+      <c r="S176" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T176" s="2" t="inlineStr"/>
+      <c r="U176" s="2" t="inlineStr"/>
+      <c r="V176" s="2" t="inlineStr"/>
+      <c r="W176" s="2" t="inlineStr"/>
+      <c r="X176" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y176" s="2" t="inlineStr"/>
+      <c r="Z176" s="2" t="inlineStr"/>
+      <c r="AA176" s="2" t="inlineStr"/>
+      <c r="AB176" s="2" t="inlineStr"/>
+      <c r="AC176" s="2" t="inlineStr"/>
+      <c r="AD176" s="2" t="inlineStr"/>
+      <c r="AE176" s="2" t="inlineStr"/>
+      <c r="AF176" s="2" t="inlineStr"/>
+      <c r="AG176" s="2" t="inlineStr"/>
+      <c r="AH176" s="2" t="inlineStr"/>
+      <c r="AI176" s="2" t="inlineStr"/>
+      <c r="AJ176" s="2" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>0ab9c88f710a4997</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>46f5fcde49f942cdafa52f104990c598da2a615146ee49a1e1afd06b01f9493b</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>69144</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K177" s="2" t="inlineStr"/>
+      <c r="L177" s="2" t="inlineStr">
+        <is>
+          <t>0.5918</t>
+        </is>
+      </c>
+      <c r="M177" s="2" t="inlineStr"/>
+      <c r="N177" s="2" t="inlineStr"/>
+      <c r="O177" s="2" t="inlineStr">
+        <is>
+          <t>0.4608294930875576</t>
+        </is>
+      </c>
+      <c r="P177" s="2" t="inlineStr"/>
+      <c r="Q177" s="2" t="inlineStr">
+        <is>
+          <t>0.13097050691244239</t>
+        </is>
+      </c>
+      <c r="R177" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:07:16.093680Z</t>
+        </is>
+      </c>
+      <c r="S177" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T177" s="2" t="inlineStr"/>
+      <c r="U177" s="2" t="inlineStr"/>
+      <c r="V177" s="2" t="inlineStr"/>
+      <c r="W177" s="2" t="inlineStr"/>
+      <c r="X177" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y177" s="2" t="inlineStr"/>
+      <c r="Z177" s="2" t="inlineStr"/>
+      <c r="AA177" s="2" t="inlineStr"/>
+      <c r="AB177" s="2" t="inlineStr"/>
+      <c r="AC177" s="2" t="inlineStr"/>
+      <c r="AD177" s="2" t="inlineStr"/>
+      <c r="AE177" s="2" t="inlineStr"/>
+      <c r="AF177" s="2" t="inlineStr"/>
+      <c r="AG177" s="2" t="inlineStr"/>
+      <c r="AH177" s="2" t="inlineStr"/>
+      <c r="AI177" s="2" t="inlineStr"/>
+      <c r="AJ177" s="2" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>b13223c6fe744dd1</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>46f5fcde49f942cdafa52f104990c598da2a615146ee49a1e1afd06b01f9493b</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>69233</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K178" s="2" t="inlineStr"/>
+      <c r="L178" s="2" t="inlineStr">
+        <is>
+          <t>0.572751</t>
+        </is>
+      </c>
+      <c r="M178" s="2" t="inlineStr"/>
+      <c r="N178" s="2" t="inlineStr"/>
+      <c r="O178" s="2" t="inlineStr">
+        <is>
+          <t>0.33003300330033003</t>
+        </is>
+      </c>
+      <c r="P178" s="2" t="inlineStr"/>
+      <c r="Q178" s="2" t="inlineStr">
+        <is>
+          <t>0.24271799669966998</t>
+        </is>
+      </c>
+      <c r="R178" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:07:17.871536Z</t>
+        </is>
+      </c>
+      <c r="S178" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T178" s="2" t="inlineStr"/>
+      <c r="U178" s="2" t="inlineStr"/>
+      <c r="V178" s="2" t="inlineStr"/>
+      <c r="W178" s="2" t="inlineStr"/>
+      <c r="X178" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y178" s="2" t="inlineStr"/>
+      <c r="Z178" s="2" t="inlineStr"/>
+      <c r="AA178" s="2" t="inlineStr"/>
+      <c r="AB178" s="2" t="inlineStr"/>
+      <c r="AC178" s="2" t="inlineStr"/>
+      <c r="AD178" s="2" t="inlineStr"/>
+      <c r="AE178" s="2" t="inlineStr"/>
+      <c r="AF178" s="2" t="inlineStr"/>
+      <c r="AG178" s="2" t="inlineStr"/>
+      <c r="AH178" s="2" t="inlineStr"/>
+      <c r="AI178" s="2" t="inlineStr"/>
+      <c r="AJ178" s="2" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>b51f7d3613504c0a</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>46f5fcde49f942cdafa52f104990c598da2a615146ee49a1e1afd06b01f9493b</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>69273</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K179" s="2" t="inlineStr"/>
+      <c r="L179" s="2" t="inlineStr">
+        <is>
+          <t>0.604693</t>
+        </is>
+      </c>
+      <c r="M179" s="2" t="inlineStr"/>
+      <c r="N179" s="2" t="inlineStr"/>
+      <c r="O179" s="2" t="inlineStr">
+        <is>
+          <t>0.5192307692307692</t>
+        </is>
+      </c>
+      <c r="P179" s="2" t="inlineStr"/>
+      <c r="Q179" s="2" t="inlineStr">
+        <is>
+          <t>0.08546223076923087</t>
+        </is>
+      </c>
+      <c r="R179" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:07:19.014536Z</t>
+        </is>
+      </c>
+      <c r="S179" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="T179" s="2" t="inlineStr"/>
+      <c r="U179" s="2" t="inlineStr"/>
+      <c r="V179" s="2" t="inlineStr"/>
+      <c r="W179" s="2" t="inlineStr"/>
+      <c r="X179" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y179" s="2" t="inlineStr"/>
+      <c r="Z179" s="2" t="inlineStr"/>
+      <c r="AA179" s="2" t="inlineStr"/>
+      <c r="AB179" s="2" t="inlineStr"/>
+      <c r="AC179" s="2" t="inlineStr"/>
+      <c r="AD179" s="2" t="inlineStr"/>
+      <c r="AE179" s="2" t="inlineStr"/>
+      <c r="AF179" s="2" t="inlineStr"/>
+      <c r="AG179" s="2" t="inlineStr"/>
+      <c r="AH179" s="2" t="inlineStr"/>
+      <c r="AI179" s="2" t="inlineStr"/>
+      <c r="AJ179" s="2" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>1e5d92e7eaec4ba7</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>46f5fcde49f942cdafa52f104990c598da2a615146ee49a1e1afd06b01f9493b</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>69507</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K180" s="2" t="inlineStr"/>
+      <c r="L180" s="2" t="inlineStr">
+        <is>
+          <t>0.638652</t>
+        </is>
+      </c>
+      <c r="M180" s="2" t="inlineStr"/>
+      <c r="N180" s="2" t="inlineStr"/>
+      <c r="O180" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P180" s="2" t="inlineStr"/>
+      <c r="Q180" s="2" t="inlineStr">
+        <is>
+          <t>0.058820067226890815</t>
+        </is>
+      </c>
+      <c r="R180" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:07:21.372634Z</t>
+        </is>
+      </c>
+      <c r="S180" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="T180" s="2" t="inlineStr"/>
+      <c r="U180" s="2" t="inlineStr"/>
+      <c r="V180" s="2" t="inlineStr"/>
+      <c r="W180" s="2" t="inlineStr"/>
+      <c r="X180" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y180" s="2" t="inlineStr"/>
+      <c r="Z180" s="2" t="inlineStr"/>
+      <c r="AA180" s="2" t="inlineStr"/>
+      <c r="AB180" s="2" t="inlineStr"/>
+      <c r="AC180" s="2" t="inlineStr"/>
+      <c r="AD180" s="2" t="inlineStr"/>
+      <c r="AE180" s="2" t="inlineStr"/>
+      <c r="AF180" s="2" t="inlineStr"/>
+      <c r="AG180" s="2" t="inlineStr"/>
+      <c r="AH180" s="2" t="inlineStr"/>
+      <c r="AI180" s="2" t="inlineStr"/>
+      <c r="AJ180" s="2" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>612aed232a5d4c7a</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>46f5fcde49f942cdafa52f104990c598da2a615146ee49a1e1afd06b01f9493b</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>69511</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K181" s="2" t="inlineStr"/>
+      <c r="L181" s="2" t="inlineStr">
+        <is>
+          <t>0.699121</t>
+        </is>
+      </c>
+      <c r="M181" s="2" t="inlineStr"/>
+      <c r="N181" s="2" t="inlineStr"/>
+      <c r="O181" s="2" t="inlineStr">
+        <is>
+          <t>0.6503496503496503</t>
+        </is>
+      </c>
+      <c r="P181" s="2" t="inlineStr"/>
+      <c r="Q181" s="2" t="inlineStr">
+        <is>
+          <t>0.04877134965034968</t>
+        </is>
+      </c>
+      <c r="R181" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:07:21.873720Z</t>
+        </is>
+      </c>
+      <c r="S181" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T181" s="2" t="inlineStr"/>
+      <c r="U181" s="2" t="inlineStr"/>
+      <c r="V181" s="2" t="inlineStr"/>
+      <c r="W181" s="2" t="inlineStr"/>
+      <c r="X181" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y181" s="2" t="inlineStr"/>
+      <c r="Z181" s="2" t="inlineStr"/>
+      <c r="AA181" s="2" t="inlineStr"/>
+      <c r="AB181" s="2" t="inlineStr"/>
+      <c r="AC181" s="2" t="inlineStr"/>
+      <c r="AD181" s="2" t="inlineStr"/>
+      <c r="AE181" s="2" t="inlineStr"/>
+      <c r="AF181" s="2" t="inlineStr"/>
+      <c r="AG181" s="2" t="inlineStr"/>
+      <c r="AH181" s="2" t="inlineStr"/>
+      <c r="AI181" s="2" t="inlineStr"/>
+      <c r="AJ181" s="2" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>ac7634025bf34118</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>46f5fcde49f942cdafa52f104990c598da2a615146ee49a1e1afd06b01f9493b</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>69512</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J182" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K182" s="2" t="inlineStr"/>
+      <c r="L182" s="2" t="inlineStr">
+        <is>
+          <t>0.752668</t>
+        </is>
+      </c>
+      <c r="M182" s="2" t="inlineStr"/>
+      <c r="N182" s="2" t="inlineStr"/>
+      <c r="O182" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P182" s="2" t="inlineStr"/>
+      <c r="Q182" s="2" t="inlineStr">
+        <is>
+          <t>0.06226552321981427</t>
+        </is>
+      </c>
+      <c r="R182" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:07:22.423811Z</t>
+        </is>
+      </c>
+      <c r="S182" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T182" s="2" t="inlineStr"/>
+      <c r="U182" s="2" t="inlineStr"/>
+      <c r="V182" s="2" t="inlineStr"/>
+      <c r="W182" s="2" t="inlineStr"/>
+      <c r="X182" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y182" s="2" t="inlineStr"/>
+      <c r="Z182" s="2" t="inlineStr"/>
+      <c r="AA182" s="2" t="inlineStr"/>
+      <c r="AB182" s="2" t="inlineStr"/>
+      <c r="AC182" s="2" t="inlineStr"/>
+      <c r="AD182" s="2" t="inlineStr"/>
+      <c r="AE182" s="2" t="inlineStr"/>
+      <c r="AF182" s="2" t="inlineStr"/>
+      <c r="AG182" s="2" t="inlineStr"/>
+      <c r="AH182" s="2" t="inlineStr"/>
+      <c r="AI182" s="2" t="inlineStr"/>
+      <c r="AJ182" s="2" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>4de18d244398494e</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>46f5fcde49f942cdafa52f104990c598da2a615146ee49a1e1afd06b01f9493b</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>69539</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K183" s="2" t="inlineStr"/>
+      <c r="L183" s="2" t="inlineStr">
+        <is>
+          <t>0.6034</t>
+        </is>
+      </c>
+      <c r="M183" s="2" t="inlineStr"/>
+      <c r="N183" s="2" t="inlineStr"/>
+      <c r="O183" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P183" s="2" t="inlineStr"/>
+      <c r="Q183" s="2" t="inlineStr">
+        <is>
+          <t>0.05385045045045056</t>
+        </is>
+      </c>
+      <c r="R183" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:07:23.619328Z</t>
+        </is>
+      </c>
+      <c r="S183" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T183" s="2" t="inlineStr"/>
+      <c r="U183" s="2" t="inlineStr"/>
+      <c r="V183" s="2" t="inlineStr"/>
+      <c r="W183" s="2" t="inlineStr"/>
+      <c r="X183" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y183" s="2" t="inlineStr"/>
+      <c r="Z183" s="2" t="inlineStr"/>
+      <c r="AA183" s="2" t="inlineStr"/>
+      <c r="AB183" s="2" t="inlineStr"/>
+      <c r="AC183" s="2" t="inlineStr"/>
+      <c r="AD183" s="2" t="inlineStr"/>
+      <c r="AE183" s="2" t="inlineStr"/>
+      <c r="AF183" s="2" t="inlineStr"/>
+      <c r="AG183" s="2" t="inlineStr"/>
+      <c r="AH183" s="2" t="inlineStr"/>
+      <c r="AI183" s="2" t="inlineStr"/>
+      <c r="AJ183" s="2" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>cf598761acb54388</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>46f5fcde49f942cdafa52f104990c598da2a615146ee49a1e1afd06b01f9493b</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>70569</t>
+        </is>
+      </c>
+      <c r="I184" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J184" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K184" s="2" t="inlineStr"/>
+      <c r="L184" s="2" t="inlineStr">
+        <is>
+          <t>0.831719</t>
+        </is>
+      </c>
+      <c r="M184" s="2" t="inlineStr"/>
+      <c r="N184" s="2" t="inlineStr"/>
+      <c r="O184" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P184" s="2" t="inlineStr"/>
+      <c r="Q184" s="2" t="inlineStr">
+        <is>
+          <t>0.2415550655737705</t>
+        </is>
+      </c>
+      <c r="R184" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:07:29.825930Z</t>
+        </is>
+      </c>
+      <c r="S184" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T184" s="2" t="inlineStr"/>
+      <c r="U184" s="2" t="inlineStr"/>
+      <c r="V184" s="2" t="inlineStr"/>
+      <c r="W184" s="2" t="inlineStr"/>
+      <c r="X184" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y184" s="2" t="inlineStr"/>
+      <c r="Z184" s="2" t="inlineStr"/>
+      <c r="AA184" s="2" t="inlineStr"/>
+      <c r="AB184" s="2" t="inlineStr"/>
+      <c r="AC184" s="2" t="inlineStr"/>
+      <c r="AD184" s="2" t="inlineStr"/>
+      <c r="AE184" s="2" t="inlineStr"/>
+      <c r="AF184" s="2" t="inlineStr"/>
+      <c r="AG184" s="2" t="inlineStr"/>
+      <c r="AH184" s="2" t="inlineStr"/>
+      <c r="AI184" s="2" t="inlineStr"/>
+      <c r="AJ184" s="2" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>dae9c62e03804d19</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>46f5fcde49f942cdafa52f104990c598da2a615146ee49a1e1afd06b01f9493b</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t>69871</t>
+        </is>
+      </c>
+      <c r="I185" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J185" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K185" s="2" t="inlineStr"/>
+      <c r="L185" s="2" t="inlineStr">
+        <is>
+          <t>0.56154</t>
+        </is>
+      </c>
+      <c r="M185" s="2" t="inlineStr"/>
+      <c r="N185" s="2" t="inlineStr"/>
+      <c r="O185" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P185" s="2" t="inlineStr"/>
+      <c r="Q185" s="2" t="inlineStr">
+        <is>
+          <t>0.12101136563876658</t>
+        </is>
+      </c>
+      <c r="R185" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:07:30.423139Z</t>
+        </is>
+      </c>
+      <c r="S185" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T185" s="2" t="inlineStr"/>
+      <c r="U185" s="2" t="inlineStr"/>
+      <c r="V185" s="2" t="inlineStr"/>
+      <c r="W185" s="2" t="inlineStr"/>
+      <c r="X185" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y185" s="2" t="inlineStr"/>
+      <c r="Z185" s="2" t="inlineStr"/>
+      <c r="AA185" s="2" t="inlineStr"/>
+      <c r="AB185" s="2" t="inlineStr"/>
+      <c r="AC185" s="2" t="inlineStr"/>
+      <c r="AD185" s="2" t="inlineStr"/>
+      <c r="AE185" s="2" t="inlineStr"/>
+      <c r="AF185" s="2" t="inlineStr"/>
+      <c r="AG185" s="2" t="inlineStr"/>
+      <c r="AH185" s="2" t="inlineStr"/>
+      <c r="AI185" s="2" t="inlineStr"/>
+      <c r="AJ185" s="2" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>e0be7eaa38d94486</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>46f5fcde49f942cdafa52f104990c598da2a615146ee49a1e1afd06b01f9493b</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>69931</t>
+        </is>
+      </c>
+      <c r="I186" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J186" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K186" s="2" t="inlineStr"/>
+      <c r="L186" s="2" t="inlineStr">
+        <is>
+          <t>0.577308</t>
+        </is>
+      </c>
+      <c r="M186" s="2" t="inlineStr"/>
+      <c r="N186" s="2" t="inlineStr"/>
+      <c r="O186" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="P186" s="2" t="inlineStr"/>
+      <c r="Q186" s="2" t="inlineStr">
+        <is>
+          <t>0.07730800000000004</t>
+        </is>
+      </c>
+      <c r="R186" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:07:31.510563Z</t>
+        </is>
+      </c>
+      <c r="S186" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:30:00Z</t>
+        </is>
+      </c>
+      <c r="T186" s="2" t="inlineStr"/>
+      <c r="U186" s="2" t="inlineStr"/>
+      <c r="V186" s="2" t="inlineStr"/>
+      <c r="W186" s="2" t="inlineStr"/>
+      <c r="X186" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y186" s="2" t="inlineStr"/>
+      <c r="Z186" s="2" t="inlineStr"/>
+      <c r="AA186" s="2" t="inlineStr"/>
+      <c r="AB186" s="2" t="inlineStr"/>
+      <c r="AC186" s="2" t="inlineStr"/>
+      <c r="AD186" s="2" t="inlineStr"/>
+      <c r="AE186" s="2" t="inlineStr"/>
+      <c r="AF186" s="2" t="inlineStr"/>
+      <c r="AG186" s="2" t="inlineStr"/>
+      <c r="AH186" s="2" t="inlineStr"/>
+      <c r="AI186" s="2" t="inlineStr"/>
+      <c r="AJ186" s="2" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>b258e8fb89934a80</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>46f5fcde49f942cdafa52f104990c598da2a615146ee49a1e1afd06b01f9493b</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>70045</t>
+        </is>
+      </c>
+      <c r="I187" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J187" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K187" s="2" t="inlineStr"/>
+      <c r="L187" s="2" t="inlineStr">
+        <is>
+          <t>0.606257</t>
+        </is>
+      </c>
+      <c r="M187" s="2" t="inlineStr"/>
+      <c r="N187" s="2" t="inlineStr"/>
+      <c r="O187" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P187" s="2" t="inlineStr"/>
+      <c r="Q187" s="2" t="inlineStr">
+        <is>
+          <t>0.04678563436123351</t>
+        </is>
+      </c>
+      <c r="R187" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:07:36.139635Z</t>
+        </is>
+      </c>
+      <c r="S187" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="T187" s="2" t="inlineStr"/>
+      <c r="U187" s="2" t="inlineStr"/>
+      <c r="V187" s="2" t="inlineStr"/>
+      <c r="W187" s="2" t="inlineStr"/>
+      <c r="X187" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y187" s="2" t="inlineStr"/>
+      <c r="Z187" s="2" t="inlineStr"/>
+      <c r="AA187" s="2" t="inlineStr"/>
+      <c r="AB187" s="2" t="inlineStr"/>
+      <c r="AC187" s="2" t="inlineStr"/>
+      <c r="AD187" s="2" t="inlineStr"/>
+      <c r="AE187" s="2" t="inlineStr"/>
+      <c r="AF187" s="2" t="inlineStr"/>
+      <c r="AG187" s="2" t="inlineStr"/>
+      <c r="AH187" s="2" t="inlineStr"/>
+      <c r="AI187" s="2" t="inlineStr"/>
+      <c r="AJ187" s="2" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>1ba7c8921a7d4eaa</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>46f5fcde49f942cdafa52f104990c598da2a615146ee49a1e1afd06b01f9493b</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H188" s="2" t="inlineStr">
+        <is>
+          <t>70301</t>
+        </is>
+      </c>
+      <c r="I188" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J188" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K188" s="2" t="inlineStr"/>
+      <c r="L188" s="2" t="inlineStr">
+        <is>
+          <t>0.658341</t>
+        </is>
+      </c>
+      <c r="M188" s="2" t="inlineStr"/>
+      <c r="N188" s="2" t="inlineStr"/>
+      <c r="O188" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="P188" s="2" t="inlineStr"/>
+      <c r="Q188" s="2" t="inlineStr">
+        <is>
+          <t>0.15834099999999995</t>
+        </is>
+      </c>
+      <c r="R188" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:07:36.649028Z</t>
+        </is>
+      </c>
+      <c r="S188" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T188" s="2" t="inlineStr"/>
+      <c r="U188" s="2" t="inlineStr"/>
+      <c r="V188" s="2" t="inlineStr"/>
+      <c r="W188" s="2" t="inlineStr"/>
+      <c r="X188" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y188" s="2" t="inlineStr"/>
+      <c r="Z188" s="2" t="inlineStr"/>
+      <c r="AA188" s="2" t="inlineStr"/>
+      <c r="AB188" s="2" t="inlineStr"/>
+      <c r="AC188" s="2" t="inlineStr"/>
+      <c r="AD188" s="2" t="inlineStr"/>
+      <c r="AE188" s="2" t="inlineStr"/>
+      <c r="AF188" s="2" t="inlineStr"/>
+      <c r="AG188" s="2" t="inlineStr"/>
+      <c r="AH188" s="2" t="inlineStr"/>
+      <c r="AI188" s="2" t="inlineStr"/>
+      <c r="AJ188" s="2" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>a8ed7c7ea88f4069</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>46f5fcde49f942cdafa52f104990c598da2a615146ee49a1e1afd06b01f9493b</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H189" s="2" t="inlineStr">
+        <is>
+          <t>70379</t>
+        </is>
+      </c>
+      <c r="I189" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J189" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K189" s="2" t="inlineStr"/>
+      <c r="L189" s="2" t="inlineStr">
+        <is>
+          <t>0.565806</t>
+        </is>
+      </c>
+      <c r="M189" s="2" t="inlineStr"/>
+      <c r="N189" s="2" t="inlineStr"/>
+      <c r="O189" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P189" s="2" t="inlineStr"/>
+      <c r="Q189" s="2" t="inlineStr">
+        <is>
+          <t>0.11535554954954952</t>
+        </is>
+      </c>
+      <c r="R189" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:07:39.444493Z</t>
+        </is>
+      </c>
+      <c r="S189" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="T189" s="2" t="inlineStr"/>
+      <c r="U189" s="2" t="inlineStr"/>
+      <c r="V189" s="2" t="inlineStr"/>
+      <c r="W189" s="2" t="inlineStr"/>
+      <c r="X189" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y189" s="2" t="inlineStr"/>
+      <c r="Z189" s="2" t="inlineStr"/>
+      <c r="AA189" s="2" t="inlineStr"/>
+      <c r="AB189" s="2" t="inlineStr"/>
+      <c r="AC189" s="2" t="inlineStr"/>
+      <c r="AD189" s="2" t="inlineStr"/>
+      <c r="AE189" s="2" t="inlineStr"/>
+      <c r="AF189" s="2" t="inlineStr"/>
+      <c r="AG189" s="2" t="inlineStr"/>
+      <c r="AH189" s="2" t="inlineStr"/>
+      <c r="AI189" s="2" t="inlineStr"/>
+      <c r="AJ189" s="2" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>191fa85c08594c2d</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>46f5fcde49f942cdafa52f104990c598da2a615146ee49a1e1afd06b01f9493b</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H190" s="2" t="inlineStr">
+        <is>
+          <t>70453</t>
+        </is>
+      </c>
+      <c r="I190" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J190" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K190" s="2" t="inlineStr"/>
+      <c r="L190" s="2" t="inlineStr">
+        <is>
+          <t>0.589642</t>
+        </is>
+      </c>
+      <c r="M190" s="2" t="inlineStr"/>
+      <c r="N190" s="2" t="inlineStr"/>
+      <c r="O190" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P190" s="2" t="inlineStr"/>
+      <c r="Q190" s="2" t="inlineStr">
+        <is>
+          <t>0.018826549356223188</t>
+        </is>
+      </c>
+      <c r="R190" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:07:41.094060Z</t>
+        </is>
+      </c>
+      <c r="S190" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="T190" s="2" t="inlineStr"/>
+      <c r="U190" s="2" t="inlineStr"/>
+      <c r="V190" s="2" t="inlineStr"/>
+      <c r="W190" s="2" t="inlineStr"/>
+      <c r="X190" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y190" s="2" t="inlineStr"/>
+      <c r="Z190" s="2" t="inlineStr"/>
+      <c r="AA190" s="2" t="inlineStr"/>
+      <c r="AB190" s="2" t="inlineStr"/>
+      <c r="AC190" s="2" t="inlineStr"/>
+      <c r="AD190" s="2" t="inlineStr"/>
+      <c r="AE190" s="2" t="inlineStr"/>
+      <c r="AF190" s="2" t="inlineStr"/>
+      <c r="AG190" s="2" t="inlineStr"/>
+      <c r="AH190" s="2" t="inlineStr"/>
+      <c r="AI190" s="2" t="inlineStr"/>
+      <c r="AJ190" s="2" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>8215d86121cf4666</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H191" s="2" t="inlineStr">
+        <is>
+          <t>68509</t>
+        </is>
+      </c>
+      <c r="I191" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J191" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K191" s="2" t="inlineStr"/>
+      <c r="L191" s="2" t="inlineStr">
+        <is>
+          <t>0.631258</t>
+        </is>
+      </c>
+      <c r="M191" s="2" t="inlineStr"/>
+      <c r="N191" s="2" t="inlineStr"/>
+      <c r="O191" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P191" s="2" t="inlineStr"/>
+      <c r="Q191" s="2" t="inlineStr">
+        <is>
+          <t>0.051426067226890804</t>
+        </is>
+      </c>
+      <c r="R191" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:26:42.602034Z</t>
+        </is>
+      </c>
+      <c r="S191" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="T191" s="2" t="inlineStr"/>
+      <c r="U191" s="2" t="inlineStr"/>
+      <c r="V191" s="2" t="inlineStr"/>
+      <c r="W191" s="2" t="inlineStr"/>
+      <c r="X191" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y191" s="2" t="inlineStr"/>
+      <c r="Z191" s="2" t="inlineStr"/>
+      <c r="AA191" s="2" t="inlineStr"/>
+      <c r="AB191" s="2" t="inlineStr"/>
+      <c r="AC191" s="2" t="inlineStr"/>
+      <c r="AD191" s="2" t="inlineStr"/>
+      <c r="AE191" s="2" t="inlineStr"/>
+      <c r="AF191" s="2" t="inlineStr"/>
+      <c r="AG191" s="2" t="inlineStr"/>
+      <c r="AH191" s="2" t="inlineStr"/>
+      <c r="AI191" s="2" t="inlineStr"/>
+      <c r="AJ191" s="2" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>9d481acbde9d40fd</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H192" s="2" t="inlineStr">
+        <is>
+          <t>68690</t>
+        </is>
+      </c>
+      <c r="I192" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J192" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K192" s="2" t="inlineStr"/>
+      <c r="L192" s="2" t="inlineStr">
+        <is>
+          <t>0.55095</t>
+        </is>
+      </c>
+      <c r="M192" s="2" t="inlineStr"/>
+      <c r="N192" s="2" t="inlineStr"/>
+      <c r="O192" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P192" s="2" t="inlineStr"/>
+      <c r="Q192" s="2" t="inlineStr">
+        <is>
+          <t>0.011779493087557658</t>
+        </is>
+      </c>
+      <c r="R192" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:26:46.197810Z</t>
+        </is>
+      </c>
+      <c r="S192" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T192" s="2" t="inlineStr"/>
+      <c r="U192" s="2" t="inlineStr"/>
+      <c r="V192" s="2" t="inlineStr"/>
+      <c r="W192" s="2" t="inlineStr"/>
+      <c r="X192" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y192" s="2" t="inlineStr"/>
+      <c r="Z192" s="2" t="inlineStr"/>
+      <c r="AA192" s="2" t="inlineStr"/>
+      <c r="AB192" s="2" t="inlineStr"/>
+      <c r="AC192" s="2" t="inlineStr"/>
+      <c r="AD192" s="2" t="inlineStr"/>
+      <c r="AE192" s="2" t="inlineStr"/>
+      <c r="AF192" s="2" t="inlineStr"/>
+      <c r="AG192" s="2" t="inlineStr"/>
+      <c r="AH192" s="2" t="inlineStr"/>
+      <c r="AI192" s="2" t="inlineStr"/>
+      <c r="AJ192" s="2" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>18d4f088314146dc</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H193" s="2" t="inlineStr">
+        <is>
+          <t>69143</t>
+        </is>
+      </c>
+      <c r="I193" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J193" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K193" s="2" t="inlineStr"/>
+      <c r="L193" s="2" t="inlineStr">
+        <is>
+          <t>0.624122</t>
+        </is>
+      </c>
+      <c r="M193" s="2" t="inlineStr"/>
+      <c r="N193" s="2" t="inlineStr"/>
+      <c r="O193" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P193" s="2" t="inlineStr"/>
+      <c r="Q193" s="2" t="inlineStr">
+        <is>
+          <t>0.004350136882129263</t>
+        </is>
+      </c>
+      <c r="R193" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:26:50.250119Z</t>
+        </is>
+      </c>
+      <c r="S193" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T193" s="2" t="inlineStr"/>
+      <c r="U193" s="2" t="inlineStr"/>
+      <c r="V193" s="2" t="inlineStr"/>
+      <c r="W193" s="2" t="inlineStr"/>
+      <c r="X193" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y193" s="2" t="inlineStr"/>
+      <c r="Z193" s="2" t="inlineStr"/>
+      <c r="AA193" s="2" t="inlineStr"/>
+      <c r="AB193" s="2" t="inlineStr"/>
+      <c r="AC193" s="2" t="inlineStr"/>
+      <c r="AD193" s="2" t="inlineStr"/>
+      <c r="AE193" s="2" t="inlineStr"/>
+      <c r="AF193" s="2" t="inlineStr"/>
+      <c r="AG193" s="2" t="inlineStr"/>
+      <c r="AH193" s="2" t="inlineStr"/>
+      <c r="AI193" s="2" t="inlineStr"/>
+      <c r="AJ193" s="2" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>f4e1b239e02a4e53</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H194" s="2" t="inlineStr">
+        <is>
+          <t>69144</t>
+        </is>
+      </c>
+      <c r="I194" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J194" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K194" s="2" t="inlineStr"/>
+      <c r="L194" s="2" t="inlineStr">
+        <is>
+          <t>0.5918</t>
+        </is>
+      </c>
+      <c r="M194" s="2" t="inlineStr"/>
+      <c r="N194" s="2" t="inlineStr"/>
+      <c r="O194" s="2" t="inlineStr">
+        <is>
+          <t>0.4608294930875576</t>
+        </is>
+      </c>
+      <c r="P194" s="2" t="inlineStr"/>
+      <c r="Q194" s="2" t="inlineStr">
+        <is>
+          <t>0.13097050691244239</t>
+        </is>
+      </c>
+      <c r="R194" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:26:50.876512Z</t>
+        </is>
+      </c>
+      <c r="S194" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T194" s="2" t="inlineStr"/>
+      <c r="U194" s="2" t="inlineStr"/>
+      <c r="V194" s="2" t="inlineStr"/>
+      <c r="W194" s="2" t="inlineStr"/>
+      <c r="X194" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y194" s="2" t="inlineStr"/>
+      <c r="Z194" s="2" t="inlineStr"/>
+      <c r="AA194" s="2" t="inlineStr"/>
+      <c r="AB194" s="2" t="inlineStr"/>
+      <c r="AC194" s="2" t="inlineStr"/>
+      <c r="AD194" s="2" t="inlineStr"/>
+      <c r="AE194" s="2" t="inlineStr"/>
+      <c r="AF194" s="2" t="inlineStr"/>
+      <c r="AG194" s="2" t="inlineStr"/>
+      <c r="AH194" s="2" t="inlineStr"/>
+      <c r="AI194" s="2" t="inlineStr"/>
+      <c r="AJ194" s="2" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>0fe66f949d634175</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H195" s="2" t="inlineStr">
+        <is>
+          <t>69233</t>
+        </is>
+      </c>
+      <c r="I195" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J195" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K195" s="2" t="inlineStr"/>
+      <c r="L195" s="2" t="inlineStr">
+        <is>
+          <t>0.572751</t>
+        </is>
+      </c>
+      <c r="M195" s="2" t="inlineStr"/>
+      <c r="N195" s="2" t="inlineStr"/>
+      <c r="O195" s="2" t="inlineStr">
+        <is>
+          <t>0.33003300330033003</t>
+        </is>
+      </c>
+      <c r="P195" s="2" t="inlineStr"/>
+      <c r="Q195" s="2" t="inlineStr">
+        <is>
+          <t>0.24271799669966998</t>
+        </is>
+      </c>
+      <c r="R195" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:26:52.692865Z</t>
+        </is>
+      </c>
+      <c r="S195" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T195" s="2" t="inlineStr"/>
+      <c r="U195" s="2" t="inlineStr"/>
+      <c r="V195" s="2" t="inlineStr"/>
+      <c r="W195" s="2" t="inlineStr"/>
+      <c r="X195" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y195" s="2" t="inlineStr"/>
+      <c r="Z195" s="2" t="inlineStr"/>
+      <c r="AA195" s="2" t="inlineStr"/>
+      <c r="AB195" s="2" t="inlineStr"/>
+      <c r="AC195" s="2" t="inlineStr"/>
+      <c r="AD195" s="2" t="inlineStr"/>
+      <c r="AE195" s="2" t="inlineStr"/>
+      <c r="AF195" s="2" t="inlineStr"/>
+      <c r="AG195" s="2" t="inlineStr"/>
+      <c r="AH195" s="2" t="inlineStr"/>
+      <c r="AI195" s="2" t="inlineStr"/>
+      <c r="AJ195" s="2" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>085f90d867734d67</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H196" s="2" t="inlineStr">
+        <is>
+          <t>69273</t>
+        </is>
+      </c>
+      <c r="I196" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J196" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K196" s="2" t="inlineStr"/>
+      <c r="L196" s="2" t="inlineStr">
+        <is>
+          <t>0.604693</t>
+        </is>
+      </c>
+      <c r="M196" s="2" t="inlineStr"/>
+      <c r="N196" s="2" t="inlineStr"/>
+      <c r="O196" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P196" s="2" t="inlineStr"/>
+      <c r="Q196" s="2" t="inlineStr">
+        <is>
+          <t>0.07417656807511741</t>
+        </is>
+      </c>
+      <c r="R196" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:26:53.902256Z</t>
+        </is>
+      </c>
+      <c r="S196" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="T196" s="2" t="inlineStr"/>
+      <c r="U196" s="2" t="inlineStr"/>
+      <c r="V196" s="2" t="inlineStr"/>
+      <c r="W196" s="2" t="inlineStr"/>
+      <c r="X196" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y196" s="2" t="inlineStr"/>
+      <c r="Z196" s="2" t="inlineStr"/>
+      <c r="AA196" s="2" t="inlineStr"/>
+      <c r="AB196" s="2" t="inlineStr"/>
+      <c r="AC196" s="2" t="inlineStr"/>
+      <c r="AD196" s="2" t="inlineStr"/>
+      <c r="AE196" s="2" t="inlineStr"/>
+      <c r="AF196" s="2" t="inlineStr"/>
+      <c r="AG196" s="2" t="inlineStr"/>
+      <c r="AH196" s="2" t="inlineStr"/>
+      <c r="AI196" s="2" t="inlineStr"/>
+      <c r="AJ196" s="2" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>b8a457c931284380</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H197" s="2" t="inlineStr">
+        <is>
+          <t>69507</t>
+        </is>
+      </c>
+      <c r="I197" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J197" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K197" s="2" t="inlineStr"/>
+      <c r="L197" s="2" t="inlineStr">
+        <is>
+          <t>0.638652</t>
+        </is>
+      </c>
+      <c r="M197" s="2" t="inlineStr"/>
+      <c r="N197" s="2" t="inlineStr"/>
+      <c r="O197" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P197" s="2" t="inlineStr"/>
+      <c r="Q197" s="2" t="inlineStr">
+        <is>
+          <t>0.058820067226890815</t>
+        </is>
+      </c>
+      <c r="R197" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:26:56.319431Z</t>
+        </is>
+      </c>
+      <c r="S197" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="T197" s="2" t="inlineStr"/>
+      <c r="U197" s="2" t="inlineStr"/>
+      <c r="V197" s="2" t="inlineStr"/>
+      <c r="W197" s="2" t="inlineStr"/>
+      <c r="X197" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y197" s="2" t="inlineStr"/>
+      <c r="Z197" s="2" t="inlineStr"/>
+      <c r="AA197" s="2" t="inlineStr"/>
+      <c r="AB197" s="2" t="inlineStr"/>
+      <c r="AC197" s="2" t="inlineStr"/>
+      <c r="AD197" s="2" t="inlineStr"/>
+      <c r="AE197" s="2" t="inlineStr"/>
+      <c r="AF197" s="2" t="inlineStr"/>
+      <c r="AG197" s="2" t="inlineStr"/>
+      <c r="AH197" s="2" t="inlineStr"/>
+      <c r="AI197" s="2" t="inlineStr"/>
+      <c r="AJ197" s="2" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>ea1abc1d234c4f3f</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H198" s="2" t="inlineStr">
+        <is>
+          <t>69511</t>
+        </is>
+      </c>
+      <c r="I198" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J198" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K198" s="2" t="inlineStr"/>
+      <c r="L198" s="2" t="inlineStr">
+        <is>
+          <t>0.699121</t>
+        </is>
+      </c>
+      <c r="M198" s="2" t="inlineStr"/>
+      <c r="N198" s="2" t="inlineStr"/>
+      <c r="O198" s="2" t="inlineStr">
+        <is>
+          <t>0.6503496503496503</t>
+        </is>
+      </c>
+      <c r="P198" s="2" t="inlineStr"/>
+      <c r="Q198" s="2" t="inlineStr">
+        <is>
+          <t>0.04877134965034968</t>
+        </is>
+      </c>
+      <c r="R198" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:26:56.857793Z</t>
+        </is>
+      </c>
+      <c r="S198" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T198" s="2" t="inlineStr"/>
+      <c r="U198" s="2" t="inlineStr"/>
+      <c r="V198" s="2" t="inlineStr"/>
+      <c r="W198" s="2" t="inlineStr"/>
+      <c r="X198" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y198" s="2" t="inlineStr"/>
+      <c r="Z198" s="2" t="inlineStr"/>
+      <c r="AA198" s="2" t="inlineStr"/>
+      <c r="AB198" s="2" t="inlineStr"/>
+      <c r="AC198" s="2" t="inlineStr"/>
+      <c r="AD198" s="2" t="inlineStr"/>
+      <c r="AE198" s="2" t="inlineStr"/>
+      <c r="AF198" s="2" t="inlineStr"/>
+      <c r="AG198" s="2" t="inlineStr"/>
+      <c r="AH198" s="2" t="inlineStr"/>
+      <c r="AI198" s="2" t="inlineStr"/>
+      <c r="AJ198" s="2" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>d6a2a67c33464736</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H199" s="2" t="inlineStr">
+        <is>
+          <t>69512</t>
+        </is>
+      </c>
+      <c r="I199" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J199" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K199" s="2" t="inlineStr"/>
+      <c r="L199" s="2" t="inlineStr">
+        <is>
+          <t>0.752668</t>
+        </is>
+      </c>
+      <c r="M199" s="2" t="inlineStr"/>
+      <c r="N199" s="2" t="inlineStr"/>
+      <c r="O199" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P199" s="2" t="inlineStr"/>
+      <c r="Q199" s="2" t="inlineStr">
+        <is>
+          <t>0.06226552321981427</t>
+        </is>
+      </c>
+      <c r="R199" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:26:57.357254Z</t>
+        </is>
+      </c>
+      <c r="S199" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T199" s="2" t="inlineStr"/>
+      <c r="U199" s="2" t="inlineStr"/>
+      <c r="V199" s="2" t="inlineStr"/>
+      <c r="W199" s="2" t="inlineStr"/>
+      <c r="X199" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y199" s="2" t="inlineStr"/>
+      <c r="Z199" s="2" t="inlineStr"/>
+      <c r="AA199" s="2" t="inlineStr"/>
+      <c r="AB199" s="2" t="inlineStr"/>
+      <c r="AC199" s="2" t="inlineStr"/>
+      <c r="AD199" s="2" t="inlineStr"/>
+      <c r="AE199" s="2" t="inlineStr"/>
+      <c r="AF199" s="2" t="inlineStr"/>
+      <c r="AG199" s="2" t="inlineStr"/>
+      <c r="AH199" s="2" t="inlineStr"/>
+      <c r="AI199" s="2" t="inlineStr"/>
+      <c r="AJ199" s="2" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>226097462a544f1f</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H200" s="2" t="inlineStr">
+        <is>
+          <t>69539</t>
+        </is>
+      </c>
+      <c r="I200" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J200" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K200" s="2" t="inlineStr"/>
+      <c r="L200" s="2" t="inlineStr">
+        <is>
+          <t>0.6034</t>
+        </is>
+      </c>
+      <c r="M200" s="2" t="inlineStr"/>
+      <c r="N200" s="2" t="inlineStr"/>
+      <c r="O200" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P200" s="2" t="inlineStr"/>
+      <c r="Q200" s="2" t="inlineStr">
+        <is>
+          <t>0.05385045045045056</t>
+        </is>
+      </c>
+      <c r="R200" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:26:58.482445Z</t>
+        </is>
+      </c>
+      <c r="S200" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T200" s="2" t="inlineStr"/>
+      <c r="U200" s="2" t="inlineStr"/>
+      <c r="V200" s="2" t="inlineStr"/>
+      <c r="W200" s="2" t="inlineStr"/>
+      <c r="X200" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y200" s="2" t="inlineStr"/>
+      <c r="Z200" s="2" t="inlineStr"/>
+      <c r="AA200" s="2" t="inlineStr"/>
+      <c r="AB200" s="2" t="inlineStr"/>
+      <c r="AC200" s="2" t="inlineStr"/>
+      <c r="AD200" s="2" t="inlineStr"/>
+      <c r="AE200" s="2" t="inlineStr"/>
+      <c r="AF200" s="2" t="inlineStr"/>
+      <c r="AG200" s="2" t="inlineStr"/>
+      <c r="AH200" s="2" t="inlineStr"/>
+      <c r="AI200" s="2" t="inlineStr"/>
+      <c r="AJ200" s="2" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>f3a2fbc3f8804bbd</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G201" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H201" s="2" t="inlineStr">
+        <is>
+          <t>70569</t>
+        </is>
+      </c>
+      <c r="I201" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J201" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K201" s="2" t="inlineStr"/>
+      <c r="L201" s="2" t="inlineStr">
+        <is>
+          <t>0.831719</t>
+        </is>
+      </c>
+      <c r="M201" s="2" t="inlineStr"/>
+      <c r="N201" s="2" t="inlineStr"/>
+      <c r="O201" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P201" s="2" t="inlineStr"/>
+      <c r="Q201" s="2" t="inlineStr">
+        <is>
+          <t>0.2415550655737705</t>
+        </is>
+      </c>
+      <c r="R201" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:27:04.870108Z</t>
+        </is>
+      </c>
+      <c r="S201" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T201" s="2" t="inlineStr"/>
+      <c r="U201" s="2" t="inlineStr"/>
+      <c r="V201" s="2" t="inlineStr"/>
+      <c r="W201" s="2" t="inlineStr"/>
+      <c r="X201" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y201" s="2" t="inlineStr"/>
+      <c r="Z201" s="2" t="inlineStr"/>
+      <c r="AA201" s="2" t="inlineStr"/>
+      <c r="AB201" s="2" t="inlineStr"/>
+      <c r="AC201" s="2" t="inlineStr"/>
+      <c r="AD201" s="2" t="inlineStr"/>
+      <c r="AE201" s="2" t="inlineStr"/>
+      <c r="AF201" s="2" t="inlineStr"/>
+      <c r="AG201" s="2" t="inlineStr"/>
+      <c r="AH201" s="2" t="inlineStr"/>
+      <c r="AI201" s="2" t="inlineStr"/>
+      <c r="AJ201" s="2" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>2a7f57d6296e46ba</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H202" s="2" t="inlineStr">
+        <is>
+          <t>69871</t>
+        </is>
+      </c>
+      <c r="I202" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J202" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K202" s="2" t="inlineStr"/>
+      <c r="L202" s="2" t="inlineStr">
+        <is>
+          <t>0.56154</t>
+        </is>
+      </c>
+      <c r="M202" s="2" t="inlineStr"/>
+      <c r="N202" s="2" t="inlineStr"/>
+      <c r="O202" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P202" s="2" t="inlineStr"/>
+      <c r="Q202" s="2" t="inlineStr">
+        <is>
+          <t>0.12101136563876658</t>
+        </is>
+      </c>
+      <c r="R202" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:27:05.368556Z</t>
+        </is>
+      </c>
+      <c r="S202" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T202" s="2" t="inlineStr"/>
+      <c r="U202" s="2" t="inlineStr"/>
+      <c r="V202" s="2" t="inlineStr"/>
+      <c r="W202" s="2" t="inlineStr"/>
+      <c r="X202" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y202" s="2" t="inlineStr"/>
+      <c r="Z202" s="2" t="inlineStr"/>
+      <c r="AA202" s="2" t="inlineStr"/>
+      <c r="AB202" s="2" t="inlineStr"/>
+      <c r="AC202" s="2" t="inlineStr"/>
+      <c r="AD202" s="2" t="inlineStr"/>
+      <c r="AE202" s="2" t="inlineStr"/>
+      <c r="AF202" s="2" t="inlineStr"/>
+      <c r="AG202" s="2" t="inlineStr"/>
+      <c r="AH202" s="2" t="inlineStr"/>
+      <c r="AI202" s="2" t="inlineStr"/>
+      <c r="AJ202" s="2" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>59124a4a296c4719</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H203" s="2" t="inlineStr">
+        <is>
+          <t>69931</t>
+        </is>
+      </c>
+      <c r="I203" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J203" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K203" s="2" t="inlineStr"/>
+      <c r="L203" s="2" t="inlineStr">
+        <is>
+          <t>0.577308</t>
+        </is>
+      </c>
+      <c r="M203" s="2" t="inlineStr"/>
+      <c r="N203" s="2" t="inlineStr"/>
+      <c r="O203" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="P203" s="2" t="inlineStr"/>
+      <c r="Q203" s="2" t="inlineStr">
+        <is>
+          <t>0.07730800000000004</t>
+        </is>
+      </c>
+      <c r="R203" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:27:06.503337Z</t>
+        </is>
+      </c>
+      <c r="S203" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:30:00Z</t>
+        </is>
+      </c>
+      <c r="T203" s="2" t="inlineStr"/>
+      <c r="U203" s="2" t="inlineStr"/>
+      <c r="V203" s="2" t="inlineStr"/>
+      <c r="W203" s="2" t="inlineStr"/>
+      <c r="X203" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y203" s="2" t="inlineStr"/>
+      <c r="Z203" s="2" t="inlineStr"/>
+      <c r="AA203" s="2" t="inlineStr"/>
+      <c r="AB203" s="2" t="inlineStr"/>
+      <c r="AC203" s="2" t="inlineStr"/>
+      <c r="AD203" s="2" t="inlineStr"/>
+      <c r="AE203" s="2" t="inlineStr"/>
+      <c r="AF203" s="2" t="inlineStr"/>
+      <c r="AG203" s="2" t="inlineStr"/>
+      <c r="AH203" s="2" t="inlineStr"/>
+      <c r="AI203" s="2" t="inlineStr"/>
+      <c r="AJ203" s="2" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>ceefab5f614c4711</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H204" s="2" t="inlineStr">
+        <is>
+          <t>70045</t>
+        </is>
+      </c>
+      <c r="I204" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J204" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K204" s="2" t="inlineStr"/>
+      <c r="L204" s="2" t="inlineStr">
+        <is>
+          <t>0.606257</t>
+        </is>
+      </c>
+      <c r="M204" s="2" t="inlineStr"/>
+      <c r="N204" s="2" t="inlineStr"/>
+      <c r="O204" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P204" s="2" t="inlineStr"/>
+      <c r="Q204" s="2" t="inlineStr">
+        <is>
+          <t>0.04678563436123351</t>
+        </is>
+      </c>
+      <c r="R204" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:27:11.034551Z</t>
+        </is>
+      </c>
+      <c r="S204" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="T204" s="2" t="inlineStr"/>
+      <c r="U204" s="2" t="inlineStr"/>
+      <c r="V204" s="2" t="inlineStr"/>
+      <c r="W204" s="2" t="inlineStr"/>
+      <c r="X204" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y204" s="2" t="inlineStr"/>
+      <c r="Z204" s="2" t="inlineStr"/>
+      <c r="AA204" s="2" t="inlineStr"/>
+      <c r="AB204" s="2" t="inlineStr"/>
+      <c r="AC204" s="2" t="inlineStr"/>
+      <c r="AD204" s="2" t="inlineStr"/>
+      <c r="AE204" s="2" t="inlineStr"/>
+      <c r="AF204" s="2" t="inlineStr"/>
+      <c r="AG204" s="2" t="inlineStr"/>
+      <c r="AH204" s="2" t="inlineStr"/>
+      <c r="AI204" s="2" t="inlineStr"/>
+      <c r="AJ204" s="2" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>856a3581ae6344cb</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H205" s="2" t="inlineStr">
+        <is>
+          <t>70301</t>
+        </is>
+      </c>
+      <c r="I205" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J205" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K205" s="2" t="inlineStr"/>
+      <c r="L205" s="2" t="inlineStr">
+        <is>
+          <t>0.658341</t>
+        </is>
+      </c>
+      <c r="M205" s="2" t="inlineStr"/>
+      <c r="N205" s="2" t="inlineStr"/>
+      <c r="O205" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="P205" s="2" t="inlineStr"/>
+      <c r="Q205" s="2" t="inlineStr">
+        <is>
+          <t>0.15834099999999995</t>
+        </is>
+      </c>
+      <c r="R205" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:27:11.579319Z</t>
+        </is>
+      </c>
+      <c r="S205" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T205" s="2" t="inlineStr"/>
+      <c r="U205" s="2" t="inlineStr"/>
+      <c r="V205" s="2" t="inlineStr"/>
+      <c r="W205" s="2" t="inlineStr"/>
+      <c r="X205" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y205" s="2" t="inlineStr"/>
+      <c r="Z205" s="2" t="inlineStr"/>
+      <c r="AA205" s="2" t="inlineStr"/>
+      <c r="AB205" s="2" t="inlineStr"/>
+      <c r="AC205" s="2" t="inlineStr"/>
+      <c r="AD205" s="2" t="inlineStr"/>
+      <c r="AE205" s="2" t="inlineStr"/>
+      <c r="AF205" s="2" t="inlineStr"/>
+      <c r="AG205" s="2" t="inlineStr"/>
+      <c r="AH205" s="2" t="inlineStr"/>
+      <c r="AI205" s="2" t="inlineStr"/>
+      <c r="AJ205" s="2" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>89ef0d59d6d34b84</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H206" s="2" t="inlineStr">
+        <is>
+          <t>70379</t>
+        </is>
+      </c>
+      <c r="I206" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J206" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K206" s="2" t="inlineStr"/>
+      <c r="L206" s="2" t="inlineStr">
+        <is>
+          <t>0.565806</t>
+        </is>
+      </c>
+      <c r="M206" s="2" t="inlineStr"/>
+      <c r="N206" s="2" t="inlineStr"/>
+      <c r="O206" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P206" s="2" t="inlineStr"/>
+      <c r="Q206" s="2" t="inlineStr">
+        <is>
+          <t>0.11535554954954952</t>
+        </is>
+      </c>
+      <c r="R206" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:27:14.606628Z</t>
+        </is>
+      </c>
+      <c r="S206" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="T206" s="2" t="inlineStr"/>
+      <c r="U206" s="2" t="inlineStr"/>
+      <c r="V206" s="2" t="inlineStr"/>
+      <c r="W206" s="2" t="inlineStr"/>
+      <c r="X206" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y206" s="2" t="inlineStr"/>
+      <c r="Z206" s="2" t="inlineStr"/>
+      <c r="AA206" s="2" t="inlineStr"/>
+      <c r="AB206" s="2" t="inlineStr"/>
+      <c r="AC206" s="2" t="inlineStr"/>
+      <c r="AD206" s="2" t="inlineStr"/>
+      <c r="AE206" s="2" t="inlineStr"/>
+      <c r="AF206" s="2" t="inlineStr"/>
+      <c r="AG206" s="2" t="inlineStr"/>
+      <c r="AH206" s="2" t="inlineStr"/>
+      <c r="AI206" s="2" t="inlineStr"/>
+      <c r="AJ206" s="2" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>eb874717f45442a1</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H207" s="2" t="inlineStr">
+        <is>
+          <t>70453</t>
+        </is>
+      </c>
+      <c r="I207" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J207" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K207" s="2" t="inlineStr"/>
+      <c r="L207" s="2" t="inlineStr">
+        <is>
+          <t>0.589642</t>
+        </is>
+      </c>
+      <c r="M207" s="2" t="inlineStr"/>
+      <c r="N207" s="2" t="inlineStr"/>
+      <c r="O207" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P207" s="2" t="inlineStr"/>
+      <c r="Q207" s="2" t="inlineStr">
+        <is>
+          <t>0.018826549356223188</t>
+        </is>
+      </c>
+      <c r="R207" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:27:16.243697Z</t>
+        </is>
+      </c>
+      <c r="S207" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="T207" s="2" t="inlineStr"/>
+      <c r="U207" s="2" t="inlineStr"/>
+      <c r="V207" s="2" t="inlineStr"/>
+      <c r="W207" s="2" t="inlineStr"/>
+      <c r="X207" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y207" s="2" t="inlineStr"/>
+      <c r="Z207" s="2" t="inlineStr"/>
+      <c r="AA207" s="2" t="inlineStr"/>
+      <c r="AB207" s="2" t="inlineStr"/>
+      <c r="AC207" s="2" t="inlineStr"/>
+      <c r="AD207" s="2" t="inlineStr"/>
+      <c r="AE207" s="2" t="inlineStr"/>
+      <c r="AF207" s="2" t="inlineStr"/>
+      <c r="AG207" s="2" t="inlineStr"/>
+      <c r="AH207" s="2" t="inlineStr"/>
+      <c r="AI207" s="2" t="inlineStr"/>
+      <c r="AJ207" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ155"/>
+  <autoFilter ref="A1:AJ207"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/gated_research/model_ledgers/lol-tiered-elo.xlsx
+++ b/data/gated_research/model_ledgers/lol-tiered-elo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$322</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$376</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ322"/>
+  <dimension ref="A1:AJ376"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -31664,14 +31664,34 @@
       <c r="W303" s="2" t="inlineStr"/>
       <c r="X303" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y303" s="2" t="inlineStr"/>
-      <c r="Z303" s="2" t="inlineStr"/>
-      <c r="AA303" s="2" t="inlineStr"/>
-      <c r="AB303" s="2" t="inlineStr"/>
-      <c r="AC303" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y303" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z303" s="2" t="inlineStr">
+        <is>
+          <t>0.510000</t>
+        </is>
+      </c>
+      <c r="AA303" s="2" t="inlineStr">
+        <is>
+          <t>0.000196</t>
+        </is>
+      </c>
+      <c r="AB303" s="2" t="inlineStr">
+        <is>
+          <t>1.6827</t>
+        </is>
+      </c>
+      <c r="AC303" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:18:21.556950Z</t>
+        </is>
+      </c>
       <c r="AD303" s="2" t="inlineStr"/>
       <c r="AE303" s="2" t="inlineStr"/>
       <c r="AF303" s="2" t="inlineStr"/>
@@ -31766,14 +31786,34 @@
       <c r="W304" s="2" t="inlineStr"/>
       <c r="X304" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y304" s="2" t="inlineStr"/>
-      <c r="Z304" s="2" t="inlineStr"/>
-      <c r="AA304" s="2" t="inlineStr"/>
-      <c r="AB304" s="2" t="inlineStr"/>
-      <c r="AC304" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y304" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z304" s="2" t="inlineStr">
+        <is>
+          <t>0.690000</t>
+        </is>
+      </c>
+      <c r="AA304" s="2" t="inlineStr">
+        <is>
+          <t>-0.000402</t>
+        </is>
+      </c>
+      <c r="AB304" s="2" t="inlineStr">
+        <is>
+          <t>0.8969</t>
+        </is>
+      </c>
+      <c r="AC304" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:41:51.054191Z</t>
+        </is>
+      </c>
       <c r="AD304" s="2" t="inlineStr"/>
       <c r="AE304" s="2" t="inlineStr"/>
       <c r="AF304" s="2" t="inlineStr"/>
@@ -31868,14 +31908,34 @@
       <c r="W305" s="2" t="inlineStr"/>
       <c r="X305" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y305" s="2" t="inlineStr"/>
-      <c r="Z305" s="2" t="inlineStr"/>
-      <c r="AA305" s="2" t="inlineStr"/>
-      <c r="AB305" s="2" t="inlineStr"/>
-      <c r="AC305" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y305" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z305" s="2" t="inlineStr">
+        <is>
+          <t>0.700000</t>
+        </is>
+      </c>
+      <c r="AA305" s="2" t="inlineStr">
+        <is>
+          <t>0.000300</t>
+        </is>
+      </c>
+      <c r="AB305" s="2" t="inlineStr">
+        <is>
+          <t>-2.0000</t>
+        </is>
+      </c>
+      <c r="AC305" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:41:52.776819Z</t>
+        </is>
+      </c>
       <c r="AD305" s="2" t="inlineStr"/>
       <c r="AE305" s="2" t="inlineStr"/>
       <c r="AF305" s="2" t="inlineStr"/>
@@ -33618,8 +33678,5516 @@
       <c r="AI322" s="2" t="inlineStr"/>
       <c r="AJ322" s="2" t="inlineStr"/>
     </row>
+    <row r="323">
+      <c r="A323" s="2" t="inlineStr">
+        <is>
+          <t>135440dfc3bf4f54</t>
+        </is>
+      </c>
+      <c r="B323" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C323" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D323" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E323" s="2" t="inlineStr">
+        <is>
+          <t>ece7c0cd0eb091a17098b0c2a66a47373f26dc93cf66c5d6b0e065fc8c34a267</t>
+        </is>
+      </c>
+      <c r="F323" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G323" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H323" s="2" t="inlineStr">
+        <is>
+          <t>69871</t>
+        </is>
+      </c>
+      <c r="I323" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J323" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K323" s="2" t="inlineStr"/>
+      <c r="L323" s="2" t="inlineStr">
+        <is>
+          <t>0.548524</t>
+        </is>
+      </c>
+      <c r="M323" s="2" t="inlineStr"/>
+      <c r="N323" s="2" t="inlineStr"/>
+      <c r="O323" s="2" t="inlineStr">
+        <is>
+          <t>0.49019607843137253</t>
+        </is>
+      </c>
+      <c r="P323" s="2" t="inlineStr"/>
+      <c r="Q323" s="2" t="inlineStr">
+        <is>
+          <t>0.05832792156862748</t>
+        </is>
+      </c>
+      <c r="R323" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:23:20.941653Z</t>
+        </is>
+      </c>
+      <c r="S323" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T323" s="2" t="inlineStr"/>
+      <c r="U323" s="2" t="inlineStr"/>
+      <c r="V323" s="2" t="inlineStr"/>
+      <c r="W323" s="2" t="inlineStr"/>
+      <c r="X323" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y323" s="2" t="inlineStr"/>
+      <c r="Z323" s="2" t="inlineStr"/>
+      <c r="AA323" s="2" t="inlineStr"/>
+      <c r="AB323" s="2" t="inlineStr"/>
+      <c r="AC323" s="2" t="inlineStr"/>
+      <c r="AD323" s="2" t="inlineStr"/>
+      <c r="AE323" s="2" t="inlineStr"/>
+      <c r="AF323" s="2" t="inlineStr"/>
+      <c r="AG323" s="2" t="inlineStr"/>
+      <c r="AH323" s="2" t="inlineStr"/>
+      <c r="AI323" s="2" t="inlineStr"/>
+      <c r="AJ323" s="2" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="2" t="inlineStr">
+        <is>
+          <t>4a77d8e384cb44c2</t>
+        </is>
+      </c>
+      <c r="B324" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C324" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D324" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E324" s="2" t="inlineStr">
+        <is>
+          <t>ece7c0cd0eb091a17098b0c2a66a47373f26dc93cf66c5d6b0e065fc8c34a267</t>
+        </is>
+      </c>
+      <c r="F324" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G324" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H324" s="2" t="inlineStr">
+        <is>
+          <t>70569</t>
+        </is>
+      </c>
+      <c r="I324" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J324" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K324" s="2" t="inlineStr"/>
+      <c r="L324" s="2" t="inlineStr">
+        <is>
+          <t>0.760884</t>
+        </is>
+      </c>
+      <c r="M324" s="2" t="inlineStr"/>
+      <c r="N324" s="2" t="inlineStr"/>
+      <c r="O324" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P324" s="2" t="inlineStr"/>
+      <c r="Q324" s="2" t="inlineStr">
+        <is>
+          <t>0.23036756807511738</t>
+        </is>
+      </c>
+      <c r="R324" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:23:21.551543Z</t>
+        </is>
+      </c>
+      <c r="S324" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T324" s="2" t="inlineStr"/>
+      <c r="U324" s="2" t="inlineStr"/>
+      <c r="V324" s="2" t="inlineStr"/>
+      <c r="W324" s="2" t="inlineStr"/>
+      <c r="X324" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y324" s="2" t="inlineStr"/>
+      <c r="Z324" s="2" t="inlineStr"/>
+      <c r="AA324" s="2" t="inlineStr"/>
+      <c r="AB324" s="2" t="inlineStr"/>
+      <c r="AC324" s="2" t="inlineStr"/>
+      <c r="AD324" s="2" t="inlineStr"/>
+      <c r="AE324" s="2" t="inlineStr"/>
+      <c r="AF324" s="2" t="inlineStr"/>
+      <c r="AG324" s="2" t="inlineStr"/>
+      <c r="AH324" s="2" t="inlineStr"/>
+      <c r="AI324" s="2" t="inlineStr"/>
+      <c r="AJ324" s="2" t="inlineStr"/>
+    </row>
+    <row r="325">
+      <c r="A325" s="2" t="inlineStr">
+        <is>
+          <t>237dd97495e34bde</t>
+        </is>
+      </c>
+      <c r="B325" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C325" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D325" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E325" s="2" t="inlineStr">
+        <is>
+          <t>ece7c0cd0eb091a17098b0c2a66a47373f26dc93cf66c5d6b0e065fc8c34a267</t>
+        </is>
+      </c>
+      <c r="F325" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G325" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H325" s="2" t="inlineStr">
+        <is>
+          <t>69930</t>
+        </is>
+      </c>
+      <c r="I325" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J325" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K325" s="2" t="inlineStr"/>
+      <c r="L325" s="2" t="inlineStr">
+        <is>
+          <t>0.559233</t>
+        </is>
+      </c>
+      <c r="M325" s="2" t="inlineStr"/>
+      <c r="N325" s="2" t="inlineStr"/>
+      <c r="O325" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P325" s="2" t="inlineStr"/>
+      <c r="Q325" s="2" t="inlineStr">
+        <is>
+          <t>0.11870436563876652</t>
+        </is>
+      </c>
+      <c r="R325" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:23:22.786436Z</t>
+        </is>
+      </c>
+      <c r="S325" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:30:00Z</t>
+        </is>
+      </c>
+      <c r="T325" s="2" t="inlineStr"/>
+      <c r="U325" s="2" t="inlineStr"/>
+      <c r="V325" s="2" t="inlineStr"/>
+      <c r="W325" s="2" t="inlineStr"/>
+      <c r="X325" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y325" s="2" t="inlineStr"/>
+      <c r="Z325" s="2" t="inlineStr"/>
+      <c r="AA325" s="2" t="inlineStr"/>
+      <c r="AB325" s="2" t="inlineStr"/>
+      <c r="AC325" s="2" t="inlineStr"/>
+      <c r="AD325" s="2" t="inlineStr"/>
+      <c r="AE325" s="2" t="inlineStr"/>
+      <c r="AF325" s="2" t="inlineStr"/>
+      <c r="AG325" s="2" t="inlineStr"/>
+      <c r="AH325" s="2" t="inlineStr"/>
+      <c r="AI325" s="2" t="inlineStr"/>
+      <c r="AJ325" s="2" t="inlineStr"/>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="inlineStr">
+        <is>
+          <t>1b0f783a0e81499c</t>
+        </is>
+      </c>
+      <c r="B326" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C326" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D326" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E326" s="2" t="inlineStr">
+        <is>
+          <t>ece7c0cd0eb091a17098b0c2a66a47373f26dc93cf66c5d6b0e065fc8c34a267</t>
+        </is>
+      </c>
+      <c r="F326" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G326" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H326" s="2" t="inlineStr">
+        <is>
+          <t>69931</t>
+        </is>
+      </c>
+      <c r="I326" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J326" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K326" s="2" t="inlineStr"/>
+      <c r="L326" s="2" t="inlineStr">
+        <is>
+          <t>0.598613</t>
+        </is>
+      </c>
+      <c r="M326" s="2" t="inlineStr"/>
+      <c r="N326" s="2" t="inlineStr"/>
+      <c r="O326" s="2" t="inlineStr">
+        <is>
+          <t>0.4807692307692307</t>
+        </is>
+      </c>
+      <c r="P326" s="2" t="inlineStr"/>
+      <c r="Q326" s="2" t="inlineStr">
+        <is>
+          <t>0.11784376923076922</t>
+        </is>
+      </c>
+      <c r="R326" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:23:23.407752Z</t>
+        </is>
+      </c>
+      <c r="S326" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:30:00Z</t>
+        </is>
+      </c>
+      <c r="T326" s="2" t="inlineStr"/>
+      <c r="U326" s="2" t="inlineStr"/>
+      <c r="V326" s="2" t="inlineStr"/>
+      <c r="W326" s="2" t="inlineStr"/>
+      <c r="X326" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y326" s="2" t="inlineStr"/>
+      <c r="Z326" s="2" t="inlineStr"/>
+      <c r="AA326" s="2" t="inlineStr"/>
+      <c r="AB326" s="2" t="inlineStr"/>
+      <c r="AC326" s="2" t="inlineStr"/>
+      <c r="AD326" s="2" t="inlineStr"/>
+      <c r="AE326" s="2" t="inlineStr"/>
+      <c r="AF326" s="2" t="inlineStr"/>
+      <c r="AG326" s="2" t="inlineStr"/>
+      <c r="AH326" s="2" t="inlineStr"/>
+      <c r="AI326" s="2" t="inlineStr"/>
+      <c r="AJ326" s="2" t="inlineStr"/>
+    </row>
+    <row r="327">
+      <c r="A327" s="2" t="inlineStr">
+        <is>
+          <t>98d78fc8c3c64532</t>
+        </is>
+      </c>
+      <c r="B327" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C327" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D327" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E327" s="2" t="inlineStr">
+        <is>
+          <t>ece7c0cd0eb091a17098b0c2a66a47373f26dc93cf66c5d6b0e065fc8c34a267</t>
+        </is>
+      </c>
+      <c r="F327" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G327" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H327" s="2" t="inlineStr">
+        <is>
+          <t>70045</t>
+        </is>
+      </c>
+      <c r="I327" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J327" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K327" s="2" t="inlineStr"/>
+      <c r="L327" s="2" t="inlineStr">
+        <is>
+          <t>0.598861</t>
+        </is>
+      </c>
+      <c r="M327" s="2" t="inlineStr"/>
+      <c r="N327" s="2" t="inlineStr"/>
+      <c r="O327" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P327" s="2" t="inlineStr"/>
+      <c r="Q327" s="2" t="inlineStr">
+        <is>
+          <t>0.14841054954954946</t>
+        </is>
+      </c>
+      <c r="R327" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:23:27.664352Z</t>
+        </is>
+      </c>
+      <c r="S327" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="T327" s="2" t="inlineStr"/>
+      <c r="U327" s="2" t="inlineStr"/>
+      <c r="V327" s="2" t="inlineStr"/>
+      <c r="W327" s="2" t="inlineStr"/>
+      <c r="X327" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y327" s="2" t="inlineStr"/>
+      <c r="Z327" s="2" t="inlineStr"/>
+      <c r="AA327" s="2" t="inlineStr"/>
+      <c r="AB327" s="2" t="inlineStr"/>
+      <c r="AC327" s="2" t="inlineStr"/>
+      <c r="AD327" s="2" t="inlineStr"/>
+      <c r="AE327" s="2" t="inlineStr"/>
+      <c r="AF327" s="2" t="inlineStr"/>
+      <c r="AG327" s="2" t="inlineStr"/>
+      <c r="AH327" s="2" t="inlineStr"/>
+      <c r="AI327" s="2" t="inlineStr"/>
+      <c r="AJ327" s="2" t="inlineStr"/>
+    </row>
+    <row r="328">
+      <c r="A328" s="2" t="inlineStr">
+        <is>
+          <t>20925fb245e244d1</t>
+        </is>
+      </c>
+      <c r="B328" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C328" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D328" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E328" s="2" t="inlineStr">
+        <is>
+          <t>ece7c0cd0eb091a17098b0c2a66a47373f26dc93cf66c5d6b0e065fc8c34a267</t>
+        </is>
+      </c>
+      <c r="F328" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G328" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H328" s="2" t="inlineStr">
+        <is>
+          <t>70301</t>
+        </is>
+      </c>
+      <c r="I328" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J328" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K328" s="2" t="inlineStr"/>
+      <c r="L328" s="2" t="inlineStr">
+        <is>
+          <t>0.584364</t>
+        </is>
+      </c>
+      <c r="M328" s="2" t="inlineStr"/>
+      <c r="N328" s="2" t="inlineStr"/>
+      <c r="O328" s="2" t="inlineStr">
+        <is>
+          <t>0.5098039215686274</t>
+        </is>
+      </c>
+      <c r="P328" s="2" t="inlineStr"/>
+      <c r="Q328" s="2" t="inlineStr">
+        <is>
+          <t>0.07456007843137258</t>
+        </is>
+      </c>
+      <c r="R328" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:23:28.197446Z</t>
+        </is>
+      </c>
+      <c r="S328" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T328" s="2" t="inlineStr"/>
+      <c r="U328" s="2" t="inlineStr"/>
+      <c r="V328" s="2" t="inlineStr"/>
+      <c r="W328" s="2" t="inlineStr"/>
+      <c r="X328" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y328" s="2" t="inlineStr"/>
+      <c r="Z328" s="2" t="inlineStr"/>
+      <c r="AA328" s="2" t="inlineStr"/>
+      <c r="AB328" s="2" t="inlineStr"/>
+      <c r="AC328" s="2" t="inlineStr"/>
+      <c r="AD328" s="2" t="inlineStr"/>
+      <c r="AE328" s="2" t="inlineStr"/>
+      <c r="AF328" s="2" t="inlineStr"/>
+      <c r="AG328" s="2" t="inlineStr"/>
+      <c r="AH328" s="2" t="inlineStr"/>
+      <c r="AI328" s="2" t="inlineStr"/>
+      <c r="AJ328" s="2" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="A329" s="2" t="inlineStr">
+        <is>
+          <t>6db333d8e0294290</t>
+        </is>
+      </c>
+      <c r="B329" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C329" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D329" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E329" s="2" t="inlineStr">
+        <is>
+          <t>ece7c0cd0eb091a17098b0c2a66a47373f26dc93cf66c5d6b0e065fc8c34a267</t>
+        </is>
+      </c>
+      <c r="F329" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G329" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H329" s="2" t="inlineStr">
+        <is>
+          <t>70349</t>
+        </is>
+      </c>
+      <c r="I329" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J329" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K329" s="2" t="inlineStr"/>
+      <c r="L329" s="2" t="inlineStr">
+        <is>
+          <t>0.671328</t>
+        </is>
+      </c>
+      <c r="M329" s="2" t="inlineStr"/>
+      <c r="N329" s="2" t="inlineStr"/>
+      <c r="O329" s="2" t="inlineStr">
+        <is>
+          <t>0.6503496503496503</t>
+        </is>
+      </c>
+      <c r="P329" s="2" t="inlineStr"/>
+      <c r="Q329" s="2" t="inlineStr">
+        <is>
+          <t>0.020978349650349726</t>
+        </is>
+      </c>
+      <c r="R329" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:23:29.924419Z</t>
+        </is>
+      </c>
+      <c r="S329" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T329" s="2" t="inlineStr"/>
+      <c r="U329" s="2" t="inlineStr"/>
+      <c r="V329" s="2" t="inlineStr"/>
+      <c r="W329" s="2" t="inlineStr"/>
+      <c r="X329" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y329" s="2" t="inlineStr"/>
+      <c r="Z329" s="2" t="inlineStr"/>
+      <c r="AA329" s="2" t="inlineStr"/>
+      <c r="AB329" s="2" t="inlineStr"/>
+      <c r="AC329" s="2" t="inlineStr"/>
+      <c r="AD329" s="2" t="inlineStr"/>
+      <c r="AE329" s="2" t="inlineStr"/>
+      <c r="AF329" s="2" t="inlineStr"/>
+      <c r="AG329" s="2" t="inlineStr"/>
+      <c r="AH329" s="2" t="inlineStr"/>
+      <c r="AI329" s="2" t="inlineStr"/>
+      <c r="AJ329" s="2" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="2" t="inlineStr">
+        <is>
+          <t>d1402de3aef64ab3</t>
+        </is>
+      </c>
+      <c r="B330" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C330" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D330" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E330" s="2" t="inlineStr">
+        <is>
+          <t>ece7c0cd0eb091a17098b0c2a66a47373f26dc93cf66c5d6b0e065fc8c34a267</t>
+        </is>
+      </c>
+      <c r="F330" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G330" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H330" s="2" t="inlineStr">
+        <is>
+          <t>70379</t>
+        </is>
+      </c>
+      <c r="I330" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J330" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K330" s="2" t="inlineStr"/>
+      <c r="L330" s="2" t="inlineStr">
+        <is>
+          <t>0.617134</t>
+        </is>
+      </c>
+      <c r="M330" s="2" t="inlineStr"/>
+      <c r="N330" s="2" t="inlineStr"/>
+      <c r="O330" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P330" s="2" t="inlineStr"/>
+      <c r="Q330" s="2" t="inlineStr">
+        <is>
+          <t>0.1766053656387665</t>
+        </is>
+      </c>
+      <c r="R330" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:23:30.872340Z</t>
+        </is>
+      </c>
+      <c r="S330" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="T330" s="2" t="inlineStr"/>
+      <c r="U330" s="2" t="inlineStr"/>
+      <c r="V330" s="2" t="inlineStr"/>
+      <c r="W330" s="2" t="inlineStr"/>
+      <c r="X330" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y330" s="2" t="inlineStr"/>
+      <c r="Z330" s="2" t="inlineStr"/>
+      <c r="AA330" s="2" t="inlineStr"/>
+      <c r="AB330" s="2" t="inlineStr"/>
+      <c r="AC330" s="2" t="inlineStr"/>
+      <c r="AD330" s="2" t="inlineStr"/>
+      <c r="AE330" s="2" t="inlineStr"/>
+      <c r="AF330" s="2" t="inlineStr"/>
+      <c r="AG330" s="2" t="inlineStr"/>
+      <c r="AH330" s="2" t="inlineStr"/>
+      <c r="AI330" s="2" t="inlineStr"/>
+      <c r="AJ330" s="2" t="inlineStr"/>
+    </row>
+    <row r="331">
+      <c r="A331" s="2" t="inlineStr">
+        <is>
+          <t>95d6abdb54454630</t>
+        </is>
+      </c>
+      <c r="B331" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C331" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D331" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E331" s="2" t="inlineStr">
+        <is>
+          <t>ece7c0cd0eb091a17098b0c2a66a47373f26dc93cf66c5d6b0e065fc8c34a267</t>
+        </is>
+      </c>
+      <c r="F331" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G331" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H331" s="2" t="inlineStr">
+        <is>
+          <t>70560</t>
+        </is>
+      </c>
+      <c r="I331" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J331" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K331" s="2" t="inlineStr"/>
+      <c r="L331" s="2" t="inlineStr">
+        <is>
+          <t>0.619485</t>
+        </is>
+      </c>
+      <c r="M331" s="2" t="inlineStr"/>
+      <c r="N331" s="2" t="inlineStr"/>
+      <c r="O331" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P331" s="2" t="inlineStr"/>
+      <c r="Q331" s="2" t="inlineStr">
+        <is>
+          <t>0.16903454954954944</t>
+        </is>
+      </c>
+      <c r="R331" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:23:34.413517Z</t>
+        </is>
+      </c>
+      <c r="S331" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T07:00:00Z</t>
+        </is>
+      </c>
+      <c r="T331" s="2" t="inlineStr"/>
+      <c r="U331" s="2" t="inlineStr"/>
+      <c r="V331" s="2" t="inlineStr"/>
+      <c r="W331" s="2" t="inlineStr"/>
+      <c r="X331" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y331" s="2" t="inlineStr"/>
+      <c r="Z331" s="2" t="inlineStr"/>
+      <c r="AA331" s="2" t="inlineStr"/>
+      <c r="AB331" s="2" t="inlineStr"/>
+      <c r="AC331" s="2" t="inlineStr"/>
+      <c r="AD331" s="2" t="inlineStr"/>
+      <c r="AE331" s="2" t="inlineStr"/>
+      <c r="AF331" s="2" t="inlineStr"/>
+      <c r="AG331" s="2" t="inlineStr"/>
+      <c r="AH331" s="2" t="inlineStr"/>
+      <c r="AI331" s="2" t="inlineStr"/>
+      <c r="AJ331" s="2" t="inlineStr"/>
+    </row>
+    <row r="332">
+      <c r="A332" s="2" t="inlineStr">
+        <is>
+          <t>7b177564b3a34c59</t>
+        </is>
+      </c>
+      <c r="B332" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C332" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D332" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E332" s="2" t="inlineStr">
+        <is>
+          <t>ece7c0cd0eb091a17098b0c2a66a47373f26dc93cf66c5d6b0e065fc8c34a267</t>
+        </is>
+      </c>
+      <c r="F332" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G332" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H332" s="2" t="inlineStr">
+        <is>
+          <t>70573</t>
+        </is>
+      </c>
+      <c r="I332" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J332" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K332" s="2" t="inlineStr"/>
+      <c r="L332" s="2" t="inlineStr">
+        <is>
+          <t>0.67786</t>
+        </is>
+      </c>
+      <c r="M332" s="2" t="inlineStr"/>
+      <c r="N332" s="2" t="inlineStr"/>
+      <c r="O332" s="2" t="inlineStr">
+        <is>
+          <t>0.4098360655737705</t>
+        </is>
+      </c>
+      <c r="P332" s="2" t="inlineStr"/>
+      <c r="Q332" s="2" t="inlineStr">
+        <is>
+          <t>0.2680239344262295</t>
+        </is>
+      </c>
+      <c r="R332" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:23:36.088767Z</t>
+        </is>
+      </c>
+      <c r="S332" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T332" s="2" t="inlineStr"/>
+      <c r="U332" s="2" t="inlineStr"/>
+      <c r="V332" s="2" t="inlineStr"/>
+      <c r="W332" s="2" t="inlineStr"/>
+      <c r="X332" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y332" s="2" t="inlineStr"/>
+      <c r="Z332" s="2" t="inlineStr"/>
+      <c r="AA332" s="2" t="inlineStr"/>
+      <c r="AB332" s="2" t="inlineStr"/>
+      <c r="AC332" s="2" t="inlineStr"/>
+      <c r="AD332" s="2" t="inlineStr"/>
+      <c r="AE332" s="2" t="inlineStr"/>
+      <c r="AF332" s="2" t="inlineStr"/>
+      <c r="AG332" s="2" t="inlineStr"/>
+      <c r="AH332" s="2" t="inlineStr"/>
+      <c r="AI332" s="2" t="inlineStr"/>
+      <c r="AJ332" s="2" t="inlineStr"/>
+    </row>
+    <row r="333">
+      <c r="A333" s="2" t="inlineStr">
+        <is>
+          <t>e994ecf46fa145e1</t>
+        </is>
+      </c>
+      <c r="B333" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C333" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D333" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E333" s="2" t="inlineStr">
+        <is>
+          <t>ece7c0cd0eb091a17098b0c2a66a47373f26dc93cf66c5d6b0e065fc8c34a267</t>
+        </is>
+      </c>
+      <c r="F333" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G333" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H333" s="2" t="inlineStr">
+        <is>
+          <t>70594</t>
+        </is>
+      </c>
+      <c r="I333" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J333" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K333" s="2" t="inlineStr"/>
+      <c r="L333" s="2" t="inlineStr">
+        <is>
+          <t>0.554132</t>
+        </is>
+      </c>
+      <c r="M333" s="2" t="inlineStr"/>
+      <c r="N333" s="2" t="inlineStr"/>
+      <c r="O333" s="2" t="inlineStr">
+        <is>
+          <t>0.5192307692307692</t>
+        </is>
+      </c>
+      <c r="P333" s="2" t="inlineStr"/>
+      <c r="Q333" s="2" t="inlineStr">
+        <is>
+          <t>0.034901230769230795</t>
+        </is>
+      </c>
+      <c r="R333" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:23:36.809033Z</t>
+        </is>
+      </c>
+      <c r="S333" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T333" s="2" t="inlineStr"/>
+      <c r="U333" s="2" t="inlineStr"/>
+      <c r="V333" s="2" t="inlineStr"/>
+      <c r="W333" s="2" t="inlineStr"/>
+      <c r="X333" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y333" s="2" t="inlineStr"/>
+      <c r="Z333" s="2" t="inlineStr"/>
+      <c r="AA333" s="2" t="inlineStr"/>
+      <c r="AB333" s="2" t="inlineStr"/>
+      <c r="AC333" s="2" t="inlineStr"/>
+      <c r="AD333" s="2" t="inlineStr"/>
+      <c r="AE333" s="2" t="inlineStr"/>
+      <c r="AF333" s="2" t="inlineStr"/>
+      <c r="AG333" s="2" t="inlineStr"/>
+      <c r="AH333" s="2" t="inlineStr"/>
+      <c r="AI333" s="2" t="inlineStr"/>
+      <c r="AJ333" s="2" t="inlineStr"/>
+    </row>
+    <row r="334">
+      <c r="A334" s="2" t="inlineStr">
+        <is>
+          <t>a3a76fb42c374227</t>
+        </is>
+      </c>
+      <c r="B334" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C334" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D334" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E334" s="2" t="inlineStr">
+        <is>
+          <t>ece7c0cd0eb091a17098b0c2a66a47373f26dc93cf66c5d6b0e065fc8c34a267</t>
+        </is>
+      </c>
+      <c r="F334" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G334" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H334" s="2" t="inlineStr">
+        <is>
+          <t>70788</t>
+        </is>
+      </c>
+      <c r="I334" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J334" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K334" s="2" t="inlineStr"/>
+      <c r="L334" s="2" t="inlineStr">
+        <is>
+          <t>0.69237</t>
+        </is>
+      </c>
+      <c r="M334" s="2" t="inlineStr"/>
+      <c r="N334" s="2" t="inlineStr"/>
+      <c r="O334" s="2" t="inlineStr">
+        <is>
+          <t>0.6805111821086262</t>
+        </is>
+      </c>
+      <c r="P334" s="2" t="inlineStr"/>
+      <c r="Q334" s="2" t="inlineStr">
+        <is>
+          <t>0.011858817891373885</t>
+        </is>
+      </c>
+      <c r="R334" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:23:40.036966Z</t>
+        </is>
+      </c>
+      <c r="S334" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="T334" s="2" t="inlineStr"/>
+      <c r="U334" s="2" t="inlineStr"/>
+      <c r="V334" s="2" t="inlineStr"/>
+      <c r="W334" s="2" t="inlineStr"/>
+      <c r="X334" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y334" s="2" t="inlineStr"/>
+      <c r="Z334" s="2" t="inlineStr"/>
+      <c r="AA334" s="2" t="inlineStr"/>
+      <c r="AB334" s="2" t="inlineStr"/>
+      <c r="AC334" s="2" t="inlineStr"/>
+      <c r="AD334" s="2" t="inlineStr"/>
+      <c r="AE334" s="2" t="inlineStr"/>
+      <c r="AF334" s="2" t="inlineStr"/>
+      <c r="AG334" s="2" t="inlineStr"/>
+      <c r="AH334" s="2" t="inlineStr"/>
+      <c r="AI334" s="2" t="inlineStr"/>
+      <c r="AJ334" s="2" t="inlineStr"/>
+    </row>
+    <row r="335">
+      <c r="A335" s="2" t="inlineStr">
+        <is>
+          <t>f888144cf55c4ff2</t>
+        </is>
+      </c>
+      <c r="B335" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C335" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D335" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E335" s="2" t="inlineStr">
+        <is>
+          <t>ece7c0cd0eb091a17098b0c2a66a47373f26dc93cf66c5d6b0e065fc8c34a267</t>
+        </is>
+      </c>
+      <c r="F335" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G335" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H335" s="2" t="inlineStr">
+        <is>
+          <t>70790</t>
+        </is>
+      </c>
+      <c r="I335" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J335" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K335" s="2" t="inlineStr"/>
+      <c r="L335" s="2" t="inlineStr">
+        <is>
+          <t>0.765261</t>
+        </is>
+      </c>
+      <c r="M335" s="2" t="inlineStr"/>
+      <c r="N335" s="2" t="inlineStr"/>
+      <c r="O335" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P335" s="2" t="inlineStr"/>
+      <c r="Q335" s="2" t="inlineStr">
+        <is>
+          <t>0.17509706557377047</t>
+        </is>
+      </c>
+      <c r="R335" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:23:41.572780Z</t>
+        </is>
+      </c>
+      <c r="S335" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="T335" s="2" t="inlineStr"/>
+      <c r="U335" s="2" t="inlineStr"/>
+      <c r="V335" s="2" t="inlineStr"/>
+      <c r="W335" s="2" t="inlineStr"/>
+      <c r="X335" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y335" s="2" t="inlineStr"/>
+      <c r="Z335" s="2" t="inlineStr"/>
+      <c r="AA335" s="2" t="inlineStr"/>
+      <c r="AB335" s="2" t="inlineStr"/>
+      <c r="AC335" s="2" t="inlineStr"/>
+      <c r="AD335" s="2" t="inlineStr"/>
+      <c r="AE335" s="2" t="inlineStr"/>
+      <c r="AF335" s="2" t="inlineStr"/>
+      <c r="AG335" s="2" t="inlineStr"/>
+      <c r="AH335" s="2" t="inlineStr"/>
+      <c r="AI335" s="2" t="inlineStr"/>
+      <c r="AJ335" s="2" t="inlineStr"/>
+    </row>
+    <row r="336">
+      <c r="A336" s="2" t="inlineStr">
+        <is>
+          <t>ab6aa4eec7694793</t>
+        </is>
+      </c>
+      <c r="B336" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C336" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D336" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E336" s="2" t="inlineStr">
+        <is>
+          <t>ece7c0cd0eb091a17098b0c2a66a47373f26dc93cf66c5d6b0e065fc8c34a267</t>
+        </is>
+      </c>
+      <c r="F336" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G336" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H336" s="2" t="inlineStr">
+        <is>
+          <t>70860</t>
+        </is>
+      </c>
+      <c r="I336" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J336" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K336" s="2" t="inlineStr"/>
+      <c r="L336" s="2" t="inlineStr">
+        <is>
+          <t>0.743992</t>
+        </is>
+      </c>
+      <c r="M336" s="2" t="inlineStr"/>
+      <c r="N336" s="2" t="inlineStr"/>
+      <c r="O336" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P336" s="2" t="inlineStr"/>
+      <c r="Q336" s="2" t="inlineStr">
+        <is>
+          <t>0.1439919999999999</t>
+        </is>
+      </c>
+      <c r="R336" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:23:42.769894Z</t>
+        </is>
+      </c>
+      <c r="S336" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T336" s="2" t="inlineStr"/>
+      <c r="U336" s="2" t="inlineStr"/>
+      <c r="V336" s="2" t="inlineStr"/>
+      <c r="W336" s="2" t="inlineStr"/>
+      <c r="X336" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y336" s="2" t="inlineStr"/>
+      <c r="Z336" s="2" t="inlineStr"/>
+      <c r="AA336" s="2" t="inlineStr"/>
+      <c r="AB336" s="2" t="inlineStr"/>
+      <c r="AC336" s="2" t="inlineStr"/>
+      <c r="AD336" s="2" t="inlineStr"/>
+      <c r="AE336" s="2" t="inlineStr"/>
+      <c r="AF336" s="2" t="inlineStr"/>
+      <c r="AG336" s="2" t="inlineStr"/>
+      <c r="AH336" s="2" t="inlineStr"/>
+      <c r="AI336" s="2" t="inlineStr"/>
+      <c r="AJ336" s="2" t="inlineStr"/>
+    </row>
+    <row r="337">
+      <c r="A337" s="2" t="inlineStr">
+        <is>
+          <t>8852415a351c4d65</t>
+        </is>
+      </c>
+      <c r="B337" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C337" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D337" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E337" s="2" t="inlineStr">
+        <is>
+          <t>ece7c0cd0eb091a17098b0c2a66a47373f26dc93cf66c5d6b0e065fc8c34a267</t>
+        </is>
+      </c>
+      <c r="F337" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G337" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H337" s="2" t="inlineStr">
+        <is>
+          <t>70862</t>
+        </is>
+      </c>
+      <c r="I337" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J337" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K337" s="2" t="inlineStr"/>
+      <c r="L337" s="2" t="inlineStr">
+        <is>
+          <t>0.697821</t>
+        </is>
+      </c>
+      <c r="M337" s="2" t="inlineStr"/>
+      <c r="N337" s="2" t="inlineStr"/>
+      <c r="O337" s="2" t="inlineStr">
+        <is>
+          <t>0.66996699669967</t>
+        </is>
+      </c>
+      <c r="P337" s="2" t="inlineStr"/>
+      <c r="Q337" s="2" t="inlineStr">
+        <is>
+          <t>0.027854003300330055</t>
+        </is>
+      </c>
+      <c r="R337" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:23:43.275515Z</t>
+        </is>
+      </c>
+      <c r="S337" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T337" s="2" t="inlineStr"/>
+      <c r="U337" s="2" t="inlineStr"/>
+      <c r="V337" s="2" t="inlineStr"/>
+      <c r="W337" s="2" t="inlineStr"/>
+      <c r="X337" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y337" s="2" t="inlineStr"/>
+      <c r="Z337" s="2" t="inlineStr"/>
+      <c r="AA337" s="2" t="inlineStr"/>
+      <c r="AB337" s="2" t="inlineStr"/>
+      <c r="AC337" s="2" t="inlineStr"/>
+      <c r="AD337" s="2" t="inlineStr"/>
+      <c r="AE337" s="2" t="inlineStr"/>
+      <c r="AF337" s="2" t="inlineStr"/>
+      <c r="AG337" s="2" t="inlineStr"/>
+      <c r="AH337" s="2" t="inlineStr"/>
+      <c r="AI337" s="2" t="inlineStr"/>
+      <c r="AJ337" s="2" t="inlineStr"/>
+    </row>
+    <row r="338">
+      <c r="A338" s="2" t="inlineStr">
+        <is>
+          <t>d78a8fcb10ab4b77</t>
+        </is>
+      </c>
+      <c r="B338" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C338" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D338" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E338" s="2" t="inlineStr">
+        <is>
+          <t>ece7c0cd0eb091a17098b0c2a66a47373f26dc93cf66c5d6b0e065fc8c34a267</t>
+        </is>
+      </c>
+      <c r="F338" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G338" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H338" s="2" t="inlineStr">
+        <is>
+          <t>70899</t>
+        </is>
+      </c>
+      <c r="I338" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J338" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K338" s="2" t="inlineStr"/>
+      <c r="L338" s="2" t="inlineStr">
+        <is>
+          <t>0.655215</t>
+        </is>
+      </c>
+      <c r="M338" s="2" t="inlineStr"/>
+      <c r="N338" s="2" t="inlineStr"/>
+      <c r="O338" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P338" s="2" t="inlineStr"/>
+      <c r="Q338" s="2" t="inlineStr">
+        <is>
+          <t>0.08439954935622318</t>
+        </is>
+      </c>
+      <c r="R338" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:23:45.849008Z</t>
+        </is>
+      </c>
+      <c r="S338" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T338" s="2" t="inlineStr"/>
+      <c r="U338" s="2" t="inlineStr"/>
+      <c r="V338" s="2" t="inlineStr"/>
+      <c r="W338" s="2" t="inlineStr"/>
+      <c r="X338" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y338" s="2" t="inlineStr"/>
+      <c r="Z338" s="2" t="inlineStr"/>
+      <c r="AA338" s="2" t="inlineStr"/>
+      <c r="AB338" s="2" t="inlineStr"/>
+      <c r="AC338" s="2" t="inlineStr"/>
+      <c r="AD338" s="2" t="inlineStr"/>
+      <c r="AE338" s="2" t="inlineStr"/>
+      <c r="AF338" s="2" t="inlineStr"/>
+      <c r="AG338" s="2" t="inlineStr"/>
+      <c r="AH338" s="2" t="inlineStr"/>
+      <c r="AI338" s="2" t="inlineStr"/>
+      <c r="AJ338" s="2" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" s="2" t="inlineStr">
+        <is>
+          <t>97f51833c40b4536</t>
+        </is>
+      </c>
+      <c r="B339" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C339" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D339" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E339" s="2" t="inlineStr">
+        <is>
+          <t>ece7c0cd0eb091a17098b0c2a66a47373f26dc93cf66c5d6b0e065fc8c34a267</t>
+        </is>
+      </c>
+      <c r="F339" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G339" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H339" s="2" t="inlineStr">
+        <is>
+          <t>70903</t>
+        </is>
+      </c>
+      <c r="I339" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J339" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K339" s="2" t="inlineStr"/>
+      <c r="L339" s="2" t="inlineStr">
+        <is>
+          <t>0.631614</t>
+        </is>
+      </c>
+      <c r="M339" s="2" t="inlineStr"/>
+      <c r="N339" s="2" t="inlineStr"/>
+      <c r="O339" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P339" s="2" t="inlineStr"/>
+      <c r="Q339" s="2" t="inlineStr">
+        <is>
+          <t>0.08206445045045052</t>
+        </is>
+      </c>
+      <c r="R339" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:23:47.868884Z</t>
+        </is>
+      </c>
+      <c r="S339" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T339" s="2" t="inlineStr"/>
+      <c r="U339" s="2" t="inlineStr"/>
+      <c r="V339" s="2" t="inlineStr"/>
+      <c r="W339" s="2" t="inlineStr"/>
+      <c r="X339" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y339" s="2" t="inlineStr"/>
+      <c r="Z339" s="2" t="inlineStr"/>
+      <c r="AA339" s="2" t="inlineStr"/>
+      <c r="AB339" s="2" t="inlineStr"/>
+      <c r="AC339" s="2" t="inlineStr"/>
+      <c r="AD339" s="2" t="inlineStr"/>
+      <c r="AE339" s="2" t="inlineStr"/>
+      <c r="AF339" s="2" t="inlineStr"/>
+      <c r="AG339" s="2" t="inlineStr"/>
+      <c r="AH339" s="2" t="inlineStr"/>
+      <c r="AI339" s="2" t="inlineStr"/>
+      <c r="AJ339" s="2" t="inlineStr"/>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="inlineStr">
+        <is>
+          <t>e5c5d8be1e4d495f</t>
+        </is>
+      </c>
+      <c r="B340" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C340" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D340" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E340" s="2" t="inlineStr">
+        <is>
+          <t>ece7c0cd0eb091a17098b0c2a66a47373f26dc93cf66c5d6b0e065fc8c34a267</t>
+        </is>
+      </c>
+      <c r="F340" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G340" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H340" s="2" t="inlineStr">
+        <is>
+          <t>71214</t>
+        </is>
+      </c>
+      <c r="I340" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J340" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K340" s="2" t="inlineStr"/>
+      <c r="L340" s="2" t="inlineStr">
+        <is>
+          <t>0.639551</t>
+        </is>
+      </c>
+      <c r="M340" s="2" t="inlineStr"/>
+      <c r="N340" s="2" t="inlineStr"/>
+      <c r="O340" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P340" s="2" t="inlineStr"/>
+      <c r="Q340" s="2" t="inlineStr">
+        <is>
+          <t>0.08007963436123344</t>
+        </is>
+      </c>
+      <c r="R340" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:23:51.370665Z</t>
+        </is>
+      </c>
+      <c r="S340" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T340" s="2" t="inlineStr"/>
+      <c r="U340" s="2" t="inlineStr"/>
+      <c r="V340" s="2" t="inlineStr"/>
+      <c r="W340" s="2" t="inlineStr"/>
+      <c r="X340" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y340" s="2" t="inlineStr"/>
+      <c r="Z340" s="2" t="inlineStr"/>
+      <c r="AA340" s="2" t="inlineStr"/>
+      <c r="AB340" s="2" t="inlineStr"/>
+      <c r="AC340" s="2" t="inlineStr"/>
+      <c r="AD340" s="2" t="inlineStr"/>
+      <c r="AE340" s="2" t="inlineStr"/>
+      <c r="AF340" s="2" t="inlineStr"/>
+      <c r="AG340" s="2" t="inlineStr"/>
+      <c r="AH340" s="2" t="inlineStr"/>
+      <c r="AI340" s="2" t="inlineStr"/>
+      <c r="AJ340" s="2" t="inlineStr"/>
+    </row>
+    <row r="341">
+      <c r="A341" s="2" t="inlineStr">
+        <is>
+          <t>b266630f057b49fb</t>
+        </is>
+      </c>
+      <c r="B341" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C341" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D341" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E341" s="2" t="inlineStr">
+        <is>
+          <t>435dd174dda6c60c4ff8f96f4d947a2fd4271193ba1a936edab2e5eb50f50832</t>
+        </is>
+      </c>
+      <c r="F341" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G341" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H341" s="2" t="inlineStr">
+        <is>
+          <t>69871</t>
+        </is>
+      </c>
+      <c r="I341" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J341" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K341" s="2" t="inlineStr"/>
+      <c r="L341" s="2" t="inlineStr">
+        <is>
+          <t>0.548988</t>
+        </is>
+      </c>
+      <c r="M341" s="2" t="inlineStr"/>
+      <c r="N341" s="2" t="inlineStr"/>
+      <c r="O341" s="2" t="inlineStr">
+        <is>
+          <t>0.49019607843137253</t>
+        </is>
+      </c>
+      <c r="P341" s="2" t="inlineStr"/>
+      <c r="Q341" s="2" t="inlineStr">
+        <is>
+          <t>0.0587919215686275</t>
+        </is>
+      </c>
+      <c r="R341" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:46:35.400509Z</t>
+        </is>
+      </c>
+      <c r="S341" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T341" s="2" t="inlineStr"/>
+      <c r="U341" s="2" t="inlineStr"/>
+      <c r="V341" s="2" t="inlineStr"/>
+      <c r="W341" s="2" t="inlineStr"/>
+      <c r="X341" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y341" s="2" t="inlineStr"/>
+      <c r="Z341" s="2" t="inlineStr"/>
+      <c r="AA341" s="2" t="inlineStr"/>
+      <c r="AB341" s="2" t="inlineStr"/>
+      <c r="AC341" s="2" t="inlineStr"/>
+      <c r="AD341" s="2" t="inlineStr"/>
+      <c r="AE341" s="2" t="inlineStr"/>
+      <c r="AF341" s="2" t="inlineStr"/>
+      <c r="AG341" s="2" t="inlineStr"/>
+      <c r="AH341" s="2" t="inlineStr"/>
+      <c r="AI341" s="2" t="inlineStr"/>
+      <c r="AJ341" s="2" t="inlineStr"/>
+    </row>
+    <row r="342">
+      <c r="A342" s="2" t="inlineStr">
+        <is>
+          <t>52f43ab110bd4b2b</t>
+        </is>
+      </c>
+      <c r="B342" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C342" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D342" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E342" s="2" t="inlineStr">
+        <is>
+          <t>435dd174dda6c60c4ff8f96f4d947a2fd4271193ba1a936edab2e5eb50f50832</t>
+        </is>
+      </c>
+      <c r="F342" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G342" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H342" s="2" t="inlineStr">
+        <is>
+          <t>70569</t>
+        </is>
+      </c>
+      <c r="I342" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J342" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K342" s="2" t="inlineStr"/>
+      <c r="L342" s="2" t="inlineStr">
+        <is>
+          <t>0.761274</t>
+        </is>
+      </c>
+      <c r="M342" s="2" t="inlineStr"/>
+      <c r="N342" s="2" t="inlineStr"/>
+      <c r="O342" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P342" s="2" t="inlineStr"/>
+      <c r="Q342" s="2" t="inlineStr">
+        <is>
+          <t>0.23075756807511738</t>
+        </is>
+      </c>
+      <c r="R342" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:46:35.956374Z</t>
+        </is>
+      </c>
+      <c r="S342" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T342" s="2" t="inlineStr"/>
+      <c r="U342" s="2" t="inlineStr"/>
+      <c r="V342" s="2" t="inlineStr"/>
+      <c r="W342" s="2" t="inlineStr"/>
+      <c r="X342" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y342" s="2" t="inlineStr"/>
+      <c r="Z342" s="2" t="inlineStr"/>
+      <c r="AA342" s="2" t="inlineStr"/>
+      <c r="AB342" s="2" t="inlineStr"/>
+      <c r="AC342" s="2" t="inlineStr"/>
+      <c r="AD342" s="2" t="inlineStr"/>
+      <c r="AE342" s="2" t="inlineStr"/>
+      <c r="AF342" s="2" t="inlineStr"/>
+      <c r="AG342" s="2" t="inlineStr"/>
+      <c r="AH342" s="2" t="inlineStr"/>
+      <c r="AI342" s="2" t="inlineStr"/>
+      <c r="AJ342" s="2" t="inlineStr"/>
+    </row>
+    <row r="343">
+      <c r="A343" s="2" t="inlineStr">
+        <is>
+          <t>a396d8de70704d89</t>
+        </is>
+      </c>
+      <c r="B343" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C343" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D343" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E343" s="2" t="inlineStr">
+        <is>
+          <t>435dd174dda6c60c4ff8f96f4d947a2fd4271193ba1a936edab2e5eb50f50832</t>
+        </is>
+      </c>
+      <c r="F343" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G343" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H343" s="2" t="inlineStr">
+        <is>
+          <t>69930</t>
+        </is>
+      </c>
+      <c r="I343" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J343" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K343" s="2" t="inlineStr"/>
+      <c r="L343" s="2" t="inlineStr">
+        <is>
+          <t>0.559697</t>
+        </is>
+      </c>
+      <c r="M343" s="2" t="inlineStr"/>
+      <c r="N343" s="2" t="inlineStr"/>
+      <c r="O343" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P343" s="2" t="inlineStr"/>
+      <c r="Q343" s="2" t="inlineStr">
+        <is>
+          <t>0.11916836563876654</t>
+        </is>
+      </c>
+      <c r="R343" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:46:37.849004Z</t>
+        </is>
+      </c>
+      <c r="S343" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:30:00Z</t>
+        </is>
+      </c>
+      <c r="T343" s="2" t="inlineStr"/>
+      <c r="U343" s="2" t="inlineStr"/>
+      <c r="V343" s="2" t="inlineStr"/>
+      <c r="W343" s="2" t="inlineStr"/>
+      <c r="X343" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y343" s="2" t="inlineStr"/>
+      <c r="Z343" s="2" t="inlineStr"/>
+      <c r="AA343" s="2" t="inlineStr"/>
+      <c r="AB343" s="2" t="inlineStr"/>
+      <c r="AC343" s="2" t="inlineStr"/>
+      <c r="AD343" s="2" t="inlineStr"/>
+      <c r="AE343" s="2" t="inlineStr"/>
+      <c r="AF343" s="2" t="inlineStr"/>
+      <c r="AG343" s="2" t="inlineStr"/>
+      <c r="AH343" s="2" t="inlineStr"/>
+      <c r="AI343" s="2" t="inlineStr"/>
+      <c r="AJ343" s="2" t="inlineStr"/>
+    </row>
+    <row r="344">
+      <c r="A344" s="2" t="inlineStr">
+        <is>
+          <t>dd4c6c85f25a4874</t>
+        </is>
+      </c>
+      <c r="B344" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C344" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D344" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E344" s="2" t="inlineStr">
+        <is>
+          <t>435dd174dda6c60c4ff8f96f4d947a2fd4271193ba1a936edab2e5eb50f50832</t>
+        </is>
+      </c>
+      <c r="F344" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G344" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H344" s="2" t="inlineStr">
+        <is>
+          <t>69931</t>
+        </is>
+      </c>
+      <c r="I344" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J344" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K344" s="2" t="inlineStr"/>
+      <c r="L344" s="2" t="inlineStr">
+        <is>
+          <t>0.599074</t>
+        </is>
+      </c>
+      <c r="M344" s="2" t="inlineStr"/>
+      <c r="N344" s="2" t="inlineStr"/>
+      <c r="O344" s="2" t="inlineStr">
+        <is>
+          <t>0.4807692307692307</t>
+        </is>
+      </c>
+      <c r="P344" s="2" t="inlineStr"/>
+      <c r="Q344" s="2" t="inlineStr">
+        <is>
+          <t>0.11830476923076927</t>
+        </is>
+      </c>
+      <c r="R344" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:46:38.426356Z</t>
+        </is>
+      </c>
+      <c r="S344" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:30:00Z</t>
+        </is>
+      </c>
+      <c r="T344" s="2" t="inlineStr"/>
+      <c r="U344" s="2" t="inlineStr"/>
+      <c r="V344" s="2" t="inlineStr"/>
+      <c r="W344" s="2" t="inlineStr"/>
+      <c r="X344" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y344" s="2" t="inlineStr"/>
+      <c r="Z344" s="2" t="inlineStr"/>
+      <c r="AA344" s="2" t="inlineStr"/>
+      <c r="AB344" s="2" t="inlineStr"/>
+      <c r="AC344" s="2" t="inlineStr"/>
+      <c r="AD344" s="2" t="inlineStr"/>
+      <c r="AE344" s="2" t="inlineStr"/>
+      <c r="AF344" s="2" t="inlineStr"/>
+      <c r="AG344" s="2" t="inlineStr"/>
+      <c r="AH344" s="2" t="inlineStr"/>
+      <c r="AI344" s="2" t="inlineStr"/>
+      <c r="AJ344" s="2" t="inlineStr"/>
+    </row>
+    <row r="345">
+      <c r="A345" s="2" t="inlineStr">
+        <is>
+          <t>2955c59af36e4e6e</t>
+        </is>
+      </c>
+      <c r="B345" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C345" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D345" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E345" s="2" t="inlineStr">
+        <is>
+          <t>435dd174dda6c60c4ff8f96f4d947a2fd4271193ba1a936edab2e5eb50f50832</t>
+        </is>
+      </c>
+      <c r="F345" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G345" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H345" s="2" t="inlineStr">
+        <is>
+          <t>70045</t>
+        </is>
+      </c>
+      <c r="I345" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J345" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K345" s="2" t="inlineStr"/>
+      <c r="L345" s="2" t="inlineStr">
+        <is>
+          <t>0.598442</t>
+        </is>
+      </c>
+      <c r="M345" s="2" t="inlineStr"/>
+      <c r="N345" s="2" t="inlineStr"/>
+      <c r="O345" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P345" s="2" t="inlineStr"/>
+      <c r="Q345" s="2" t="inlineStr">
+        <is>
+          <t>0.14799154954954952</t>
+        </is>
+      </c>
+      <c r="R345" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:46:42.979538Z</t>
+        </is>
+      </c>
+      <c r="S345" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="T345" s="2" t="inlineStr"/>
+      <c r="U345" s="2" t="inlineStr"/>
+      <c r="V345" s="2" t="inlineStr"/>
+      <c r="W345" s="2" t="inlineStr"/>
+      <c r="X345" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y345" s="2" t="inlineStr"/>
+      <c r="Z345" s="2" t="inlineStr"/>
+      <c r="AA345" s="2" t="inlineStr"/>
+      <c r="AB345" s="2" t="inlineStr"/>
+      <c r="AC345" s="2" t="inlineStr"/>
+      <c r="AD345" s="2" t="inlineStr"/>
+      <c r="AE345" s="2" t="inlineStr"/>
+      <c r="AF345" s="2" t="inlineStr"/>
+      <c r="AG345" s="2" t="inlineStr"/>
+      <c r="AH345" s="2" t="inlineStr"/>
+      <c r="AI345" s="2" t="inlineStr"/>
+      <c r="AJ345" s="2" t="inlineStr"/>
+    </row>
+    <row r="346">
+      <c r="A346" s="2" t="inlineStr">
+        <is>
+          <t>4ab7fb6f781a4cc6</t>
+        </is>
+      </c>
+      <c r="B346" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C346" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D346" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E346" s="2" t="inlineStr">
+        <is>
+          <t>435dd174dda6c60c4ff8f96f4d947a2fd4271193ba1a936edab2e5eb50f50832</t>
+        </is>
+      </c>
+      <c r="F346" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G346" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H346" s="2" t="inlineStr">
+        <is>
+          <t>70301</t>
+        </is>
+      </c>
+      <c r="I346" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J346" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K346" s="2" t="inlineStr"/>
+      <c r="L346" s="2" t="inlineStr">
+        <is>
+          <t>0.584826</t>
+        </is>
+      </c>
+      <c r="M346" s="2" t="inlineStr"/>
+      <c r="N346" s="2" t="inlineStr"/>
+      <c r="O346" s="2" t="inlineStr">
+        <is>
+          <t>0.5098039215686274</t>
+        </is>
+      </c>
+      <c r="P346" s="2" t="inlineStr"/>
+      <c r="Q346" s="2" t="inlineStr">
+        <is>
+          <t>0.07502207843137254</t>
+        </is>
+      </c>
+      <c r="R346" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:46:43.543254Z</t>
+        </is>
+      </c>
+      <c r="S346" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T346" s="2" t="inlineStr"/>
+      <c r="U346" s="2" t="inlineStr"/>
+      <c r="V346" s="2" t="inlineStr"/>
+      <c r="W346" s="2" t="inlineStr"/>
+      <c r="X346" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y346" s="2" t="inlineStr"/>
+      <c r="Z346" s="2" t="inlineStr"/>
+      <c r="AA346" s="2" t="inlineStr"/>
+      <c r="AB346" s="2" t="inlineStr"/>
+      <c r="AC346" s="2" t="inlineStr"/>
+      <c r="AD346" s="2" t="inlineStr"/>
+      <c r="AE346" s="2" t="inlineStr"/>
+      <c r="AF346" s="2" t="inlineStr"/>
+      <c r="AG346" s="2" t="inlineStr"/>
+      <c r="AH346" s="2" t="inlineStr"/>
+      <c r="AI346" s="2" t="inlineStr"/>
+      <c r="AJ346" s="2" t="inlineStr"/>
+    </row>
+    <row r="347">
+      <c r="A347" s="2" t="inlineStr">
+        <is>
+          <t>9c9bdd99b3224f2c</t>
+        </is>
+      </c>
+      <c r="B347" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C347" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D347" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E347" s="2" t="inlineStr">
+        <is>
+          <t>435dd174dda6c60c4ff8f96f4d947a2fd4271193ba1a936edab2e5eb50f50832</t>
+        </is>
+      </c>
+      <c r="F347" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G347" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H347" s="2" t="inlineStr">
+        <is>
+          <t>70349</t>
+        </is>
+      </c>
+      <c r="I347" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J347" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K347" s="2" t="inlineStr"/>
+      <c r="L347" s="2" t="inlineStr">
+        <is>
+          <t>0.670959</t>
+        </is>
+      </c>
+      <c r="M347" s="2" t="inlineStr"/>
+      <c r="N347" s="2" t="inlineStr"/>
+      <c r="O347" s="2" t="inlineStr">
+        <is>
+          <t>0.6503496503496503</t>
+        </is>
+      </c>
+      <c r="P347" s="2" t="inlineStr"/>
+      <c r="Q347" s="2" t="inlineStr">
+        <is>
+          <t>0.020609349650349662</t>
+        </is>
+      </c>
+      <c r="R347" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:46:45.880955Z</t>
+        </is>
+      </c>
+      <c r="S347" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T347" s="2" t="inlineStr"/>
+      <c r="U347" s="2" t="inlineStr"/>
+      <c r="V347" s="2" t="inlineStr"/>
+      <c r="W347" s="2" t="inlineStr"/>
+      <c r="X347" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y347" s="2" t="inlineStr"/>
+      <c r="Z347" s="2" t="inlineStr"/>
+      <c r="AA347" s="2" t="inlineStr"/>
+      <c r="AB347" s="2" t="inlineStr"/>
+      <c r="AC347" s="2" t="inlineStr"/>
+      <c r="AD347" s="2" t="inlineStr"/>
+      <c r="AE347" s="2" t="inlineStr"/>
+      <c r="AF347" s="2" t="inlineStr"/>
+      <c r="AG347" s="2" t="inlineStr"/>
+      <c r="AH347" s="2" t="inlineStr"/>
+      <c r="AI347" s="2" t="inlineStr"/>
+      <c r="AJ347" s="2" t="inlineStr"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="2" t="inlineStr">
+        <is>
+          <t>0a2277fa1694498b</t>
+        </is>
+      </c>
+      <c r="B348" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C348" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D348" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E348" s="2" t="inlineStr">
+        <is>
+          <t>435dd174dda6c60c4ff8f96f4d947a2fd4271193ba1a936edab2e5eb50f50832</t>
+        </is>
+      </c>
+      <c r="F348" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G348" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H348" s="2" t="inlineStr">
+        <is>
+          <t>70379</t>
+        </is>
+      </c>
+      <c r="I348" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J348" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K348" s="2" t="inlineStr"/>
+      <c r="L348" s="2" t="inlineStr">
+        <is>
+          <t>0.616726</t>
+        </is>
+      </c>
+      <c r="M348" s="2" t="inlineStr"/>
+      <c r="N348" s="2" t="inlineStr"/>
+      <c r="O348" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P348" s="2" t="inlineStr"/>
+      <c r="Q348" s="2" t="inlineStr">
+        <is>
+          <t>0.17619736563876653</t>
+        </is>
+      </c>
+      <c r="R348" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:46:47.360389Z</t>
+        </is>
+      </c>
+      <c r="S348" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="T348" s="2" t="inlineStr"/>
+      <c r="U348" s="2" t="inlineStr"/>
+      <c r="V348" s="2" t="inlineStr"/>
+      <c r="W348" s="2" t="inlineStr"/>
+      <c r="X348" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y348" s="2" t="inlineStr"/>
+      <c r="Z348" s="2" t="inlineStr"/>
+      <c r="AA348" s="2" t="inlineStr"/>
+      <c r="AB348" s="2" t="inlineStr"/>
+      <c r="AC348" s="2" t="inlineStr"/>
+      <c r="AD348" s="2" t="inlineStr"/>
+      <c r="AE348" s="2" t="inlineStr"/>
+      <c r="AF348" s="2" t="inlineStr"/>
+      <c r="AG348" s="2" t="inlineStr"/>
+      <c r="AH348" s="2" t="inlineStr"/>
+      <c r="AI348" s="2" t="inlineStr"/>
+      <c r="AJ348" s="2" t="inlineStr"/>
+    </row>
+    <row r="349">
+      <c r="A349" s="2" t="inlineStr">
+        <is>
+          <t>57ec60b7c9ab4ecd</t>
+        </is>
+      </c>
+      <c r="B349" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C349" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D349" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E349" s="2" t="inlineStr">
+        <is>
+          <t>435dd174dda6c60c4ff8f96f4d947a2fd4271193ba1a936edab2e5eb50f50832</t>
+        </is>
+      </c>
+      <c r="F349" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G349" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H349" s="2" t="inlineStr">
+        <is>
+          <t>70560</t>
+        </is>
+      </c>
+      <c r="I349" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J349" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K349" s="2" t="inlineStr"/>
+      <c r="L349" s="2" t="inlineStr">
+        <is>
+          <t>0.619949</t>
+        </is>
+      </c>
+      <c r="M349" s="2" t="inlineStr"/>
+      <c r="N349" s="2" t="inlineStr"/>
+      <c r="O349" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P349" s="2" t="inlineStr"/>
+      <c r="Q349" s="2" t="inlineStr">
+        <is>
+          <t>0.16949854954954946</t>
+        </is>
+      </c>
+      <c r="R349" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:46:51.046541Z</t>
+        </is>
+      </c>
+      <c r="S349" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T07:00:00Z</t>
+        </is>
+      </c>
+      <c r="T349" s="2" t="inlineStr"/>
+      <c r="U349" s="2" t="inlineStr"/>
+      <c r="V349" s="2" t="inlineStr"/>
+      <c r="W349" s="2" t="inlineStr"/>
+      <c r="X349" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y349" s="2" t="inlineStr"/>
+      <c r="Z349" s="2" t="inlineStr"/>
+      <c r="AA349" s="2" t="inlineStr"/>
+      <c r="AB349" s="2" t="inlineStr"/>
+      <c r="AC349" s="2" t="inlineStr"/>
+      <c r="AD349" s="2" t="inlineStr"/>
+      <c r="AE349" s="2" t="inlineStr"/>
+      <c r="AF349" s="2" t="inlineStr"/>
+      <c r="AG349" s="2" t="inlineStr"/>
+      <c r="AH349" s="2" t="inlineStr"/>
+      <c r="AI349" s="2" t="inlineStr"/>
+      <c r="AJ349" s="2" t="inlineStr"/>
+    </row>
+    <row r="350">
+      <c r="A350" s="2" t="inlineStr">
+        <is>
+          <t>affd00f4b2684aab</t>
+        </is>
+      </c>
+      <c r="B350" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C350" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D350" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E350" s="2" t="inlineStr">
+        <is>
+          <t>435dd174dda6c60c4ff8f96f4d947a2fd4271193ba1a936edab2e5eb50f50832</t>
+        </is>
+      </c>
+      <c r="F350" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G350" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H350" s="2" t="inlineStr">
+        <is>
+          <t>70573</t>
+        </is>
+      </c>
+      <c r="I350" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J350" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K350" s="2" t="inlineStr"/>
+      <c r="L350" s="2" t="inlineStr">
+        <is>
+          <t>0.678297</t>
+        </is>
+      </c>
+      <c r="M350" s="2" t="inlineStr"/>
+      <c r="N350" s="2" t="inlineStr"/>
+      <c r="O350" s="2" t="inlineStr">
+        <is>
+          <t>0.4098360655737705</t>
+        </is>
+      </c>
+      <c r="P350" s="2" t="inlineStr"/>
+      <c r="Q350" s="2" t="inlineStr">
+        <is>
+          <t>0.26846093442622954</t>
+        </is>
+      </c>
+      <c r="R350" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:46:53.175280Z</t>
+        </is>
+      </c>
+      <c r="S350" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T350" s="2" t="inlineStr"/>
+      <c r="U350" s="2" t="inlineStr"/>
+      <c r="V350" s="2" t="inlineStr"/>
+      <c r="W350" s="2" t="inlineStr"/>
+      <c r="X350" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y350" s="2" t="inlineStr"/>
+      <c r="Z350" s="2" t="inlineStr"/>
+      <c r="AA350" s="2" t="inlineStr"/>
+      <c r="AB350" s="2" t="inlineStr"/>
+      <c r="AC350" s="2" t="inlineStr"/>
+      <c r="AD350" s="2" t="inlineStr"/>
+      <c r="AE350" s="2" t="inlineStr"/>
+      <c r="AF350" s="2" t="inlineStr"/>
+      <c r="AG350" s="2" t="inlineStr"/>
+      <c r="AH350" s="2" t="inlineStr"/>
+      <c r="AI350" s="2" t="inlineStr"/>
+      <c r="AJ350" s="2" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="2" t="inlineStr">
+        <is>
+          <t>637a9c6521194301</t>
+        </is>
+      </c>
+      <c r="B351" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C351" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D351" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E351" s="2" t="inlineStr">
+        <is>
+          <t>435dd174dda6c60c4ff8f96f4d947a2fd4271193ba1a936edab2e5eb50f50832</t>
+        </is>
+      </c>
+      <c r="F351" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G351" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H351" s="2" t="inlineStr">
+        <is>
+          <t>70594</t>
+        </is>
+      </c>
+      <c r="I351" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J351" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K351" s="2" t="inlineStr"/>
+      <c r="L351" s="2" t="inlineStr">
+        <is>
+          <t>0.553408</t>
+        </is>
+      </c>
+      <c r="M351" s="2" t="inlineStr"/>
+      <c r="N351" s="2" t="inlineStr"/>
+      <c r="O351" s="2" t="inlineStr">
+        <is>
+          <t>0.5192307692307692</t>
+        </is>
+      </c>
+      <c r="P351" s="2" t="inlineStr"/>
+      <c r="Q351" s="2" t="inlineStr">
+        <is>
+          <t>0.03417723076923085</t>
+        </is>
+      </c>
+      <c r="R351" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:46:53.893898Z</t>
+        </is>
+      </c>
+      <c r="S351" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T351" s="2" t="inlineStr"/>
+      <c r="U351" s="2" t="inlineStr"/>
+      <c r="V351" s="2" t="inlineStr"/>
+      <c r="W351" s="2" t="inlineStr"/>
+      <c r="X351" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y351" s="2" t="inlineStr"/>
+      <c r="Z351" s="2" t="inlineStr"/>
+      <c r="AA351" s="2" t="inlineStr"/>
+      <c r="AB351" s="2" t="inlineStr"/>
+      <c r="AC351" s="2" t="inlineStr"/>
+      <c r="AD351" s="2" t="inlineStr"/>
+      <c r="AE351" s="2" t="inlineStr"/>
+      <c r="AF351" s="2" t="inlineStr"/>
+      <c r="AG351" s="2" t="inlineStr"/>
+      <c r="AH351" s="2" t="inlineStr"/>
+      <c r="AI351" s="2" t="inlineStr"/>
+      <c r="AJ351" s="2" t="inlineStr"/>
+    </row>
+    <row r="352">
+      <c r="A352" s="2" t="inlineStr">
+        <is>
+          <t>4b2c3ea593d74eaa</t>
+        </is>
+      </c>
+      <c r="B352" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C352" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D352" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E352" s="2" t="inlineStr">
+        <is>
+          <t>435dd174dda6c60c4ff8f96f4d947a2fd4271193ba1a936edab2e5eb50f50832</t>
+        </is>
+      </c>
+      <c r="F352" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G352" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H352" s="2" t="inlineStr">
+        <is>
+          <t>70788</t>
+        </is>
+      </c>
+      <c r="I352" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J352" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K352" s="2" t="inlineStr"/>
+      <c r="L352" s="2" t="inlineStr">
+        <is>
+          <t>0.692797</t>
+        </is>
+      </c>
+      <c r="M352" s="2" t="inlineStr"/>
+      <c r="N352" s="2" t="inlineStr"/>
+      <c r="O352" s="2" t="inlineStr">
+        <is>
+          <t>0.6805111821086262</t>
+        </is>
+      </c>
+      <c r="P352" s="2" t="inlineStr"/>
+      <c r="Q352" s="2" t="inlineStr">
+        <is>
+          <t>0.01228581789137384</t>
+        </is>
+      </c>
+      <c r="R352" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:46:58.145389Z</t>
+        </is>
+      </c>
+      <c r="S352" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="T352" s="2" t="inlineStr"/>
+      <c r="U352" s="2" t="inlineStr"/>
+      <c r="V352" s="2" t="inlineStr"/>
+      <c r="W352" s="2" t="inlineStr"/>
+      <c r="X352" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y352" s="2" t="inlineStr"/>
+      <c r="Z352" s="2" t="inlineStr"/>
+      <c r="AA352" s="2" t="inlineStr"/>
+      <c r="AB352" s="2" t="inlineStr"/>
+      <c r="AC352" s="2" t="inlineStr"/>
+      <c r="AD352" s="2" t="inlineStr"/>
+      <c r="AE352" s="2" t="inlineStr"/>
+      <c r="AF352" s="2" t="inlineStr"/>
+      <c r="AG352" s="2" t="inlineStr"/>
+      <c r="AH352" s="2" t="inlineStr"/>
+      <c r="AI352" s="2" t="inlineStr"/>
+      <c r="AJ352" s="2" t="inlineStr"/>
+    </row>
+    <row r="353">
+      <c r="A353" s="2" t="inlineStr">
+        <is>
+          <t>05c28b1492be4095</t>
+        </is>
+      </c>
+      <c r="B353" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C353" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D353" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E353" s="2" t="inlineStr">
+        <is>
+          <t>435dd174dda6c60c4ff8f96f4d947a2fd4271193ba1a936edab2e5eb50f50832</t>
+        </is>
+      </c>
+      <c r="F353" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G353" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H353" s="2" t="inlineStr">
+        <is>
+          <t>70790</t>
+        </is>
+      </c>
+      <c r="I353" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J353" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K353" s="2" t="inlineStr"/>
+      <c r="L353" s="2" t="inlineStr">
+        <is>
+          <t>0.764979</t>
+        </is>
+      </c>
+      <c r="M353" s="2" t="inlineStr"/>
+      <c r="N353" s="2" t="inlineStr"/>
+      <c r="O353" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P353" s="2" t="inlineStr"/>
+      <c r="Q353" s="2" t="inlineStr">
+        <is>
+          <t>0.17481506557377047</t>
+        </is>
+      </c>
+      <c r="R353" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:46:59.292665Z</t>
+        </is>
+      </c>
+      <c r="S353" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="T353" s="2" t="inlineStr"/>
+      <c r="U353" s="2" t="inlineStr"/>
+      <c r="V353" s="2" t="inlineStr"/>
+      <c r="W353" s="2" t="inlineStr"/>
+      <c r="X353" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y353" s="2" t="inlineStr"/>
+      <c r="Z353" s="2" t="inlineStr"/>
+      <c r="AA353" s="2" t="inlineStr"/>
+      <c r="AB353" s="2" t="inlineStr"/>
+      <c r="AC353" s="2" t="inlineStr"/>
+      <c r="AD353" s="2" t="inlineStr"/>
+      <c r="AE353" s="2" t="inlineStr"/>
+      <c r="AF353" s="2" t="inlineStr"/>
+      <c r="AG353" s="2" t="inlineStr"/>
+      <c r="AH353" s="2" t="inlineStr"/>
+      <c r="AI353" s="2" t="inlineStr"/>
+      <c r="AJ353" s="2" t="inlineStr"/>
+    </row>
+    <row r="354">
+      <c r="A354" s="2" t="inlineStr">
+        <is>
+          <t>7a09f4361c7f4a0e</t>
+        </is>
+      </c>
+      <c r="B354" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C354" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D354" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E354" s="2" t="inlineStr">
+        <is>
+          <t>435dd174dda6c60c4ff8f96f4d947a2fd4271193ba1a936edab2e5eb50f50832</t>
+        </is>
+      </c>
+      <c r="F354" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G354" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H354" s="2" t="inlineStr">
+        <is>
+          <t>70860</t>
+        </is>
+      </c>
+      <c r="I354" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J354" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K354" s="2" t="inlineStr"/>
+      <c r="L354" s="2" t="inlineStr">
+        <is>
+          <t>0.744385</t>
+        </is>
+      </c>
+      <c r="M354" s="2" t="inlineStr"/>
+      <c r="N354" s="2" t="inlineStr"/>
+      <c r="O354" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P354" s="2" t="inlineStr"/>
+      <c r="Q354" s="2" t="inlineStr">
+        <is>
+          <t>0.14438499999999987</t>
+        </is>
+      </c>
+      <c r="R354" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:47:00.687985Z</t>
+        </is>
+      </c>
+      <c r="S354" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T354" s="2" t="inlineStr"/>
+      <c r="U354" s="2" t="inlineStr"/>
+      <c r="V354" s="2" t="inlineStr"/>
+      <c r="W354" s="2" t="inlineStr"/>
+      <c r="X354" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y354" s="2" t="inlineStr"/>
+      <c r="Z354" s="2" t="inlineStr"/>
+      <c r="AA354" s="2" t="inlineStr"/>
+      <c r="AB354" s="2" t="inlineStr"/>
+      <c r="AC354" s="2" t="inlineStr"/>
+      <c r="AD354" s="2" t="inlineStr"/>
+      <c r="AE354" s="2" t="inlineStr"/>
+      <c r="AF354" s="2" t="inlineStr"/>
+      <c r="AG354" s="2" t="inlineStr"/>
+      <c r="AH354" s="2" t="inlineStr"/>
+      <c r="AI354" s="2" t="inlineStr"/>
+      <c r="AJ354" s="2" t="inlineStr"/>
+    </row>
+    <row r="355">
+      <c r="A355" s="2" t="inlineStr">
+        <is>
+          <t>94c0c891de52480c</t>
+        </is>
+      </c>
+      <c r="B355" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C355" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D355" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E355" s="2" t="inlineStr">
+        <is>
+          <t>435dd174dda6c60c4ff8f96f4d947a2fd4271193ba1a936edab2e5eb50f50832</t>
+        </is>
+      </c>
+      <c r="F355" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G355" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H355" s="2" t="inlineStr">
+        <is>
+          <t>70862</t>
+        </is>
+      </c>
+      <c r="I355" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J355" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K355" s="2" t="inlineStr"/>
+      <c r="L355" s="2" t="inlineStr">
+        <is>
+          <t>0.698245</t>
+        </is>
+      </c>
+      <c r="M355" s="2" t="inlineStr"/>
+      <c r="N355" s="2" t="inlineStr"/>
+      <c r="O355" s="2" t="inlineStr">
+        <is>
+          <t>0.66996699669967</t>
+        </is>
+      </c>
+      <c r="P355" s="2" t="inlineStr"/>
+      <c r="Q355" s="2" t="inlineStr">
+        <is>
+          <t>0.028278003300330035</t>
+        </is>
+      </c>
+      <c r="R355" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:47:01.435651Z</t>
+        </is>
+      </c>
+      <c r="S355" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T355" s="2" t="inlineStr"/>
+      <c r="U355" s="2" t="inlineStr"/>
+      <c r="V355" s="2" t="inlineStr"/>
+      <c r="W355" s="2" t="inlineStr"/>
+      <c r="X355" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y355" s="2" t="inlineStr"/>
+      <c r="Z355" s="2" t="inlineStr"/>
+      <c r="AA355" s="2" t="inlineStr"/>
+      <c r="AB355" s="2" t="inlineStr"/>
+      <c r="AC355" s="2" t="inlineStr"/>
+      <c r="AD355" s="2" t="inlineStr"/>
+      <c r="AE355" s="2" t="inlineStr"/>
+      <c r="AF355" s="2" t="inlineStr"/>
+      <c r="AG355" s="2" t="inlineStr"/>
+      <c r="AH355" s="2" t="inlineStr"/>
+      <c r="AI355" s="2" t="inlineStr"/>
+      <c r="AJ355" s="2" t="inlineStr"/>
+    </row>
+    <row r="356">
+      <c r="A356" s="2" t="inlineStr">
+        <is>
+          <t>081796a04ad74d26</t>
+        </is>
+      </c>
+      <c r="B356" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C356" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D356" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E356" s="2" t="inlineStr">
+        <is>
+          <t>435dd174dda6c60c4ff8f96f4d947a2fd4271193ba1a936edab2e5eb50f50832</t>
+        </is>
+      </c>
+      <c r="F356" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G356" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H356" s="2" t="inlineStr">
+        <is>
+          <t>70899</t>
+        </is>
+      </c>
+      <c r="I356" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J356" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K356" s="2" t="inlineStr"/>
+      <c r="L356" s="2" t="inlineStr">
+        <is>
+          <t>0.655659</t>
+        </is>
+      </c>
+      <c r="M356" s="2" t="inlineStr"/>
+      <c r="N356" s="2" t="inlineStr"/>
+      <c r="O356" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P356" s="2" t="inlineStr"/>
+      <c r="Q356" s="2" t="inlineStr">
+        <is>
+          <t>0.08484354935622318</t>
+        </is>
+      </c>
+      <c r="R356" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:47:03.963274Z</t>
+        </is>
+      </c>
+      <c r="S356" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T356" s="2" t="inlineStr"/>
+      <c r="U356" s="2" t="inlineStr"/>
+      <c r="V356" s="2" t="inlineStr"/>
+      <c r="W356" s="2" t="inlineStr"/>
+      <c r="X356" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y356" s="2" t="inlineStr"/>
+      <c r="Z356" s="2" t="inlineStr"/>
+      <c r="AA356" s="2" t="inlineStr"/>
+      <c r="AB356" s="2" t="inlineStr"/>
+      <c r="AC356" s="2" t="inlineStr"/>
+      <c r="AD356" s="2" t="inlineStr"/>
+      <c r="AE356" s="2" t="inlineStr"/>
+      <c r="AF356" s="2" t="inlineStr"/>
+      <c r="AG356" s="2" t="inlineStr"/>
+      <c r="AH356" s="2" t="inlineStr"/>
+      <c r="AI356" s="2" t="inlineStr"/>
+      <c r="AJ356" s="2" t="inlineStr"/>
+    </row>
+    <row r="357">
+      <c r="A357" s="2" t="inlineStr">
+        <is>
+          <t>bf9d8c42e4cf498d</t>
+        </is>
+      </c>
+      <c r="B357" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C357" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D357" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E357" s="2" t="inlineStr">
+        <is>
+          <t>435dd174dda6c60c4ff8f96f4d947a2fd4271193ba1a936edab2e5eb50f50832</t>
+        </is>
+      </c>
+      <c r="F357" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G357" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H357" s="2" t="inlineStr">
+        <is>
+          <t>70903</t>
+        </is>
+      </c>
+      <c r="I357" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J357" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K357" s="2" t="inlineStr"/>
+      <c r="L357" s="2" t="inlineStr">
+        <is>
+          <t>0.632067</t>
+        </is>
+      </c>
+      <c r="M357" s="2" t="inlineStr"/>
+      <c r="N357" s="2" t="inlineStr"/>
+      <c r="O357" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P357" s="2" t="inlineStr"/>
+      <c r="Q357" s="2" t="inlineStr">
+        <is>
+          <t>0.08251745045045056</t>
+        </is>
+      </c>
+      <c r="R357" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:47:05.965482Z</t>
+        </is>
+      </c>
+      <c r="S357" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T357" s="2" t="inlineStr"/>
+      <c r="U357" s="2" t="inlineStr"/>
+      <c r="V357" s="2" t="inlineStr"/>
+      <c r="W357" s="2" t="inlineStr"/>
+      <c r="X357" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y357" s="2" t="inlineStr"/>
+      <c r="Z357" s="2" t="inlineStr"/>
+      <c r="AA357" s="2" t="inlineStr"/>
+      <c r="AB357" s="2" t="inlineStr"/>
+      <c r="AC357" s="2" t="inlineStr"/>
+      <c r="AD357" s="2" t="inlineStr"/>
+      <c r="AE357" s="2" t="inlineStr"/>
+      <c r="AF357" s="2" t="inlineStr"/>
+      <c r="AG357" s="2" t="inlineStr"/>
+      <c r="AH357" s="2" t="inlineStr"/>
+      <c r="AI357" s="2" t="inlineStr"/>
+      <c r="AJ357" s="2" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="2" t="inlineStr">
+        <is>
+          <t>0ea9c730842040d6</t>
+        </is>
+      </c>
+      <c r="B358" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C358" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D358" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E358" s="2" t="inlineStr">
+        <is>
+          <t>435dd174dda6c60c4ff8f96f4d947a2fd4271193ba1a936edab2e5eb50f50832</t>
+        </is>
+      </c>
+      <c r="F358" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G358" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H358" s="2" t="inlineStr">
+        <is>
+          <t>71214</t>
+        </is>
+      </c>
+      <c r="I358" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J358" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K358" s="2" t="inlineStr"/>
+      <c r="L358" s="2" t="inlineStr">
+        <is>
+          <t>0.639158</t>
+        </is>
+      </c>
+      <c r="M358" s="2" t="inlineStr"/>
+      <c r="N358" s="2" t="inlineStr"/>
+      <c r="O358" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P358" s="2" t="inlineStr"/>
+      <c r="Q358" s="2" t="inlineStr">
+        <is>
+          <t>0.07968663436123347</t>
+        </is>
+      </c>
+      <c r="R358" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:47:09.243957Z</t>
+        </is>
+      </c>
+      <c r="S358" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T358" s="2" t="inlineStr"/>
+      <c r="U358" s="2" t="inlineStr"/>
+      <c r="V358" s="2" t="inlineStr"/>
+      <c r="W358" s="2" t="inlineStr"/>
+      <c r="X358" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y358" s="2" t="inlineStr"/>
+      <c r="Z358" s="2" t="inlineStr"/>
+      <c r="AA358" s="2" t="inlineStr"/>
+      <c r="AB358" s="2" t="inlineStr"/>
+      <c r="AC358" s="2" t="inlineStr"/>
+      <c r="AD358" s="2" t="inlineStr"/>
+      <c r="AE358" s="2" t="inlineStr"/>
+      <c r="AF358" s="2" t="inlineStr"/>
+      <c r="AG358" s="2" t="inlineStr"/>
+      <c r="AH358" s="2" t="inlineStr"/>
+      <c r="AI358" s="2" t="inlineStr"/>
+      <c r="AJ358" s="2" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" s="2" t="inlineStr">
+        <is>
+          <t>8c11704386324163</t>
+        </is>
+      </c>
+      <c r="B359" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C359" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D359" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E359" s="2" t="inlineStr">
+        <is>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
+        </is>
+      </c>
+      <c r="F359" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G359" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H359" s="2" t="inlineStr">
+        <is>
+          <t>69871</t>
+        </is>
+      </c>
+      <c r="I359" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J359" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K359" s="2" t="inlineStr"/>
+      <c r="L359" s="2" t="inlineStr">
+        <is>
+          <t>0.54899</t>
+        </is>
+      </c>
+      <c r="M359" s="2" t="inlineStr"/>
+      <c r="N359" s="2" t="inlineStr"/>
+      <c r="O359" s="2" t="inlineStr">
+        <is>
+          <t>0.49019607843137253</t>
+        </is>
+      </c>
+      <c r="P359" s="2" t="inlineStr"/>
+      <c r="Q359" s="2" t="inlineStr">
+        <is>
+          <t>0.05879392156862745</t>
+        </is>
+      </c>
+      <c r="R359" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:56:13.554249Z</t>
+        </is>
+      </c>
+      <c r="S359" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T359" s="2" t="inlineStr"/>
+      <c r="U359" s="2" t="inlineStr"/>
+      <c r="V359" s="2" t="inlineStr"/>
+      <c r="W359" s="2" t="inlineStr"/>
+      <c r="X359" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y359" s="2" t="inlineStr"/>
+      <c r="Z359" s="2" t="inlineStr"/>
+      <c r="AA359" s="2" t="inlineStr"/>
+      <c r="AB359" s="2" t="inlineStr"/>
+      <c r="AC359" s="2" t="inlineStr"/>
+      <c r="AD359" s="2" t="inlineStr"/>
+      <c r="AE359" s="2" t="inlineStr"/>
+      <c r="AF359" s="2" t="inlineStr"/>
+      <c r="AG359" s="2" t="inlineStr"/>
+      <c r="AH359" s="2" t="inlineStr"/>
+      <c r="AI359" s="2" t="inlineStr"/>
+      <c r="AJ359" s="2" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="A360" s="2" t="inlineStr">
+        <is>
+          <t>9922c3f5340a4c42</t>
+        </is>
+      </c>
+      <c r="B360" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C360" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D360" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E360" s="2" t="inlineStr">
+        <is>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
+        </is>
+      </c>
+      <c r="F360" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G360" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H360" s="2" t="inlineStr">
+        <is>
+          <t>70569</t>
+        </is>
+      </c>
+      <c r="I360" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J360" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K360" s="2" t="inlineStr"/>
+      <c r="L360" s="2" t="inlineStr">
+        <is>
+          <t>0.761043</t>
+        </is>
+      </c>
+      <c r="M360" s="2" t="inlineStr"/>
+      <c r="N360" s="2" t="inlineStr"/>
+      <c r="O360" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P360" s="2" t="inlineStr"/>
+      <c r="Q360" s="2" t="inlineStr">
+        <is>
+          <t>0.2305265680751174</t>
+        </is>
+      </c>
+      <c r="R360" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:56:15.101150Z</t>
+        </is>
+      </c>
+      <c r="S360" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T360" s="2" t="inlineStr"/>
+      <c r="U360" s="2" t="inlineStr"/>
+      <c r="V360" s="2" t="inlineStr"/>
+      <c r="W360" s="2" t="inlineStr"/>
+      <c r="X360" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y360" s="2" t="inlineStr"/>
+      <c r="Z360" s="2" t="inlineStr"/>
+      <c r="AA360" s="2" t="inlineStr"/>
+      <c r="AB360" s="2" t="inlineStr"/>
+      <c r="AC360" s="2" t="inlineStr"/>
+      <c r="AD360" s="2" t="inlineStr"/>
+      <c r="AE360" s="2" t="inlineStr"/>
+      <c r="AF360" s="2" t="inlineStr"/>
+      <c r="AG360" s="2" t="inlineStr"/>
+      <c r="AH360" s="2" t="inlineStr"/>
+      <c r="AI360" s="2" t="inlineStr"/>
+      <c r="AJ360" s="2" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" s="2" t="inlineStr">
+        <is>
+          <t>a49adebc8a924faa</t>
+        </is>
+      </c>
+      <c r="B361" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C361" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D361" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E361" s="2" t="inlineStr">
+        <is>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
+        </is>
+      </c>
+      <c r="F361" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G361" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H361" s="2" t="inlineStr">
+        <is>
+          <t>69930</t>
+        </is>
+      </c>
+      <c r="I361" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J361" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K361" s="2" t="inlineStr"/>
+      <c r="L361" s="2" t="inlineStr">
+        <is>
+          <t>0.559679</t>
+        </is>
+      </c>
+      <c r="M361" s="2" t="inlineStr"/>
+      <c r="N361" s="2" t="inlineStr"/>
+      <c r="O361" s="2" t="inlineStr">
+        <is>
+          <t>0.4291845493562232</t>
+        </is>
+      </c>
+      <c r="P361" s="2" t="inlineStr"/>
+      <c r="Q361" s="2" t="inlineStr">
+        <is>
+          <t>0.13049445064377685</t>
+        </is>
+      </c>
+      <c r="R361" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:56:15.697510Z</t>
+        </is>
+      </c>
+      <c r="S361" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:30:00Z</t>
+        </is>
+      </c>
+      <c r="T361" s="2" t="inlineStr"/>
+      <c r="U361" s="2" t="inlineStr"/>
+      <c r="V361" s="2" t="inlineStr"/>
+      <c r="W361" s="2" t="inlineStr"/>
+      <c r="X361" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y361" s="2" t="inlineStr"/>
+      <c r="Z361" s="2" t="inlineStr"/>
+      <c r="AA361" s="2" t="inlineStr"/>
+      <c r="AB361" s="2" t="inlineStr"/>
+      <c r="AC361" s="2" t="inlineStr"/>
+      <c r="AD361" s="2" t="inlineStr"/>
+      <c r="AE361" s="2" t="inlineStr"/>
+      <c r="AF361" s="2" t="inlineStr"/>
+      <c r="AG361" s="2" t="inlineStr"/>
+      <c r="AH361" s="2" t="inlineStr"/>
+      <c r="AI361" s="2" t="inlineStr"/>
+      <c r="AJ361" s="2" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="A362" s="2" t="inlineStr">
+        <is>
+          <t>f1c70bd714364ad8</t>
+        </is>
+      </c>
+      <c r="B362" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C362" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D362" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E362" s="2" t="inlineStr">
+        <is>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
+        </is>
+      </c>
+      <c r="F362" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G362" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H362" s="2" t="inlineStr">
+        <is>
+          <t>69931</t>
+        </is>
+      </c>
+      <c r="I362" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J362" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K362" s="2" t="inlineStr"/>
+      <c r="L362" s="2" t="inlineStr">
+        <is>
+          <t>0.598983</t>
+        </is>
+      </c>
+      <c r="M362" s="2" t="inlineStr"/>
+      <c r="N362" s="2" t="inlineStr"/>
+      <c r="O362" s="2" t="inlineStr">
+        <is>
+          <t>0.4807692307692307</t>
+        </is>
+      </c>
+      <c r="P362" s="2" t="inlineStr"/>
+      <c r="Q362" s="2" t="inlineStr">
+        <is>
+          <t>0.11821376923076932</t>
+        </is>
+      </c>
+      <c r="R362" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:56:16.191719Z</t>
+        </is>
+      </c>
+      <c r="S362" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:30:00Z</t>
+        </is>
+      </c>
+      <c r="T362" s="2" t="inlineStr"/>
+      <c r="U362" s="2" t="inlineStr"/>
+      <c r="V362" s="2" t="inlineStr"/>
+      <c r="W362" s="2" t="inlineStr"/>
+      <c r="X362" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y362" s="2" t="inlineStr"/>
+      <c r="Z362" s="2" t="inlineStr"/>
+      <c r="AA362" s="2" t="inlineStr"/>
+      <c r="AB362" s="2" t="inlineStr"/>
+      <c r="AC362" s="2" t="inlineStr"/>
+      <c r="AD362" s="2" t="inlineStr"/>
+      <c r="AE362" s="2" t="inlineStr"/>
+      <c r="AF362" s="2" t="inlineStr"/>
+      <c r="AG362" s="2" t="inlineStr"/>
+      <c r="AH362" s="2" t="inlineStr"/>
+      <c r="AI362" s="2" t="inlineStr"/>
+      <c r="AJ362" s="2" t="inlineStr"/>
+    </row>
+    <row r="363">
+      <c r="A363" s="2" t="inlineStr">
+        <is>
+          <t>df3044adc64240cc</t>
+        </is>
+      </c>
+      <c r="B363" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C363" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D363" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E363" s="2" t="inlineStr">
+        <is>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
+        </is>
+      </c>
+      <c r="F363" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G363" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H363" s="2" t="inlineStr">
+        <is>
+          <t>70045</t>
+        </is>
+      </c>
+      <c r="I363" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J363" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K363" s="2" t="inlineStr"/>
+      <c r="L363" s="2" t="inlineStr">
+        <is>
+          <t>0.598175</t>
+        </is>
+      </c>
+      <c r="M363" s="2" t="inlineStr"/>
+      <c r="N363" s="2" t="inlineStr"/>
+      <c r="O363" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P363" s="2" t="inlineStr"/>
+      <c r="Q363" s="2" t="inlineStr">
+        <is>
+          <t>0.1477245495495495</t>
+        </is>
+      </c>
+      <c r="R363" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:56:20.348944Z</t>
+        </is>
+      </c>
+      <c r="S363" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="T363" s="2" t="inlineStr"/>
+      <c r="U363" s="2" t="inlineStr"/>
+      <c r="V363" s="2" t="inlineStr"/>
+      <c r="W363" s="2" t="inlineStr"/>
+      <c r="X363" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y363" s="2" t="inlineStr"/>
+      <c r="Z363" s="2" t="inlineStr"/>
+      <c r="AA363" s="2" t="inlineStr"/>
+      <c r="AB363" s="2" t="inlineStr"/>
+      <c r="AC363" s="2" t="inlineStr"/>
+      <c r="AD363" s="2" t="inlineStr"/>
+      <c r="AE363" s="2" t="inlineStr"/>
+      <c r="AF363" s="2" t="inlineStr"/>
+      <c r="AG363" s="2" t="inlineStr"/>
+      <c r="AH363" s="2" t="inlineStr"/>
+      <c r="AI363" s="2" t="inlineStr"/>
+      <c r="AJ363" s="2" t="inlineStr"/>
+    </row>
+    <row r="364">
+      <c r="A364" s="2" t="inlineStr">
+        <is>
+          <t>4a2fe8986c5d4f72</t>
+        </is>
+      </c>
+      <c r="B364" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C364" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D364" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E364" s="2" t="inlineStr">
+        <is>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
+        </is>
+      </c>
+      <c r="F364" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G364" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H364" s="2" t="inlineStr">
+        <is>
+          <t>70301</t>
+        </is>
+      </c>
+      <c r="I364" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J364" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K364" s="2" t="inlineStr"/>
+      <c r="L364" s="2" t="inlineStr">
+        <is>
+          <t>0.584761</t>
+        </is>
+      </c>
+      <c r="M364" s="2" t="inlineStr"/>
+      <c r="N364" s="2" t="inlineStr"/>
+      <c r="O364" s="2" t="inlineStr">
+        <is>
+          <t>0.5098039215686274</t>
+        </is>
+      </c>
+      <c r="P364" s="2" t="inlineStr"/>
+      <c r="Q364" s="2" t="inlineStr">
+        <is>
+          <t>0.07495707843137256</t>
+        </is>
+      </c>
+      <c r="R364" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:56:20.853410Z</t>
+        </is>
+      </c>
+      <c r="S364" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T364" s="2" t="inlineStr"/>
+      <c r="U364" s="2" t="inlineStr"/>
+      <c r="V364" s="2" t="inlineStr"/>
+      <c r="W364" s="2" t="inlineStr"/>
+      <c r="X364" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y364" s="2" t="inlineStr"/>
+      <c r="Z364" s="2" t="inlineStr"/>
+      <c r="AA364" s="2" t="inlineStr"/>
+      <c r="AB364" s="2" t="inlineStr"/>
+      <c r="AC364" s="2" t="inlineStr"/>
+      <c r="AD364" s="2" t="inlineStr"/>
+      <c r="AE364" s="2" t="inlineStr"/>
+      <c r="AF364" s="2" t="inlineStr"/>
+      <c r="AG364" s="2" t="inlineStr"/>
+      <c r="AH364" s="2" t="inlineStr"/>
+      <c r="AI364" s="2" t="inlineStr"/>
+      <c r="AJ364" s="2" t="inlineStr"/>
+    </row>
+    <row r="365">
+      <c r="A365" s="2" t="inlineStr">
+        <is>
+          <t>8adeae1af2cb4ad1</t>
+        </is>
+      </c>
+      <c r="B365" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C365" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D365" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E365" s="2" t="inlineStr">
+        <is>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
+        </is>
+      </c>
+      <c r="F365" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G365" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H365" s="2" t="inlineStr">
+        <is>
+          <t>70349</t>
+        </is>
+      </c>
+      <c r="I365" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J365" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K365" s="2" t="inlineStr"/>
+      <c r="L365" s="2" t="inlineStr">
+        <is>
+          <t>0.670593</t>
+        </is>
+      </c>
+      <c r="M365" s="2" t="inlineStr"/>
+      <c r="N365" s="2" t="inlineStr"/>
+      <c r="O365" s="2" t="inlineStr">
+        <is>
+          <t>0.6296296296296295</t>
+        </is>
+      </c>
+      <c r="P365" s="2" t="inlineStr"/>
+      <c r="Q365" s="2" t="inlineStr">
+        <is>
+          <t>0.040963370370370455</t>
+        </is>
+      </c>
+      <c r="R365" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:56:22.599351Z</t>
+        </is>
+      </c>
+      <c r="S365" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T365" s="2" t="inlineStr"/>
+      <c r="U365" s="2" t="inlineStr"/>
+      <c r="V365" s="2" t="inlineStr"/>
+      <c r="W365" s="2" t="inlineStr"/>
+      <c r="X365" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y365" s="2" t="inlineStr"/>
+      <c r="Z365" s="2" t="inlineStr"/>
+      <c r="AA365" s="2" t="inlineStr"/>
+      <c r="AB365" s="2" t="inlineStr"/>
+      <c r="AC365" s="2" t="inlineStr"/>
+      <c r="AD365" s="2" t="inlineStr"/>
+      <c r="AE365" s="2" t="inlineStr"/>
+      <c r="AF365" s="2" t="inlineStr"/>
+      <c r="AG365" s="2" t="inlineStr"/>
+      <c r="AH365" s="2" t="inlineStr"/>
+      <c r="AI365" s="2" t="inlineStr"/>
+      <c r="AJ365" s="2" t="inlineStr"/>
+    </row>
+    <row r="366">
+      <c r="A366" s="2" t="inlineStr">
+        <is>
+          <t>e33817ecf9d547d1</t>
+        </is>
+      </c>
+      <c r="B366" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C366" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D366" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E366" s="2" t="inlineStr">
+        <is>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
+        </is>
+      </c>
+      <c r="F366" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G366" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H366" s="2" t="inlineStr">
+        <is>
+          <t>70379</t>
+        </is>
+      </c>
+      <c r="I366" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J366" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K366" s="2" t="inlineStr"/>
+      <c r="L366" s="2" t="inlineStr">
+        <is>
+          <t>0.616429</t>
+        </is>
+      </c>
+      <c r="M366" s="2" t="inlineStr"/>
+      <c r="N366" s="2" t="inlineStr"/>
+      <c r="O366" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P366" s="2" t="inlineStr"/>
+      <c r="Q366" s="2" t="inlineStr">
+        <is>
+          <t>0.17590036563876654</t>
+        </is>
+      </c>
+      <c r="R366" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:56:23.555880Z</t>
+        </is>
+      </c>
+      <c r="S366" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="T366" s="2" t="inlineStr"/>
+      <c r="U366" s="2" t="inlineStr"/>
+      <c r="V366" s="2" t="inlineStr"/>
+      <c r="W366" s="2" t="inlineStr"/>
+      <c r="X366" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y366" s="2" t="inlineStr"/>
+      <c r="Z366" s="2" t="inlineStr"/>
+      <c r="AA366" s="2" t="inlineStr"/>
+      <c r="AB366" s="2" t="inlineStr"/>
+      <c r="AC366" s="2" t="inlineStr"/>
+      <c r="AD366" s="2" t="inlineStr"/>
+      <c r="AE366" s="2" t="inlineStr"/>
+      <c r="AF366" s="2" t="inlineStr"/>
+      <c r="AG366" s="2" t="inlineStr"/>
+      <c r="AH366" s="2" t="inlineStr"/>
+      <c r="AI366" s="2" t="inlineStr"/>
+      <c r="AJ366" s="2" t="inlineStr"/>
+    </row>
+    <row r="367">
+      <c r="A367" s="2" t="inlineStr">
+        <is>
+          <t>e33653f61bf84ef4</t>
+        </is>
+      </c>
+      <c r="B367" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C367" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D367" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E367" s="2" t="inlineStr">
+        <is>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
+        </is>
+      </c>
+      <c r="F367" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G367" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H367" s="2" t="inlineStr">
+        <is>
+          <t>70560</t>
+        </is>
+      </c>
+      <c r="I367" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J367" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K367" s="2" t="inlineStr"/>
+      <c r="L367" s="2" t="inlineStr">
+        <is>
+          <t>0.602126</t>
+        </is>
+      </c>
+      <c r="M367" s="2" t="inlineStr"/>
+      <c r="N367" s="2" t="inlineStr"/>
+      <c r="O367" s="2" t="inlineStr">
+        <is>
+          <t>0.5098039215686274</t>
+        </is>
+      </c>
+      <c r="P367" s="2" t="inlineStr"/>
+      <c r="Q367" s="2" t="inlineStr">
+        <is>
+          <t>0.09232207843137263</t>
+        </is>
+      </c>
+      <c r="R367" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:56:26.928954Z</t>
+        </is>
+      </c>
+      <c r="S367" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T07:00:00Z</t>
+        </is>
+      </c>
+      <c r="T367" s="2" t="inlineStr"/>
+      <c r="U367" s="2" t="inlineStr"/>
+      <c r="V367" s="2" t="inlineStr"/>
+      <c r="W367" s="2" t="inlineStr"/>
+      <c r="X367" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y367" s="2" t="inlineStr"/>
+      <c r="Z367" s="2" t="inlineStr"/>
+      <c r="AA367" s="2" t="inlineStr"/>
+      <c r="AB367" s="2" t="inlineStr"/>
+      <c r="AC367" s="2" t="inlineStr"/>
+      <c r="AD367" s="2" t="inlineStr"/>
+      <c r="AE367" s="2" t="inlineStr"/>
+      <c r="AF367" s="2" t="inlineStr"/>
+      <c r="AG367" s="2" t="inlineStr"/>
+      <c r="AH367" s="2" t="inlineStr"/>
+      <c r="AI367" s="2" t="inlineStr"/>
+      <c r="AJ367" s="2" t="inlineStr"/>
+    </row>
+    <row r="368">
+      <c r="A368" s="2" t="inlineStr">
+        <is>
+          <t>352327989706404e</t>
+        </is>
+      </c>
+      <c r="B368" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C368" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D368" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E368" s="2" t="inlineStr">
+        <is>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
+        </is>
+      </c>
+      <c r="F368" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G368" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H368" s="2" t="inlineStr">
+        <is>
+          <t>70573</t>
+        </is>
+      </c>
+      <c r="I368" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J368" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K368" s="2" t="inlineStr"/>
+      <c r="L368" s="2" t="inlineStr">
+        <is>
+          <t>0.678118</t>
+        </is>
+      </c>
+      <c r="M368" s="2" t="inlineStr"/>
+      <c r="N368" s="2" t="inlineStr"/>
+      <c r="O368" s="2" t="inlineStr">
+        <is>
+          <t>0.4098360655737705</t>
+        </is>
+      </c>
+      <c r="P368" s="2" t="inlineStr"/>
+      <c r="Q368" s="2" t="inlineStr">
+        <is>
+          <t>0.2682819344262295</t>
+        </is>
+      </c>
+      <c r="R368" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:56:28.210290Z</t>
+        </is>
+      </c>
+      <c r="S368" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T368" s="2" t="inlineStr"/>
+      <c r="U368" s="2" t="inlineStr"/>
+      <c r="V368" s="2" t="inlineStr"/>
+      <c r="W368" s="2" t="inlineStr"/>
+      <c r="X368" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y368" s="2" t="inlineStr"/>
+      <c r="Z368" s="2" t="inlineStr"/>
+      <c r="AA368" s="2" t="inlineStr"/>
+      <c r="AB368" s="2" t="inlineStr"/>
+      <c r="AC368" s="2" t="inlineStr"/>
+      <c r="AD368" s="2" t="inlineStr"/>
+      <c r="AE368" s="2" t="inlineStr"/>
+      <c r="AF368" s="2" t="inlineStr"/>
+      <c r="AG368" s="2" t="inlineStr"/>
+      <c r="AH368" s="2" t="inlineStr"/>
+      <c r="AI368" s="2" t="inlineStr"/>
+      <c r="AJ368" s="2" t="inlineStr"/>
+    </row>
+    <row r="369">
+      <c r="A369" s="2" t="inlineStr">
+        <is>
+          <t>d1e390b0f9774a56</t>
+        </is>
+      </c>
+      <c r="B369" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C369" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D369" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E369" s="2" t="inlineStr">
+        <is>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
+        </is>
+      </c>
+      <c r="F369" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G369" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H369" s="2" t="inlineStr">
+        <is>
+          <t>70594</t>
+        </is>
+      </c>
+      <c r="I369" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J369" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K369" s="2" t="inlineStr"/>
+      <c r="L369" s="2" t="inlineStr">
+        <is>
+          <t>0.553149</t>
+        </is>
+      </c>
+      <c r="M369" s="2" t="inlineStr"/>
+      <c r="N369" s="2" t="inlineStr"/>
+      <c r="O369" s="2" t="inlineStr">
+        <is>
+          <t>0.5192307692307692</t>
+        </is>
+      </c>
+      <c r="P369" s="2" t="inlineStr"/>
+      <c r="Q369" s="2" t="inlineStr">
+        <is>
+          <t>0.03391823076923084</t>
+        </is>
+      </c>
+      <c r="R369" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:56:29.341663Z</t>
+        </is>
+      </c>
+      <c r="S369" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T369" s="2" t="inlineStr"/>
+      <c r="U369" s="2" t="inlineStr"/>
+      <c r="V369" s="2" t="inlineStr"/>
+      <c r="W369" s="2" t="inlineStr"/>
+      <c r="X369" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y369" s="2" t="inlineStr"/>
+      <c r="Z369" s="2" t="inlineStr"/>
+      <c r="AA369" s="2" t="inlineStr"/>
+      <c r="AB369" s="2" t="inlineStr"/>
+      <c r="AC369" s="2" t="inlineStr"/>
+      <c r="AD369" s="2" t="inlineStr"/>
+      <c r="AE369" s="2" t="inlineStr"/>
+      <c r="AF369" s="2" t="inlineStr"/>
+      <c r="AG369" s="2" t="inlineStr"/>
+      <c r="AH369" s="2" t="inlineStr"/>
+      <c r="AI369" s="2" t="inlineStr"/>
+      <c r="AJ369" s="2" t="inlineStr"/>
+    </row>
+    <row r="370">
+      <c r="A370" s="2" t="inlineStr">
+        <is>
+          <t>9a0779b558744d3b</t>
+        </is>
+      </c>
+      <c r="B370" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C370" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D370" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E370" s="2" t="inlineStr">
+        <is>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
+        </is>
+      </c>
+      <c r="F370" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G370" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H370" s="2" t="inlineStr">
+        <is>
+          <t>70788</t>
+        </is>
+      </c>
+      <c r="I370" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J370" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K370" s="2" t="inlineStr"/>
+      <c r="L370" s="2" t="inlineStr">
+        <is>
+          <t>0.692554</t>
+        </is>
+      </c>
+      <c r="M370" s="2" t="inlineStr"/>
+      <c r="N370" s="2" t="inlineStr"/>
+      <c r="O370" s="2" t="inlineStr">
+        <is>
+          <t>0.6805111821086262</t>
+        </is>
+      </c>
+      <c r="P370" s="2" t="inlineStr"/>
+      <c r="Q370" s="2" t="inlineStr">
+        <is>
+          <t>0.012042817891373847</t>
+        </is>
+      </c>
+      <c r="R370" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:56:33.192924Z</t>
+        </is>
+      </c>
+      <c r="S370" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="T370" s="2" t="inlineStr"/>
+      <c r="U370" s="2" t="inlineStr"/>
+      <c r="V370" s="2" t="inlineStr"/>
+      <c r="W370" s="2" t="inlineStr"/>
+      <c r="X370" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y370" s="2" t="inlineStr"/>
+      <c r="Z370" s="2" t="inlineStr"/>
+      <c r="AA370" s="2" t="inlineStr"/>
+      <c r="AB370" s="2" t="inlineStr"/>
+      <c r="AC370" s="2" t="inlineStr"/>
+      <c r="AD370" s="2" t="inlineStr"/>
+      <c r="AE370" s="2" t="inlineStr"/>
+      <c r="AF370" s="2" t="inlineStr"/>
+      <c r="AG370" s="2" t="inlineStr"/>
+      <c r="AH370" s="2" t="inlineStr"/>
+      <c r="AI370" s="2" t="inlineStr"/>
+      <c r="AJ370" s="2" t="inlineStr"/>
+    </row>
+    <row r="371">
+      <c r="A371" s="2" t="inlineStr">
+        <is>
+          <t>81e9fadda3844370</t>
+        </is>
+      </c>
+      <c r="B371" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C371" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D371" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E371" s="2" t="inlineStr">
+        <is>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
+        </is>
+      </c>
+      <c r="F371" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G371" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H371" s="2" t="inlineStr">
+        <is>
+          <t>70790</t>
+        </is>
+      </c>
+      <c r="I371" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J371" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K371" s="2" t="inlineStr"/>
+      <c r="L371" s="2" t="inlineStr">
+        <is>
+          <t>0.764526</t>
+        </is>
+      </c>
+      <c r="M371" s="2" t="inlineStr"/>
+      <c r="N371" s="2" t="inlineStr"/>
+      <c r="O371" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P371" s="2" t="inlineStr"/>
+      <c r="Q371" s="2" t="inlineStr">
+        <is>
+          <t>0.17436206557377054</t>
+        </is>
+      </c>
+      <c r="R371" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:56:34.263579Z</t>
+        </is>
+      </c>
+      <c r="S371" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="T371" s="2" t="inlineStr"/>
+      <c r="U371" s="2" t="inlineStr"/>
+      <c r="V371" s="2" t="inlineStr"/>
+      <c r="W371" s="2" t="inlineStr"/>
+      <c r="X371" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y371" s="2" t="inlineStr"/>
+      <c r="Z371" s="2" t="inlineStr"/>
+      <c r="AA371" s="2" t="inlineStr"/>
+      <c r="AB371" s="2" t="inlineStr"/>
+      <c r="AC371" s="2" t="inlineStr"/>
+      <c r="AD371" s="2" t="inlineStr"/>
+      <c r="AE371" s="2" t="inlineStr"/>
+      <c r="AF371" s="2" t="inlineStr"/>
+      <c r="AG371" s="2" t="inlineStr"/>
+      <c r="AH371" s="2" t="inlineStr"/>
+      <c r="AI371" s="2" t="inlineStr"/>
+      <c r="AJ371" s="2" t="inlineStr"/>
+    </row>
+    <row r="372">
+      <c r="A372" s="2" t="inlineStr">
+        <is>
+          <t>a56348dbec86461c</t>
+        </is>
+      </c>
+      <c r="B372" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C372" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D372" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E372" s="2" t="inlineStr">
+        <is>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
+        </is>
+      </c>
+      <c r="F372" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G372" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H372" s="2" t="inlineStr">
+        <is>
+          <t>70860</t>
+        </is>
+      </c>
+      <c r="I372" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J372" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K372" s="2" t="inlineStr"/>
+      <c r="L372" s="2" t="inlineStr">
+        <is>
+          <t>0.744077</t>
+        </is>
+      </c>
+      <c r="M372" s="2" t="inlineStr"/>
+      <c r="N372" s="2" t="inlineStr"/>
+      <c r="O372" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P372" s="2" t="inlineStr"/>
+      <c r="Q372" s="2" t="inlineStr">
+        <is>
+          <t>0.1440769999999999</t>
+        </is>
+      </c>
+      <c r="R372" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:56:34.906561Z</t>
+        </is>
+      </c>
+      <c r="S372" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T372" s="2" t="inlineStr"/>
+      <c r="U372" s="2" t="inlineStr"/>
+      <c r="V372" s="2" t="inlineStr"/>
+      <c r="W372" s="2" t="inlineStr"/>
+      <c r="X372" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y372" s="2" t="inlineStr"/>
+      <c r="Z372" s="2" t="inlineStr"/>
+      <c r="AA372" s="2" t="inlineStr"/>
+      <c r="AB372" s="2" t="inlineStr"/>
+      <c r="AC372" s="2" t="inlineStr"/>
+      <c r="AD372" s="2" t="inlineStr"/>
+      <c r="AE372" s="2" t="inlineStr"/>
+      <c r="AF372" s="2" t="inlineStr"/>
+      <c r="AG372" s="2" t="inlineStr"/>
+      <c r="AH372" s="2" t="inlineStr"/>
+      <c r="AI372" s="2" t="inlineStr"/>
+      <c r="AJ372" s="2" t="inlineStr"/>
+    </row>
+    <row r="373">
+      <c r="A373" s="2" t="inlineStr">
+        <is>
+          <t>3d923efefa514069</t>
+        </is>
+      </c>
+      <c r="B373" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C373" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D373" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E373" s="2" t="inlineStr">
+        <is>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
+        </is>
+      </c>
+      <c r="F373" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G373" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H373" s="2" t="inlineStr">
+        <is>
+          <t>70862</t>
+        </is>
+      </c>
+      <c r="I373" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J373" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K373" s="2" t="inlineStr"/>
+      <c r="L373" s="2" t="inlineStr">
+        <is>
+          <t>0.697999</t>
+        </is>
+      </c>
+      <c r="M373" s="2" t="inlineStr"/>
+      <c r="N373" s="2" t="inlineStr"/>
+      <c r="O373" s="2" t="inlineStr">
+        <is>
+          <t>0.6503496503496503</t>
+        </is>
+      </c>
+      <c r="P373" s="2" t="inlineStr"/>
+      <c r="Q373" s="2" t="inlineStr">
+        <is>
+          <t>0.047649349650349726</t>
+        </is>
+      </c>
+      <c r="R373" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:56:35.496841Z</t>
+        </is>
+      </c>
+      <c r="S373" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T373" s="2" t="inlineStr"/>
+      <c r="U373" s="2" t="inlineStr"/>
+      <c r="V373" s="2" t="inlineStr"/>
+      <c r="W373" s="2" t="inlineStr"/>
+      <c r="X373" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y373" s="2" t="inlineStr"/>
+      <c r="Z373" s="2" t="inlineStr"/>
+      <c r="AA373" s="2" t="inlineStr"/>
+      <c r="AB373" s="2" t="inlineStr"/>
+      <c r="AC373" s="2" t="inlineStr"/>
+      <c r="AD373" s="2" t="inlineStr"/>
+      <c r="AE373" s="2" t="inlineStr"/>
+      <c r="AF373" s="2" t="inlineStr"/>
+      <c r="AG373" s="2" t="inlineStr"/>
+      <c r="AH373" s="2" t="inlineStr"/>
+      <c r="AI373" s="2" t="inlineStr"/>
+      <c r="AJ373" s="2" t="inlineStr"/>
+    </row>
+    <row r="374">
+      <c r="A374" s="2" t="inlineStr">
+        <is>
+          <t>fcc1f1e498364ada</t>
+        </is>
+      </c>
+      <c r="B374" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C374" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D374" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E374" s="2" t="inlineStr">
+        <is>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
+        </is>
+      </c>
+      <c r="F374" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G374" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H374" s="2" t="inlineStr">
+        <is>
+          <t>70899</t>
+        </is>
+      </c>
+      <c r="I374" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J374" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K374" s="2" t="inlineStr"/>
+      <c r="L374" s="2" t="inlineStr">
+        <is>
+          <t>0.655472</t>
+        </is>
+      </c>
+      <c r="M374" s="2" t="inlineStr"/>
+      <c r="N374" s="2" t="inlineStr"/>
+      <c r="O374" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P374" s="2" t="inlineStr"/>
+      <c r="Q374" s="2" t="inlineStr">
+        <is>
+          <t>0.08465654935622324</t>
+        </is>
+      </c>
+      <c r="R374" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:56:37.925941Z</t>
+        </is>
+      </c>
+      <c r="S374" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T374" s="2" t="inlineStr"/>
+      <c r="U374" s="2" t="inlineStr"/>
+      <c r="V374" s="2" t="inlineStr"/>
+      <c r="W374" s="2" t="inlineStr"/>
+      <c r="X374" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y374" s="2" t="inlineStr"/>
+      <c r="Z374" s="2" t="inlineStr"/>
+      <c r="AA374" s="2" t="inlineStr"/>
+      <c r="AB374" s="2" t="inlineStr"/>
+      <c r="AC374" s="2" t="inlineStr"/>
+      <c r="AD374" s="2" t="inlineStr"/>
+      <c r="AE374" s="2" t="inlineStr"/>
+      <c r="AF374" s="2" t="inlineStr"/>
+      <c r="AG374" s="2" t="inlineStr"/>
+      <c r="AH374" s="2" t="inlineStr"/>
+      <c r="AI374" s="2" t="inlineStr"/>
+      <c r="AJ374" s="2" t="inlineStr"/>
+    </row>
+    <row r="375">
+      <c r="A375" s="2" t="inlineStr">
+        <is>
+          <t>be1cd3d463534f94</t>
+        </is>
+      </c>
+      <c r="B375" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C375" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D375" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E375" s="2" t="inlineStr">
+        <is>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
+        </is>
+      </c>
+      <c r="F375" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G375" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H375" s="2" t="inlineStr">
+        <is>
+          <t>70903</t>
+        </is>
+      </c>
+      <c r="I375" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J375" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K375" s="2" t="inlineStr"/>
+      <c r="L375" s="2" t="inlineStr">
+        <is>
+          <t>0.631922</t>
+        </is>
+      </c>
+      <c r="M375" s="2" t="inlineStr"/>
+      <c r="N375" s="2" t="inlineStr"/>
+      <c r="O375" s="2" t="inlineStr">
+        <is>
+          <t>0.5192307692307692</t>
+        </is>
+      </c>
+      <c r="P375" s="2" t="inlineStr"/>
+      <c r="Q375" s="2" t="inlineStr">
+        <is>
+          <t>0.11269123076923082</t>
+        </is>
+      </c>
+      <c r="R375" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:56:39.588429Z</t>
+        </is>
+      </c>
+      <c r="S375" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T375" s="2" t="inlineStr"/>
+      <c r="U375" s="2" t="inlineStr"/>
+      <c r="V375" s="2" t="inlineStr"/>
+      <c r="W375" s="2" t="inlineStr"/>
+      <c r="X375" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y375" s="2" t="inlineStr"/>
+      <c r="Z375" s="2" t="inlineStr"/>
+      <c r="AA375" s="2" t="inlineStr"/>
+      <c r="AB375" s="2" t="inlineStr"/>
+      <c r="AC375" s="2" t="inlineStr"/>
+      <c r="AD375" s="2" t="inlineStr"/>
+      <c r="AE375" s="2" t="inlineStr"/>
+      <c r="AF375" s="2" t="inlineStr"/>
+      <c r="AG375" s="2" t="inlineStr"/>
+      <c r="AH375" s="2" t="inlineStr"/>
+      <c r="AI375" s="2" t="inlineStr"/>
+      <c r="AJ375" s="2" t="inlineStr"/>
+    </row>
+    <row r="376">
+      <c r="A376" s="2" t="inlineStr">
+        <is>
+          <t>a2b40f88bad1492a</t>
+        </is>
+      </c>
+      <c r="B376" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C376" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D376" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E376" s="2" t="inlineStr">
+        <is>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
+        </is>
+      </c>
+      <c r="F376" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G376" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H376" s="2" t="inlineStr">
+        <is>
+          <t>71214</t>
+        </is>
+      </c>
+      <c r="I376" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J376" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K376" s="2" t="inlineStr"/>
+      <c r="L376" s="2" t="inlineStr">
+        <is>
+          <t>0.638828</t>
+        </is>
+      </c>
+      <c r="M376" s="2" t="inlineStr"/>
+      <c r="N376" s="2" t="inlineStr"/>
+      <c r="O376" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P376" s="2" t="inlineStr"/>
+      <c r="Q376" s="2" t="inlineStr">
+        <is>
+          <t>0.07935663436123341</t>
+        </is>
+      </c>
+      <c r="R376" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:56:42.235304Z</t>
+        </is>
+      </c>
+      <c r="S376" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T376" s="2" t="inlineStr"/>
+      <c r="U376" s="2" t="inlineStr"/>
+      <c r="V376" s="2" t="inlineStr"/>
+      <c r="W376" s="2" t="inlineStr"/>
+      <c r="X376" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y376" s="2" t="inlineStr"/>
+      <c r="Z376" s="2" t="inlineStr"/>
+      <c r="AA376" s="2" t="inlineStr"/>
+      <c r="AB376" s="2" t="inlineStr"/>
+      <c r="AC376" s="2" t="inlineStr"/>
+      <c r="AD376" s="2" t="inlineStr"/>
+      <c r="AE376" s="2" t="inlineStr"/>
+      <c r="AF376" s="2" t="inlineStr"/>
+      <c r="AG376" s="2" t="inlineStr"/>
+      <c r="AH376" s="2" t="inlineStr"/>
+      <c r="AI376" s="2" t="inlineStr"/>
+      <c r="AJ376" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ322"/>
+  <autoFilter ref="A1:AJ376"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/gated_research/model_ledgers/lol-tiered-elo.xlsx
+++ b/data/gated_research/model_ledgers/lol-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$376</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$425</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ376"/>
+  <dimension ref="A1:AJ425"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -32030,14 +32030,34 @@
       <c r="W306" s="2" t="inlineStr"/>
       <c r="X306" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y306" s="2" t="inlineStr"/>
-      <c r="Z306" s="2" t="inlineStr"/>
-      <c r="AA306" s="2" t="inlineStr"/>
-      <c r="AB306" s="2" t="inlineStr"/>
-      <c r="AC306" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y306" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z306" s="2" t="inlineStr">
+        <is>
+          <t>0.520000</t>
+        </is>
+      </c>
+      <c r="AA306" s="2" t="inlineStr">
+        <is>
+          <t>0.000769</t>
+        </is>
+      </c>
+      <c r="AB306" s="2" t="inlineStr">
+        <is>
+          <t>-1.5000</t>
+        </is>
+      </c>
+      <c r="AC306" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:01:21.114079Z</t>
+        </is>
+      </c>
       <c r="AD306" s="2" t="inlineStr"/>
       <c r="AE306" s="2" t="inlineStr"/>
       <c r="AF306" s="2" t="inlineStr"/>
@@ -37436,14 +37456,34 @@
       <c r="W359" s="2" t="inlineStr"/>
       <c r="X359" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y359" s="2" t="inlineStr"/>
-      <c r="Z359" s="2" t="inlineStr"/>
-      <c r="AA359" s="2" t="inlineStr"/>
-      <c r="AB359" s="2" t="inlineStr"/>
-      <c r="AC359" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y359" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z359" s="2" t="inlineStr">
+        <is>
+          <t>0.490000</t>
+        </is>
+      </c>
+      <c r="AA359" s="2" t="inlineStr">
+        <is>
+          <t>-0.000196</t>
+        </is>
+      </c>
+      <c r="AB359" s="2" t="inlineStr">
+        <is>
+          <t>1.0400</t>
+        </is>
+      </c>
+      <c r="AC359" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:26.940711Z</t>
+        </is>
+      </c>
       <c r="AD359" s="2" t="inlineStr"/>
       <c r="AE359" s="2" t="inlineStr"/>
       <c r="AF359" s="2" t="inlineStr"/>
@@ -37538,14 +37578,34 @@
       <c r="W360" s="2" t="inlineStr"/>
       <c r="X360" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y360" s="2" t="inlineStr"/>
-      <c r="Z360" s="2" t="inlineStr"/>
-      <c r="AA360" s="2" t="inlineStr"/>
-      <c r="AB360" s="2" t="inlineStr"/>
-      <c r="AC360" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y360" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z360" s="2" t="inlineStr">
+        <is>
+          <t>0.530000</t>
+        </is>
+      </c>
+      <c r="AA360" s="2" t="inlineStr">
+        <is>
+          <t>-0.000516</t>
+        </is>
+      </c>
+      <c r="AB360" s="2" t="inlineStr">
+        <is>
+          <t>-2.0000</t>
+        </is>
+      </c>
+      <c r="AC360" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:28.320203Z</t>
+        </is>
+      </c>
       <c r="AD360" s="2" t="inlineStr"/>
       <c r="AE360" s="2" t="inlineStr"/>
       <c r="AF360" s="2" t="inlineStr"/>
@@ -39186,8 +39246,5126 @@
       <c r="AI376" s="2" t="inlineStr"/>
       <c r="AJ376" s="2" t="inlineStr"/>
     </row>
+    <row r="377">
+      <c r="A377" s="2" t="inlineStr">
+        <is>
+          <t>87a88abac0384aa8</t>
+        </is>
+      </c>
+      <c r="B377" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C377" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D377" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E377" s="2" t="inlineStr">
+        <is>
+          <t>4863ace20696b49ac8d86afb992436652bb1bb2b13aa3380a50818cc662a18c0</t>
+        </is>
+      </c>
+      <c r="F377" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G377" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H377" s="2" t="inlineStr">
+        <is>
+          <t>69931</t>
+        </is>
+      </c>
+      <c r="I377" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J377" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K377" s="2" t="inlineStr"/>
+      <c r="L377" s="2" t="inlineStr">
+        <is>
+          <t>0.597761</t>
+        </is>
+      </c>
+      <c r="M377" s="2" t="inlineStr"/>
+      <c r="N377" s="2" t="inlineStr"/>
+      <c r="O377" s="2" t="inlineStr">
+        <is>
+          <t>0.49019607843137253</t>
+        </is>
+      </c>
+      <c r="P377" s="2" t="inlineStr"/>
+      <c r="Q377" s="2" t="inlineStr">
+        <is>
+          <t>0.10756492156862746</t>
+        </is>
+      </c>
+      <c r="R377" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:04:41.345485Z</t>
+        </is>
+      </c>
+      <c r="S377" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:30:00Z</t>
+        </is>
+      </c>
+      <c r="T377" s="2" t="inlineStr"/>
+      <c r="U377" s="2" t="inlineStr"/>
+      <c r="V377" s="2" t="inlineStr"/>
+      <c r="W377" s="2" t="inlineStr"/>
+      <c r="X377" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y377" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z377" s="2" t="inlineStr">
+        <is>
+          <t>0.490000</t>
+        </is>
+      </c>
+      <c r="AA377" s="2" t="inlineStr">
+        <is>
+          <t>-0.000196</t>
+        </is>
+      </c>
+      <c r="AB377" s="2" t="inlineStr">
+        <is>
+          <t>-1.2500</t>
+        </is>
+      </c>
+      <c r="AC377" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:22:40.040736Z</t>
+        </is>
+      </c>
+      <c r="AD377" s="2" t="inlineStr"/>
+      <c r="AE377" s="2" t="inlineStr"/>
+      <c r="AF377" s="2" t="inlineStr"/>
+      <c r="AG377" s="2" t="inlineStr"/>
+      <c r="AH377" s="2" t="inlineStr"/>
+      <c r="AI377" s="2" t="inlineStr"/>
+      <c r="AJ377" s="2" t="inlineStr"/>
+    </row>
+    <row r="378">
+      <c r="A378" s="2" t="inlineStr">
+        <is>
+          <t>1706e8c4d2e8442c</t>
+        </is>
+      </c>
+      <c r="B378" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C378" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D378" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E378" s="2" t="inlineStr">
+        <is>
+          <t>4863ace20696b49ac8d86afb992436652bb1bb2b13aa3380a50818cc662a18c0</t>
+        </is>
+      </c>
+      <c r="F378" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G378" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H378" s="2" t="inlineStr">
+        <is>
+          <t>70045</t>
+        </is>
+      </c>
+      <c r="I378" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J378" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K378" s="2" t="inlineStr"/>
+      <c r="L378" s="2" t="inlineStr">
+        <is>
+          <t>0.598437</t>
+        </is>
+      </c>
+      <c r="M378" s="2" t="inlineStr"/>
+      <c r="N378" s="2" t="inlineStr"/>
+      <c r="O378" s="2" t="inlineStr">
+        <is>
+          <t>0.49019607843137253</t>
+        </is>
+      </c>
+      <c r="P378" s="2" t="inlineStr"/>
+      <c r="Q378" s="2" t="inlineStr">
+        <is>
+          <t>0.10824092156862747</t>
+        </is>
+      </c>
+      <c r="R378" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:04:46.146013Z</t>
+        </is>
+      </c>
+      <c r="S378" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="T378" s="2" t="inlineStr"/>
+      <c r="U378" s="2" t="inlineStr"/>
+      <c r="V378" s="2" t="inlineStr"/>
+      <c r="W378" s="2" t="inlineStr"/>
+      <c r="X378" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y378" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z378" s="2" t="inlineStr">
+        <is>
+          <t>0.490000</t>
+        </is>
+      </c>
+      <c r="AA378" s="2" t="inlineStr">
+        <is>
+          <t>-0.000196</t>
+        </is>
+      </c>
+      <c r="AB378" s="2" t="inlineStr">
+        <is>
+          <t>1.3000</t>
+        </is>
+      </c>
+      <c r="AC378" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:30.823247Z</t>
+        </is>
+      </c>
+      <c r="AD378" s="2" t="inlineStr"/>
+      <c r="AE378" s="2" t="inlineStr"/>
+      <c r="AF378" s="2" t="inlineStr"/>
+      <c r="AG378" s="2" t="inlineStr"/>
+      <c r="AH378" s="2" t="inlineStr"/>
+      <c r="AI378" s="2" t="inlineStr"/>
+      <c r="AJ378" s="2" t="inlineStr"/>
+    </row>
+    <row r="379">
+      <c r="A379" s="2" t="inlineStr">
+        <is>
+          <t>ba82c2d2ecfb418e</t>
+        </is>
+      </c>
+      <c r="B379" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C379" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D379" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E379" s="2" t="inlineStr">
+        <is>
+          <t>4863ace20696b49ac8d86afb992436652bb1bb2b13aa3380a50818cc662a18c0</t>
+        </is>
+      </c>
+      <c r="F379" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G379" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H379" s="2" t="inlineStr">
+        <is>
+          <t>70349</t>
+        </is>
+      </c>
+      <c r="I379" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J379" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K379" s="2" t="inlineStr"/>
+      <c r="L379" s="2" t="inlineStr">
+        <is>
+          <t>0.67052</t>
+        </is>
+      </c>
+      <c r="M379" s="2" t="inlineStr"/>
+      <c r="N379" s="2" t="inlineStr"/>
+      <c r="O379" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P379" s="2" t="inlineStr"/>
+      <c r="Q379" s="2" t="inlineStr">
+        <is>
+          <t>0.09068806722689082</t>
+        </is>
+      </c>
+      <c r="R379" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:04:49.037567Z</t>
+        </is>
+      </c>
+      <c r="S379" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T379" s="2" t="inlineStr"/>
+      <c r="U379" s="2" t="inlineStr"/>
+      <c r="V379" s="2" t="inlineStr"/>
+      <c r="W379" s="2" t="inlineStr"/>
+      <c r="X379" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y379" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z379" s="2" t="inlineStr">
+        <is>
+          <t>0.580000</t>
+        </is>
+      </c>
+      <c r="AA379" s="2" t="inlineStr">
+        <is>
+          <t>0.000168</t>
+        </is>
+      </c>
+      <c r="AB379" s="2" t="inlineStr">
+        <is>
+          <t>1.2681</t>
+        </is>
+      </c>
+      <c r="AC379" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:22:41.363832Z</t>
+        </is>
+      </c>
+      <c r="AD379" s="2" t="inlineStr"/>
+      <c r="AE379" s="2" t="inlineStr"/>
+      <c r="AF379" s="2" t="inlineStr"/>
+      <c r="AG379" s="2" t="inlineStr"/>
+      <c r="AH379" s="2" t="inlineStr"/>
+      <c r="AI379" s="2" t="inlineStr"/>
+      <c r="AJ379" s="2" t="inlineStr"/>
+    </row>
+    <row r="380">
+      <c r="A380" s="2" t="inlineStr">
+        <is>
+          <t>635b56c807d347dd</t>
+        </is>
+      </c>
+      <c r="B380" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C380" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D380" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E380" s="2" t="inlineStr">
+        <is>
+          <t>4863ace20696b49ac8d86afb992436652bb1bb2b13aa3380a50818cc662a18c0</t>
+        </is>
+      </c>
+      <c r="F380" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G380" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H380" s="2" t="inlineStr">
+        <is>
+          <t>70379</t>
+        </is>
+      </c>
+      <c r="I380" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J380" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K380" s="2" t="inlineStr"/>
+      <c r="L380" s="2" t="inlineStr">
+        <is>
+          <t>0.616597</t>
+        </is>
+      </c>
+      <c r="M380" s="2" t="inlineStr"/>
+      <c r="N380" s="2" t="inlineStr"/>
+      <c r="O380" s="2" t="inlineStr">
+        <is>
+          <t>0.5192307692307692</t>
+        </is>
+      </c>
+      <c r="P380" s="2" t="inlineStr"/>
+      <c r="Q380" s="2" t="inlineStr">
+        <is>
+          <t>0.09736623076923079</t>
+        </is>
+      </c>
+      <c r="R380" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:04:49.603785Z</t>
+        </is>
+      </c>
+      <c r="S380" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="T380" s="2" t="inlineStr"/>
+      <c r="U380" s="2" t="inlineStr"/>
+      <c r="V380" s="2" t="inlineStr"/>
+      <c r="W380" s="2" t="inlineStr"/>
+      <c r="X380" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y380" s="2" t="inlineStr"/>
+      <c r="Z380" s="2" t="inlineStr"/>
+      <c r="AA380" s="2" t="inlineStr"/>
+      <c r="AB380" s="2" t="inlineStr"/>
+      <c r="AC380" s="2" t="inlineStr"/>
+      <c r="AD380" s="2" t="inlineStr"/>
+      <c r="AE380" s="2" t="inlineStr"/>
+      <c r="AF380" s="2" t="inlineStr"/>
+      <c r="AG380" s="2" t="inlineStr"/>
+      <c r="AH380" s="2" t="inlineStr"/>
+      <c r="AI380" s="2" t="inlineStr"/>
+      <c r="AJ380" s="2" t="inlineStr"/>
+    </row>
+    <row r="381">
+      <c r="A381" s="2" t="inlineStr">
+        <is>
+          <t>c37899afbd5340d8</t>
+        </is>
+      </c>
+      <c r="B381" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C381" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D381" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E381" s="2" t="inlineStr">
+        <is>
+          <t>4863ace20696b49ac8d86afb992436652bb1bb2b13aa3380a50818cc662a18c0</t>
+        </is>
+      </c>
+      <c r="F381" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G381" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H381" s="2" t="inlineStr">
+        <is>
+          <t>70560</t>
+        </is>
+      </c>
+      <c r="I381" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J381" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K381" s="2" t="inlineStr"/>
+      <c r="L381" s="2" t="inlineStr">
+        <is>
+          <t>0.601063</t>
+        </is>
+      </c>
+      <c r="M381" s="2" t="inlineStr"/>
+      <c r="N381" s="2" t="inlineStr"/>
+      <c r="O381" s="2" t="inlineStr">
+        <is>
+          <t>0.5098039215686274</t>
+        </is>
+      </c>
+      <c r="P381" s="2" t="inlineStr"/>
+      <c r="Q381" s="2" t="inlineStr">
+        <is>
+          <t>0.0912590784313726</t>
+        </is>
+      </c>
+      <c r="R381" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:04:52.910341Z</t>
+        </is>
+      </c>
+      <c r="S381" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T07:00:00Z</t>
+        </is>
+      </c>
+      <c r="T381" s="2" t="inlineStr"/>
+      <c r="U381" s="2" t="inlineStr"/>
+      <c r="V381" s="2" t="inlineStr"/>
+      <c r="W381" s="2" t="inlineStr"/>
+      <c r="X381" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y381" s="2" t="inlineStr"/>
+      <c r="Z381" s="2" t="inlineStr"/>
+      <c r="AA381" s="2" t="inlineStr"/>
+      <c r="AB381" s="2" t="inlineStr"/>
+      <c r="AC381" s="2" t="inlineStr"/>
+      <c r="AD381" s="2" t="inlineStr"/>
+      <c r="AE381" s="2" t="inlineStr"/>
+      <c r="AF381" s="2" t="inlineStr"/>
+      <c r="AG381" s="2" t="inlineStr"/>
+      <c r="AH381" s="2" t="inlineStr"/>
+      <c r="AI381" s="2" t="inlineStr"/>
+      <c r="AJ381" s="2" t="inlineStr"/>
+    </row>
+    <row r="382">
+      <c r="A382" s="2" t="inlineStr">
+        <is>
+          <t>38404a2d2b6d4d17</t>
+        </is>
+      </c>
+      <c r="B382" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C382" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D382" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E382" s="2" t="inlineStr">
+        <is>
+          <t>4863ace20696b49ac8d86afb992436652bb1bb2b13aa3380a50818cc662a18c0</t>
+        </is>
+      </c>
+      <c r="F382" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G382" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H382" s="2" t="inlineStr">
+        <is>
+          <t>70573</t>
+        </is>
+      </c>
+      <c r="I382" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J382" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K382" s="2" t="inlineStr"/>
+      <c r="L382" s="2" t="inlineStr">
+        <is>
+          <t>0.67671</t>
+        </is>
+      </c>
+      <c r="M382" s="2" t="inlineStr"/>
+      <c r="N382" s="2" t="inlineStr"/>
+      <c r="O382" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P382" s="2" t="inlineStr"/>
+      <c r="Q382" s="2" t="inlineStr">
+        <is>
+          <t>0.22625954954954952</t>
+        </is>
+      </c>
+      <c r="R382" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:04:54.465187Z</t>
+        </is>
+      </c>
+      <c r="S382" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T382" s="2" t="inlineStr"/>
+      <c r="U382" s="2" t="inlineStr"/>
+      <c r="V382" s="2" t="inlineStr"/>
+      <c r="W382" s="2" t="inlineStr"/>
+      <c r="X382" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y382" s="2" t="inlineStr"/>
+      <c r="Z382" s="2" t="inlineStr"/>
+      <c r="AA382" s="2" t="inlineStr"/>
+      <c r="AB382" s="2" t="inlineStr"/>
+      <c r="AC382" s="2" t="inlineStr"/>
+      <c r="AD382" s="2" t="inlineStr"/>
+      <c r="AE382" s="2" t="inlineStr"/>
+      <c r="AF382" s="2" t="inlineStr"/>
+      <c r="AG382" s="2" t="inlineStr"/>
+      <c r="AH382" s="2" t="inlineStr"/>
+      <c r="AI382" s="2" t="inlineStr"/>
+      <c r="AJ382" s="2" t="inlineStr"/>
+    </row>
+    <row r="383">
+      <c r="A383" s="2" t="inlineStr">
+        <is>
+          <t>7e5ee2ffa7354857</t>
+        </is>
+      </c>
+      <c r="B383" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C383" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D383" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E383" s="2" t="inlineStr">
+        <is>
+          <t>4863ace20696b49ac8d86afb992436652bb1bb2b13aa3380a50818cc662a18c0</t>
+        </is>
+      </c>
+      <c r="F383" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G383" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H383" s="2" t="inlineStr">
+        <is>
+          <t>70790</t>
+        </is>
+      </c>
+      <c r="I383" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J383" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K383" s="2" t="inlineStr"/>
+      <c r="L383" s="2" t="inlineStr">
+        <is>
+          <t>0.764157</t>
+        </is>
+      </c>
+      <c r="M383" s="2" t="inlineStr"/>
+      <c r="N383" s="2" t="inlineStr"/>
+      <c r="O383" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P383" s="2" t="inlineStr"/>
+      <c r="Q383" s="2" t="inlineStr">
+        <is>
+          <t>0.17399306557377048</t>
+        </is>
+      </c>
+      <c r="R383" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:04:59.045853Z</t>
+        </is>
+      </c>
+      <c r="S383" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="T383" s="2" t="inlineStr"/>
+      <c r="U383" s="2" t="inlineStr"/>
+      <c r="V383" s="2" t="inlineStr"/>
+      <c r="W383" s="2" t="inlineStr"/>
+      <c r="X383" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y383" s="2" t="inlineStr"/>
+      <c r="Z383" s="2" t="inlineStr"/>
+      <c r="AA383" s="2" t="inlineStr"/>
+      <c r="AB383" s="2" t="inlineStr"/>
+      <c r="AC383" s="2" t="inlineStr"/>
+      <c r="AD383" s="2" t="inlineStr"/>
+      <c r="AE383" s="2" t="inlineStr"/>
+      <c r="AF383" s="2" t="inlineStr"/>
+      <c r="AG383" s="2" t="inlineStr"/>
+      <c r="AH383" s="2" t="inlineStr"/>
+      <c r="AI383" s="2" t="inlineStr"/>
+      <c r="AJ383" s="2" t="inlineStr"/>
+    </row>
+    <row r="384">
+      <c r="A384" s="2" t="inlineStr">
+        <is>
+          <t>785468f250e044a1</t>
+        </is>
+      </c>
+      <c r="B384" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C384" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D384" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E384" s="2" t="inlineStr">
+        <is>
+          <t>4863ace20696b49ac8d86afb992436652bb1bb2b13aa3380a50818cc662a18c0</t>
+        </is>
+      </c>
+      <c r="F384" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G384" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H384" s="2" t="inlineStr">
+        <is>
+          <t>70860</t>
+        </is>
+      </c>
+      <c r="I384" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J384" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K384" s="2" t="inlineStr"/>
+      <c r="L384" s="2" t="inlineStr">
+        <is>
+          <t>0.74277</t>
+        </is>
+      </c>
+      <c r="M384" s="2" t="inlineStr"/>
+      <c r="N384" s="2" t="inlineStr"/>
+      <c r="O384" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P384" s="2" t="inlineStr"/>
+      <c r="Q384" s="2" t="inlineStr">
+        <is>
+          <t>0.14276999999999995</t>
+        </is>
+      </c>
+      <c r="R384" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:05:00.679298Z</t>
+        </is>
+      </c>
+      <c r="S384" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T384" s="2" t="inlineStr"/>
+      <c r="U384" s="2" t="inlineStr"/>
+      <c r="V384" s="2" t="inlineStr"/>
+      <c r="W384" s="2" t="inlineStr"/>
+      <c r="X384" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y384" s="2" t="inlineStr"/>
+      <c r="Z384" s="2" t="inlineStr"/>
+      <c r="AA384" s="2" t="inlineStr"/>
+      <c r="AB384" s="2" t="inlineStr"/>
+      <c r="AC384" s="2" t="inlineStr"/>
+      <c r="AD384" s="2" t="inlineStr"/>
+      <c r="AE384" s="2" t="inlineStr"/>
+      <c r="AF384" s="2" t="inlineStr"/>
+      <c r="AG384" s="2" t="inlineStr"/>
+      <c r="AH384" s="2" t="inlineStr"/>
+      <c r="AI384" s="2" t="inlineStr"/>
+      <c r="AJ384" s="2" t="inlineStr"/>
+    </row>
+    <row r="385">
+      <c r="A385" s="2" t="inlineStr">
+        <is>
+          <t>0f4bf6d669af4763</t>
+        </is>
+      </c>
+      <c r="B385" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C385" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D385" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E385" s="2" t="inlineStr">
+        <is>
+          <t>4863ace20696b49ac8d86afb992436652bb1bb2b13aa3380a50818cc662a18c0</t>
+        </is>
+      </c>
+      <c r="F385" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G385" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H385" s="2" t="inlineStr">
+        <is>
+          <t>70899</t>
+        </is>
+      </c>
+      <c r="I385" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J385" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K385" s="2" t="inlineStr"/>
+      <c r="L385" s="2" t="inlineStr">
+        <is>
+          <t>0.639787</t>
+        </is>
+      </c>
+      <c r="M385" s="2" t="inlineStr"/>
+      <c r="N385" s="2" t="inlineStr"/>
+      <c r="O385" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P385" s="2" t="inlineStr"/>
+      <c r="Q385" s="2" t="inlineStr">
+        <is>
+          <t>0.08031563436123346</t>
+        </is>
+      </c>
+      <c r="R385" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:05:03.095654Z</t>
+        </is>
+      </c>
+      <c r="S385" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T385" s="2" t="inlineStr"/>
+      <c r="U385" s="2" t="inlineStr"/>
+      <c r="V385" s="2" t="inlineStr"/>
+      <c r="W385" s="2" t="inlineStr"/>
+      <c r="X385" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y385" s="2" t="inlineStr"/>
+      <c r="Z385" s="2" t="inlineStr"/>
+      <c r="AA385" s="2" t="inlineStr"/>
+      <c r="AB385" s="2" t="inlineStr"/>
+      <c r="AC385" s="2" t="inlineStr"/>
+      <c r="AD385" s="2" t="inlineStr"/>
+      <c r="AE385" s="2" t="inlineStr"/>
+      <c r="AF385" s="2" t="inlineStr"/>
+      <c r="AG385" s="2" t="inlineStr"/>
+      <c r="AH385" s="2" t="inlineStr"/>
+      <c r="AI385" s="2" t="inlineStr"/>
+      <c r="AJ385" s="2" t="inlineStr"/>
+    </row>
+    <row r="386">
+      <c r="A386" s="2" t="inlineStr">
+        <is>
+          <t>4b5bc91a922249c7</t>
+        </is>
+      </c>
+      <c r="B386" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C386" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D386" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E386" s="2" t="inlineStr">
+        <is>
+          <t>4863ace20696b49ac8d86afb992436652bb1bb2b13aa3380a50818cc662a18c0</t>
+        </is>
+      </c>
+      <c r="F386" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G386" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H386" s="2" t="inlineStr">
+        <is>
+          <t>70903</t>
+        </is>
+      </c>
+      <c r="I386" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J386" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K386" s="2" t="inlineStr"/>
+      <c r="L386" s="2" t="inlineStr">
+        <is>
+          <t>0.630589</t>
+        </is>
+      </c>
+      <c r="M386" s="2" t="inlineStr"/>
+      <c r="N386" s="2" t="inlineStr"/>
+      <c r="O386" s="2" t="inlineStr">
+        <is>
+          <t>0.5192307692307692</t>
+        </is>
+      </c>
+      <c r="P386" s="2" t="inlineStr"/>
+      <c r="Q386" s="2" t="inlineStr">
+        <is>
+          <t>0.11135823076923079</t>
+        </is>
+      </c>
+      <c r="R386" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:05:04.823774Z</t>
+        </is>
+      </c>
+      <c r="S386" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T386" s="2" t="inlineStr"/>
+      <c r="U386" s="2" t="inlineStr"/>
+      <c r="V386" s="2" t="inlineStr"/>
+      <c r="W386" s="2" t="inlineStr"/>
+      <c r="X386" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y386" s="2" t="inlineStr"/>
+      <c r="Z386" s="2" t="inlineStr"/>
+      <c r="AA386" s="2" t="inlineStr"/>
+      <c r="AB386" s="2" t="inlineStr"/>
+      <c r="AC386" s="2" t="inlineStr"/>
+      <c r="AD386" s="2" t="inlineStr"/>
+      <c r="AE386" s="2" t="inlineStr"/>
+      <c r="AF386" s="2" t="inlineStr"/>
+      <c r="AG386" s="2" t="inlineStr"/>
+      <c r="AH386" s="2" t="inlineStr"/>
+      <c r="AI386" s="2" t="inlineStr"/>
+      <c r="AJ386" s="2" t="inlineStr"/>
+    </row>
+    <row r="387">
+      <c r="A387" s="2" t="inlineStr">
+        <is>
+          <t>4d6b2959fa8c465b</t>
+        </is>
+      </c>
+      <c r="B387" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C387" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D387" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E387" s="2" t="inlineStr">
+        <is>
+          <t>15c411e044ffe51b6ddc3409c537ef2b1f842259403eab8a9ab62a4cd0e52b5d</t>
+        </is>
+      </c>
+      <c r="F387" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G387" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H387" s="2" t="inlineStr">
+        <is>
+          <t>70560</t>
+        </is>
+      </c>
+      <c r="I387" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J387" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K387" s="2" t="inlineStr"/>
+      <c r="L387" s="2" t="inlineStr">
+        <is>
+          <t>0.600785</t>
+        </is>
+      </c>
+      <c r="M387" s="2" t="inlineStr"/>
+      <c r="N387" s="2" t="inlineStr"/>
+      <c r="O387" s="2" t="inlineStr">
+        <is>
+          <t>0.5192307692307692</t>
+        </is>
+      </c>
+      <c r="P387" s="2" t="inlineStr"/>
+      <c r="Q387" s="2" t="inlineStr">
+        <is>
+          <t>0.08155423076923085</t>
+        </is>
+      </c>
+      <c r="R387" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:02:52.013040Z</t>
+        </is>
+      </c>
+      <c r="S387" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T07:00:00Z</t>
+        </is>
+      </c>
+      <c r="T387" s="2" t="inlineStr"/>
+      <c r="U387" s="2" t="inlineStr"/>
+      <c r="V387" s="2" t="inlineStr"/>
+      <c r="W387" s="2" t="inlineStr"/>
+      <c r="X387" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y387" s="2" t="inlineStr"/>
+      <c r="Z387" s="2" t="inlineStr"/>
+      <c r="AA387" s="2" t="inlineStr"/>
+      <c r="AB387" s="2" t="inlineStr"/>
+      <c r="AC387" s="2" t="inlineStr"/>
+      <c r="AD387" s="2" t="inlineStr"/>
+      <c r="AE387" s="2" t="inlineStr"/>
+      <c r="AF387" s="2" t="inlineStr"/>
+      <c r="AG387" s="2" t="inlineStr"/>
+      <c r="AH387" s="2" t="inlineStr"/>
+      <c r="AI387" s="2" t="inlineStr"/>
+      <c r="AJ387" s="2" t="inlineStr"/>
+    </row>
+    <row r="388">
+      <c r="A388" s="2" t="inlineStr">
+        <is>
+          <t>9240394c355948c7</t>
+        </is>
+      </c>
+      <c r="B388" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C388" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D388" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E388" s="2" t="inlineStr">
+        <is>
+          <t>15c411e044ffe51b6ddc3409c537ef2b1f842259403eab8a9ab62a4cd0e52b5d</t>
+        </is>
+      </c>
+      <c r="F388" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G388" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H388" s="2" t="inlineStr">
+        <is>
+          <t>70573</t>
+        </is>
+      </c>
+      <c r="I388" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J388" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K388" s="2" t="inlineStr"/>
+      <c r="L388" s="2" t="inlineStr">
+        <is>
+          <t>0.676848</t>
+        </is>
+      </c>
+      <c r="M388" s="2" t="inlineStr"/>
+      <c r="N388" s="2" t="inlineStr"/>
+      <c r="O388" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P388" s="2" t="inlineStr"/>
+      <c r="Q388" s="2" t="inlineStr">
+        <is>
+          <t>0.2263975495495495</t>
+        </is>
+      </c>
+      <c r="R388" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:02:53.305511Z</t>
+        </is>
+      </c>
+      <c r="S388" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T388" s="2" t="inlineStr"/>
+      <c r="U388" s="2" t="inlineStr"/>
+      <c r="V388" s="2" t="inlineStr"/>
+      <c r="W388" s="2" t="inlineStr"/>
+      <c r="X388" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y388" s="2" t="inlineStr"/>
+      <c r="Z388" s="2" t="inlineStr"/>
+      <c r="AA388" s="2" t="inlineStr"/>
+      <c r="AB388" s="2" t="inlineStr"/>
+      <c r="AC388" s="2" t="inlineStr"/>
+      <c r="AD388" s="2" t="inlineStr"/>
+      <c r="AE388" s="2" t="inlineStr"/>
+      <c r="AF388" s="2" t="inlineStr"/>
+      <c r="AG388" s="2" t="inlineStr"/>
+      <c r="AH388" s="2" t="inlineStr"/>
+      <c r="AI388" s="2" t="inlineStr"/>
+      <c r="AJ388" s="2" t="inlineStr"/>
+    </row>
+    <row r="389">
+      <c r="A389" s="2" t="inlineStr">
+        <is>
+          <t>c6e29c96743745a2</t>
+        </is>
+      </c>
+      <c r="B389" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C389" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D389" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E389" s="2" t="inlineStr">
+        <is>
+          <t>15c411e044ffe51b6ddc3409c537ef2b1f842259403eab8a9ab62a4cd0e52b5d</t>
+        </is>
+      </c>
+      <c r="F389" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G389" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H389" s="2" t="inlineStr">
+        <is>
+          <t>70790</t>
+        </is>
+      </c>
+      <c r="I389" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J389" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K389" s="2" t="inlineStr"/>
+      <c r="L389" s="2" t="inlineStr">
+        <is>
+          <t>0.765746</t>
+        </is>
+      </c>
+      <c r="M389" s="2" t="inlineStr"/>
+      <c r="N389" s="2" t="inlineStr"/>
+      <c r="O389" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P389" s="2" t="inlineStr"/>
+      <c r="Q389" s="2" t="inlineStr">
+        <is>
+          <t>0.17558206557377054</t>
+        </is>
+      </c>
+      <c r="R389" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:02:58.913511Z</t>
+        </is>
+      </c>
+      <c r="S389" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="T389" s="2" t="inlineStr"/>
+      <c r="U389" s="2" t="inlineStr"/>
+      <c r="V389" s="2" t="inlineStr"/>
+      <c r="W389" s="2" t="inlineStr"/>
+      <c r="X389" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y389" s="2" t="inlineStr"/>
+      <c r="Z389" s="2" t="inlineStr"/>
+      <c r="AA389" s="2" t="inlineStr"/>
+      <c r="AB389" s="2" t="inlineStr"/>
+      <c r="AC389" s="2" t="inlineStr"/>
+      <c r="AD389" s="2" t="inlineStr"/>
+      <c r="AE389" s="2" t="inlineStr"/>
+      <c r="AF389" s="2" t="inlineStr"/>
+      <c r="AG389" s="2" t="inlineStr"/>
+      <c r="AH389" s="2" t="inlineStr"/>
+      <c r="AI389" s="2" t="inlineStr"/>
+      <c r="AJ389" s="2" t="inlineStr"/>
+    </row>
+    <row r="390">
+      <c r="A390" s="2" t="inlineStr">
+        <is>
+          <t>c3c4916dcad54829</t>
+        </is>
+      </c>
+      <c r="B390" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C390" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D390" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E390" s="2" t="inlineStr">
+        <is>
+          <t>15c411e044ffe51b6ddc3409c537ef2b1f842259403eab8a9ab62a4cd0e52b5d</t>
+        </is>
+      </c>
+      <c r="F390" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G390" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H390" s="2" t="inlineStr">
+        <is>
+          <t>70860</t>
+        </is>
+      </c>
+      <c r="I390" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J390" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K390" s="2" t="inlineStr"/>
+      <c r="L390" s="2" t="inlineStr">
+        <is>
+          <t>0.742921</t>
+        </is>
+      </c>
+      <c r="M390" s="2" t="inlineStr"/>
+      <c r="N390" s="2" t="inlineStr"/>
+      <c r="O390" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P390" s="2" t="inlineStr"/>
+      <c r="Q390" s="2" t="inlineStr">
+        <is>
+          <t>0.14292099999999996</t>
+        </is>
+      </c>
+      <c r="R390" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:03:00.013255Z</t>
+        </is>
+      </c>
+      <c r="S390" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T390" s="2" t="inlineStr"/>
+      <c r="U390" s="2" t="inlineStr"/>
+      <c r="V390" s="2" t="inlineStr"/>
+      <c r="W390" s="2" t="inlineStr"/>
+      <c r="X390" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y390" s="2" t="inlineStr"/>
+      <c r="Z390" s="2" t="inlineStr"/>
+      <c r="AA390" s="2" t="inlineStr"/>
+      <c r="AB390" s="2" t="inlineStr"/>
+      <c r="AC390" s="2" t="inlineStr"/>
+      <c r="AD390" s="2" t="inlineStr"/>
+      <c r="AE390" s="2" t="inlineStr"/>
+      <c r="AF390" s="2" t="inlineStr"/>
+      <c r="AG390" s="2" t="inlineStr"/>
+      <c r="AH390" s="2" t="inlineStr"/>
+      <c r="AI390" s="2" t="inlineStr"/>
+      <c r="AJ390" s="2" t="inlineStr"/>
+    </row>
+    <row r="391">
+      <c r="A391" s="2" t="inlineStr">
+        <is>
+          <t>888172921d3445ff</t>
+        </is>
+      </c>
+      <c r="B391" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C391" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D391" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E391" s="2" t="inlineStr">
+        <is>
+          <t>15c411e044ffe51b6ddc3409c537ef2b1f842259403eab8a9ab62a4cd0e52b5d</t>
+        </is>
+      </c>
+      <c r="F391" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G391" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H391" s="2" t="inlineStr">
+        <is>
+          <t>70903</t>
+        </is>
+      </c>
+      <c r="I391" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J391" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K391" s="2" t="inlineStr"/>
+      <c r="L391" s="2" t="inlineStr">
+        <is>
+          <t>0.630579</t>
+        </is>
+      </c>
+      <c r="M391" s="2" t="inlineStr"/>
+      <c r="N391" s="2" t="inlineStr"/>
+      <c r="O391" s="2" t="inlineStr">
+        <is>
+          <t>0.5098039215686274</t>
+        </is>
+      </c>
+      <c r="P391" s="2" t="inlineStr"/>
+      <c r="Q391" s="2" t="inlineStr">
+        <is>
+          <t>0.12077507843137258</t>
+        </is>
+      </c>
+      <c r="R391" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:03:04.184730Z</t>
+        </is>
+      </c>
+      <c r="S391" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T391" s="2" t="inlineStr"/>
+      <c r="U391" s="2" t="inlineStr"/>
+      <c r="V391" s="2" t="inlineStr"/>
+      <c r="W391" s="2" t="inlineStr"/>
+      <c r="X391" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y391" s="2" t="inlineStr"/>
+      <c r="Z391" s="2" t="inlineStr"/>
+      <c r="AA391" s="2" t="inlineStr"/>
+      <c r="AB391" s="2" t="inlineStr"/>
+      <c r="AC391" s="2" t="inlineStr"/>
+      <c r="AD391" s="2" t="inlineStr"/>
+      <c r="AE391" s="2" t="inlineStr"/>
+      <c r="AF391" s="2" t="inlineStr"/>
+      <c r="AG391" s="2" t="inlineStr"/>
+      <c r="AH391" s="2" t="inlineStr"/>
+      <c r="AI391" s="2" t="inlineStr"/>
+      <c r="AJ391" s="2" t="inlineStr"/>
+    </row>
+    <row r="392">
+      <c r="A392" s="2" t="inlineStr">
+        <is>
+          <t>79609c39f1d44f61</t>
+        </is>
+      </c>
+      <c r="B392" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C392" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D392" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E392" s="2" t="inlineStr">
+        <is>
+          <t>15c411e044ffe51b6ddc3409c537ef2b1f842259403eab8a9ab62a4cd0e52b5d</t>
+        </is>
+      </c>
+      <c r="F392" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G392" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H392" s="2" t="inlineStr">
+        <is>
+          <t>70904</t>
+        </is>
+      </c>
+      <c r="I392" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J392" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K392" s="2" t="inlineStr"/>
+      <c r="L392" s="2" t="inlineStr">
+        <is>
+          <t>0.869317</t>
+        </is>
+      </c>
+      <c r="M392" s="2" t="inlineStr"/>
+      <c r="N392" s="2" t="inlineStr"/>
+      <c r="O392" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P392" s="2" t="inlineStr"/>
+      <c r="Q392" s="2" t="inlineStr">
+        <is>
+          <t>0.17891452321981427</t>
+        </is>
+      </c>
+      <c r="R392" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:03:04.649608Z</t>
+        </is>
+      </c>
+      <c r="S392" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T392" s="2" t="inlineStr"/>
+      <c r="U392" s="2" t="inlineStr"/>
+      <c r="V392" s="2" t="inlineStr"/>
+      <c r="W392" s="2" t="inlineStr"/>
+      <c r="X392" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y392" s="2" t="inlineStr"/>
+      <c r="Z392" s="2" t="inlineStr"/>
+      <c r="AA392" s="2" t="inlineStr"/>
+      <c r="AB392" s="2" t="inlineStr"/>
+      <c r="AC392" s="2" t="inlineStr"/>
+      <c r="AD392" s="2" t="inlineStr"/>
+      <c r="AE392" s="2" t="inlineStr"/>
+      <c r="AF392" s="2" t="inlineStr"/>
+      <c r="AG392" s="2" t="inlineStr"/>
+      <c r="AH392" s="2" t="inlineStr"/>
+      <c r="AI392" s="2" t="inlineStr"/>
+      <c r="AJ392" s="2" t="inlineStr"/>
+    </row>
+    <row r="393">
+      <c r="A393" s="2" t="inlineStr">
+        <is>
+          <t>627e1ccdb2b34604</t>
+        </is>
+      </c>
+      <c r="B393" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C393" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D393" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E393" s="2" t="inlineStr">
+        <is>
+          <t>15c411e044ffe51b6ddc3409c537ef2b1f842259403eab8a9ab62a4cd0e52b5d</t>
+        </is>
+      </c>
+      <c r="F393" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G393" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H393" s="2" t="inlineStr">
+        <is>
+          <t>71214</t>
+        </is>
+      </c>
+      <c r="I393" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J393" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K393" s="2" t="inlineStr"/>
+      <c r="L393" s="2" t="inlineStr">
+        <is>
+          <t>0.684535</t>
+        </is>
+      </c>
+      <c r="M393" s="2" t="inlineStr"/>
+      <c r="N393" s="2" t="inlineStr"/>
+      <c r="O393" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P393" s="2" t="inlineStr"/>
+      <c r="Q393" s="2" t="inlineStr">
+        <is>
+          <t>0.11371954935622319</t>
+        </is>
+      </c>
+      <c r="R393" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:03:06.937491Z</t>
+        </is>
+      </c>
+      <c r="S393" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T393" s="2" t="inlineStr"/>
+      <c r="U393" s="2" t="inlineStr"/>
+      <c r="V393" s="2" t="inlineStr"/>
+      <c r="W393" s="2" t="inlineStr"/>
+      <c r="X393" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y393" s="2" t="inlineStr"/>
+      <c r="Z393" s="2" t="inlineStr"/>
+      <c r="AA393" s="2" t="inlineStr"/>
+      <c r="AB393" s="2" t="inlineStr"/>
+      <c r="AC393" s="2" t="inlineStr"/>
+      <c r="AD393" s="2" t="inlineStr"/>
+      <c r="AE393" s="2" t="inlineStr"/>
+      <c r="AF393" s="2" t="inlineStr"/>
+      <c r="AG393" s="2" t="inlineStr"/>
+      <c r="AH393" s="2" t="inlineStr"/>
+      <c r="AI393" s="2" t="inlineStr"/>
+      <c r="AJ393" s="2" t="inlineStr"/>
+    </row>
+    <row r="394">
+      <c r="A394" s="2" t="inlineStr">
+        <is>
+          <t>45b814f3625a4a29</t>
+        </is>
+      </c>
+      <c r="B394" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C394" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D394" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E394" s="2" t="inlineStr">
+        <is>
+          <t>4304963c152f1e881f634fa0b66ab59152f3edd6692257c1d27d76a5cb0a3df3</t>
+        </is>
+      </c>
+      <c r="F394" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G394" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H394" s="2" t="inlineStr">
+        <is>
+          <t>70560</t>
+        </is>
+      </c>
+      <c r="I394" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J394" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K394" s="2" t="inlineStr"/>
+      <c r="L394" s="2" t="inlineStr">
+        <is>
+          <t>0.601292</t>
+        </is>
+      </c>
+      <c r="M394" s="2" t="inlineStr"/>
+      <c r="N394" s="2" t="inlineStr"/>
+      <c r="O394" s="2" t="inlineStr">
+        <is>
+          <t>0.5192307692307692</t>
+        </is>
+      </c>
+      <c r="P394" s="2" t="inlineStr"/>
+      <c r="Q394" s="2" t="inlineStr">
+        <is>
+          <t>0.08206123076923089</t>
+        </is>
+      </c>
+      <c r="R394" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:24:36.724531Z</t>
+        </is>
+      </c>
+      <c r="S394" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T07:00:00Z</t>
+        </is>
+      </c>
+      <c r="T394" s="2" t="inlineStr"/>
+      <c r="U394" s="2" t="inlineStr"/>
+      <c r="V394" s="2" t="inlineStr"/>
+      <c r="W394" s="2" t="inlineStr"/>
+      <c r="X394" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y394" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z394" s="2" t="inlineStr"/>
+      <c r="AA394" s="2" t="inlineStr"/>
+      <c r="AB394" s="2" t="inlineStr">
+        <is>
+          <t>-1.2500</t>
+        </is>
+      </c>
+      <c r="AC394" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:57:08.051188Z</t>
+        </is>
+      </c>
+      <c r="AD394" s="2" t="inlineStr"/>
+      <c r="AE394" s="2" t="inlineStr"/>
+      <c r="AF394" s="2" t="inlineStr"/>
+      <c r="AG394" s="2" t="inlineStr"/>
+      <c r="AH394" s="2" t="inlineStr"/>
+      <c r="AI394" s="2" t="inlineStr"/>
+      <c r="AJ394" s="2" t="inlineStr"/>
+    </row>
+    <row r="395">
+      <c r="A395" s="2" t="inlineStr">
+        <is>
+          <t>279d6b160ad04bd8</t>
+        </is>
+      </c>
+      <c r="B395" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C395" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D395" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E395" s="2" t="inlineStr">
+        <is>
+          <t>4304963c152f1e881f634fa0b66ab59152f3edd6692257c1d27d76a5cb0a3df3</t>
+        </is>
+      </c>
+      <c r="F395" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G395" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H395" s="2" t="inlineStr">
+        <is>
+          <t>70573</t>
+        </is>
+      </c>
+      <c r="I395" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J395" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K395" s="2" t="inlineStr"/>
+      <c r="L395" s="2" t="inlineStr">
+        <is>
+          <t>0.677029</t>
+        </is>
+      </c>
+      <c r="M395" s="2" t="inlineStr"/>
+      <c r="N395" s="2" t="inlineStr"/>
+      <c r="O395" s="2" t="inlineStr">
+        <is>
+          <t>0.4608294930875576</t>
+        </is>
+      </c>
+      <c r="P395" s="2" t="inlineStr"/>
+      <c r="Q395" s="2" t="inlineStr">
+        <is>
+          <t>0.21619950691244239</t>
+        </is>
+      </c>
+      <c r="R395" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:24:37.742493Z</t>
+        </is>
+      </c>
+      <c r="S395" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T395" s="2" t="inlineStr"/>
+      <c r="U395" s="2" t="inlineStr"/>
+      <c r="V395" s="2" t="inlineStr"/>
+      <c r="W395" s="2" t="inlineStr"/>
+      <c r="X395" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y395" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z395" s="2" t="inlineStr"/>
+      <c r="AA395" s="2" t="inlineStr"/>
+      <c r="AB395" s="2" t="inlineStr">
+        <is>
+          <t>-1.7500</t>
+        </is>
+      </c>
+      <c r="AC395" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:57:09.864967Z</t>
+        </is>
+      </c>
+      <c r="AD395" s="2" t="inlineStr"/>
+      <c r="AE395" s="2" t="inlineStr"/>
+      <c r="AF395" s="2" t="inlineStr"/>
+      <c r="AG395" s="2" t="inlineStr"/>
+      <c r="AH395" s="2" t="inlineStr"/>
+      <c r="AI395" s="2" t="inlineStr"/>
+      <c r="AJ395" s="2" t="inlineStr"/>
+    </row>
+    <row r="396">
+      <c r="A396" s="2" t="inlineStr">
+        <is>
+          <t>bf4afd4983e742c8</t>
+        </is>
+      </c>
+      <c r="B396" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C396" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D396" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E396" s="2" t="inlineStr">
+        <is>
+          <t>4304963c152f1e881f634fa0b66ab59152f3edd6692257c1d27d76a5cb0a3df3</t>
+        </is>
+      </c>
+      <c r="F396" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G396" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H396" s="2" t="inlineStr">
+        <is>
+          <t>70790</t>
+        </is>
+      </c>
+      <c r="I396" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J396" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K396" s="2" t="inlineStr"/>
+      <c r="L396" s="2" t="inlineStr">
+        <is>
+          <t>0.764249</t>
+        </is>
+      </c>
+      <c r="M396" s="2" t="inlineStr"/>
+      <c r="N396" s="2" t="inlineStr"/>
+      <c r="O396" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P396" s="2" t="inlineStr"/>
+      <c r="Q396" s="2" t="inlineStr">
+        <is>
+          <t>0.17408506557377046</t>
+        </is>
+      </c>
+      <c r="R396" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:24:42.381233Z</t>
+        </is>
+      </c>
+      <c r="S396" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="T396" s="2" t="inlineStr"/>
+      <c r="U396" s="2" t="inlineStr"/>
+      <c r="V396" s="2" t="inlineStr"/>
+      <c r="W396" s="2" t="inlineStr"/>
+      <c r="X396" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y396" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z396" s="2" t="inlineStr"/>
+      <c r="AA396" s="2" t="inlineStr"/>
+      <c r="AB396" s="2" t="inlineStr">
+        <is>
+          <t>1.3889</t>
+        </is>
+      </c>
+      <c r="AC396" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:57:11.614134Z</t>
+        </is>
+      </c>
+      <c r="AD396" s="2" t="inlineStr"/>
+      <c r="AE396" s="2" t="inlineStr"/>
+      <c r="AF396" s="2" t="inlineStr"/>
+      <c r="AG396" s="2" t="inlineStr"/>
+      <c r="AH396" s="2" t="inlineStr"/>
+      <c r="AI396" s="2" t="inlineStr"/>
+      <c r="AJ396" s="2" t="inlineStr"/>
+    </row>
+    <row r="397">
+      <c r="A397" s="2" t="inlineStr">
+        <is>
+          <t>93ccd1fdb5384299</t>
+        </is>
+      </c>
+      <c r="B397" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C397" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D397" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E397" s="2" t="inlineStr">
+        <is>
+          <t>4304963c152f1e881f634fa0b66ab59152f3edd6692257c1d27d76a5cb0a3df3</t>
+        </is>
+      </c>
+      <c r="F397" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G397" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H397" s="2" t="inlineStr">
+        <is>
+          <t>70860</t>
+        </is>
+      </c>
+      <c r="I397" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J397" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K397" s="2" t="inlineStr"/>
+      <c r="L397" s="2" t="inlineStr">
+        <is>
+          <t>0.742815</t>
+        </is>
+      </c>
+      <c r="M397" s="2" t="inlineStr"/>
+      <c r="N397" s="2" t="inlineStr"/>
+      <c r="O397" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P397" s="2" t="inlineStr"/>
+      <c r="Q397" s="2" t="inlineStr">
+        <is>
+          <t>0.14281499999999991</t>
+        </is>
+      </c>
+      <c r="R397" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:24:43.466107Z</t>
+        </is>
+      </c>
+      <c r="S397" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T397" s="2" t="inlineStr"/>
+      <c r="U397" s="2" t="inlineStr"/>
+      <c r="V397" s="2" t="inlineStr"/>
+      <c r="W397" s="2" t="inlineStr"/>
+      <c r="X397" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y397" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z397" s="2" t="inlineStr"/>
+      <c r="AA397" s="2" t="inlineStr"/>
+      <c r="AB397" s="2" t="inlineStr">
+        <is>
+          <t>-2.0000</t>
+        </is>
+      </c>
+      <c r="AC397" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:57:13.321503Z</t>
+        </is>
+      </c>
+      <c r="AD397" s="2" t="inlineStr"/>
+      <c r="AE397" s="2" t="inlineStr"/>
+      <c r="AF397" s="2" t="inlineStr"/>
+      <c r="AG397" s="2" t="inlineStr"/>
+      <c r="AH397" s="2" t="inlineStr"/>
+      <c r="AI397" s="2" t="inlineStr"/>
+      <c r="AJ397" s="2" t="inlineStr"/>
+    </row>
+    <row r="398">
+      <c r="A398" s="2" t="inlineStr">
+        <is>
+          <t>4ee89ff4a55c4814</t>
+        </is>
+      </c>
+      <c r="B398" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C398" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D398" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E398" s="2" t="inlineStr">
+        <is>
+          <t>4304963c152f1e881f634fa0b66ab59152f3edd6692257c1d27d76a5cb0a3df3</t>
+        </is>
+      </c>
+      <c r="F398" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G398" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H398" s="2" t="inlineStr">
+        <is>
+          <t>70903</t>
+        </is>
+      </c>
+      <c r="I398" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J398" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K398" s="2" t="inlineStr"/>
+      <c r="L398" s="2" t="inlineStr">
+        <is>
+          <t>0.630956</t>
+        </is>
+      </c>
+      <c r="M398" s="2" t="inlineStr"/>
+      <c r="N398" s="2" t="inlineStr"/>
+      <c r="O398" s="2" t="inlineStr">
+        <is>
+          <t>0.4694835680751174</t>
+        </is>
+      </c>
+      <c r="P398" s="2" t="inlineStr"/>
+      <c r="Q398" s="2" t="inlineStr">
+        <is>
+          <t>0.1614724319248826</t>
+        </is>
+      </c>
+      <c r="R398" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:24:47.491847Z</t>
+        </is>
+      </c>
+      <c r="S398" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T398" s="2" t="inlineStr"/>
+      <c r="U398" s="2" t="inlineStr"/>
+      <c r="V398" s="2" t="inlineStr"/>
+      <c r="W398" s="2" t="inlineStr"/>
+      <c r="X398" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y398" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z398" s="2" t="inlineStr"/>
+      <c r="AA398" s="2" t="inlineStr"/>
+      <c r="AB398" s="2" t="inlineStr">
+        <is>
+          <t>1.6950</t>
+        </is>
+      </c>
+      <c r="AC398" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:57:15.067781Z</t>
+        </is>
+      </c>
+      <c r="AD398" s="2" t="inlineStr"/>
+      <c r="AE398" s="2" t="inlineStr"/>
+      <c r="AF398" s="2" t="inlineStr"/>
+      <c r="AG398" s="2" t="inlineStr"/>
+      <c r="AH398" s="2" t="inlineStr"/>
+      <c r="AI398" s="2" t="inlineStr"/>
+      <c r="AJ398" s="2" t="inlineStr"/>
+    </row>
+    <row r="399">
+      <c r="A399" s="2" t="inlineStr">
+        <is>
+          <t>01e781f7cba44d52</t>
+        </is>
+      </c>
+      <c r="B399" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C399" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D399" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E399" s="2" t="inlineStr">
+        <is>
+          <t>4304963c152f1e881f634fa0b66ab59152f3edd6692257c1d27d76a5cb0a3df3</t>
+        </is>
+      </c>
+      <c r="F399" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G399" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H399" s="2" t="inlineStr">
+        <is>
+          <t>71214</t>
+        </is>
+      </c>
+      <c r="I399" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J399" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K399" s="2" t="inlineStr"/>
+      <c r="L399" s="2" t="inlineStr">
+        <is>
+          <t>0.683106</t>
+        </is>
+      </c>
+      <c r="M399" s="2" t="inlineStr"/>
+      <c r="N399" s="2" t="inlineStr"/>
+      <c r="O399" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P399" s="2" t="inlineStr"/>
+      <c r="Q399" s="2" t="inlineStr">
+        <is>
+          <t>0.0929420655737705</t>
+        </is>
+      </c>
+      <c r="R399" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:24:49.962390Z</t>
+        </is>
+      </c>
+      <c r="S399" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T399" s="2" t="inlineStr"/>
+      <c r="U399" s="2" t="inlineStr"/>
+      <c r="V399" s="2" t="inlineStr"/>
+      <c r="W399" s="2" t="inlineStr"/>
+      <c r="X399" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y399" s="2" t="inlineStr"/>
+      <c r="Z399" s="2" t="inlineStr"/>
+      <c r="AA399" s="2" t="inlineStr"/>
+      <c r="AB399" s="2" t="inlineStr"/>
+      <c r="AC399" s="2" t="inlineStr"/>
+      <c r="AD399" s="2" t="inlineStr"/>
+      <c r="AE399" s="2" t="inlineStr"/>
+      <c r="AF399" s="2" t="inlineStr"/>
+      <c r="AG399" s="2" t="inlineStr"/>
+      <c r="AH399" s="2" t="inlineStr"/>
+      <c r="AI399" s="2" t="inlineStr"/>
+      <c r="AJ399" s="2" t="inlineStr"/>
+    </row>
+    <row r="400">
+      <c r="A400" s="2" t="inlineStr">
+        <is>
+          <t>f66d0b8fdf214a12</t>
+        </is>
+      </c>
+      <c r="B400" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C400" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D400" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E400" s="2" t="inlineStr">
+        <is>
+          <t>5e9799a515295e9b079eacaa53a2e35352183239a18c1b173f4a540a52770140</t>
+        </is>
+      </c>
+      <c r="F400" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G400" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H400" s="2" t="inlineStr">
+        <is>
+          <t>72342</t>
+        </is>
+      </c>
+      <c r="I400" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J400" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K400" s="2" t="inlineStr"/>
+      <c r="L400" s="2" t="inlineStr">
+        <is>
+          <t>0.577591</t>
+        </is>
+      </c>
+      <c r="M400" s="2" t="inlineStr"/>
+      <c r="N400" s="2" t="inlineStr"/>
+      <c r="O400" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P400" s="2" t="inlineStr"/>
+      <c r="Q400" s="2" t="inlineStr">
+        <is>
+          <t>0.1370623656387665</t>
+        </is>
+      </c>
+      <c r="R400" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T19:00:23.215720Z</t>
+        </is>
+      </c>
+      <c r="S400" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="T400" s="2" t="inlineStr"/>
+      <c r="U400" s="2" t="inlineStr"/>
+      <c r="V400" s="2" t="inlineStr"/>
+      <c r="W400" s="2" t="inlineStr"/>
+      <c r="X400" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y400" s="2" t="inlineStr"/>
+      <c r="Z400" s="2" t="inlineStr"/>
+      <c r="AA400" s="2" t="inlineStr"/>
+      <c r="AB400" s="2" t="inlineStr"/>
+      <c r="AC400" s="2" t="inlineStr"/>
+      <c r="AD400" s="2" t="inlineStr"/>
+      <c r="AE400" s="2" t="inlineStr"/>
+      <c r="AF400" s="2" t="inlineStr"/>
+      <c r="AG400" s="2" t="inlineStr"/>
+      <c r="AH400" s="2" t="inlineStr"/>
+      <c r="AI400" s="2" t="inlineStr"/>
+      <c r="AJ400" s="2" t="inlineStr"/>
+    </row>
+    <row r="401">
+      <c r="A401" s="2" t="inlineStr">
+        <is>
+          <t>e9a6bc4aadd640d2</t>
+        </is>
+      </c>
+      <c r="B401" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C401" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D401" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E401" s="2" t="inlineStr">
+        <is>
+          <t>5e9799a515295e9b079eacaa53a2e35352183239a18c1b173f4a540a52770140</t>
+        </is>
+      </c>
+      <c r="F401" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G401" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H401" s="2" t="inlineStr">
+        <is>
+          <t>72428</t>
+        </is>
+      </c>
+      <c r="I401" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J401" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K401" s="2" t="inlineStr"/>
+      <c r="L401" s="2" t="inlineStr">
+        <is>
+          <t>0.698729</t>
+        </is>
+      </c>
+      <c r="M401" s="2" t="inlineStr"/>
+      <c r="N401" s="2" t="inlineStr"/>
+      <c r="O401" s="2" t="inlineStr">
+        <is>
+          <t>0.4807692307692307</t>
+        </is>
+      </c>
+      <c r="P401" s="2" t="inlineStr"/>
+      <c r="Q401" s="2" t="inlineStr">
+        <is>
+          <t>0.21795976923076932</t>
+        </is>
+      </c>
+      <c r="R401" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T19:00:23.742910Z</t>
+        </is>
+      </c>
+      <c r="S401" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T401" s="2" t="inlineStr"/>
+      <c r="U401" s="2" t="inlineStr"/>
+      <c r="V401" s="2" t="inlineStr"/>
+      <c r="W401" s="2" t="inlineStr"/>
+      <c r="X401" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y401" s="2" t="inlineStr"/>
+      <c r="Z401" s="2" t="inlineStr"/>
+      <c r="AA401" s="2" t="inlineStr"/>
+      <c r="AB401" s="2" t="inlineStr"/>
+      <c r="AC401" s="2" t="inlineStr"/>
+      <c r="AD401" s="2" t="inlineStr"/>
+      <c r="AE401" s="2" t="inlineStr"/>
+      <c r="AF401" s="2" t="inlineStr"/>
+      <c r="AG401" s="2" t="inlineStr"/>
+      <c r="AH401" s="2" t="inlineStr"/>
+      <c r="AI401" s="2" t="inlineStr"/>
+      <c r="AJ401" s="2" t="inlineStr"/>
+    </row>
+    <row r="402">
+      <c r="A402" s="2" t="inlineStr">
+        <is>
+          <t>a3531c1c368c4b7f</t>
+        </is>
+      </c>
+      <c r="B402" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C402" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D402" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E402" s="2" t="inlineStr">
+        <is>
+          <t>5e9799a515295e9b079eacaa53a2e35352183239a18c1b173f4a540a52770140</t>
+        </is>
+      </c>
+      <c r="F402" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G402" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H402" s="2" t="inlineStr">
+        <is>
+          <t>72438</t>
+        </is>
+      </c>
+      <c r="I402" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J402" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K402" s="2" t="inlineStr"/>
+      <c r="L402" s="2" t="inlineStr">
+        <is>
+          <t>0.631431</t>
+        </is>
+      </c>
+      <c r="M402" s="2" t="inlineStr"/>
+      <c r="N402" s="2" t="inlineStr"/>
+      <c r="O402" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P402" s="2" t="inlineStr"/>
+      <c r="Q402" s="2" t="inlineStr">
+        <is>
+          <t>0.10091456807511734</t>
+        </is>
+      </c>
+      <c r="R402" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T19:00:24.265807Z</t>
+        </is>
+      </c>
+      <c r="S402" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T402" s="2" t="inlineStr"/>
+      <c r="U402" s="2" t="inlineStr"/>
+      <c r="V402" s="2" t="inlineStr"/>
+      <c r="W402" s="2" t="inlineStr"/>
+      <c r="X402" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y402" s="2" t="inlineStr"/>
+      <c r="Z402" s="2" t="inlineStr"/>
+      <c r="AA402" s="2" t="inlineStr"/>
+      <c r="AB402" s="2" t="inlineStr"/>
+      <c r="AC402" s="2" t="inlineStr"/>
+      <c r="AD402" s="2" t="inlineStr"/>
+      <c r="AE402" s="2" t="inlineStr"/>
+      <c r="AF402" s="2" t="inlineStr"/>
+      <c r="AG402" s="2" t="inlineStr"/>
+      <c r="AH402" s="2" t="inlineStr"/>
+      <c r="AI402" s="2" t="inlineStr"/>
+      <c r="AJ402" s="2" t="inlineStr"/>
+    </row>
+    <row r="403">
+      <c r="A403" s="2" t="inlineStr">
+        <is>
+          <t>695deab7cbbf440f</t>
+        </is>
+      </c>
+      <c r="B403" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C403" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D403" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E403" s="2" t="inlineStr">
+        <is>
+          <t>a435118c0d96357d246620424b583b0e8bb85e7581f7dfaff6a1a2190d73a589</t>
+        </is>
+      </c>
+      <c r="F403" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G403" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H403" s="2" t="inlineStr">
+        <is>
+          <t>72342</t>
+        </is>
+      </c>
+      <c r="I403" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J403" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K403" s="2" t="inlineStr"/>
+      <c r="L403" s="2" t="inlineStr">
+        <is>
+          <t>0.577738</t>
+        </is>
+      </c>
+      <c r="M403" s="2" t="inlineStr"/>
+      <c r="N403" s="2" t="inlineStr"/>
+      <c r="O403" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P403" s="2" t="inlineStr"/>
+      <c r="Q403" s="2" t="inlineStr">
+        <is>
+          <t>0.1372093656387665</t>
+        </is>
+      </c>
+      <c r="R403" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:05:08.530710Z</t>
+        </is>
+      </c>
+      <c r="S403" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="T403" s="2" t="inlineStr"/>
+      <c r="U403" s="2" t="inlineStr"/>
+      <c r="V403" s="2" t="inlineStr"/>
+      <c r="W403" s="2" t="inlineStr"/>
+      <c r="X403" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y403" s="2" t="inlineStr"/>
+      <c r="Z403" s="2" t="inlineStr"/>
+      <c r="AA403" s="2" t="inlineStr"/>
+      <c r="AB403" s="2" t="inlineStr"/>
+      <c r="AC403" s="2" t="inlineStr"/>
+      <c r="AD403" s="2" t="inlineStr"/>
+      <c r="AE403" s="2" t="inlineStr"/>
+      <c r="AF403" s="2" t="inlineStr"/>
+      <c r="AG403" s="2" t="inlineStr"/>
+      <c r="AH403" s="2" t="inlineStr"/>
+      <c r="AI403" s="2" t="inlineStr"/>
+      <c r="AJ403" s="2" t="inlineStr"/>
+    </row>
+    <row r="404">
+      <c r="A404" s="2" t="inlineStr">
+        <is>
+          <t>5032b70b5a234162</t>
+        </is>
+      </c>
+      <c r="B404" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C404" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D404" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E404" s="2" t="inlineStr">
+        <is>
+          <t>a435118c0d96357d246620424b583b0e8bb85e7581f7dfaff6a1a2190d73a589</t>
+        </is>
+      </c>
+      <c r="F404" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G404" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H404" s="2" t="inlineStr">
+        <is>
+          <t>72428</t>
+        </is>
+      </c>
+      <c r="I404" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J404" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K404" s="2" t="inlineStr"/>
+      <c r="L404" s="2" t="inlineStr">
+        <is>
+          <t>0.697219</t>
+        </is>
+      </c>
+      <c r="M404" s="2" t="inlineStr"/>
+      <c r="N404" s="2" t="inlineStr"/>
+      <c r="O404" s="2" t="inlineStr">
+        <is>
+          <t>0.4694835680751174</t>
+        </is>
+      </c>
+      <c r="P404" s="2" t="inlineStr"/>
+      <c r="Q404" s="2" t="inlineStr">
+        <is>
+          <t>0.22773543192488266</t>
+        </is>
+      </c>
+      <c r="R404" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:05:09.254946Z</t>
+        </is>
+      </c>
+      <c r="S404" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T404" s="2" t="inlineStr"/>
+      <c r="U404" s="2" t="inlineStr"/>
+      <c r="V404" s="2" t="inlineStr"/>
+      <c r="W404" s="2" t="inlineStr"/>
+      <c r="X404" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y404" s="2" t="inlineStr"/>
+      <c r="Z404" s="2" t="inlineStr"/>
+      <c r="AA404" s="2" t="inlineStr"/>
+      <c r="AB404" s="2" t="inlineStr"/>
+      <c r="AC404" s="2" t="inlineStr"/>
+      <c r="AD404" s="2" t="inlineStr"/>
+      <c r="AE404" s="2" t="inlineStr"/>
+      <c r="AF404" s="2" t="inlineStr"/>
+      <c r="AG404" s="2" t="inlineStr"/>
+      <c r="AH404" s="2" t="inlineStr"/>
+      <c r="AI404" s="2" t="inlineStr"/>
+      <c r="AJ404" s="2" t="inlineStr"/>
+    </row>
+    <row r="405">
+      <c r="A405" s="2" t="inlineStr">
+        <is>
+          <t>f7dc46b9f8ff46c3</t>
+        </is>
+      </c>
+      <c r="B405" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C405" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D405" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E405" s="2" t="inlineStr">
+        <is>
+          <t>a435118c0d96357d246620424b583b0e8bb85e7581f7dfaff6a1a2190d73a589</t>
+        </is>
+      </c>
+      <c r="F405" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G405" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H405" s="2" t="inlineStr">
+        <is>
+          <t>72438</t>
+        </is>
+      </c>
+      <c r="I405" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J405" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K405" s="2" t="inlineStr"/>
+      <c r="L405" s="2" t="inlineStr">
+        <is>
+          <t>0.627939</t>
+        </is>
+      </c>
+      <c r="M405" s="2" t="inlineStr"/>
+      <c r="N405" s="2" t="inlineStr"/>
+      <c r="O405" s="2" t="inlineStr">
+        <is>
+          <t>0.4807692307692307</t>
+        </is>
+      </c>
+      <c r="P405" s="2" t="inlineStr"/>
+      <c r="Q405" s="2" t="inlineStr">
+        <is>
+          <t>0.1471697692307693</t>
+        </is>
+      </c>
+      <c r="R405" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:05:09.957391Z</t>
+        </is>
+      </c>
+      <c r="S405" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T405" s="2" t="inlineStr"/>
+      <c r="U405" s="2" t="inlineStr"/>
+      <c r="V405" s="2" t="inlineStr"/>
+      <c r="W405" s="2" t="inlineStr"/>
+      <c r="X405" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y405" s="2" t="inlineStr"/>
+      <c r="Z405" s="2" t="inlineStr"/>
+      <c r="AA405" s="2" t="inlineStr"/>
+      <c r="AB405" s="2" t="inlineStr"/>
+      <c r="AC405" s="2" t="inlineStr"/>
+      <c r="AD405" s="2" t="inlineStr"/>
+      <c r="AE405" s="2" t="inlineStr"/>
+      <c r="AF405" s="2" t="inlineStr"/>
+      <c r="AG405" s="2" t="inlineStr"/>
+      <c r="AH405" s="2" t="inlineStr"/>
+      <c r="AI405" s="2" t="inlineStr"/>
+      <c r="AJ405" s="2" t="inlineStr"/>
+    </row>
+    <row r="406">
+      <c r="A406" s="2" t="inlineStr">
+        <is>
+          <t>87cb0a3288504e44</t>
+        </is>
+      </c>
+      <c r="B406" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C406" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D406" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E406" s="2" t="inlineStr">
+        <is>
+          <t>a435118c0d96357d246620424b583b0e8bb85e7581f7dfaff6a1a2190d73a589</t>
+        </is>
+      </c>
+      <c r="F406" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G406" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H406" s="2" t="inlineStr">
+        <is>
+          <t>72722</t>
+        </is>
+      </c>
+      <c r="I406" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J406" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K406" s="2" t="inlineStr"/>
+      <c r="L406" s="2" t="inlineStr">
+        <is>
+          <t>0.607082</t>
+        </is>
+      </c>
+      <c r="M406" s="2" t="inlineStr"/>
+      <c r="N406" s="2" t="inlineStr"/>
+      <c r="O406" s="2" t="inlineStr">
+        <is>
+          <t>0.4608294930875576</t>
+        </is>
+      </c>
+      <c r="P406" s="2" t="inlineStr"/>
+      <c r="Q406" s="2" t="inlineStr">
+        <is>
+          <t>0.1462525069124424</t>
+        </is>
+      </c>
+      <c r="R406" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:05:14.159072Z</t>
+        </is>
+      </c>
+      <c r="S406" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T406" s="2" t="inlineStr"/>
+      <c r="U406" s="2" t="inlineStr"/>
+      <c r="V406" s="2" t="inlineStr"/>
+      <c r="W406" s="2" t="inlineStr"/>
+      <c r="X406" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y406" s="2" t="inlineStr"/>
+      <c r="Z406" s="2" t="inlineStr"/>
+      <c r="AA406" s="2" t="inlineStr"/>
+      <c r="AB406" s="2" t="inlineStr"/>
+      <c r="AC406" s="2" t="inlineStr"/>
+      <c r="AD406" s="2" t="inlineStr"/>
+      <c r="AE406" s="2" t="inlineStr"/>
+      <c r="AF406" s="2" t="inlineStr"/>
+      <c r="AG406" s="2" t="inlineStr"/>
+      <c r="AH406" s="2" t="inlineStr"/>
+      <c r="AI406" s="2" t="inlineStr"/>
+      <c r="AJ406" s="2" t="inlineStr"/>
+    </row>
+    <row r="407">
+      <c r="A407" s="2" t="inlineStr">
+        <is>
+          <t>a29b404d314e4483</t>
+        </is>
+      </c>
+      <c r="B407" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C407" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D407" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E407" s="2" t="inlineStr">
+        <is>
+          <t>a435118c0d96357d246620424b583b0e8bb85e7581f7dfaff6a1a2190d73a589</t>
+        </is>
+      </c>
+      <c r="F407" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G407" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H407" s="2" t="inlineStr">
+        <is>
+          <t>72871</t>
+        </is>
+      </c>
+      <c r="I407" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J407" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K407" s="2" t="inlineStr"/>
+      <c r="L407" s="2" t="inlineStr">
+        <is>
+          <t>0.694309</t>
+        </is>
+      </c>
+      <c r="M407" s="2" t="inlineStr"/>
+      <c r="N407" s="2" t="inlineStr"/>
+      <c r="O407" s="2" t="inlineStr">
+        <is>
+          <t>0.49019607843137253</t>
+        </is>
+      </c>
+      <c r="P407" s="2" t="inlineStr"/>
+      <c r="Q407" s="2" t="inlineStr">
+        <is>
+          <t>0.20411292156862743</t>
+        </is>
+      </c>
+      <c r="R407" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:05:23.319056Z</t>
+        </is>
+      </c>
+      <c r="S407" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="T407" s="2" t="inlineStr"/>
+      <c r="U407" s="2" t="inlineStr"/>
+      <c r="V407" s="2" t="inlineStr"/>
+      <c r="W407" s="2" t="inlineStr"/>
+      <c r="X407" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y407" s="2" t="inlineStr"/>
+      <c r="Z407" s="2" t="inlineStr"/>
+      <c r="AA407" s="2" t="inlineStr"/>
+      <c r="AB407" s="2" t="inlineStr"/>
+      <c r="AC407" s="2" t="inlineStr"/>
+      <c r="AD407" s="2" t="inlineStr"/>
+      <c r="AE407" s="2" t="inlineStr"/>
+      <c r="AF407" s="2" t="inlineStr"/>
+      <c r="AG407" s="2" t="inlineStr"/>
+      <c r="AH407" s="2" t="inlineStr"/>
+      <c r="AI407" s="2" t="inlineStr"/>
+      <c r="AJ407" s="2" t="inlineStr"/>
+    </row>
+    <row r="408">
+      <c r="A408" s="2" t="inlineStr">
+        <is>
+          <t>0f3a427298d44cc7</t>
+        </is>
+      </c>
+      <c r="B408" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C408" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D408" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E408" s="2" t="inlineStr">
+        <is>
+          <t>20c3e63bf190142bb6f2572c6657565aa9ec5e7d6e42d68fb9f7442c3368e41c</t>
+        </is>
+      </c>
+      <c r="F408" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G408" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H408" s="2" t="inlineStr">
+        <is>
+          <t>72342</t>
+        </is>
+      </c>
+      <c r="I408" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J408" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K408" s="2" t="inlineStr"/>
+      <c r="L408" s="2" t="inlineStr">
+        <is>
+          <t>0.577338</t>
+        </is>
+      </c>
+      <c r="M408" s="2" t="inlineStr"/>
+      <c r="N408" s="2" t="inlineStr"/>
+      <c r="O408" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P408" s="2" t="inlineStr"/>
+      <c r="Q408" s="2" t="inlineStr">
+        <is>
+          <t>0.1268875495495495</t>
+        </is>
+      </c>
+      <c r="R408" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:11:24.549565Z</t>
+        </is>
+      </c>
+      <c r="S408" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="T408" s="2" t="inlineStr"/>
+      <c r="U408" s="2" t="inlineStr"/>
+      <c r="V408" s="2" t="inlineStr"/>
+      <c r="W408" s="2" t="inlineStr"/>
+      <c r="X408" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y408" s="2" t="inlineStr"/>
+      <c r="Z408" s="2" t="inlineStr"/>
+      <c r="AA408" s="2" t="inlineStr"/>
+      <c r="AB408" s="2" t="inlineStr"/>
+      <c r="AC408" s="2" t="inlineStr"/>
+      <c r="AD408" s="2" t="inlineStr"/>
+      <c r="AE408" s="2" t="inlineStr"/>
+      <c r="AF408" s="2" t="inlineStr"/>
+      <c r="AG408" s="2" t="inlineStr"/>
+      <c r="AH408" s="2" t="inlineStr"/>
+      <c r="AI408" s="2" t="inlineStr"/>
+      <c r="AJ408" s="2" t="inlineStr"/>
+    </row>
+    <row r="409">
+      <c r="A409" s="2" t="inlineStr">
+        <is>
+          <t>4bd72c110bc14254</t>
+        </is>
+      </c>
+      <c r="B409" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C409" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D409" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E409" s="2" t="inlineStr">
+        <is>
+          <t>20c3e63bf190142bb6f2572c6657565aa9ec5e7d6e42d68fb9f7442c3368e41c</t>
+        </is>
+      </c>
+      <c r="F409" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G409" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H409" s="2" t="inlineStr">
+        <is>
+          <t>72428</t>
+        </is>
+      </c>
+      <c r="I409" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J409" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K409" s="2" t="inlineStr"/>
+      <c r="L409" s="2" t="inlineStr">
+        <is>
+          <t>0.696401</t>
+        </is>
+      </c>
+      <c r="M409" s="2" t="inlineStr"/>
+      <c r="N409" s="2" t="inlineStr"/>
+      <c r="O409" s="2" t="inlineStr">
+        <is>
+          <t>0.4694835680751174</t>
+        </is>
+      </c>
+      <c r="P409" s="2" t="inlineStr"/>
+      <c r="Q409" s="2" t="inlineStr">
+        <is>
+          <t>0.22691743192488267</t>
+        </is>
+      </c>
+      <c r="R409" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:11:25.101843Z</t>
+        </is>
+      </c>
+      <c r="S409" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T409" s="2" t="inlineStr"/>
+      <c r="U409" s="2" t="inlineStr"/>
+      <c r="V409" s="2" t="inlineStr"/>
+      <c r="W409" s="2" t="inlineStr"/>
+      <c r="X409" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y409" s="2" t="inlineStr"/>
+      <c r="Z409" s="2" t="inlineStr"/>
+      <c r="AA409" s="2" t="inlineStr"/>
+      <c r="AB409" s="2" t="inlineStr"/>
+      <c r="AC409" s="2" t="inlineStr"/>
+      <c r="AD409" s="2" t="inlineStr"/>
+      <c r="AE409" s="2" t="inlineStr"/>
+      <c r="AF409" s="2" t="inlineStr"/>
+      <c r="AG409" s="2" t="inlineStr"/>
+      <c r="AH409" s="2" t="inlineStr"/>
+      <c r="AI409" s="2" t="inlineStr"/>
+      <c r="AJ409" s="2" t="inlineStr"/>
+    </row>
+    <row r="410">
+      <c r="A410" s="2" t="inlineStr">
+        <is>
+          <t>517572305ff54a6a</t>
+        </is>
+      </c>
+      <c r="B410" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C410" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D410" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E410" s="2" t="inlineStr">
+        <is>
+          <t>20c3e63bf190142bb6f2572c6657565aa9ec5e7d6e42d68fb9f7442c3368e41c</t>
+        </is>
+      </c>
+      <c r="F410" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G410" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H410" s="2" t="inlineStr">
+        <is>
+          <t>72438</t>
+        </is>
+      </c>
+      <c r="I410" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J410" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K410" s="2" t="inlineStr"/>
+      <c r="L410" s="2" t="inlineStr">
+        <is>
+          <t>0.627391</t>
+        </is>
+      </c>
+      <c r="M410" s="2" t="inlineStr"/>
+      <c r="N410" s="2" t="inlineStr"/>
+      <c r="O410" s="2" t="inlineStr">
+        <is>
+          <t>0.4807692307692307</t>
+        </is>
+      </c>
+      <c r="P410" s="2" t="inlineStr"/>
+      <c r="Q410" s="2" t="inlineStr">
+        <is>
+          <t>0.1466217692307693</t>
+        </is>
+      </c>
+      <c r="R410" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:11:25.625490Z</t>
+        </is>
+      </c>
+      <c r="S410" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T410" s="2" t="inlineStr"/>
+      <c r="U410" s="2" t="inlineStr"/>
+      <c r="V410" s="2" t="inlineStr"/>
+      <c r="W410" s="2" t="inlineStr"/>
+      <c r="X410" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y410" s="2" t="inlineStr"/>
+      <c r="Z410" s="2" t="inlineStr"/>
+      <c r="AA410" s="2" t="inlineStr"/>
+      <c r="AB410" s="2" t="inlineStr"/>
+      <c r="AC410" s="2" t="inlineStr"/>
+      <c r="AD410" s="2" t="inlineStr"/>
+      <c r="AE410" s="2" t="inlineStr"/>
+      <c r="AF410" s="2" t="inlineStr"/>
+      <c r="AG410" s="2" t="inlineStr"/>
+      <c r="AH410" s="2" t="inlineStr"/>
+      <c r="AI410" s="2" t="inlineStr"/>
+      <c r="AJ410" s="2" t="inlineStr"/>
+    </row>
+    <row r="411">
+      <c r="A411" s="2" t="inlineStr">
+        <is>
+          <t>b12a13a3af934282</t>
+        </is>
+      </c>
+      <c r="B411" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C411" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D411" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E411" s="2" t="inlineStr">
+        <is>
+          <t>20c3e63bf190142bb6f2572c6657565aa9ec5e7d6e42d68fb9f7442c3368e41c</t>
+        </is>
+      </c>
+      <c r="F411" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G411" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H411" s="2" t="inlineStr">
+        <is>
+          <t>72722</t>
+        </is>
+      </c>
+      <c r="I411" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J411" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K411" s="2" t="inlineStr"/>
+      <c r="L411" s="2" t="inlineStr">
+        <is>
+          <t>0.606572</t>
+        </is>
+      </c>
+      <c r="M411" s="2" t="inlineStr"/>
+      <c r="N411" s="2" t="inlineStr"/>
+      <c r="O411" s="2" t="inlineStr">
+        <is>
+          <t>0.4608294930875576</t>
+        </is>
+      </c>
+      <c r="P411" s="2" t="inlineStr"/>
+      <c r="Q411" s="2" t="inlineStr">
+        <is>
+          <t>0.1457425069124424</t>
+        </is>
+      </c>
+      <c r="R411" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:11:27.939734Z</t>
+        </is>
+      </c>
+      <c r="S411" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T411" s="2" t="inlineStr"/>
+      <c r="U411" s="2" t="inlineStr"/>
+      <c r="V411" s="2" t="inlineStr"/>
+      <c r="W411" s="2" t="inlineStr"/>
+      <c r="X411" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y411" s="2" t="inlineStr"/>
+      <c r="Z411" s="2" t="inlineStr"/>
+      <c r="AA411" s="2" t="inlineStr"/>
+      <c r="AB411" s="2" t="inlineStr"/>
+      <c r="AC411" s="2" t="inlineStr"/>
+      <c r="AD411" s="2" t="inlineStr"/>
+      <c r="AE411" s="2" t="inlineStr"/>
+      <c r="AF411" s="2" t="inlineStr"/>
+      <c r="AG411" s="2" t="inlineStr"/>
+      <c r="AH411" s="2" t="inlineStr"/>
+      <c r="AI411" s="2" t="inlineStr"/>
+      <c r="AJ411" s="2" t="inlineStr"/>
+    </row>
+    <row r="412">
+      <c r="A412" s="2" t="inlineStr">
+        <is>
+          <t>4589e6a3521440df</t>
+        </is>
+      </c>
+      <c r="B412" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C412" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D412" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E412" s="2" t="inlineStr">
+        <is>
+          <t>20c3e63bf190142bb6f2572c6657565aa9ec5e7d6e42d68fb9f7442c3368e41c</t>
+        </is>
+      </c>
+      <c r="F412" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G412" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H412" s="2" t="inlineStr">
+        <is>
+          <t>72752</t>
+        </is>
+      </c>
+      <c r="I412" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J412" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K412" s="2" t="inlineStr"/>
+      <c r="L412" s="2" t="inlineStr">
+        <is>
+          <t>0.675931</t>
+        </is>
+      </c>
+      <c r="M412" s="2" t="inlineStr"/>
+      <c r="N412" s="2" t="inlineStr"/>
+      <c r="O412" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P412" s="2" t="inlineStr"/>
+      <c r="Q412" s="2" t="inlineStr">
+        <is>
+          <t>0.10511554935622314</t>
+        </is>
+      </c>
+      <c r="R412" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:11:31.144533Z</t>
+        </is>
+      </c>
+      <c r="S412" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T412" s="2" t="inlineStr"/>
+      <c r="U412" s="2" t="inlineStr"/>
+      <c r="V412" s="2" t="inlineStr"/>
+      <c r="W412" s="2" t="inlineStr"/>
+      <c r="X412" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y412" s="2" t="inlineStr"/>
+      <c r="Z412" s="2" t="inlineStr"/>
+      <c r="AA412" s="2" t="inlineStr"/>
+      <c r="AB412" s="2" t="inlineStr"/>
+      <c r="AC412" s="2" t="inlineStr"/>
+      <c r="AD412" s="2" t="inlineStr"/>
+      <c r="AE412" s="2" t="inlineStr"/>
+      <c r="AF412" s="2" t="inlineStr"/>
+      <c r="AG412" s="2" t="inlineStr"/>
+      <c r="AH412" s="2" t="inlineStr"/>
+      <c r="AI412" s="2" t="inlineStr"/>
+      <c r="AJ412" s="2" t="inlineStr"/>
+    </row>
+    <row r="413">
+      <c r="A413" s="2" t="inlineStr">
+        <is>
+          <t>a10599744915478a</t>
+        </is>
+      </c>
+      <c r="B413" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C413" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D413" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E413" s="2" t="inlineStr">
+        <is>
+          <t>20c3e63bf190142bb6f2572c6657565aa9ec5e7d6e42d68fb9f7442c3368e41c</t>
+        </is>
+      </c>
+      <c r="F413" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G413" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H413" s="2" t="inlineStr">
+        <is>
+          <t>72871</t>
+        </is>
+      </c>
+      <c r="I413" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J413" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K413" s="2" t="inlineStr"/>
+      <c r="L413" s="2" t="inlineStr">
+        <is>
+          <t>0.693495</t>
+        </is>
+      </c>
+      <c r="M413" s="2" t="inlineStr"/>
+      <c r="N413" s="2" t="inlineStr"/>
+      <c r="O413" s="2" t="inlineStr">
+        <is>
+          <t>0.49019607843137253</t>
+        </is>
+      </c>
+      <c r="P413" s="2" t="inlineStr"/>
+      <c r="Q413" s="2" t="inlineStr">
+        <is>
+          <t>0.20329892156862744</t>
+        </is>
+      </c>
+      <c r="R413" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:11:34.589523Z</t>
+        </is>
+      </c>
+      <c r="S413" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="T413" s="2" t="inlineStr"/>
+      <c r="U413" s="2" t="inlineStr"/>
+      <c r="V413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
+      <c r="X413" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y413" s="2" t="inlineStr"/>
+      <c r="Z413" s="2" t="inlineStr"/>
+      <c r="AA413" s="2" t="inlineStr"/>
+      <c r="AB413" s="2" t="inlineStr"/>
+      <c r="AC413" s="2" t="inlineStr"/>
+      <c r="AD413" s="2" t="inlineStr"/>
+      <c r="AE413" s="2" t="inlineStr"/>
+      <c r="AF413" s="2" t="inlineStr"/>
+      <c r="AG413" s="2" t="inlineStr"/>
+      <c r="AH413" s="2" t="inlineStr"/>
+      <c r="AI413" s="2" t="inlineStr"/>
+      <c r="AJ413" s="2" t="inlineStr"/>
+    </row>
+    <row r="414">
+      <c r="A414" s="2" t="inlineStr">
+        <is>
+          <t>c82d7efc584444fb</t>
+        </is>
+      </c>
+      <c r="B414" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C414" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D414" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E414" s="2" t="inlineStr">
+        <is>
+          <t>0ce178a4c74d95939d4859ae617369533b2f8010eb3d4b4914c35d385598199f</t>
+        </is>
+      </c>
+      <c r="F414" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G414" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H414" s="2" t="inlineStr">
+        <is>
+          <t>72342</t>
+        </is>
+      </c>
+      <c r="I414" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J414" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K414" s="2" t="inlineStr"/>
+      <c r="L414" s="2" t="inlineStr">
+        <is>
+          <t>0.576777</t>
+        </is>
+      </c>
+      <c r="M414" s="2" t="inlineStr"/>
+      <c r="N414" s="2" t="inlineStr"/>
+      <c r="O414" s="2" t="inlineStr">
+        <is>
+          <t>0.4608294930875576</t>
+        </is>
+      </c>
+      <c r="P414" s="2" t="inlineStr"/>
+      <c r="Q414" s="2" t="inlineStr">
+        <is>
+          <t>0.11594750691244238</t>
+        </is>
+      </c>
+      <c r="R414" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:17:13.181900Z</t>
+        </is>
+      </c>
+      <c r="S414" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="T414" s="2" t="inlineStr"/>
+      <c r="U414" s="2" t="inlineStr"/>
+      <c r="V414" s="2" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
+      <c r="X414" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y414" s="2" t="inlineStr"/>
+      <c r="Z414" s="2" t="inlineStr"/>
+      <c r="AA414" s="2" t="inlineStr"/>
+      <c r="AB414" s="2" t="inlineStr"/>
+      <c r="AC414" s="2" t="inlineStr"/>
+      <c r="AD414" s="2" t="inlineStr"/>
+      <c r="AE414" s="2" t="inlineStr"/>
+      <c r="AF414" s="2" t="inlineStr"/>
+      <c r="AG414" s="2" t="inlineStr"/>
+      <c r="AH414" s="2" t="inlineStr"/>
+      <c r="AI414" s="2" t="inlineStr"/>
+      <c r="AJ414" s="2" t="inlineStr"/>
+    </row>
+    <row r="415">
+      <c r="A415" s="2" t="inlineStr">
+        <is>
+          <t>5ff71a8695934c6f</t>
+        </is>
+      </c>
+      <c r="B415" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C415" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D415" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E415" s="2" t="inlineStr">
+        <is>
+          <t>0ce178a4c74d95939d4859ae617369533b2f8010eb3d4b4914c35d385598199f</t>
+        </is>
+      </c>
+      <c r="F415" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G415" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H415" s="2" t="inlineStr">
+        <is>
+          <t>72428</t>
+        </is>
+      </c>
+      <c r="I415" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J415" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K415" s="2" t="inlineStr"/>
+      <c r="L415" s="2" t="inlineStr">
+        <is>
+          <t>0.695854</t>
+        </is>
+      </c>
+      <c r="M415" s="2" t="inlineStr"/>
+      <c r="N415" s="2" t="inlineStr"/>
+      <c r="O415" s="2" t="inlineStr">
+        <is>
+          <t>0.4807692307692307</t>
+        </is>
+      </c>
+      <c r="P415" s="2" t="inlineStr"/>
+      <c r="Q415" s="2" t="inlineStr">
+        <is>
+          <t>0.21508476923076925</t>
+        </is>
+      </c>
+      <c r="R415" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:17:13.882621Z</t>
+        </is>
+      </c>
+      <c r="S415" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T415" s="2" t="inlineStr"/>
+      <c r="U415" s="2" t="inlineStr"/>
+      <c r="V415" s="2" t="inlineStr"/>
+      <c r="W415" s="2" t="inlineStr"/>
+      <c r="X415" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y415" s="2" t="inlineStr"/>
+      <c r="Z415" s="2" t="inlineStr"/>
+      <c r="AA415" s="2" t="inlineStr"/>
+      <c r="AB415" s="2" t="inlineStr"/>
+      <c r="AC415" s="2" t="inlineStr"/>
+      <c r="AD415" s="2" t="inlineStr"/>
+      <c r="AE415" s="2" t="inlineStr"/>
+      <c r="AF415" s="2" t="inlineStr"/>
+      <c r="AG415" s="2" t="inlineStr"/>
+      <c r="AH415" s="2" t="inlineStr"/>
+      <c r="AI415" s="2" t="inlineStr"/>
+      <c r="AJ415" s="2" t="inlineStr"/>
+    </row>
+    <row r="416">
+      <c r="A416" s="2" t="inlineStr">
+        <is>
+          <t>8b8db3327dca4ac4</t>
+        </is>
+      </c>
+      <c r="B416" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C416" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D416" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E416" s="2" t="inlineStr">
+        <is>
+          <t>0ce178a4c74d95939d4859ae617369533b2f8010eb3d4b4914c35d385598199f</t>
+        </is>
+      </c>
+      <c r="F416" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G416" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H416" s="2" t="inlineStr">
+        <is>
+          <t>72438</t>
+        </is>
+      </c>
+      <c r="I416" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J416" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K416" s="2" t="inlineStr"/>
+      <c r="L416" s="2" t="inlineStr">
+        <is>
+          <t>0.627806</t>
+        </is>
+      </c>
+      <c r="M416" s="2" t="inlineStr"/>
+      <c r="N416" s="2" t="inlineStr"/>
+      <c r="O416" s="2" t="inlineStr">
+        <is>
+          <t>0.4807692307692307</t>
+        </is>
+      </c>
+      <c r="P416" s="2" t="inlineStr"/>
+      <c r="Q416" s="2" t="inlineStr">
+        <is>
+          <t>0.14703676923076925</t>
+        </is>
+      </c>
+      <c r="R416" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:17:14.377522Z</t>
+        </is>
+      </c>
+      <c r="S416" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T416" s="2" t="inlineStr"/>
+      <c r="U416" s="2" t="inlineStr"/>
+      <c r="V416" s="2" t="inlineStr"/>
+      <c r="W416" s="2" t="inlineStr"/>
+      <c r="X416" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y416" s="2" t="inlineStr"/>
+      <c r="Z416" s="2" t="inlineStr"/>
+      <c r="AA416" s="2" t="inlineStr"/>
+      <c r="AB416" s="2" t="inlineStr"/>
+      <c r="AC416" s="2" t="inlineStr"/>
+      <c r="AD416" s="2" t="inlineStr"/>
+      <c r="AE416" s="2" t="inlineStr"/>
+      <c r="AF416" s="2" t="inlineStr"/>
+      <c r="AG416" s="2" t="inlineStr"/>
+      <c r="AH416" s="2" t="inlineStr"/>
+      <c r="AI416" s="2" t="inlineStr"/>
+      <c r="AJ416" s="2" t="inlineStr"/>
+    </row>
+    <row r="417">
+      <c r="A417" s="2" t="inlineStr">
+        <is>
+          <t>117555790de54b5c</t>
+        </is>
+      </c>
+      <c r="B417" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C417" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D417" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E417" s="2" t="inlineStr">
+        <is>
+          <t>0ce178a4c74d95939d4859ae617369533b2f8010eb3d4b4914c35d385598199f</t>
+        </is>
+      </c>
+      <c r="F417" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G417" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H417" s="2" t="inlineStr">
+        <is>
+          <t>72722</t>
+        </is>
+      </c>
+      <c r="I417" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J417" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K417" s="2" t="inlineStr"/>
+      <c r="L417" s="2" t="inlineStr">
+        <is>
+          <t>0.60596</t>
+        </is>
+      </c>
+      <c r="M417" s="2" t="inlineStr"/>
+      <c r="N417" s="2" t="inlineStr"/>
+      <c r="O417" s="2" t="inlineStr">
+        <is>
+          <t>0.4608294930875576</t>
+        </is>
+      </c>
+      <c r="P417" s="2" t="inlineStr"/>
+      <c r="Q417" s="2" t="inlineStr">
+        <is>
+          <t>0.14513050691244245</t>
+        </is>
+      </c>
+      <c r="R417" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:17:16.639756Z</t>
+        </is>
+      </c>
+      <c r="S417" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T417" s="2" t="inlineStr"/>
+      <c r="U417" s="2" t="inlineStr"/>
+      <c r="V417" s="2" t="inlineStr"/>
+      <c r="W417" s="2" t="inlineStr"/>
+      <c r="X417" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y417" s="2" t="inlineStr"/>
+      <c r="Z417" s="2" t="inlineStr"/>
+      <c r="AA417" s="2" t="inlineStr"/>
+      <c r="AB417" s="2" t="inlineStr"/>
+      <c r="AC417" s="2" t="inlineStr"/>
+      <c r="AD417" s="2" t="inlineStr"/>
+      <c r="AE417" s="2" t="inlineStr"/>
+      <c r="AF417" s="2" t="inlineStr"/>
+      <c r="AG417" s="2" t="inlineStr"/>
+      <c r="AH417" s="2" t="inlineStr"/>
+      <c r="AI417" s="2" t="inlineStr"/>
+      <c r="AJ417" s="2" t="inlineStr"/>
+    </row>
+    <row r="418">
+      <c r="A418" s="2" t="inlineStr">
+        <is>
+          <t>05a3c49ebc6e4002</t>
+        </is>
+      </c>
+      <c r="B418" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C418" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D418" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E418" s="2" t="inlineStr">
+        <is>
+          <t>0ce178a4c74d95939d4859ae617369533b2f8010eb3d4b4914c35d385598199f</t>
+        </is>
+      </c>
+      <c r="F418" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G418" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H418" s="2" t="inlineStr">
+        <is>
+          <t>72752</t>
+        </is>
+      </c>
+      <c r="I418" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J418" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K418" s="2" t="inlineStr"/>
+      <c r="L418" s="2" t="inlineStr">
+        <is>
+          <t>0.675398</t>
+        </is>
+      </c>
+      <c r="M418" s="2" t="inlineStr"/>
+      <c r="N418" s="2" t="inlineStr"/>
+      <c r="O418" s="2" t="inlineStr">
+        <is>
+          <t>0.3802281368821293</t>
+        </is>
+      </c>
+      <c r="P418" s="2" t="inlineStr"/>
+      <c r="Q418" s="2" t="inlineStr">
+        <is>
+          <t>0.29516986311787075</t>
+        </is>
+      </c>
+      <c r="R418" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:17:19.659383Z</t>
+        </is>
+      </c>
+      <c r="S418" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T418" s="2" t="inlineStr"/>
+      <c r="U418" s="2" t="inlineStr"/>
+      <c r="V418" s="2" t="inlineStr"/>
+      <c r="W418" s="2" t="inlineStr"/>
+      <c r="X418" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y418" s="2" t="inlineStr"/>
+      <c r="Z418" s="2" t="inlineStr"/>
+      <c r="AA418" s="2" t="inlineStr"/>
+      <c r="AB418" s="2" t="inlineStr"/>
+      <c r="AC418" s="2" t="inlineStr"/>
+      <c r="AD418" s="2" t="inlineStr"/>
+      <c r="AE418" s="2" t="inlineStr"/>
+      <c r="AF418" s="2" t="inlineStr"/>
+      <c r="AG418" s="2" t="inlineStr"/>
+      <c r="AH418" s="2" t="inlineStr"/>
+      <c r="AI418" s="2" t="inlineStr"/>
+      <c r="AJ418" s="2" t="inlineStr"/>
+    </row>
+    <row r="419">
+      <c r="A419" s="2" t="inlineStr">
+        <is>
+          <t>dcd41e124a3942c0</t>
+        </is>
+      </c>
+      <c r="B419" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C419" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D419" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E419" s="2" t="inlineStr">
+        <is>
+          <t>0ce178a4c74d95939d4859ae617369533b2f8010eb3d4b4914c35d385598199f</t>
+        </is>
+      </c>
+      <c r="F419" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G419" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H419" s="2" t="inlineStr">
+        <is>
+          <t>72871</t>
+        </is>
+      </c>
+      <c r="I419" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J419" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K419" s="2" t="inlineStr"/>
+      <c r="L419" s="2" t="inlineStr">
+        <is>
+          <t>0.692946</t>
+        </is>
+      </c>
+      <c r="M419" s="2" t="inlineStr"/>
+      <c r="N419" s="2" t="inlineStr"/>
+      <c r="O419" s="2" t="inlineStr">
+        <is>
+          <t>0.49019607843137253</t>
+        </is>
+      </c>
+      <c r="P419" s="2" t="inlineStr"/>
+      <c r="Q419" s="2" t="inlineStr">
+        <is>
+          <t>0.20274992156862742</t>
+        </is>
+      </c>
+      <c r="R419" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:17:23.138834Z</t>
+        </is>
+      </c>
+      <c r="S419" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="T419" s="2" t="inlineStr"/>
+      <c r="U419" s="2" t="inlineStr"/>
+      <c r="V419" s="2" t="inlineStr"/>
+      <c r="W419" s="2" t="inlineStr"/>
+      <c r="X419" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y419" s="2" t="inlineStr"/>
+      <c r="Z419" s="2" t="inlineStr"/>
+      <c r="AA419" s="2" t="inlineStr"/>
+      <c r="AB419" s="2" t="inlineStr"/>
+      <c r="AC419" s="2" t="inlineStr"/>
+      <c r="AD419" s="2" t="inlineStr"/>
+      <c r="AE419" s="2" t="inlineStr"/>
+      <c r="AF419" s="2" t="inlineStr"/>
+      <c r="AG419" s="2" t="inlineStr"/>
+      <c r="AH419" s="2" t="inlineStr"/>
+      <c r="AI419" s="2" t="inlineStr"/>
+      <c r="AJ419" s="2" t="inlineStr"/>
+    </row>
+    <row r="420">
+      <c r="A420" s="2" t="inlineStr">
+        <is>
+          <t>ca2f6410522b40b7</t>
+        </is>
+      </c>
+      <c r="B420" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C420" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D420" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E420" s="2" t="inlineStr">
+        <is>
+          <t>326a42c58f2a208dee1dc4f634e9901156f475883f7f16a3237a5e1b513fa5f9</t>
+        </is>
+      </c>
+      <c r="F420" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G420" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H420" s="2" t="inlineStr">
+        <is>
+          <t>71980</t>
+        </is>
+      </c>
+      <c r="I420" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J420" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K420" s="2" t="inlineStr"/>
+      <c r="L420" s="2" t="inlineStr">
+        <is>
+          <t>0.637212</t>
+        </is>
+      </c>
+      <c r="M420" s="2" t="inlineStr"/>
+      <c r="N420" s="2" t="inlineStr"/>
+      <c r="O420" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P420" s="2" t="inlineStr"/>
+      <c r="Q420" s="2" t="inlineStr">
+        <is>
+          <t>0.09804149308755761</t>
+        </is>
+      </c>
+      <c r="R420" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:23:54.049058Z</t>
+        </is>
+      </c>
+      <c r="S420" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="T420" s="2" t="inlineStr"/>
+      <c r="U420" s="2" t="inlineStr"/>
+      <c r="V420" s="2" t="inlineStr"/>
+      <c r="W420" s="2" t="inlineStr"/>
+      <c r="X420" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y420" s="2" t="inlineStr"/>
+      <c r="Z420" s="2" t="inlineStr"/>
+      <c r="AA420" s="2" t="inlineStr"/>
+      <c r="AB420" s="2" t="inlineStr"/>
+      <c r="AC420" s="2" t="inlineStr"/>
+      <c r="AD420" s="2" t="inlineStr"/>
+      <c r="AE420" s="2" t="inlineStr"/>
+      <c r="AF420" s="2" t="inlineStr"/>
+      <c r="AG420" s="2" t="inlineStr"/>
+      <c r="AH420" s="2" t="inlineStr"/>
+      <c r="AI420" s="2" t="inlineStr"/>
+      <c r="AJ420" s="2" t="inlineStr"/>
+    </row>
+    <row r="421">
+      <c r="A421" s="2" t="inlineStr">
+        <is>
+          <t>c507ed6484624abb</t>
+        </is>
+      </c>
+      <c r="B421" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C421" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D421" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E421" s="2" t="inlineStr">
+        <is>
+          <t>326a42c58f2a208dee1dc4f634e9901156f475883f7f16a3237a5e1b513fa5f9</t>
+        </is>
+      </c>
+      <c r="F421" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G421" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H421" s="2" t="inlineStr">
+        <is>
+          <t>72342</t>
+        </is>
+      </c>
+      <c r="I421" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J421" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K421" s="2" t="inlineStr"/>
+      <c r="L421" s="2" t="inlineStr">
+        <is>
+          <t>0.576745</t>
+        </is>
+      </c>
+      <c r="M421" s="2" t="inlineStr"/>
+      <c r="N421" s="2" t="inlineStr"/>
+      <c r="O421" s="2" t="inlineStr">
+        <is>
+          <t>0.4608294930875576</t>
+        </is>
+      </c>
+      <c r="P421" s="2" t="inlineStr"/>
+      <c r="Q421" s="2" t="inlineStr">
+        <is>
+          <t>0.11591550691244235</t>
+        </is>
+      </c>
+      <c r="R421" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:23:56.287371Z</t>
+        </is>
+      </c>
+      <c r="S421" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="T421" s="2" t="inlineStr"/>
+      <c r="U421" s="2" t="inlineStr"/>
+      <c r="V421" s="2" t="inlineStr"/>
+      <c r="W421" s="2" t="inlineStr"/>
+      <c r="X421" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y421" s="2" t="inlineStr"/>
+      <c r="Z421" s="2" t="inlineStr"/>
+      <c r="AA421" s="2" t="inlineStr"/>
+      <c r="AB421" s="2" t="inlineStr"/>
+      <c r="AC421" s="2" t="inlineStr"/>
+      <c r="AD421" s="2" t="inlineStr"/>
+      <c r="AE421" s="2" t="inlineStr"/>
+      <c r="AF421" s="2" t="inlineStr"/>
+      <c r="AG421" s="2" t="inlineStr"/>
+      <c r="AH421" s="2" t="inlineStr"/>
+      <c r="AI421" s="2" t="inlineStr"/>
+      <c r="AJ421" s="2" t="inlineStr"/>
+    </row>
+    <row r="422">
+      <c r="A422" s="2" t="inlineStr">
+        <is>
+          <t>d92c55c13eaa4d89</t>
+        </is>
+      </c>
+      <c r="B422" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C422" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D422" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E422" s="2" t="inlineStr">
+        <is>
+          <t>326a42c58f2a208dee1dc4f634e9901156f475883f7f16a3237a5e1b513fa5f9</t>
+        </is>
+      </c>
+      <c r="F422" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G422" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H422" s="2" t="inlineStr">
+        <is>
+          <t>72428</t>
+        </is>
+      </c>
+      <c r="I422" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J422" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K422" s="2" t="inlineStr"/>
+      <c r="L422" s="2" t="inlineStr">
+        <is>
+          <t>0.695606</t>
+        </is>
+      </c>
+      <c r="M422" s="2" t="inlineStr"/>
+      <c r="N422" s="2" t="inlineStr"/>
+      <c r="O422" s="2" t="inlineStr">
+        <is>
+          <t>0.4807692307692307</t>
+        </is>
+      </c>
+      <c r="P422" s="2" t="inlineStr"/>
+      <c r="Q422" s="2" t="inlineStr">
+        <is>
+          <t>0.21483676923076922</t>
+        </is>
+      </c>
+      <c r="R422" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:23:56.826662Z</t>
+        </is>
+      </c>
+      <c r="S422" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T422" s="2" t="inlineStr"/>
+      <c r="U422" s="2" t="inlineStr"/>
+      <c r="V422" s="2" t="inlineStr"/>
+      <c r="W422" s="2" t="inlineStr"/>
+      <c r="X422" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y422" s="2" t="inlineStr"/>
+      <c r="Z422" s="2" t="inlineStr"/>
+      <c r="AA422" s="2" t="inlineStr"/>
+      <c r="AB422" s="2" t="inlineStr"/>
+      <c r="AC422" s="2" t="inlineStr"/>
+      <c r="AD422" s="2" t="inlineStr"/>
+      <c r="AE422" s="2" t="inlineStr"/>
+      <c r="AF422" s="2" t="inlineStr"/>
+      <c r="AG422" s="2" t="inlineStr"/>
+      <c r="AH422" s="2" t="inlineStr"/>
+      <c r="AI422" s="2" t="inlineStr"/>
+      <c r="AJ422" s="2" t="inlineStr"/>
+    </row>
+    <row r="423">
+      <c r="A423" s="2" t="inlineStr">
+        <is>
+          <t>187aa74996bd4040</t>
+        </is>
+      </c>
+      <c r="B423" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C423" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D423" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E423" s="2" t="inlineStr">
+        <is>
+          <t>326a42c58f2a208dee1dc4f634e9901156f475883f7f16a3237a5e1b513fa5f9</t>
+        </is>
+      </c>
+      <c r="F423" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G423" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H423" s="2" t="inlineStr">
+        <is>
+          <t>72438</t>
+        </is>
+      </c>
+      <c r="I423" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J423" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K423" s="2" t="inlineStr"/>
+      <c r="L423" s="2" t="inlineStr">
+        <is>
+          <t>0.627435</t>
+        </is>
+      </c>
+      <c r="M423" s="2" t="inlineStr"/>
+      <c r="N423" s="2" t="inlineStr"/>
+      <c r="O423" s="2" t="inlineStr">
+        <is>
+          <t>0.4807692307692307</t>
+        </is>
+      </c>
+      <c r="P423" s="2" t="inlineStr"/>
+      <c r="Q423" s="2" t="inlineStr">
+        <is>
+          <t>0.14666576923076924</t>
+        </is>
+      </c>
+      <c r="R423" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:23:57.410433Z</t>
+        </is>
+      </c>
+      <c r="S423" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T423" s="2" t="inlineStr"/>
+      <c r="U423" s="2" t="inlineStr"/>
+      <c r="V423" s="2" t="inlineStr"/>
+      <c r="W423" s="2" t="inlineStr"/>
+      <c r="X423" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y423" s="2" t="inlineStr"/>
+      <c r="Z423" s="2" t="inlineStr"/>
+      <c r="AA423" s="2" t="inlineStr"/>
+      <c r="AB423" s="2" t="inlineStr"/>
+      <c r="AC423" s="2" t="inlineStr"/>
+      <c r="AD423" s="2" t="inlineStr"/>
+      <c r="AE423" s="2" t="inlineStr"/>
+      <c r="AF423" s="2" t="inlineStr"/>
+      <c r="AG423" s="2" t="inlineStr"/>
+      <c r="AH423" s="2" t="inlineStr"/>
+      <c r="AI423" s="2" t="inlineStr"/>
+      <c r="AJ423" s="2" t="inlineStr"/>
+    </row>
+    <row r="424">
+      <c r="A424" s="2" t="inlineStr">
+        <is>
+          <t>b7bc50132bb14a01</t>
+        </is>
+      </c>
+      <c r="B424" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C424" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D424" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E424" s="2" t="inlineStr">
+        <is>
+          <t>326a42c58f2a208dee1dc4f634e9901156f475883f7f16a3237a5e1b513fa5f9</t>
+        </is>
+      </c>
+      <c r="F424" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G424" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H424" s="2" t="inlineStr">
+        <is>
+          <t>72722</t>
+        </is>
+      </c>
+      <c r="I424" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J424" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K424" s="2" t="inlineStr"/>
+      <c r="L424" s="2" t="inlineStr">
+        <is>
+          <t>0.605705</t>
+        </is>
+      </c>
+      <c r="M424" s="2" t="inlineStr"/>
+      <c r="N424" s="2" t="inlineStr"/>
+      <c r="O424" s="2" t="inlineStr">
+        <is>
+          <t>0.4694835680751174</t>
+        </is>
+      </c>
+      <c r="P424" s="2" t="inlineStr"/>
+      <c r="Q424" s="2" t="inlineStr">
+        <is>
+          <t>0.13622143192488267</t>
+        </is>
+      </c>
+      <c r="R424" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:23:59.567486Z</t>
+        </is>
+      </c>
+      <c r="S424" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T424" s="2" t="inlineStr"/>
+      <c r="U424" s="2" t="inlineStr"/>
+      <c r="V424" s="2" t="inlineStr"/>
+      <c r="W424" s="2" t="inlineStr"/>
+      <c r="X424" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y424" s="2" t="inlineStr"/>
+      <c r="Z424" s="2" t="inlineStr"/>
+      <c r="AA424" s="2" t="inlineStr"/>
+      <c r="AB424" s="2" t="inlineStr"/>
+      <c r="AC424" s="2" t="inlineStr"/>
+      <c r="AD424" s="2" t="inlineStr"/>
+      <c r="AE424" s="2" t="inlineStr"/>
+      <c r="AF424" s="2" t="inlineStr"/>
+      <c r="AG424" s="2" t="inlineStr"/>
+      <c r="AH424" s="2" t="inlineStr"/>
+      <c r="AI424" s="2" t="inlineStr"/>
+      <c r="AJ424" s="2" t="inlineStr"/>
+    </row>
+    <row r="425">
+      <c r="A425" s="2" t="inlineStr">
+        <is>
+          <t>f2e5c49b4eab4d12</t>
+        </is>
+      </c>
+      <c r="B425" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C425" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D425" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E425" s="2" t="inlineStr">
+        <is>
+          <t>326a42c58f2a208dee1dc4f634e9901156f475883f7f16a3237a5e1b513fa5f9</t>
+        </is>
+      </c>
+      <c r="F425" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G425" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H425" s="2" t="inlineStr">
+        <is>
+          <t>72871</t>
+        </is>
+      </c>
+      <c r="I425" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J425" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K425" s="2" t="inlineStr"/>
+      <c r="L425" s="2" t="inlineStr">
+        <is>
+          <t>0.692705</t>
+        </is>
+      </c>
+      <c r="M425" s="2" t="inlineStr"/>
+      <c r="N425" s="2" t="inlineStr"/>
+      <c r="O425" s="2" t="inlineStr">
+        <is>
+          <t>0.49019607843137253</t>
+        </is>
+      </c>
+      <c r="P425" s="2" t="inlineStr"/>
+      <c r="Q425" s="2" t="inlineStr">
+        <is>
+          <t>0.2025089215686275</t>
+        </is>
+      </c>
+      <c r="R425" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:24:07.921330Z</t>
+        </is>
+      </c>
+      <c r="S425" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="T425" s="2" t="inlineStr"/>
+      <c r="U425" s="2" t="inlineStr"/>
+      <c r="V425" s="2" t="inlineStr"/>
+      <c r="W425" s="2" t="inlineStr"/>
+      <c r="X425" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y425" s="2" t="inlineStr"/>
+      <c r="Z425" s="2" t="inlineStr"/>
+      <c r="AA425" s="2" t="inlineStr"/>
+      <c r="AB425" s="2" t="inlineStr"/>
+      <c r="AC425" s="2" t="inlineStr"/>
+      <c r="AD425" s="2" t="inlineStr"/>
+      <c r="AE425" s="2" t="inlineStr"/>
+      <c r="AF425" s="2" t="inlineStr"/>
+      <c r="AG425" s="2" t="inlineStr"/>
+      <c r="AH425" s="2" t="inlineStr"/>
+      <c r="AI425" s="2" t="inlineStr"/>
+      <c r="AJ425" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ376"/>
+  <autoFilter ref="A1:AJ425"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/gated_research/model_ledgers/lol-tiered-elo.xlsx
+++ b/data/gated_research/model_ledgers/lol-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$425</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$431</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ425"/>
+  <dimension ref="A1:AJ431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -43838,14 +43838,34 @@
       <c r="W420" s="2" t="inlineStr"/>
       <c r="X420" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y420" s="2" t="inlineStr"/>
-      <c r="Z420" s="2" t="inlineStr"/>
-      <c r="AA420" s="2" t="inlineStr"/>
-      <c r="AB420" s="2" t="inlineStr"/>
-      <c r="AC420" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y420" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z420" s="2" t="inlineStr">
+        <is>
+          <t>0.540000</t>
+        </is>
+      </c>
+      <c r="AA420" s="2" t="inlineStr">
+        <is>
+          <t>0.000829</t>
+        </is>
+      </c>
+      <c r="AB420" s="2" t="inlineStr">
+        <is>
+          <t>1.2821</t>
+        </is>
+      </c>
+      <c r="AC420" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:27:29.130490Z</t>
+        </is>
+      </c>
       <c r="AD420" s="2" t="inlineStr"/>
       <c r="AE420" s="2" t="inlineStr"/>
       <c r="AF420" s="2" t="inlineStr"/>
@@ -44364,8 +44384,620 @@
       <c r="AI425" s="2" t="inlineStr"/>
       <c r="AJ425" s="2" t="inlineStr"/>
     </row>
+    <row r="426">
+      <c r="A426" s="2" t="inlineStr">
+        <is>
+          <t>cfbc7885a5b54c95</t>
+        </is>
+      </c>
+      <c r="B426" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C426" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D426" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E426" s="2" t="inlineStr">
+        <is>
+          <t>d3791916ff32605dd2265e280637577dccc694ea8768ae90edb98370e9029821</t>
+        </is>
+      </c>
+      <c r="F426" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G426" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H426" s="2" t="inlineStr">
+        <is>
+          <t>72342</t>
+        </is>
+      </c>
+      <c r="I426" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J426" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K426" s="2" t="inlineStr"/>
+      <c r="L426" s="2" t="inlineStr">
+        <is>
+          <t>0.576862</t>
+        </is>
+      </c>
+      <c r="M426" s="2" t="inlineStr"/>
+      <c r="N426" s="2" t="inlineStr"/>
+      <c r="O426" s="2" t="inlineStr">
+        <is>
+          <t>0.4608294930875576</t>
+        </is>
+      </c>
+      <c r="P426" s="2" t="inlineStr"/>
+      <c r="Q426" s="2" t="inlineStr">
+        <is>
+          <t>0.11603250691244238</t>
+        </is>
+      </c>
+      <c r="R426" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:31:07.695348Z</t>
+        </is>
+      </c>
+      <c r="S426" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="T426" s="2" t="inlineStr"/>
+      <c r="U426" s="2" t="inlineStr"/>
+      <c r="V426" s="2" t="inlineStr"/>
+      <c r="W426" s="2" t="inlineStr"/>
+      <c r="X426" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y426" s="2" t="inlineStr"/>
+      <c r="Z426" s="2" t="inlineStr"/>
+      <c r="AA426" s="2" t="inlineStr"/>
+      <c r="AB426" s="2" t="inlineStr"/>
+      <c r="AC426" s="2" t="inlineStr"/>
+      <c r="AD426" s="2" t="inlineStr"/>
+      <c r="AE426" s="2" t="inlineStr"/>
+      <c r="AF426" s="2" t="inlineStr"/>
+      <c r="AG426" s="2" t="inlineStr"/>
+      <c r="AH426" s="2" t="inlineStr"/>
+      <c r="AI426" s="2" t="inlineStr"/>
+      <c r="AJ426" s="2" t="inlineStr"/>
+    </row>
+    <row r="427">
+      <c r="A427" s="2" t="inlineStr">
+        <is>
+          <t>a000869386d64551</t>
+        </is>
+      </c>
+      <c r="B427" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C427" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D427" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E427" s="2" t="inlineStr">
+        <is>
+          <t>d3791916ff32605dd2265e280637577dccc694ea8768ae90edb98370e9029821</t>
+        </is>
+      </c>
+      <c r="F427" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G427" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H427" s="2" t="inlineStr">
+        <is>
+          <t>72428</t>
+        </is>
+      </c>
+      <c r="I427" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J427" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K427" s="2" t="inlineStr"/>
+      <c r="L427" s="2" t="inlineStr">
+        <is>
+          <t>0.695648</t>
+        </is>
+      </c>
+      <c r="M427" s="2" t="inlineStr"/>
+      <c r="N427" s="2" t="inlineStr"/>
+      <c r="O427" s="2" t="inlineStr">
+        <is>
+          <t>0.4807692307692307</t>
+        </is>
+      </c>
+      <c r="P427" s="2" t="inlineStr"/>
+      <c r="Q427" s="2" t="inlineStr">
+        <is>
+          <t>0.21487876923076932</t>
+        </is>
+      </c>
+      <c r="R427" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:31:08.212012Z</t>
+        </is>
+      </c>
+      <c r="S427" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T427" s="2" t="inlineStr"/>
+      <c r="U427" s="2" t="inlineStr"/>
+      <c r="V427" s="2" t="inlineStr"/>
+      <c r="W427" s="2" t="inlineStr"/>
+      <c r="X427" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y427" s="2" t="inlineStr"/>
+      <c r="Z427" s="2" t="inlineStr"/>
+      <c r="AA427" s="2" t="inlineStr"/>
+      <c r="AB427" s="2" t="inlineStr"/>
+      <c r="AC427" s="2" t="inlineStr"/>
+      <c r="AD427" s="2" t="inlineStr"/>
+      <c r="AE427" s="2" t="inlineStr"/>
+      <c r="AF427" s="2" t="inlineStr"/>
+      <c r="AG427" s="2" t="inlineStr"/>
+      <c r="AH427" s="2" t="inlineStr"/>
+      <c r="AI427" s="2" t="inlineStr"/>
+      <c r="AJ427" s="2" t="inlineStr"/>
+    </row>
+    <row r="428">
+      <c r="A428" s="2" t="inlineStr">
+        <is>
+          <t>43ed026cdd474df8</t>
+        </is>
+      </c>
+      <c r="B428" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C428" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D428" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E428" s="2" t="inlineStr">
+        <is>
+          <t>d3791916ff32605dd2265e280637577dccc694ea8768ae90edb98370e9029821</t>
+        </is>
+      </c>
+      <c r="F428" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G428" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H428" s="2" t="inlineStr">
+        <is>
+          <t>72438</t>
+        </is>
+      </c>
+      <c r="I428" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J428" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K428" s="2" t="inlineStr"/>
+      <c r="L428" s="2" t="inlineStr">
+        <is>
+          <t>0.627171</t>
+        </is>
+      </c>
+      <c r="M428" s="2" t="inlineStr"/>
+      <c r="N428" s="2" t="inlineStr"/>
+      <c r="O428" s="2" t="inlineStr">
+        <is>
+          <t>0.4807692307692307</t>
+        </is>
+      </c>
+      <c r="P428" s="2" t="inlineStr"/>
+      <c r="Q428" s="2" t="inlineStr">
+        <is>
+          <t>0.1464017692307693</t>
+        </is>
+      </c>
+      <c r="R428" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:31:08.974236Z</t>
+        </is>
+      </c>
+      <c r="S428" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T428" s="2" t="inlineStr"/>
+      <c r="U428" s="2" t="inlineStr"/>
+      <c r="V428" s="2" t="inlineStr"/>
+      <c r="W428" s="2" t="inlineStr"/>
+      <c r="X428" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y428" s="2" t="inlineStr"/>
+      <c r="Z428" s="2" t="inlineStr"/>
+      <c r="AA428" s="2" t="inlineStr"/>
+      <c r="AB428" s="2" t="inlineStr"/>
+      <c r="AC428" s="2" t="inlineStr"/>
+      <c r="AD428" s="2" t="inlineStr"/>
+      <c r="AE428" s="2" t="inlineStr"/>
+      <c r="AF428" s="2" t="inlineStr"/>
+      <c r="AG428" s="2" t="inlineStr"/>
+      <c r="AH428" s="2" t="inlineStr"/>
+      <c r="AI428" s="2" t="inlineStr"/>
+      <c r="AJ428" s="2" t="inlineStr"/>
+    </row>
+    <row r="429">
+      <c r="A429" s="2" t="inlineStr">
+        <is>
+          <t>c7c2d29e6e024e5d</t>
+        </is>
+      </c>
+      <c r="B429" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C429" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D429" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E429" s="2" t="inlineStr">
+        <is>
+          <t>d3791916ff32605dd2265e280637577dccc694ea8768ae90edb98370e9029821</t>
+        </is>
+      </c>
+      <c r="F429" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G429" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H429" s="2" t="inlineStr">
+        <is>
+          <t>72722</t>
+        </is>
+      </c>
+      <c r="I429" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J429" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K429" s="2" t="inlineStr"/>
+      <c r="L429" s="2" t="inlineStr">
+        <is>
+          <t>0.605845</t>
+        </is>
+      </c>
+      <c r="M429" s="2" t="inlineStr"/>
+      <c r="N429" s="2" t="inlineStr"/>
+      <c r="O429" s="2" t="inlineStr">
+        <is>
+          <t>0.49019607843137253</t>
+        </is>
+      </c>
+      <c r="P429" s="2" t="inlineStr"/>
+      <c r="Q429" s="2" t="inlineStr">
+        <is>
+          <t>0.11564892156862744</t>
+        </is>
+      </c>
+      <c r="R429" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:31:11.080798Z</t>
+        </is>
+      </c>
+      <c r="S429" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T429" s="2" t="inlineStr"/>
+      <c r="U429" s="2" t="inlineStr"/>
+      <c r="V429" s="2" t="inlineStr"/>
+      <c r="W429" s="2" t="inlineStr"/>
+      <c r="X429" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y429" s="2" t="inlineStr"/>
+      <c r="Z429" s="2" t="inlineStr"/>
+      <c r="AA429" s="2" t="inlineStr"/>
+      <c r="AB429" s="2" t="inlineStr"/>
+      <c r="AC429" s="2" t="inlineStr"/>
+      <c r="AD429" s="2" t="inlineStr"/>
+      <c r="AE429" s="2" t="inlineStr"/>
+      <c r="AF429" s="2" t="inlineStr"/>
+      <c r="AG429" s="2" t="inlineStr"/>
+      <c r="AH429" s="2" t="inlineStr"/>
+      <c r="AI429" s="2" t="inlineStr"/>
+      <c r="AJ429" s="2" t="inlineStr"/>
+    </row>
+    <row r="430">
+      <c r="A430" s="2" t="inlineStr">
+        <is>
+          <t>e0a35e8290234342</t>
+        </is>
+      </c>
+      <c r="B430" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C430" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D430" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E430" s="2" t="inlineStr">
+        <is>
+          <t>d3791916ff32605dd2265e280637577dccc694ea8768ae90edb98370e9029821</t>
+        </is>
+      </c>
+      <c r="F430" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G430" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H430" s="2" t="inlineStr">
+        <is>
+          <t>72752</t>
+        </is>
+      </c>
+      <c r="I430" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J430" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K430" s="2" t="inlineStr"/>
+      <c r="L430" s="2" t="inlineStr">
+        <is>
+          <t>0.675074</t>
+        </is>
+      </c>
+      <c r="M430" s="2" t="inlineStr"/>
+      <c r="N430" s="2" t="inlineStr"/>
+      <c r="O430" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P430" s="2" t="inlineStr"/>
+      <c r="Q430" s="2" t="inlineStr">
+        <is>
+          <t>0.09524206722689077</t>
+        </is>
+      </c>
+      <c r="R430" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:31:14.111862Z</t>
+        </is>
+      </c>
+      <c r="S430" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T430" s="2" t="inlineStr"/>
+      <c r="U430" s="2" t="inlineStr"/>
+      <c r="V430" s="2" t="inlineStr"/>
+      <c r="W430" s="2" t="inlineStr"/>
+      <c r="X430" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y430" s="2" t="inlineStr"/>
+      <c r="Z430" s="2" t="inlineStr"/>
+      <c r="AA430" s="2" t="inlineStr"/>
+      <c r="AB430" s="2" t="inlineStr"/>
+      <c r="AC430" s="2" t="inlineStr"/>
+      <c r="AD430" s="2" t="inlineStr"/>
+      <c r="AE430" s="2" t="inlineStr"/>
+      <c r="AF430" s="2" t="inlineStr"/>
+      <c r="AG430" s="2" t="inlineStr"/>
+      <c r="AH430" s="2" t="inlineStr"/>
+      <c r="AI430" s="2" t="inlineStr"/>
+      <c r="AJ430" s="2" t="inlineStr"/>
+    </row>
+    <row r="431">
+      <c r="A431" s="2" t="inlineStr">
+        <is>
+          <t>f1b0e96e8c134eef</t>
+        </is>
+      </c>
+      <c r="B431" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C431" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D431" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E431" s="2" t="inlineStr">
+        <is>
+          <t>d3791916ff32605dd2265e280637577dccc694ea8768ae90edb98370e9029821</t>
+        </is>
+      </c>
+      <c r="F431" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G431" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H431" s="2" t="inlineStr">
+        <is>
+          <t>72871</t>
+        </is>
+      </c>
+      <c r="I431" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J431" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K431" s="2" t="inlineStr"/>
+      <c r="L431" s="2" t="inlineStr">
+        <is>
+          <t>0.692853</t>
+        </is>
+      </c>
+      <c r="M431" s="2" t="inlineStr"/>
+      <c r="N431" s="2" t="inlineStr"/>
+      <c r="O431" s="2" t="inlineStr">
+        <is>
+          <t>0.49019607843137253</t>
+        </is>
+      </c>
+      <c r="P431" s="2" t="inlineStr"/>
+      <c r="Q431" s="2" t="inlineStr">
+        <is>
+          <t>0.20265692156862752</t>
+        </is>
+      </c>
+      <c r="R431" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:31:18.039096Z</t>
+        </is>
+      </c>
+      <c r="S431" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="T431" s="2" t="inlineStr"/>
+      <c r="U431" s="2" t="inlineStr"/>
+      <c r="V431" s="2" t="inlineStr"/>
+      <c r="W431" s="2" t="inlineStr"/>
+      <c r="X431" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y431" s="2" t="inlineStr"/>
+      <c r="Z431" s="2" t="inlineStr"/>
+      <c r="AA431" s="2" t="inlineStr"/>
+      <c r="AB431" s="2" t="inlineStr"/>
+      <c r="AC431" s="2" t="inlineStr"/>
+      <c r="AD431" s="2" t="inlineStr"/>
+      <c r="AE431" s="2" t="inlineStr"/>
+      <c r="AF431" s="2" t="inlineStr"/>
+      <c r="AG431" s="2" t="inlineStr"/>
+      <c r="AH431" s="2" t="inlineStr"/>
+      <c r="AI431" s="2" t="inlineStr"/>
+      <c r="AJ431" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ425"/>
+  <autoFilter ref="A1:AJ431"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>